--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -545,7 +545,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  Generado: 2026-06-15</t>
+          <t>Quarter: Q2 2026  |  Generado: 2026-06-16</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>22</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11828</v>
+        <v>11837</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9405</v>
+        <v>9883</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>54%</t>
         </is>
       </c>
     </row>
@@ -657,14 +657,14 @@
         <v>23</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>12473</v>
+        <v>12482</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>10054</v>
+        <v>10532</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>54%</t>
         </is>
       </c>
     </row>
@@ -759,17 +759,17 @@
         <v>15</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>6228</v>
+        <v>6237</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>3912</v>
+        <v>4390</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10140</v>
+        <v>10627</v>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>59%</t>
         </is>
       </c>
     </row>
@@ -1010,11 +1010,11 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Component 16</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>270</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Botón Primario</t>
+          <t>Component 16</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -1130,11 +1130,11 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Botón Primario</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>114</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -1150,11 +1150,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>barras</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1170,11 +1170,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1190,11 +1190,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>barras</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1210,11 +1210,11 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>settings</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1230,11 +1230,11 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1250,11 +1250,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1270,11 +1270,11 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -1290,11 +1290,11 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1310,11 +1310,11 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>AGENDA</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>92</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>22</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>11828</v>
+        <v>11837</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>21233</v>
+        <v>21720</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -604,14 +604,14 @@
         <v>22</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11837</v>
+        <v>11902</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9883</v>
+        <v>9931</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>55%</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         <v>23</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>12482</v>
+        <v>12547</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>10532</v>
+        <v>10580</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
@@ -827,17 +827,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1592</v>
+        <v>1657</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>511</v>
+        <v>559</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>2103</v>
+        <v>2216</v>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>643</v>
+        <v>636</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -1174,7 +1174,7 @@
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1250,11 +1250,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -1294,7 +1294,7 @@
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -1857,17 +1857,17 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>22</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>11837</v>
+        <v>11902</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>21720</v>
+        <v>21833</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -64,6 +64,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FFD94F3D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="FFF5A623"/>
       <sz val="10"/>
     </font>
@@ -71,12 +77,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF1A7FA8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FFD94F3D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -140,16 +140,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  Generado: 2026-06-16</t>
+          <t>Quarter: Q2 2026  |  Generado: 2026-06-17</t>
         </is>
       </c>
     </row>
@@ -589,90 +589,293 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>11902</v>
+        <v>2437</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>9931</v>
+        <v>5545</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>1215</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>3557</v>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>1900</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>8303</v>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>25727</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>179865</v>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>6522</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>7315</v>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>11902</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>9931</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Ecommerce</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Auto Efectivo</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>6110</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>9633</v>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>3604</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>10108</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>645</v>
-      </c>
-      <c r="F6" s="6" t="n">
-        <v>649</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="D13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>343</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>23</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>12547</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>10580</v>
-      </c>
-      <c r="G7" s="11" t="inlineStr">
-        <is>
-          <t>54%</t>
+      <c r="C14" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>202</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>59760</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>235721</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -684,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -742,136 +945,816 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Pagos — Débito Automático</t>
         </is>
       </c>
       <c r="D2" s="6" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>6237</v>
+        <v>474</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>4390</v>
+        <v>820</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>10627</v>
+        <v>1294</v>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>37%</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Seguros MEP 2025</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>4008</v>
+        <v>1950</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>4982</v>
+        <v>4706</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>8990</v>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>45%</t>
+        <v>6656</v>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>29%</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Raspa &amp; Gana</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>1657</v>
+        <v>11</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>559</v>
+        <v>9</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>2216</v>
-      </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>20</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>55%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Auto Efectivo — One Click</t>
+          <t>Modales MEP</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>CAR</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>663</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>1047</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1710</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Aviso de Siniestros</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>552</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>2510</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>3062</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Web Pública</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>342</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>1253</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>1595</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>21%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Web Privada</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>7050</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>8608</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>TRIN</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>1446</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>16460</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>17906</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Home Empresas</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>24281</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>163405</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>187686</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>6522</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>7315</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>13837</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Modelo Día 2026</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>6237</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>4390</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>10627</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Portal de Suscripción &amp; Emisión</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4008</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>4982</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>8990</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Vida Ley &amp; SCTR</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>1657</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>559</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2216</v>
+      </c>
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>SOAT</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1224</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>963</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>2187</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>1550</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1723</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>3273</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Auto Efectivo</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="n">
         <v>645</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F18" s="6" t="n">
         <v>649</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G18" s="6" t="n">
         <v>1294</v>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>1830</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>2241</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>4071</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>861</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>4057</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>4918</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>2104</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>4149</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>6253</v>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>912</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>4879</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>5791</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>588</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1668</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>343</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>1464</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>1807</v>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>19%</t>
         </is>
       </c>
     </row>
@@ -886,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -920,801 +1803,3601 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>desk Table cell</t>
+          <t>menú</t>
         </is>
       </c>
       <c r="D2" s="14" t="n">
-        <v>2624</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
-        <v>666</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>646</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>More</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>636</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>card_accion</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>311</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Component 16</t>
+          <t>card_atajo_home</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>270</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Dropdown filter page</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>159</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>width fixed pagination</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>shoppingcart</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>135</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>135</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Botón Primario</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>126</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>Star</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Bottom app bar</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>115</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>barras</t>
+          <t>documento simple</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>Seguros card</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>110</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>descarga documento</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>108</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>sirena emergencia</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>107</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Card_ beneficios</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>106</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>beneficios vehiculares</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>ahorros</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>103</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Property 33</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>95</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>65</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls Glass</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>30</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>30</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>29</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>compare_arrow</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Caja formulario complex L M</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Contenido desktop</t>
+          <t>Suggested search (Deprecated)</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Formulario L M complex</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Banner mobile</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>15</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Contenido mobile</t>
+          <t>celda L</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>Step 04</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>Step 05</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Somos Corredores</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>CajaFormulario</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Upload icon</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Menu Item</t>
+        </is>
+      </c>
+      <c r="D43" s="14" t="n">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="n">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="n">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D47" s="14" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Menu title</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="D51" s="14" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Commercial Chips</t>
+        </is>
+      </c>
+      <c r="D53" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>HealthAndSafe</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Notification Item</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>eye_close</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="D59" s="14" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D60" s="14" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="D61" s="14" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="n">
+        <v>96329</v>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="n">
+        <v>16943</v>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D64" s="14" t="n">
+        <v>9112</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D65" s="14" t="n">
+        <v>8640</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>8256</v>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>5595</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="D68" s="14" t="n">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>celda S</t>
+        </is>
+      </c>
+      <c r="D69" s="14" t="n">
+        <v>2366</v>
+      </c>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="D71" s="14" t="n">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>eye_close</t>
+        </is>
+      </c>
+      <c r="D72" s="14" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Notification Item</t>
+        </is>
+      </c>
+      <c r="D73" s="14" t="n">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Indicator step</t>
+        </is>
+      </c>
+      <c r="D74" s="14" t="n">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="D75" s="14" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="D76" s="14" t="n">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="D77" s="14" t="n">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="D78" s="14" t="n">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Apps</t>
+        </is>
+      </c>
+      <c r="D79" s="14" t="n">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Bar Progress</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="n">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D81" s="14" t="n">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D82" s="14" t="n">
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D83" s="14" t="n">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Pegar Icon</t>
+        </is>
+      </c>
+      <c r="D84" s="14" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>copy</t>
+        </is>
+      </c>
+      <c r="D85" s="14" t="n">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>DirectionDown</t>
+        </is>
+      </c>
+      <c r="D86" s="14" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D87" s="14" t="n">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>DirectionRight</t>
+        </is>
+      </c>
+      <c r="D88" s="14" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D89" s="14" t="n">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Label in</t>
+        </is>
+      </c>
+      <c r="D90" s="14" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="D91" s="14" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Left Label</t>
+        </is>
+      </c>
+      <c r="D92" s="14" t="n">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown Input</t>
+        </is>
+      </c>
+      <c r="D93" s="14" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D94" s="14" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D95" s="14" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="D96" s="14" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D97" s="14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D98" s="14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Component 9</t>
+        </is>
+      </c>
+      <c r="D99" s="14" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D100" s="14" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="D101" s="14" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>desk Table cell</t>
+        </is>
+      </c>
+      <c r="D102" s="14" t="n">
+        <v>2624</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Left Label</t>
+        </is>
+      </c>
+      <c r="D103" s="14" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D104" s="14" t="n">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D105" s="14" t="n">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>DirectionDown</t>
+        </is>
+      </c>
+      <c r="D106" s="14" t="n">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Component 16</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown filter page</t>
+        </is>
+      </c>
+      <c r="D108" s="14" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>width fixed pagination</t>
+        </is>
+      </c>
+      <c r="D109" s="14" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Indicator Circle</t>
+        </is>
+      </c>
+      <c r="D110" s="14" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Line Tracking Vertical</t>
+        </is>
+      </c>
+      <c r="D111" s="14" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Botón Primario</t>
+        </is>
+      </c>
+      <c r="D112" s="14" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>DirectionUp</t>
+        </is>
+      </c>
+      <c r="D113" s="14" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="D114" s="14" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>barras</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>settings</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>billetera</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Indicator step</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="120" ht="20" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>create account</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
           <t>Ecommerce</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Auto Efectivo</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Carousel</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="n">
-        <v>9</v>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="123" ht="20" customHeight="1">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="n">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="124" ht="20" customHeight="1">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Menu Item</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="126" ht="20" customHeight="1">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>celda</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Property 33</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="129" ht="20" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="n">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Indicator step</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="133" ht="20" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Left Label</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="134" ht="20" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="135" ht="20" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="136" ht="20" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="140" ht="20" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="142" ht="20" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="n">
+        <v>3135</v>
+      </c>
+    </row>
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="n">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>Property 33</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="n">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="145" ht="20" customHeight="1">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="n">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="146" ht="20" customHeight="1">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="147" ht="20" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="150" ht="20" customHeight="1">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="n">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>CardProductPromo</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>Cotizar</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>Close Icon</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="158" ht="20" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="159" ht="20" customHeight="1">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>CardMenúMobile</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="160" ht="20" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D160" s="14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="161" ht="20" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>CardMenú</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="162" ht="20" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="D162" s="14" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>Property 33</t>
+        </is>
+      </c>
+      <c r="D163" s="14" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="164" ht="20" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="D164" s="14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="D165" s="14" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="166" ht="20" customHeight="1">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="D166" s="14" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="167" ht="20" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D167" s="14" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="D168" s="14" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>compare_arrow</t>
+        </is>
+      </c>
+      <c r="D169" s="14" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="170" ht="20" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="172" ht="20" customHeight="1">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D172" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>SecciónDescripción</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="174" ht="20" customHeight="1">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D174" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D175" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="176" ht="20" customHeight="1">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="D176" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="177" ht="20" customHeight="1">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>operador</t>
+        </is>
+      </c>
+      <c r="D177" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D178" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="179" ht="20" customHeight="1">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>Átomo mobile</t>
+        </is>
+      </c>
+      <c r="D179" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>SeccionCanales</t>
+        </is>
+      </c>
+      <c r="D180" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" ht="20" customHeight="1">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>PersonalInjuy</t>
+        </is>
+      </c>
+      <c r="D181" s="14" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +5411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1793,7 +5476,7 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -1821,53 +5504,270 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>645</v>
+        <v>6110</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1294</v>
+        <v>15743</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>343</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>2437</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
           <t>Modelo Día</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="F6" s="7" t="n">
         <v>11902</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>21833</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>25727</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>205592</v>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>6522</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>13837</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1900</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>10203</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1215</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>4772</v>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>3604</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>13712</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -70,6 +70,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FF1D9E75"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="FFF5A623"/>
       <sz val="10"/>
     </font>
@@ -77,12 +83,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF1A7FA8"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF1D9E75"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -143,16 +143,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -604,14 +604,14 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2437</v>
+        <v>2680</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5545</v>
+        <v>5302</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -633,14 +633,14 @@
         <v>12</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1215</v>
+        <v>3647</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>3557</v>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>25%</t>
+        <v>967</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1900</v>
+        <v>4743</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>8303</v>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>19%</t>
+        <v>2412</v>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>25727</v>
+        <v>154195</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>179865</v>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>13%</t>
+        <v>26003</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -720,14 +720,14 @@
         <v>5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>6522</v>
+        <v>10174</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>7315</v>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>47%</t>
+        <v>3543</v>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
     </row>
@@ -749,14 +749,14 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>11902</v>
+        <v>13591</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>9931</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>55%</t>
+        <v>8241</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -778,14 +778,14 @@
         <v>16</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>6110</v>
+        <v>10028</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>9633</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>5579</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
     </row>
@@ -804,17 +804,17 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3604</v>
+        <v>10104</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>10108</v>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>26%</t>
+        <v>2700</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
     </row>
@@ -836,38 +836,38 @@
         <v>6</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>343</v>
+        <v>1422</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1464</v>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>19%</t>
+        <v>337</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="10" t="n">
-        <v>202</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>59760</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>235721</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t>20%</t>
+      <c r="D14" s="11" t="n">
+        <v>188</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>210584</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>55084</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
     </row>
@@ -962,17 +962,17 @@
         <v>4</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>474</v>
+        <v>574</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>820</v>
+        <v>720</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>1294</v>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>44%</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
         <v>11</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>1950</v>
+        <v>2093</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>4706</v>
+        <v>4563</v>
       </c>
       <c r="G3" s="6" t="n">
         <v>6656</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>31%</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       <c r="G4" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>55%</t>
         </is>
@@ -1098,17 +1098,17 @@
         <v>5</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>663</v>
+        <v>1037</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>1047</v>
+        <v>665</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1710</v>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>39%</t>
+        <v>1702</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
     </row>
@@ -1132,17 +1132,17 @@
         <v>7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>552</v>
+        <v>2610</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2510</v>
+        <v>302</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3062</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>18%</t>
+        <v>2912</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1166,17 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>342</v>
+        <v>1272</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1253</v>
+        <v>275</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1595</v>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>21%</t>
+        <v>1547</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -1197,20 +1197,20 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>1558</v>
+        <v>3471</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>7050</v>
+        <v>2137</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8608</v>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>18%</t>
+        <v>5608</v>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -1231,20 +1231,20 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1446</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>16460</v>
+        <v>0</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>17906</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1268,17 +1268,17 @@
         <v>37</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>24281</v>
+        <v>154195</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>163405</v>
+        <v>26003</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>187686</v>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>13%</t>
+        <v>180198</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
         <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>6522</v>
+        <v>10174</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>7315</v>
+        <v>3543</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>13837</v>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>47%</t>
+        <v>13717</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
     </row>
@@ -1336,17 +1336,17 @@
         <v>15</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>6237</v>
+        <v>7697</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4390</v>
+        <v>2930</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>10627</v>
       </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>59%</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>72%</t>
         </is>
       </c>
     </row>
@@ -1370,17 +1370,17 @@
         <v>6</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4008</v>
+        <v>4145</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4982</v>
+        <v>4844</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>8990</v>
+        <v>8989</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -1404,17 +1404,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1657</v>
+        <v>1749</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>559</v>
+        <v>467</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>2216</v>
       </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>75%</t>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
     </row>
@@ -1438,17 +1438,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1224</v>
+        <v>1508</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>963</v>
+        <v>679</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>2187</v>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>56%</t>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
     </row>
@@ -1472,17 +1472,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1550</v>
+        <v>2007</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1723</v>
+        <v>1266</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>3273</v>
       </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>47%</t>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
     </row>
@@ -1506,17 +1506,17 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>645</v>
+        <v>825</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>649</v>
+        <v>469</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>1294</v>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
     </row>
@@ -1540,17 +1540,17 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1830</v>
+        <v>2329</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>2241</v>
+        <v>1742</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>4071</v>
       </c>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>45%</t>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>57%</t>
         </is>
       </c>
     </row>
@@ -1574,17 +1574,17 @@
         <v>11</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>861</v>
+        <v>3359</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4057</v>
+        <v>1423</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4918</v>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>18%</t>
+        <v>4782</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
     </row>
@@ -1639,20 +1639,20 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2104</v>
+        <v>4525</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4149</v>
+        <v>1006</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6253</v>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>34%</t>
+        <v>5531</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -1676,17 +1676,17 @@
         <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>912</v>
+        <v>4204</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4879</v>
+        <v>1427</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5791</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>16%</t>
+        <v>5631</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -1710,17 +1710,17 @@
         <v>14</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>588</v>
+        <v>1375</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1080</v>
+        <v>267</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1668</v>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>35%</t>
+        <v>1642</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -1744,17 +1744,17 @@
         <v>6</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>343</v>
+        <v>1422</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1464</v>
+        <v>337</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1807</v>
-      </c>
-      <c r="H25" s="8" t="inlineStr">
-        <is>
-          <t>19%</t>
+        <v>1759</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
     </row>
@@ -1933,11 +1933,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>message</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>204</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>shoppingcart</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
@@ -1973,11 +1973,11 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>shoppingcart</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1993,11 +1993,11 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Star</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -2033,11 +2033,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Star</t>
+          <t>Bottom app bar</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -2053,11 +2053,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Bottom app bar</t>
+          <t>documento simple</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>documento simple</t>
+          <t>Seguros card</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -2093,11 +2093,11 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Seguros card</t>
+          <t>sirena emergencia</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -2133,11 +2133,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>sirena emergencia</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2213,11 +2213,11 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>1500</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -2233,11 +2233,11 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Suggested search (Deprecated)</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>255</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>250</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2273,11 +2273,11 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>196</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
@@ -2293,11 +2293,11 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -2313,11 +2313,11 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -2333,11 +2333,11 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>celda L</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>95</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -2353,11 +2353,11 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Suggested search (Deprecated)</t>
+          <t>Step 04</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -2373,11 +2373,11 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Step 05</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>59</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -2413,11 +2413,11 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>Upload icon</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -2433,11 +2433,11 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Step 03</t>
+          <t>Userflow</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -2453,11 +2453,11 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -2473,11 +2473,11 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>celda L</t>
+          <t>celda S</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -2493,11 +2493,11 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Step 04</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -2513,11 +2513,11 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Step 05</t>
+          <t>titulo-fila</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -2533,11 +2533,11 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>generate ai</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>More</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2573,11 +2573,11 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>arrow_carrousel</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2593,11 +2593,11 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Upload icon</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2613,11 +2613,11 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>3264</v>
+        <v>520</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2633,11 +2633,11 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>640</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>544</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>HealthAndSafe</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>316</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>276</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>eye_close</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>272</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>272</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2753,11 +2753,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>160</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2773,11 +2773,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>160</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>136</v>
+        <v>58</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2813,11 +2813,11 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2833,11 +2833,11 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>HealthAndSafe</t>
+          <t>Beneficio | card</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>96</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2893,11 +2893,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>eye_close</t>
+          <t>Beneficio | card mobile</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>93</v>
+        <v>42</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>68</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2953,11 +2953,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>generate ai</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2993,11 +2993,11 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -3013,11 +3013,11 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>96329</v>
+        <v>4980</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>celda S</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>16943</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -3053,11 +3053,11 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>eye_close</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>9112</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -3073,11 +3073,11 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>8640</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -3093,11 +3093,11 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>8256</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -3113,11 +3113,11 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>5595</v>
+        <v>948</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -3133,11 +3133,11 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>4319</v>
+        <v>793</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -3153,11 +3153,11 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>celda S</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>2366</v>
+        <v>780</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>2109</v>
+        <v>697</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>1868</v>
+        <v>692</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -3213,11 +3213,11 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>eye_close</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>1671</v>
+        <v>692</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -3233,11 +3233,11 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>1536</v>
+        <v>692</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -3253,11 +3253,11 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>account</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>1166</v>
+        <v>564</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -3273,11 +3273,11 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>1080</v>
+        <v>518</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -3293,11 +3293,11 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>1080</v>
+        <v>514</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -3313,11 +3313,11 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>Home_Header</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>1019</v>
+        <v>511</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3333,11 +3333,11 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Action 1</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>948</v>
+        <v>496</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Action 2</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>793</v>
+        <v>496</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3373,11 +3373,11 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Menu_Mobile</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>780</v>
+        <v>482</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3393,11 +3393,11 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>titulo-fila</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>697</v>
+        <v>433</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
@@ -3413,11 +3413,11 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Pegar Icon</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>1440</v>
+        <v>484</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
@@ -3433,11 +3433,11 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>copy</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>569</v>
+        <v>439</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
@@ -3453,11 +3453,11 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Pegar Icon</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>484</v>
+        <v>328</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
@@ -3473,11 +3473,11 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>DirectionRight</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>439</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -3493,11 +3493,11 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>power</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>328</v>
+        <v>212</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>306</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -3533,11 +3533,11 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>DirectionRight</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>268</v>
+        <v>139</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
@@ -3553,11 +3553,11 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Component 9</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>240</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -3573,11 +3573,11 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>228</v>
+        <v>93</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
@@ -3593,11 +3593,11 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>Logo Horizontal</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>212</v>
+        <v>73</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
@@ -3613,11 +3613,11 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>204</v>
+        <v>61</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
@@ -3633,11 +3633,11 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>190</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
@@ -3653,11 +3653,11 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Card Dashboard</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>153</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>150</v>
+        <v>47</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
@@ -3693,11 +3693,11 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>Frame 1707479054</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>139</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
@@ -3713,11 +3713,11 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Frame 1707479133</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
@@ -3733,11 +3733,11 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
@@ -3753,11 +3753,11 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Component 9</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
@@ -3773,11 +3773,11 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>93</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
@@ -3793,11 +3793,11 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>666</v>
+        <v>643</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
@@ -3853,11 +3853,11 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>646</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
@@ -3873,11 +3873,11 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Component 16</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>636</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
@@ -3893,11 +3893,11 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>Botón Primario</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>311</v>
+        <v>180</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -3913,11 +3913,11 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Component 16</t>
+          <t>Dropdown filter page</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>270</v>
+        <v>159</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Dropdown filter page</t>
+          <t>width fixed pagination</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
@@ -3953,11 +3953,11 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>width fixed pagination</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
@@ -3973,11 +3973,11 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>135</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>135</v>
+        <v>115</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4013,11 +4013,11 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Botón Primario</t>
+          <t>barras</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4033,11 +4033,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>settings</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4053,11 +4053,11 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>barras</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4093,11 +4093,11 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4113,11 +4113,11 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4133,11 +4133,11 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
@@ -4153,11 +4153,11 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>106</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
@@ -4173,11 +4173,11 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>AGENDA</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -4193,11 +4193,11 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4213,11 +4213,11 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>1632</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4233,11 +4233,11 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>635</v>
+        <v>352</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4253,11 +4253,11 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>celda</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>380</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4273,11 +4273,11 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>336</v>
+        <v>248</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>celda</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>312</v>
+        <v>224</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Property 33</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>272</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4333,11 +4333,11 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>272</v>
+        <v>159</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4353,11 +4353,11 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>248</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4373,11 +4373,11 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>212</v>
+        <v>119</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4393,11 +4393,11 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>210</v>
+        <v>118</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4413,11 +4413,11 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>184</v>
+        <v>105</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4433,11 +4433,11 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>174</v>
+        <v>104</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4453,11 +4453,11 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>159</v>
+        <v>86</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4493,11 +4493,11 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>153</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4513,11 +4513,11 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>139</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4533,11 +4533,11 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>Component 120</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>136</v>
+        <v>56</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4573,11 +4573,11 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>119</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4593,11 +4593,11 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>106</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4613,11 +4613,11 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>3135</v>
+        <v>280</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4633,11 +4633,11 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>1095</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4653,11 +4653,11 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Property 33</t>
+          <t>CardProductPromo</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>1058</v>
+        <v>200</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4673,11 +4673,11 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>495</v>
+        <v>165</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4693,11 +4693,11 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>373</v>
+        <v>95</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>300</v>
+        <v>95</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4733,11 +4733,11 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>270</v>
+        <v>88</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,11 +4753,11 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>264</v>
+        <v>73</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>CardMenúMobile</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>264</v>
+        <v>73</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>200</v>
+        <v>73</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4813,11 +4813,11 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>CardMenú</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>195</v>
+        <v>71</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>149</v>
+        <v>70</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4853,11 +4853,11 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>BotónCategoría</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4873,11 +4873,11 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4913,11 +4913,11 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -4973,11 +4973,11 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -4993,11 +4993,11 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>MedicalService</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5013,11 +5013,11 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>570</v>
+        <v>52</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5033,11 +5033,11 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Property 33</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>140</v>
+        <v>42</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5053,11 +5053,11 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5073,11 +5073,11 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>SecciónDescripción</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5093,11 +5093,11 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>52</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>operador</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5153,11 +5153,11 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>compare_arrow</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>SeccionCanales</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5193,11 +5193,11 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>PersonalInjuy</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5213,11 +5213,11 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5233,11 +5233,11 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>LogosCollab</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>CoberturasIconos</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5293,11 +5293,11 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>operador</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5333,11 +5333,11 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5353,11 +5353,11 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Átomo mobile</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5476,7 +5476,7 @@
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>50%</t>
         </is>
@@ -5507,19 +5507,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>39%</t>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
         <v>16</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>6110</v>
+        <v>10028</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>15743</v>
+        <v>15607</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -5538,19 +5538,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>19%</t>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>81%</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
         <v>6</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>343</v>
+        <v>1422</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1807</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2437</v>
+        <v>2680</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>7982</v>
@@ -5600,19 +5600,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
-        <is>
-          <t>55%</t>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>62%</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
         <v>22</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>11902</v>
+        <v>13591</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>21833</v>
+        <v>21832</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -5631,19 +5631,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>13%</t>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>25727</v>
+        <v>154195</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>205592</v>
+        <v>180198</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -5662,19 +5662,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>47%</t>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>74%</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6522</v>
+        <v>10174</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>13837</v>
+        <v>13717</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -5693,19 +5693,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>19%</t>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1900</v>
+        <v>4743</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>10203</v>
+        <v>7155</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -5724,19 +5724,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>25%</t>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1215</v>
+        <v>3647</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4772</v>
+        <v>4614</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -5755,19 +5755,19 @@
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>26%</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3604</v>
+        <v>10104</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>13712</v>
+        <v>12804</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -659,17 +659,17 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4743</v>
+        <v>7035</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2412</v>
+        <v>2896</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>71%</t>
         </is>
       </c>
     </row>
@@ -688,13 +688,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>154195</v>
+        <v>169195</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>26003</v>
+        <v>28141</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -804,13 +804,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10104</v>
+        <v>10619</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2700</v>
+        <v>2826</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -857,17 +857,17 @@
         <v>24</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>210584</v>
+        <v>228391</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>55084</v>
+        <v>57832</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -1197,20 +1197,20 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3471</v>
+        <v>5763</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2137</v>
+        <v>2621</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>5608</v>
+        <v>8384</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>69%</t>
         </is>
       </c>
     </row>
@@ -1231,20 +1231,20 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0</v>
+        <v>2138</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17138</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>4525</v>
+        <v>5041</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1006</v>
+        <v>1132</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>5531</v>
+        <v>6173</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -1710,13 +1710,13 @@
         <v>14</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>267</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>520</v>
+        <v>640</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2653,11 +2653,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>103</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2673,11 +2673,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>HealthAndSafe</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>HealthAndSafe</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>eye_close</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2733,11 +2733,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>eye_close</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2753,11 +2753,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2773,11 +2773,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2793,11 +2793,11 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2813,11 +2813,11 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2833,11 +2833,11 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>time</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Beneficio | card</t>
+          <t>Apps</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Beneficio | card</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -2893,11 +2893,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Beneficio | card mobile</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -2913,11 +2913,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -2933,11 +2933,11 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Beneficio | card mobile</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -2953,11 +2953,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>generate ai</t>
+          <t>Banner | errores</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Atajos | Beneficios (new)</t>
+          <t>generate ai</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -2993,11 +2993,11 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>account</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>4980</v>
+        <v>5595</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>697</v>
+        <v>769</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>tiktok</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>692</v>
+        <v>769</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -3213,11 +3213,11 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>692</v>
+        <v>769</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -3233,11 +3233,11 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>692</v>
+        <v>697</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>518</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -3297,7 +3297,7 @@
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>280</v>
+        <v>304</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>95</v>
+        <v>105</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>CardMenúMobile</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
@@ -4813,11 +4813,11 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4853,11 +4853,11 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>CardMenú</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4873,11 +4873,11 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>BotónCategoría</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -4973,11 +4973,11 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>154195</v>
+        <v>169195</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>180198</v>
+        <v>197336</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -5695,17 +5695,17 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4743</v>
+        <v>7035</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>7155</v>
+        <v>9931</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -5761,13 +5761,13 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10104</v>
+        <v>10619</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>12804</v>
+        <v>13445</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -545,7 +545,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  Generado: 2026-06-17</t>
+          <t>Quarter: Q2 2026  |  Generado: 2026-06-18</t>
         </is>
       </c>
     </row>
@@ -749,10 +749,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>13591</v>
+        <v>13615</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8241</v>
+        <v>8209</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -775,13 +775,13 @@
         <v>6</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>10028</v>
+        <v>9789</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5579</v>
+        <v>5487</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
@@ -804,17 +804,17 @@
         <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10619</v>
+        <v>1842</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2826</v>
+        <v>404</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -833,13 +833,13 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>1422</v>
+        <v>450</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>337</v>
+        <v>104</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -857,13 +857,13 @@
         <v>24</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>228391</v>
+        <v>218427</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>57832</v>
+        <v>55053</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -1404,17 +1404,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1749</v>
+        <v>1773</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2216</v>
+        <v>2208</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1571,16 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3359</v>
+        <v>3120</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1423</v>
+        <v>1331</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4782</v>
+        <v>4451</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5041</v>
+        <v>1842</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1132</v>
+        <v>404</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6173</v>
+        <v>2246</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -1673,20 +1673,20 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4204</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1427</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5631</v>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>0</v>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1707,20 +1707,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1374</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1641</v>
-      </c>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>84%</t>
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1741,16 +1741,16 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1422</v>
+        <v>450</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>337</v>
+        <v>104</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1759</v>
+        <v>554</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
@@ -4017,7 +4017,7 @@
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
@@ -4073,11 +4073,11 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
@@ -4097,7 +4097,7 @@
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4237,7 +4237,7 @@
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>352</v>
+        <v>336</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4293,11 +4293,11 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4373,11 +4373,11 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4393,11 +4393,11 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4437,7 +4437,7 @@
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4453,11 +4453,11 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4533,11 +4533,11 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Infotip</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4553,11 +4553,11 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Component 120</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4573,11 +4573,11 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Component 120</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>304</v>
+        <v>78</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4633,11 +4633,11 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>217</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4653,11 +4653,11 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4673,11 +4673,11 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4693,11 +4693,11 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>105</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4713,11 +4713,11 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>105</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4733,11 +4733,11 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4753,11 +4753,11 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>80</v>
+        <v>17</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4773,11 +4773,11 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>77</v>
+        <v>16</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4813,11 +4813,11 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>73</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4833,11 +4833,11 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4853,11 +4853,11 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -4873,11 +4873,11 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -4893,11 +4893,11 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -4913,11 +4913,11 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Link Details</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>62</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -4933,11 +4933,11 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>account</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>payments</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -4973,11 +4973,11 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>47</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -4993,11 +4993,11 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5017,7 +5017,7 @@
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5057,7 +5057,7 @@
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5073,11 +5073,11 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5093,11 +5093,11 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>SecciónDescripción</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5133,11 +5133,11 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>operador</t>
+          <t>LogosCollab</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5153,11 +5153,11 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>SeccionCanales</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5197,7 +5197,7 @@
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5213,11 +5213,11 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>problema eléctrico</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5233,11 +5233,11 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>LogosCollab</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5253,11 +5253,11 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>CoberturasIconos</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>menu</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5293,11 +5293,11 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>robo de autopartes</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5313,11 +5313,11 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>operador</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5333,11 +5333,11 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>CoberturasIconos</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5353,11 +5353,11 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5373,11 +5373,11 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5393,11 +5393,11 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>10028</v>
+        <v>9789</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>15607</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -5544,13 +5544,13 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1422</v>
+        <v>450</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1759</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -5609,10 +5609,10 @@
         <v>22</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>13591</v>
+        <v>13615</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>21832</v>
+        <v>21824</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -5752,22 +5752,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>72</v>
+        <v>21</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>10619</v>
+        <v>1842</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>13445</v>
+        <v>2246</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -768,104 +768,249 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>9789</v>
+        <v>1508</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5487</v>
+        <v>679</v>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>69%</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1842</v>
+        <v>2007</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>404</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>82%</t>
+        <v>1266</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>61%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>825</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>469</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <v>450</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>104</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E14" s="7" t="n">
+        <v>2329</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>1742</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>3120</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1331</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>3684</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1197</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>10823</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>2882</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1422</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>337</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C19" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="D14" s="11" t="n">
-        <v>144</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>218427</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>55053</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="D19" s="11" t="n">
+        <v>207</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>232064</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>58961</v>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -873,9 +1018,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1426,7 +1571,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1460,7 +1605,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1494,7 +1639,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1528,7 +1673,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1562,7 +1707,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1596,7 +1741,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1605,20 +1750,20 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>3684</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
+        <v>1197</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>4881</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -1639,16 +1784,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1842</v>
+        <v>5041</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>404</v>
+        <v>1132</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2246</v>
+        <v>6173</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
@@ -1673,20 +1818,20 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0</v>
+        <v>4389</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>1477</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5866</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -1707,20 +1852,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>1393</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="8" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1666</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -1741,16 +1886,16 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>450</v>
+        <v>1422</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>104</v>
+        <v>337</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>554</v>
+        <v>1759</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
@@ -1769,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4208,16 +4353,16 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>340</v>
+        <v>41</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4228,7 +4373,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -4237,7 +4382,7 @@
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>336</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4248,16 +4393,16 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>celda</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>312</v>
+        <v>31</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4268,16 +4413,16 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>248</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4288,16 +4433,16 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>212</v>
+        <v>29</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4308,16 +4453,16 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>number_deskop</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4328,16 +4473,16 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>159</v>
+        <v>23</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4348,16 +4493,16 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>139</v>
+        <v>21</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4368,16 +4513,16 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4388,16 +4533,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4408,16 +4553,16 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4428,16 +4573,16 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4448,16 +4593,16 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>shield</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>86</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4468,16 +4613,16 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>tarjeta de crédito</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>85</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4488,16 +4633,16 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Póliza Salud</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4508,16 +4653,16 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4528,16 +4673,16 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4548,16 +4693,16 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Infotip</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4568,16 +4713,16 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Component 120</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4588,687 +4733,687 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
       <c r="A142" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>78</v>
+        <v>149</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>30</v>
+        <v>102</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>call</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
       <c r="A149" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>grid view</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
       <c r="A150" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
       <c r="A151" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
       <c r="A152" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
       <c r="A154" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
       <c r="A155" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
       <c r="A156" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
       <c r="A157" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Link Details</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>tarjeta de crédito</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>payments</t>
+          <t>asset_promo</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
       <c r="A161" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>Image Frame</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Slider Controls Glass</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
       <c r="A163" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
       <c r="A164" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
       <c r="A165" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Caja formulario complex L M</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>Contenido desktop</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
       <c r="A168" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>LogosCollab</t>
+          <t>Formulario L M complex</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>Banner mobile</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>problema eléctrico</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Contenido mobile</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>security</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -5277,127 +5422,2127 @@
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>robo de autopartes</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>operador</t>
+          <t>CajaFormulario</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>CoberturasIconos</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Card_Mobile_funciona 1</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Card_Mobile_funciona 3</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Auto Efectivo</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>Card_Mobile_funciona 4</t>
+        </is>
+      </c>
+      <c r="D181" s="14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D182" s="14" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="183" ht="20" customHeight="1">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="D183" s="14" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="184" ht="20" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="D184" s="14" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="185" ht="20" customHeight="1">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>add</t>
+        </is>
+      </c>
+      <c r="D185" s="14" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="186" ht="20" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="D186" s="14" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D187" s="14" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="188" ht="20" customHeight="1">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>Toast</t>
+        </is>
+      </c>
+      <c r="D188" s="14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="189" ht="20" customHeight="1">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="D189" s="14" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="190" ht="20" customHeight="1">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D190" s="14" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>Smile</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" ht="20" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="193" ht="20" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>hoist</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="194" ht="20" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Indicator Mobile</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="195" ht="20" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+      <c r="D195" s="14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196" ht="20" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Commercial Chips</t>
+        </is>
+      </c>
+      <c r="D196" s="14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="D197" s="14" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="198" ht="20" customHeight="1">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="199" ht="20" customHeight="1">
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Step 01</t>
+        </is>
+      </c>
+      <c r="D199" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" ht="20" customHeight="1">
+      <c r="A200" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Step 02</t>
+        </is>
+      </c>
+      <c r="D200" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="201" ht="20" customHeight="1">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Step 03</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="202" ht="20" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Menu Item</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="203" ht="20" customHeight="1">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>celda</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D204" s="14" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="205" ht="20" customHeight="1">
+      <c r="A205" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>Menu title</t>
+        </is>
+      </c>
+      <c r="D205" s="14" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="206" ht="20" customHeight="1">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Component 120</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="207" ht="20" customHeight="1">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>directionLeft</t>
+        </is>
+      </c>
+      <c r="D207" s="14" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="208" ht="20" customHeight="1">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D208" s="14" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1">
+      <c r="A209" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="D209" s="14" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="210" ht="20" customHeight="1">
+      <c r="A210" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Star</t>
+        </is>
+      </c>
+      <c r="D210" s="14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" ht="20" customHeight="1">
+      <c r="A211" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>Topbar</t>
+        </is>
+      </c>
+      <c r="D211" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="212" ht="20" customHeight="1">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="D212" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" ht="20" customHeight="1">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="D213" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" ht="20" customHeight="1">
+      <c r="A214" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D214" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" ht="20" customHeight="1">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>LocationPin</t>
+        </is>
+      </c>
+      <c r="D215" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>Indicator Mobile</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="217" ht="20" customHeight="1">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Step 01</t>
+        </is>
+      </c>
+      <c r="D217" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="218" ht="20" customHeight="1">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Bar Progress</t>
+        </is>
+      </c>
+      <c r="D218" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="219" ht="20" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Step 02</t>
+        </is>
+      </c>
+      <c r="D219" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="220" ht="20" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>torito</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="221" ht="20" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="223" ht="20" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="D223" s="14" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="224" ht="20" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D224" s="14" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="225" ht="20" customHeight="1">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>Menu Item</t>
+        </is>
+      </c>
+      <c r="D225" s="14" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="226" ht="20" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>01 Info</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="227" ht="20" customHeight="1">
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>ArrowLeft</t>
+        </is>
+      </c>
+      <c r="D227" s="14" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="228" ht="20" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="D228" s="14" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="229" ht="20" customHeight="1">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>whatsapp</t>
+        </is>
+      </c>
+      <c r="D229" s="14" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="230" ht="20" customHeight="1">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="D231" s="14" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="232" ht="20" customHeight="1">
+      <c r="A232" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>Chip Deleteable</t>
+        </is>
+      </c>
+      <c r="D232" s="14" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="233" ht="20" customHeight="1">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>correo electronico</t>
+        </is>
+      </c>
+      <c r="D233" s="14" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="234" ht="20" customHeight="1">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>Menu title</t>
+        </is>
+      </c>
+      <c r="D234" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="235" ht="20" customHeight="1">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>addcircle</t>
+        </is>
+      </c>
+      <c r="D235" s="14" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" ht="20" customHeight="1">
+      <c r="A236" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>call</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="238" ht="20" customHeight="1">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D238" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="239" ht="20" customHeight="1">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>generando ia</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="240" ht="20" customHeight="1">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>creditcard</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="241" ht="20" customHeight="1">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>A.white</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D242" s="14" t="n">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="243" ht="20" customHeight="1">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="244" ht="20" customHeight="1">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>CardProductPromo</t>
+        </is>
+      </c>
+      <c r="D244" s="14" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="245" ht="20" customHeight="1">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="246" ht="20" customHeight="1">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Cotizar</t>
+        </is>
+      </c>
+      <c r="D246" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="247" ht="20" customHeight="1">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D247" s="14" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="248" ht="20" customHeight="1">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Close Icon</t>
+        </is>
+      </c>
+      <c r="D248" s="14" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="249" ht="20" customHeight="1">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D249" s="14" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="250" ht="20" customHeight="1">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>CardMenúMobile</t>
+        </is>
+      </c>
+      <c r="D250" s="14" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="251" ht="20" customHeight="1">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D251" s="14" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="252" ht="20" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>CardMenú</t>
+        </is>
+      </c>
+      <c r="D252" s="14" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="253" ht="20" customHeight="1">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="D253" s="14" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="254" ht="20" customHeight="1">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D254" s="14" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="255" ht="20" customHeight="1">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>ShieldHeart</t>
+        </is>
+      </c>
+      <c r="D255" s="14" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="256" ht="20" customHeight="1">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>BotónCategoría</t>
+        </is>
+      </c>
+      <c r="D256" s="14" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="257" ht="20" customHeight="1">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Slider</t>
+        </is>
+      </c>
+      <c r="D257" s="14" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="258" ht="20" customHeight="1">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>_Link Icon</t>
+        </is>
+      </c>
+      <c r="D258" s="14" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="259" ht="20" customHeight="1">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>_Button Icon</t>
+        </is>
+      </c>
+      <c r="D259" s="14" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="260" ht="20" customHeight="1">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D260" s="14" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="261" ht="20" customHeight="1">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D261" s="14" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="262" ht="20" customHeight="1">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B262" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>grid view</t>
+        </is>
+      </c>
+      <c r="D262" s="14" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="263" ht="20" customHeight="1">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="D263" s="14" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="264" ht="20" customHeight="1">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D264" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="265" ht="20" customHeight="1">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>SecciónDescripción</t>
+        </is>
+      </c>
+      <c r="D265" s="14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="266" ht="20" customHeight="1">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D266" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="267" ht="20" customHeight="1">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D267" s="14" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="268" ht="20" customHeight="1">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>operador</t>
+        </is>
+      </c>
+      <c r="D268" s="14" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="269" ht="20" customHeight="1">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D269" s="14" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="270" ht="20" customHeight="1">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>SeccionCanales</t>
+        </is>
+      </c>
+      <c r="D270" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271" ht="20" customHeight="1">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>PersonalInjuy</t>
+        </is>
+      </c>
+      <c r="D271" s="14" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272" ht="20" customHeight="1">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D272" s="14" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="273" ht="20" customHeight="1">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>LogosCollab</t>
+        </is>
+      </c>
+      <c r="D273" s="14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="274" ht="20" customHeight="1">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>CoberturasIconos</t>
+        </is>
+      </c>
+      <c r="D274" s="14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" ht="20" customHeight="1">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D275" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="276" ht="20" customHeight="1">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D276" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="277" ht="20" customHeight="1">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>menu</t>
+        </is>
+      </c>
+      <c r="D277" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="278" ht="20" customHeight="1">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>title_+_badges_download</t>
+        </is>
+      </c>
+      <c r="D278" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="279" ht="20" customHeight="1">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
         <is>
           <t>instagram</t>
         </is>
       </c>
-      <c r="D181" s="14" t="n">
-        <v>2</v>
+      <c r="D279" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="280" ht="20" customHeight="1">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="D280" s="14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="281" ht="20" customHeight="1">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="D281" s="14" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5411,7 +7556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5473,19 +7618,19 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D2" s="10" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>645</v>
+        <v>825</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>1294</v>
@@ -5544,13 +7689,13 @@
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>450</v>
+        <v>1422</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>554</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -5711,7 +7856,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Somos Corredores</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -5724,50 +7869,205 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>79%</t>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3647</v>
+        <v>1508</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4614</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>3647</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>3684</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>4881</v>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2007</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>3273</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>2329</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>4071</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>4451</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
           <t>Web Corporativa</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>21</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>1842</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>2246</v>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>72</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>10823</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>13705</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -952,7 +952,7 @@
         <v>72</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10823</v>
+        <v>10822</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>2882</v>
@@ -1005,7 +1005,7 @@
         <v>207</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>232064</v>
+        <v>232063</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>58961</v>
@@ -1821,13 +1821,13 @@
         <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4389</v>
+        <v>4388</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>1477</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5866</v>
+        <v>5865</v>
       </c>
       <c r="H23" s="9" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         <v>72</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>10823</v>
+        <v>10822</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>13705</v>
+        <v>13704</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -64,7 +64,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFD94F3D"/>
+      <color rgb="FFF5A623"/>
       <sz val="10"/>
     </font>
     <font>
@@ -76,7 +76,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFF5A623"/>
+      <color rgb="FFD94F3D"/>
       <sz val="10"/>
     </font>
     <font>
@@ -545,7 +545,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  Generado: 2026-06-18</t>
+          <t>Quarter: Q2 2026  |  Generado: 2026-06-19</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>2680</v>
+        <v>3018</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>5302</v>
+        <v>1112</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -633,14 +633,14 @@
         <v>12</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3647</v>
+        <v>3852</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>967</v>
+        <v>600</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -662,14 +662,14 @@
         <v>8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7035</v>
+        <v>8343</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>2896</v>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>71%</t>
+        <v>845</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
         <v>2</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>169195</v>
+        <v>34401</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>28141</v>
+        <v>2561</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>93%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>10174</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3543</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -746,17 +746,17 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>13615</v>
+        <v>11224</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8209</v>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>62%</t>
+        <v>6637</v>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
     </row>
@@ -778,14 +778,14 @@
         <v>1</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>1508</v>
+        <v>1583</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>679</v>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>526</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -807,14 +807,14 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2007</v>
+        <v>2296</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1266</v>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>847</v>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -836,14 +836,14 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>825</v>
+        <v>921</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>469</v>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>334</v>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -865,14 +865,14 @@
         <v>2</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2329</v>
+        <v>2650</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>1742</v>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>57%</t>
+        <v>1163</v>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
     </row>
@@ -891,17 +891,17 @@
         <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1331</v>
+        <v>0</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -920,17 +920,17 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3684</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1197</v>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>10822</v>
+        <v>1666</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2882</v>
+        <v>212</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1422</v>
+        <v>224</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
         <v>24</v>
       </c>
       <c r="D19" s="11" t="n">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>232063</v>
+        <v>70178</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>58961</v>
+        <v>14871</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>83%</t>
         </is>
       </c>
     </row>
@@ -1107,17 +1107,17 @@
         <v>4</v>
       </c>
       <c r="E2" s="7" t="n">
-        <v>574</v>
+        <v>608</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>720</v>
+        <v>248</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1294</v>
+        <v>856</v>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>71%</t>
         </is>
       </c>
     </row>
@@ -1141,17 +1141,17 @@
         <v>11</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>2093</v>
+        <v>2395</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>4563</v>
+        <v>859</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>6656</v>
+        <v>3254</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>74%</t>
         </is>
       </c>
     </row>
@@ -1175,17 +1175,17 @@
         <v>1</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>55%</t>
+        <v>17</v>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>76%</t>
         </is>
       </c>
     </row>
@@ -1212,14 +1212,14 @@
         <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>67%</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
         <v>5</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1037</v>
+        <v>1193</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>665</v>
+        <v>434</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1702</v>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>1627</v>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
         <v>7</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>2610</v>
+        <v>2659</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2912</v>
+        <v>2825</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -1311,17 +1311,17 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1272</v>
+        <v>1308</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>1547</v>
+        <v>1519</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -1345,17 +1345,17 @@
         <v>6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>5763</v>
+        <v>7035</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2621</v>
+        <v>634</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8384</v>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>7669</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>92%</t>
         </is>
       </c>
     </row>
@@ -1379,17 +1379,17 @@
         <v>7</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>15000</v>
+        <v>15205</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>2138</v>
+        <v>866</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>17138</v>
+        <v>16071</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>95%</t>
         </is>
       </c>
     </row>
@@ -1410,20 +1410,20 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>154195</v>
+        <v>19196</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>26003</v>
+        <v>1695</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>180198</v>
+        <v>20891</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>92%</t>
         </is>
       </c>
     </row>
@@ -1444,20 +1444,20 @@
         </is>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10174</v>
+        <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3543</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>13717</v>
+        <v>0</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1478,20 +1478,20 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7697</v>
+        <v>5260</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2930</v>
+        <v>1584</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>10627</v>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>72%</t>
+        <v>6844</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>77%</t>
         </is>
       </c>
     </row>
@@ -1515,17 +1515,17 @@
         <v>6</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4145</v>
+        <v>4163</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>4844</v>
+        <v>4695</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>8989</v>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>46%</t>
+        <v>8858</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>47%</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1773</v>
+        <v>1801</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>435</v>
+        <v>358</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2208</v>
+        <v>2159</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>83%</t>
         </is>
       </c>
     </row>
@@ -1583,17 +1583,17 @@
         <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1508</v>
+        <v>1583</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>679</v>
+        <v>526</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>2187</v>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>69%</t>
+        <v>2109</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
     </row>
@@ -1617,17 +1617,17 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2007</v>
+        <v>2296</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1266</v>
+        <v>847</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>3273</v>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>61%</t>
+        <v>3143</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -1651,17 +1651,17 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>825</v>
+        <v>921</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>469</v>
+        <v>334</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>1294</v>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>64%</t>
+        <v>1255</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
     </row>
@@ -1685,17 +1685,17 @@
         <v>2</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>2329</v>
+        <v>2650</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1742</v>
+        <v>1163</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>4071</v>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>57%</t>
+        <v>3813</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
     </row>
@@ -1716,20 +1716,20 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1331</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>4451</v>
+        <v>0</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1750,20 +1750,20 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3684</v>
+        <v>0</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1197</v>
+        <v>0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>4881</v>
-      </c>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>0</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1784,20 +1784,20 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5041</v>
+        <v>562</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>1132</v>
+        <v>74</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>6173</v>
+        <v>636</v>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -1818,20 +1818,20 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4388</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1477</v>
+        <v>0</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>5865</v>
-      </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>75%</t>
+        <v>0</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1852,20 +1852,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1393</v>
+        <v>1104</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1666</v>
+        <v>1242</v>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -1886,20 +1886,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1422</v>
+        <v>224</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>337</v>
+        <v>34</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1759</v>
+        <v>258</v>
       </c>
       <c r="H25" s="9" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1958,11 +1958,11 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>menú</t>
+          <t>card_accion</t>
         </is>
       </c>
       <c r="D2" s="14" t="n">
-        <v>1761</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -1978,11 +1978,11 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>card_atajo_home</t>
         </is>
       </c>
       <c r="D3" s="14" t="n">
-        <v>527</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
@@ -1998,11 +1998,11 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>documento simple</t>
         </is>
       </c>
       <c r="D4" s="14" t="n">
-        <v>368</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -2018,11 +2018,11 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Seguros card</t>
         </is>
       </c>
       <c r="D5" s="14" t="n">
-        <v>352</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -2038,11 +2038,11 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>card_accion</t>
+          <t>Card_ beneficios</t>
         </is>
       </c>
       <c r="D6" s="14" t="n">
-        <v>217</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -2058,11 +2058,11 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>card_atajo_home</t>
+          <t>beneficios vehiculares</t>
         </is>
       </c>
       <c r="D7" s="14" t="n">
-        <v>212</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -2078,11 +2078,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>177</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -2098,11 +2098,11 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>shoppingcart</t>
+          <t>carro</t>
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>177</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -2118,11 +2118,11 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>chat</t>
+          <t>buscar clínicas</t>
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>176</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -2138,11 +2138,11 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>hogar</t>
         </is>
       </c>
       <c r="D11" s="14" t="n">
-        <v>174</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -2158,11 +2158,11 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Star</t>
+          <t>drag</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>162</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -2178,11 +2178,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Bottom app bar</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D13" s="14" t="n">
-        <v>138</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -2198,11 +2198,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>documento simple</t>
+          <t>error duda</t>
         </is>
       </c>
       <c r="D14" s="14" t="n">
-        <v>100</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -2218,11 +2218,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Seguros card</t>
+          <t>logo beneficios</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>sirena emergencia</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -2258,11 +2258,11 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>descarga documento</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -2278,11 +2278,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>informacion de poliza</t>
+          <t>Bottom Navigation</t>
         </is>
       </c>
       <c r="D18" s="14" t="n">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -2298,11 +2298,11 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Card_ beneficios</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -2318,11 +2318,11 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>beneficios vehiculares</t>
+          <t>card_atajo</t>
         </is>
       </c>
       <c r="D20" s="14" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -2338,11 +2338,11 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>ahorros</t>
+          <t>Cobertuas y exclusiones | DSK</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -2358,11 +2358,11 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Suggested search (Deprecated)</t>
         </is>
       </c>
       <c r="D22" s="14" t="n">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -2378,11 +2378,11 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Suggested search (Deprecated)</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
@@ -2398,11 +2398,11 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
@@ -2438,11 +2438,11 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>celda L</t>
         </is>
       </c>
       <c r="D26" s="14" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1">
@@ -2458,11 +2458,11 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Step 03</t>
+          <t>Step 04</t>
         </is>
       </c>
       <c r="D27" s="14" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
@@ -2478,11 +2478,11 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>celda L</t>
+          <t>Step 05</t>
         </is>
       </c>
       <c r="D28" s="14" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -2498,11 +2498,11 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Step 04</t>
+          <t>Upload icon</t>
         </is>
       </c>
       <c r="D29" s="14" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
@@ -2518,11 +2518,11 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Step 05</t>
+          <t>Userflow</t>
         </is>
       </c>
       <c r="D30" s="14" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -2538,11 +2538,11 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D31" s="14" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
@@ -2558,11 +2558,11 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Upload icon</t>
+          <t>celda S</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
-        <v>31</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
@@ -2578,11 +2578,11 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Userflow</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D33" s="14" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -2598,11 +2598,11 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>ArrowLeft</t>
+          <t>titulo-fila</t>
         </is>
       </c>
       <c r="D34" s="14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1">
@@ -2618,11 +2618,11 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>celda S</t>
+          <t>Respuesta</t>
         </is>
       </c>
       <c r="D35" s="14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1">
@@ -2638,11 +2638,11 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D36" s="14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>titulo-fila</t>
+          <t>audifonos</t>
         </is>
       </c>
       <c r="D37" s="14" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1">
@@ -2678,11 +2678,11 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>generate ai</t>
+          <t>Container Drag and Drop</t>
         </is>
       </c>
       <c r="D38" s="14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -2698,11 +2698,11 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="D39" s="14" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -2718,11 +2718,11 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>arrow_carrousel</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D40" s="14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1">
@@ -2738,11 +2738,11 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D41" s="14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1">
@@ -2758,11 +2758,11 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>HealthAndSafe</t>
         </is>
       </c>
       <c r="D42" s="14" t="n">
-        <v>640</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -2778,11 +2778,11 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D43" s="14" t="n">
-        <v>160</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1">
@@ -2798,11 +2798,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D44" s="14" t="n">
-        <v>160</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
@@ -2818,11 +2818,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
       <c r="D45" s="14" t="n">
-        <v>105</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
@@ -2838,11 +2838,11 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>HealthAndSafe</t>
+          <t>Menu_Mobile</t>
         </is>
       </c>
       <c r="D46" s="14" t="n">
-        <v>96</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -2858,11 +2858,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D47" s="14" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
@@ -2878,11 +2878,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>eye_close</t>
+          <t>NorthEast</t>
         </is>
       </c>
       <c r="D48" s="14" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
@@ -2898,11 +2898,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Menú_Desktop</t>
         </is>
       </c>
       <c r="D49" s="14" t="n">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1">
@@ -2918,11 +2918,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D50" s="14" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1">
@@ -2938,11 +2938,11 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D51" s="14" t="n">
-        <v>61</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1">
@@ -2958,11 +2958,11 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>beneficios reconocerte</t>
         </is>
       </c>
       <c r="D52" s="14" t="n">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1">
@@ -2978,11 +2978,11 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D53" s="14" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1">
@@ -2998,11 +2998,11 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>filter</t>
         </is>
       </c>
       <c r="D54" s="14" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Beneficio | card</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D55" s="14" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1">
@@ -3038,11 +3038,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Feed</t>
         </is>
       </c>
       <c r="D56" s="14" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -3058,11 +3058,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D57" s="14" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1">
@@ -3078,11 +3078,11 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Beneficio | card mobile</t>
+          <t>trofeo</t>
         </is>
       </c>
       <c r="D58" s="14" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -3098,11 +3098,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Banner | errores</t>
+          <t>vida ley</t>
         </is>
       </c>
       <c r="D59" s="14" t="n">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -3118,11 +3118,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>generate ai</t>
+          <t>tratamiento</t>
         </is>
       </c>
       <c r="D60" s="14" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1">
@@ -3138,11 +3138,11 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>Right Label</t>
         </is>
       </c>
       <c r="D61" s="14" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
@@ -3158,11 +3158,11 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>celda S</t>
         </is>
       </c>
       <c r="D62" s="14" t="n">
-        <v>5595</v>
+        <v>494</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -3178,11 +3178,11 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>celda S</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D63" s="14" t="n">
-        <v>2366</v>
+        <v>295</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>eye_close</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D64" s="14" t="n">
-        <v>1671</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -3218,11 +3218,11 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D65" s="14" t="n">
-        <v>1536</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
@@ -3238,11 +3238,11 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>Download Icon</t>
         </is>
       </c>
       <c r="D66" s="14" t="n">
-        <v>1019</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
@@ -3258,11 +3258,11 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>day_format</t>
         </is>
       </c>
       <c r="D67" s="14" t="n">
-        <v>948</v>
+        <v>84</v>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
@@ -3278,11 +3278,11 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Apps</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D68" s="14" t="n">
-        <v>793</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -3298,11 +3298,11 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D69" s="14" t="n">
-        <v>780</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" ht="20" customHeight="1">
@@ -3318,11 +3318,11 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="D70" s="14" t="n">
-        <v>769</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" ht="20" customHeight="1">
@@ -3338,11 +3338,11 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="D71" s="14" t="n">
-        <v>769</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" ht="20" customHeight="1">
@@ -3358,11 +3358,11 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="D72" s="14" t="n">
-        <v>769</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
@@ -3378,11 +3378,11 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="D73" s="14" t="n">
-        <v>697</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
@@ -3398,11 +3398,11 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>account</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="D74" s="14" t="n">
-        <v>564</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="D75" s="14" t="n">
-        <v>550</v>
+        <v>58</v>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
@@ -3438,11 +3438,11 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="D76" s="14" t="n">
-        <v>523</v>
+        <v>40</v>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Home_Header</t>
+          <t>Userflow</t>
         </is>
       </c>
       <c r="D77" s="14" t="n">
-        <v>511</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
@@ -3478,11 +3478,11 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Action 1</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D78" s="14" t="n">
-        <v>496</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
@@ -3498,11 +3498,11 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Action 2</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D79" s="14" t="n">
-        <v>496</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -3518,11 +3518,11 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Menu_Mobile</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D80" s="14" t="n">
-        <v>482</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -3538,811 +3538,811 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>titulo-fila</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D81" s="14" t="n">
-        <v>433</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Pegar Icon</t>
+          <t>desk Table cell</t>
         </is>
       </c>
       <c r="D82" s="14" t="n">
-        <v>484</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D83" s="14" t="n">
-        <v>439</v>
+        <v>643</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>Component 16</t>
         </is>
       </c>
       <c r="D84" s="14" t="n">
-        <v>328</v>
+        <v>267</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>DirectionRight</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D85" s="14" t="n">
-        <v>268</v>
+        <v>232</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>Botón Primario</t>
         </is>
       </c>
       <c r="D86" s="14" t="n">
-        <v>212</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Dropdown filter page</t>
         </is>
       </c>
       <c r="D87" s="14" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>width fixed pagination</t>
         </is>
       </c>
       <c r="D88" s="14" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Component 9</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D89" s="14" t="n">
-        <v>94</v>
+        <v>135</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D90" s="14" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D91" s="14" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D92" s="14" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D93" s="14" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Card Dashboard</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D94" s="14" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>BtnBackNext</t>
         </is>
       </c>
       <c r="D95" s="14" t="n">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Frame 1707479054</t>
+          <t>Pregunta formulario</t>
         </is>
       </c>
       <c r="D96" s="14" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Frame 1707479133</t>
+          <t>barras</t>
         </is>
       </c>
       <c r="D97" s="14" t="n">
-        <v>44</v>
+        <v>86</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>list</t>
         </is>
       </c>
       <c r="D98" s="14" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D99" s="14" t="n">
-        <v>32</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D100" s="14" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>informacion de poliza</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D101" s="14" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>desk Table cell</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D102" s="14" t="n">
-        <v>2624</v>
+        <v>41</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D103" s="14" t="n">
-        <v>643</v>
+        <v>31</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D104" s="14" t="n">
-        <v>311</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Component 16</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D105" s="14" t="n">
-        <v>270</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Botón Primario</t>
+          <t>number_deskop</t>
         </is>
       </c>
       <c r="D106" s="14" t="n">
-        <v>180</v>
+        <v>24</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Dropdown filter page</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D107" s="14" t="n">
-        <v>159</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>width fixed pagination</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D108" s="14" t="n">
-        <v>159</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D109" s="14" t="n">
-        <v>135</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D110" s="14" t="n">
-        <v>116</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D111" s="14" t="n">
-        <v>116</v>
+        <v>17</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>barras</t>
+          <t>tarjeta de crédito</t>
         </is>
       </c>
       <c r="D112" s="14" t="n">
-        <v>112</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>settings</t>
+          <t>Póliza Salud</t>
         </is>
       </c>
       <c r="D113" s="14" t="n">
-        <v>111</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D114" s="14" t="n">
-        <v>109</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D115" s="14" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>face</t>
         </is>
       </c>
       <c r="D116" s="14" t="n">
-        <v>108</v>
+        <v>10</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>soat</t>
         </is>
       </c>
       <c r="D117" s="14" t="n">
-        <v>107</v>
+        <v>10</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>01_card selector</t>
         </is>
       </c>
       <c r="D118" s="14" t="n">
-        <v>103</v>
+        <v>10</v>
       </c>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>vehiculares</t>
         </is>
       </c>
       <c r="D119" s="14" t="n">
-        <v>96</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>AGENDA</t>
+          <t>Card_Cross_RT_Deskop_Cob</t>
         </is>
       </c>
       <c r="D120" s="14" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>AddCard</t>
         </is>
       </c>
       <c r="D121" s="14" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" ht="20" customHeight="1">
@@ -4353,16 +4353,16 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D122" s="14" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -4373,16 +4373,16 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D123" s="14" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
@@ -4393,16 +4393,16 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D124" s="14" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" ht="20" customHeight="1">
@@ -4413,16 +4413,16 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D125" s="14" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126" ht="20" customHeight="1">
@@ -4433,16 +4433,16 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Infotip</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D126" s="14" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -4453,16 +4453,16 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>number_deskop</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D127" s="14" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" ht="20" customHeight="1">
@@ -4473,16 +4473,16 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D128" s="14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" ht="20" customHeight="1">
@@ -4493,16 +4493,16 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D129" s="14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -4513,16 +4513,16 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>eye_open</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="D130" s="14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -4533,16 +4533,16 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D131" s="14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" ht="20" customHeight="1">
@@ -4553,16 +4553,16 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D132" s="14" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="133" ht="20" customHeight="1">
@@ -4573,16 +4573,16 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Step 03</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D133" s="14" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" ht="20" customHeight="1">
@@ -4593,16 +4593,16 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>shield</t>
+          <t>tarjeta de crédito</t>
         </is>
       </c>
       <c r="D134" s="14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" ht="20" customHeight="1">
@@ -4613,16 +4613,16 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>tarjeta de crédito</t>
+          <t>asset_promo</t>
         </is>
       </c>
       <c r="D135" s="14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136" ht="20" customHeight="1">
@@ -4633,16 +4633,16 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Póliza Salud</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D136" s="14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="137" ht="20" customHeight="1">
@@ -4653,16 +4653,16 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Image Frame</t>
         </is>
       </c>
       <c r="D137" s="14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -4673,16 +4673,16 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D138" s="14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="139" ht="20" customHeight="1">
@@ -4693,16 +4693,16 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D139" s="14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" ht="20" customHeight="1">
@@ -4713,16 +4713,16 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D140" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141" ht="20" customHeight="1">
@@ -4733,16 +4733,16 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>BtnAyuda</t>
         </is>
       </c>
       <c r="D141" s="14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="142" ht="20" customHeight="1">
@@ -4753,16 +4753,16 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="D142" s="14" t="n">
-        <v>149</v>
+        <v>29</v>
       </c>
     </row>
     <row r="143" ht="20" customHeight="1">
@@ -4773,16 +4773,16 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D143" s="14" t="n">
-        <v>105</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" ht="20" customHeight="1">
@@ -4793,16 +4793,16 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Caja formulario complex L M</t>
         </is>
       </c>
       <c r="D144" s="14" t="n">
-        <v>102</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145" ht="20" customHeight="1">
@@ -4813,16 +4813,16 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>Contenido desktop</t>
         </is>
       </c>
       <c r="D145" s="14" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" ht="20" customHeight="1">
@@ -4833,16 +4833,16 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>Formulario L M complex</t>
         </is>
       </c>
       <c r="D146" s="14" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" ht="20" customHeight="1">
@@ -4853,16 +4853,16 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>Banner mobile</t>
         </is>
       </c>
       <c r="D147" s="14" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" ht="20" customHeight="1">
@@ -4873,16 +4873,16 @@
       </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" ht="20" customHeight="1">
@@ -4893,16 +4893,16 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Contenido mobile</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" ht="20" customHeight="1">
@@ -4913,16 +4913,16 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" ht="20" customHeight="1">
@@ -4933,16 +4933,16 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Infotip</t>
+          <t>CajaFormulario</t>
         </is>
       </c>
       <c r="D151" s="14" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" ht="20" customHeight="1">
@@ -4953,16 +4953,16 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Carousel</t>
         </is>
       </c>
       <c r="D152" s="14" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153" ht="20" customHeight="1">
@@ -4973,16 +4973,16 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Card_Mobile_funciona 1</t>
         </is>
       </c>
       <c r="D153" s="14" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" ht="20" customHeight="1">
@@ -4993,16 +4993,16 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Card_Mobile_funciona 3</t>
         </is>
       </c>
       <c r="D154" s="14" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -5013,16 +5013,16 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Card_Mobile_funciona 4</t>
         </is>
       </c>
       <c r="D155" s="14" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" ht="20" customHeight="1">
@@ -5033,16 +5033,16 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>eye_open</t>
+          <t>Card_Mobile_funciona 5</t>
         </is>
       </c>
       <c r="D156" s="14" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157" ht="20" customHeight="1">
@@ -5053,16 +5053,16 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>Card_Mobile_funciona 6</t>
         </is>
       </c>
       <c r="D157" s="14" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" ht="20" customHeight="1">
@@ -5073,16 +5073,16 @@
       </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>tarjeta de crédito</t>
+          <t>Emergencias</t>
         </is>
       </c>
       <c r="D158" s="14" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -5093,16 +5093,16 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>asset_promo</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D159" s="14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" ht="20" customHeight="1">
@@ -5113,16 +5113,16 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D160" s="14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" ht="20" customHeight="1">
@@ -5133,16 +5133,16 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Image Frame</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D161" s="14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -5153,16 +5153,16 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls Glass</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D162" s="14" t="n">
-        <v>30</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163" ht="20" customHeight="1">
@@ -5173,16 +5173,16 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D163" s="14" t="n">
-        <v>30</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164" ht="20" customHeight="1">
@@ -5193,16 +5193,16 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D164" s="14" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
     </row>
     <row r="165" ht="20" customHeight="1">
@@ -5213,16 +5213,16 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D165" s="14" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="166" ht="20" customHeight="1">
@@ -5233,16 +5233,16 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Caja formulario complex L M</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D166" s="14" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="167" ht="20" customHeight="1">
@@ -5253,16 +5253,16 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Contenido desktop</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D167" s="14" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168" ht="20" customHeight="1">
@@ -5273,16 +5273,16 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Formulario L M complex</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D168" s="14" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169" ht="20" customHeight="1">
@@ -5293,16 +5293,16 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Banner mobile</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D169" s="14" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170" ht="20" customHeight="1">
@@ -5313,16 +5313,16 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D170" s="14" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171" ht="20" customHeight="1">
@@ -5333,16 +5333,16 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D171" s="14" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -5353,16 +5353,16 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D172" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" ht="20" customHeight="1">
@@ -5373,16 +5373,16 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Contenido mobile</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D173" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" ht="20" customHeight="1">
@@ -5393,16 +5393,16 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D174" s="14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175" ht="20" customHeight="1">
@@ -5413,16 +5413,16 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>choque</t>
         </is>
       </c>
       <c r="D175" s="14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176" ht="20" customHeight="1">
@@ -5433,16 +5433,16 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="D176" s="14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177" ht="20" customHeight="1">
@@ -5453,16 +5453,16 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>CajaFormulario</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D177" s="14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178" ht="20" customHeight="1">
@@ -5473,16 +5473,16 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="D178" s="14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179" ht="20" customHeight="1">
@@ -5493,16 +5493,16 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 1</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D179" s="14" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -5513,16 +5513,16 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D180" s="14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" ht="20" customHeight="1">
@@ -5533,2016 +5533,736 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 4</t>
+          <t>BtnAyuda</t>
         </is>
       </c>
       <c r="D181" s="14" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182" ht="20" customHeight="1">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>grid view</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D182" s="14" t="n">
-        <v>154</v>
+        <v>31</v>
       </c>
     </row>
     <row r="183" ht="20" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D183" s="14" t="n">
-        <v>151</v>
+        <v>26</v>
       </c>
     </row>
     <row r="184" ht="20" customHeight="1">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D184" s="14" t="n">
-        <v>116</v>
+        <v>26</v>
       </c>
     </row>
     <row r="185" ht="20" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D185" s="14" t="n">
-        <v>109</v>
+        <v>25</v>
       </c>
     </row>
     <row r="186" ht="20" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D186" s="14" t="n">
-        <v>107</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" ht="20" customHeight="1">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D187" s="14" t="n">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="188" ht="20" customHeight="1">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D188" s="14" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189" ht="20" customHeight="1">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D189" s="14" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" ht="20" customHeight="1">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D190" s="14" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" ht="20" customHeight="1">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D191" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" ht="20" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>hogar</t>
         </is>
       </c>
       <c r="D192" s="14" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" ht="20" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>hoist</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D193" s="14" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="194" ht="20" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D194" s="14" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195" ht="20" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>emergency</t>
+          <t>vida inversión</t>
         </is>
       </c>
       <c r="D195" s="14" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" ht="20" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D196" s="14" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" ht="20" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D197" s="14" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" ht="20" customHeight="1">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D198" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" ht="20" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>user</t>
         </is>
       </c>
       <c r="D199" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" ht="20" customHeight="1">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D200" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" ht="20" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Step 03</t>
+          <t>Beneficios</t>
         </is>
       </c>
       <c r="D201" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" ht="20" customHeight="1">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>SecciónDescripción</t>
         </is>
       </c>
       <c r="D202" s="14" t="n">
-        <v>340</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" ht="20" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>celda</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D203" s="14" t="n">
-        <v>312</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" ht="20" customHeight="1">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D204" s="14" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" ht="20" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D205" s="14" t="n">
-        <v>85</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" ht="20" customHeight="1">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Component 120</t>
+          <t>LogosCollab</t>
         </is>
       </c>
       <c r="D206" s="14" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" ht="20" customHeight="1">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>avión</t>
         </is>
       </c>
       <c r="D207" s="14" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" ht="20" customHeight="1">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>call</t>
+          <t>generales</t>
         </is>
       </c>
       <c r="D208" s="14" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" ht="20" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>SeccionCanales</t>
         </is>
       </c>
       <c r="D209" s="14" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" ht="20" customHeight="1">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Star</t>
+          <t>CoberturasIconos</t>
         </is>
       </c>
       <c r="D210" s="14" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" ht="20" customHeight="1">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D211" s="14" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" ht="20" customHeight="1">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>instagram</t>
+          <t>PersonalInjuy</t>
         </is>
       </c>
       <c r="D212" s="14" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" ht="20" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>tiktok</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D213" s="14" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" ht="20" customHeight="1">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D214" s="14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" ht="20" customHeight="1">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>LocationPin</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D215" s="14" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" ht="20" customHeight="1">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D216" s="14" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" ht="20" customHeight="1">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D217" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="218" ht="20" customHeight="1">
-      <c r="A218" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B218" s="4" t="inlineStr">
-        <is>
-          <t>Viajes</t>
-        </is>
-      </c>
-      <c r="C218" s="4" t="inlineStr">
-        <is>
-          <t>Bar Progress</t>
-        </is>
-      </c>
-      <c r="D218" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="219" ht="20" customHeight="1">
-      <c r="A219" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B219" s="4" t="inlineStr">
-        <is>
-          <t>Viajes</t>
-        </is>
-      </c>
-      <c r="C219" s="4" t="inlineStr">
-        <is>
-          <t>Step 02</t>
-        </is>
-      </c>
-      <c r="D219" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="220" ht="20" customHeight="1">
-      <c r="A220" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B220" s="4" t="inlineStr">
-        <is>
-          <t>Viajes</t>
-        </is>
-      </c>
-      <c r="C220" s="4" t="inlineStr">
-        <is>
-          <t>torito</t>
-        </is>
-      </c>
-      <c r="D220" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="221" ht="20" customHeight="1">
-      <c r="A221" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B221" s="4" t="inlineStr">
-        <is>
-          <t>Viajes</t>
-        </is>
-      </c>
-      <c r="C221" s="4" t="inlineStr">
-        <is>
-          <t>mail</t>
-        </is>
-      </c>
-      <c r="D221" s="14" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="222" ht="20" customHeight="1">
-      <c r="A222" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B222" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C222" s="4" t="inlineStr">
-        <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="D222" s="14" t="n">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="223" ht="20" customHeight="1">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B223" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C223" s="4" t="inlineStr">
-        <is>
-          <t>Slider Controls</t>
-        </is>
-      </c>
-      <c r="D223" s="14" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="224" ht="20" customHeight="1">
-      <c r="A224" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B224" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C224" s="4" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="D224" s="14" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="225" ht="20" customHeight="1">
-      <c r="A225" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B225" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="inlineStr">
-        <is>
-          <t>Menu Item</t>
-        </is>
-      </c>
-      <c r="D225" s="14" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="226" ht="20" customHeight="1">
-      <c r="A226" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B226" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C226" s="4" t="inlineStr">
-        <is>
-          <t>01 Info</t>
-        </is>
-      </c>
-      <c r="D226" s="14" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="227" ht="20" customHeight="1">
-      <c r="A227" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B227" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C227" s="4" t="inlineStr">
-        <is>
-          <t>ArrowLeft</t>
-        </is>
-      </c>
-      <c r="D227" s="14" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="228" ht="20" customHeight="1">
-      <c r="A228" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B228" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C228" s="4" t="inlineStr">
-        <is>
-          <t>Simple</t>
-        </is>
-      </c>
-      <c r="D228" s="14" t="n">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="229" ht="20" customHeight="1">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C229" s="4" t="inlineStr">
-        <is>
-          <t>whatsapp</t>
-        </is>
-      </c>
-      <c r="D229" s="14" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1">
-      <c r="A230" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B230" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C230" s="4" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D230" s="14" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="231" ht="20" customHeight="1">
-      <c r="A231" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B231" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C231" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="D231" s="14" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="232" ht="20" customHeight="1">
-      <c r="A232" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B232" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C232" s="4" t="inlineStr">
-        <is>
-          <t>Chip Deleteable</t>
-        </is>
-      </c>
-      <c r="D232" s="14" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="233" ht="20" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B233" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C233" s="4" t="inlineStr">
-        <is>
-          <t>correo electronico</t>
-        </is>
-      </c>
-      <c r="D233" s="14" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="234" ht="20" customHeight="1">
-      <c r="A234" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B234" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C234" s="4" t="inlineStr">
-        <is>
-          <t>Menu title</t>
-        </is>
-      </c>
-      <c r="D234" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="235" ht="20" customHeight="1">
-      <c r="A235" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B235" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C235" s="4" t="inlineStr">
-        <is>
-          <t>addcircle</t>
-        </is>
-      </c>
-      <c r="D235" s="14" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="236" ht="20" customHeight="1">
-      <c r="A236" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B236" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C236" s="4" t="inlineStr">
-        <is>
-          <t>call</t>
-        </is>
-      </c>
-      <c r="D236" s="14" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="237" ht="20" customHeight="1">
-      <c r="A237" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B237" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C237" s="4" t="inlineStr">
-        <is>
-          <t>payments</t>
-        </is>
-      </c>
-      <c r="D237" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="238" ht="20" customHeight="1">
-      <c r="A238" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B238" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C238" s="4" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="D238" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="239" ht="20" customHeight="1">
-      <c r="A239" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B239" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C239" s="4" t="inlineStr">
-        <is>
-          <t>generando ia</t>
-        </is>
-      </c>
-      <c r="D239" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="240" ht="20" customHeight="1">
-      <c r="A240" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B240" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C240" s="4" t="inlineStr">
-        <is>
-          <t>creditcard</t>
-        </is>
-      </c>
-      <c r="D240" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="241" ht="20" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B241" s="4" t="inlineStr">
-        <is>
-          <t>VDT</t>
-        </is>
-      </c>
-      <c r="C241" s="4" t="inlineStr">
-        <is>
-          <t>A.white</t>
-        </is>
-      </c>
-      <c r="D241" s="14" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="242" ht="20" customHeight="1">
-      <c r="A242" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B242" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C242" s="4" t="inlineStr">
-        <is>
-          <t>grid view</t>
-        </is>
-      </c>
-      <c r="D242" s="14" t="n">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="243" ht="20" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B243" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C243" s="4" t="inlineStr">
-        <is>
-          <t>Icon</t>
-        </is>
-      </c>
-      <c r="D243" s="14" t="n">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="244" ht="20" customHeight="1">
-      <c r="A244" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B244" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C244" s="4" t="inlineStr">
-        <is>
-          <t>CardProductPromo</t>
-        </is>
-      </c>
-      <c r="D244" s="14" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="245" ht="20" customHeight="1">
-      <c r="A245" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B245" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C245" s="4" t="inlineStr">
-        <is>
-          <t>Slider Controls</t>
-        </is>
-      </c>
-      <c r="D245" s="14" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="246" ht="20" customHeight="1">
-      <c r="A246" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B246" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C246" s="4" t="inlineStr">
-        <is>
-          <t>Cotizar</t>
-        </is>
-      </c>
-      <c r="D246" s="14" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="247" ht="20" customHeight="1">
-      <c r="A247" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B247" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C247" s="4" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="D247" s="14" t="n">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="248" ht="20" customHeight="1">
-      <c r="A248" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B248" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C248" s="4" t="inlineStr">
-        <is>
-          <t>Close Icon</t>
-        </is>
-      </c>
-      <c r="D248" s="14" t="n">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="249" ht="20" customHeight="1">
-      <c r="A249" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B249" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C249" s="4" t="inlineStr">
-        <is>
-          <t>Scroll</t>
-        </is>
-      </c>
-      <c r="D249" s="14" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="250" ht="20" customHeight="1">
-      <c r="A250" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B250" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C250" s="4" t="inlineStr">
-        <is>
-          <t>CardMenúMobile</t>
-        </is>
-      </c>
-      <c r="D250" s="14" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="251" ht="20" customHeight="1">
-      <c r="A251" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B251" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="D251" s="14" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="252" ht="20" customHeight="1">
-      <c r="A252" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B252" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C252" s="4" t="inlineStr">
-        <is>
-          <t>CardMenú</t>
-        </is>
-      </c>
-      <c r="D252" s="14" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="253" ht="20" customHeight="1">
-      <c r="A253" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B253" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C253" s="4" t="inlineStr">
-        <is>
-          <t>Status Control</t>
-        </is>
-      </c>
-      <c r="D253" s="14" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="254" ht="20" customHeight="1">
-      <c r="A254" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B254" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C254" s="4" t="inlineStr">
-        <is>
-          <t>WithoutShieldHeart</t>
-        </is>
-      </c>
-      <c r="D254" s="14" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="255" ht="20" customHeight="1">
-      <c r="A255" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B255" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C255" s="4" t="inlineStr">
-        <is>
-          <t>ShieldHeart</t>
-        </is>
-      </c>
-      <c r="D255" s="14" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="256" ht="20" customHeight="1">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B256" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C256" s="4" t="inlineStr">
-        <is>
-          <t>BotónCategoría</t>
-        </is>
-      </c>
-      <c r="D256" s="14" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="257" ht="20" customHeight="1">
-      <c r="A257" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B257" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C257" s="4" t="inlineStr">
-        <is>
-          <t>Slider</t>
-        </is>
-      </c>
-      <c r="D257" s="14" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="258" ht="20" customHeight="1">
-      <c r="A258" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B258" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C258" s="4" t="inlineStr">
-        <is>
-          <t>_Link Icon</t>
-        </is>
-      </c>
-      <c r="D258" s="14" t="n">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="259" ht="20" customHeight="1">
-      <c r="A259" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B259" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C259" s="4" t="inlineStr">
-        <is>
-          <t>_Button Icon</t>
-        </is>
-      </c>
-      <c r="D259" s="14" t="n">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="260" ht="20" customHeight="1">
-      <c r="A260" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B260" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C260" s="4" t="inlineStr">
-        <is>
-          <t>Car</t>
-        </is>
-      </c>
-      <c r="D260" s="14" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="261" ht="20" customHeight="1">
-      <c r="A261" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B261" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C261" s="4" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="D261" s="14" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="262" ht="20" customHeight="1">
-      <c r="A262" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>grid view</t>
-        </is>
-      </c>
-      <c r="D262" s="14" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="263" ht="20" customHeight="1">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>facebook</t>
-        </is>
-      </c>
-      <c r="D263" s="14" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="264" ht="20" customHeight="1">
-      <c r="A264" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="D264" s="14" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="265" ht="20" customHeight="1">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="inlineStr">
-        <is>
-          <t>SecciónDescripción</t>
-        </is>
-      </c>
-      <c r="D265" s="14" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="266" ht="20" customHeight="1">
-      <c r="A266" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="inlineStr">
-        <is>
-          <t>Icon</t>
-        </is>
-      </c>
-      <c r="D266" s="14" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="267" ht="20" customHeight="1">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="D267" s="14" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="268" ht="20" customHeight="1">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="inlineStr">
-        <is>
-          <t>operador</t>
-        </is>
-      </c>
-      <c r="D268" s="14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="269" ht="20" customHeight="1">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>WithoutShieldHeart</t>
-        </is>
-      </c>
-      <c r="D269" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="270" ht="20" customHeight="1">
-      <c r="A270" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>SeccionCanales</t>
-        </is>
-      </c>
-      <c r="D270" s="14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="271" ht="20" customHeight="1">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>PersonalInjuy</t>
-        </is>
-      </c>
-      <c r="D271" s="14" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="272" ht="20" customHeight="1">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D272" s="14" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="273" ht="20" customHeight="1">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>LogosCollab</t>
-        </is>
-      </c>
-      <c r="D273" s="14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="274" ht="20" customHeight="1">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>CoberturasIconos</t>
-        </is>
-      </c>
-      <c r="D274" s="14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="275" ht="20" customHeight="1">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>Scroll</t>
-        </is>
-      </c>
-      <c r="D275" s="14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="276" ht="20" customHeight="1">
-      <c r="A276" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D276" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="277" ht="20" customHeight="1">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>menu</t>
-        </is>
-      </c>
-      <c r="D277" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="278" ht="20" customHeight="1">
-      <c r="A278" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C278" s="4" t="inlineStr">
-        <is>
-          <t>title_+_badges_download</t>
-        </is>
-      </c>
-      <c r="D278" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="279" ht="20" customHeight="1">
-      <c r="A279" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>instagram</t>
-        </is>
-      </c>
-      <c r="D279" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="280" ht="20" customHeight="1">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="D280" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="281" ht="20" customHeight="1">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>youtube</t>
-        </is>
-      </c>
-      <c r="D281" s="14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7618,22 +6338,22 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>64%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>825</v>
+        <v>921</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1294</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
@@ -7652,7 +6372,7 @@
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>64%</t>
         </is>
@@ -7680,22 +6400,22 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1422</v>
+        <v>224</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>1759</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
@@ -7711,22 +6431,22 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
         <v>17</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>2680</v>
+        <v>3018</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>7982</v>
+        <v>4130</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -7742,22 +6462,22 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>62%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>63%</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>13615</v>
+        <v>11224</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>21824</v>
+        <v>17861</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -7773,22 +6493,22 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>169195</v>
+        <v>34401</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>197336</v>
+        <v>36962</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -7804,22 +6524,22 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>10174</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>13717</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -7835,22 +6555,22 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>71%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>91%</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>7035</v>
+        <v>8343</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9931</v>
+        <v>9188</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -7866,22 +6586,22 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>69%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>75%</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1508</v>
+        <v>1583</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>2187</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -7897,22 +6617,22 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>3647</v>
+        <v>3852</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>4614</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -7928,22 +6648,22 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3684</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>4881</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -7959,22 +6679,22 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>61%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>73%</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
         <v>1</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>2007</v>
+        <v>2296</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>3273</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -7990,22 +6710,22 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>57%</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>69%</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>2329</v>
+        <v>2650</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>4071</v>
+        <v>3813</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -8021,22 +6741,22 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3120</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8052,22 +6772,22 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>10822</v>
+        <v>1666</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>13704</v>
+        <v>1878</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -754,16 +754,16 @@
         <v>3</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>13064</v>
+        <v>13859</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7007</v>
+        <v>7467</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
@@ -914,20 +914,20 @@
         <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>0</v>
+        <v>3596</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -946,20 +946,20 @@
         <v>1</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>3906</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>687</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -978,20 +978,20 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>1419</v>
+        <v>11118</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>172</v>
+        <v>2066</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -1010,20 +1010,20 @@
         <v>1</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>233</v>
+        <v>1424</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -1488,20 +1488,20 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>7100</v>
+        <v>7895</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1954</v>
+        <v>2414</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>77%</t>
         </is>
       </c>
     </row>
@@ -1726,20 +1726,20 @@
         </is>
       </c>
       <c r="D20" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0</v>
+        <v>3596</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
+        <v>599</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
     </row>
@@ -1760,20 +1760,20 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>3906</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0</v>
+        <v>687</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>29</v>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -1794,20 +1794,20 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>5094</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0</v>
+        <v>731</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -1828,20 +1828,20 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0</v>
+        <v>4605</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -1896,20 +1896,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>233</v>
+        <v>1424</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E476"/>
+  <dimension ref="A1:E577"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8229,11 +8229,11 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
-        <v>653</v>
+        <v>685</v>
       </c>
     </row>
     <row r="253">
@@ -8254,11 +8254,11 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
-        <v>489</v>
+        <v>653</v>
       </c>
     </row>
     <row r="254">
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="E254" s="7" t="n">
-        <v>470</v>
+        <v>553</v>
       </c>
     </row>
     <row r="255">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="E255" s="7" t="n">
-        <v>430</v>
+        <v>551</v>
       </c>
     </row>
     <row r="256">
@@ -8329,11 +8329,11 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
-        <v>335</v>
+        <v>512</v>
       </c>
     </row>
     <row r="257">
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="E257" s="7" t="n">
-        <v>325</v>
+        <v>347</v>
       </c>
     </row>
     <row r="258">
@@ -8379,11 +8379,11 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
     </row>
     <row r="259">
@@ -8404,11 +8404,11 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
     </row>
     <row r="260">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="261">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="E261" s="7" t="n">
-        <v>112</v>
+        <v>139</v>
       </c>
     </row>
     <row r="262">
@@ -8479,11 +8479,11 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="263">
@@ -8504,11 +8504,11 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E263" s="7" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="264">
@@ -8554,11 +8554,11 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E265" s="7" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="266">
@@ -8579,11 +8579,11 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="267">
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="E268" s="7" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="269">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="270">
@@ -8679,11 +8679,11 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="271">
@@ -8704,11 +8704,11 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E271" s="7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="272">
@@ -8729,11 +8729,11 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="273">
@@ -8754,11 +8754,11 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E273" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="274">
@@ -8779,11 +8779,11 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="275">
@@ -8804,11 +8804,11 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E275" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="276">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E277" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="278">
@@ -8879,11 +8879,11 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="279">
@@ -8904,11 +8904,11 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E279" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280">
@@ -8929,11 +8929,11 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281">
@@ -8954,11 +8954,11 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E281" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282">
@@ -8979,11 +8979,11 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -8999,16 +8999,16 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E283" s="7" t="n">
-        <v>1316</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284">
@@ -9024,16 +9024,16 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
-        <v>1258</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -9054,11 +9054,11 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E285" s="7" t="n">
-        <v>531</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="286">
@@ -9079,11 +9079,11 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
-        <v>184</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="287">
@@ -9104,11 +9104,11 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E287" s="7" t="n">
-        <v>178</v>
+        <v>531</v>
       </c>
     </row>
     <row r="288">
@@ -9129,11 +9129,11 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="289">
@@ -9154,11 +9154,11 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
-        <v>126</v>
+        <v>178</v>
       </c>
     </row>
     <row r="290">
@@ -9179,11 +9179,11 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
-        <v>107</v>
+        <v>161</v>
       </c>
     </row>
     <row r="291">
@@ -9204,11 +9204,11 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
     </row>
     <row r="292">
@@ -9229,11 +9229,11 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="293">
@@ -9254,11 +9254,11 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E293" s="7" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="294">
@@ -9279,11 +9279,11 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="295">
@@ -9304,11 +9304,11 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="296">
@@ -9329,11 +9329,11 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="297">
@@ -9354,11 +9354,11 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E297" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298">
@@ -9379,11 +9379,11 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="299">
@@ -9404,11 +9404,11 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E299" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="300">
@@ -9429,11 +9429,11 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E301" s="7" t="n">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -9504,11 +9504,11 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E303" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -9524,16 +9524,16 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
-        <v>1216</v>
+        <v>3</v>
       </c>
     </row>
     <row r="305">
@@ -9549,16 +9549,16 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
     </row>
     <row r="306">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>77</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="307">
@@ -9604,11 +9604,11 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>66</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308">
@@ -9629,11 +9629,11 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="309">
@@ -9654,11 +9654,11 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
     </row>
     <row r="310">
@@ -9679,11 +9679,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="311">
@@ -9704,11 +9704,11 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
     </row>
     <row r="312">
@@ -9729,11 +9729,11 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="313">
@@ -9754,11 +9754,11 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="314">
@@ -9779,11 +9779,11 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="315">
@@ -9804,11 +9804,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="316">
@@ -9829,11 +9829,11 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317">
@@ -9854,11 +9854,11 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="318">
@@ -9879,11 +9879,11 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319">
@@ -9904,11 +9904,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
@@ -9929,11 +9929,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -9954,11 +9954,11 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E321" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -9979,11 +9979,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323">
@@ -10004,11 +10004,11 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="324">
@@ -10029,11 +10029,11 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E325" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
@@ -10104,11 +10104,11 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E327" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
@@ -10129,11 +10129,11 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="329">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E329" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
@@ -10189,51 +10189,51 @@
     <row r="331">
       <c r="A331" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E331" s="7" t="n">
-        <v>305</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
@@ -10254,11 +10254,11 @@
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E333" s="7" t="n">
-        <v>164</v>
+        <v>305</v>
       </c>
     </row>
     <row r="334">
@@ -10279,11 +10279,11 @@
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
-        <v>110</v>
+        <v>243</v>
       </c>
     </row>
     <row r="335">
@@ -10304,11 +10304,11 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
     </row>
     <row r="336">
@@ -10329,11 +10329,11 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="337">
@@ -10354,11 +10354,11 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E337" s="7" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="338">
@@ -10379,11 +10379,11 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="339">
@@ -10404,11 +10404,11 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E339" s="7" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="340">
@@ -10429,11 +10429,11 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="341">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E341" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="342">
@@ -10479,11 +10479,11 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="343">
@@ -10504,11 +10504,11 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E343" s="7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="344">
@@ -10529,11 +10529,11 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="345">
@@ -10554,11 +10554,11 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E345" s="7" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="346">
@@ -10579,11 +10579,11 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="347">
@@ -10604,11 +10604,11 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E347" s="7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="348">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
@@ -10654,11 +10654,11 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
@@ -10679,11 +10679,11 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351">
@@ -10704,11 +10704,11 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E351" s="7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="352">
@@ -10729,11 +10729,11 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="353">
@@ -10754,11 +10754,11 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E353" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="354">
@@ -10779,11 +10779,11 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="355">
@@ -10804,11 +10804,11 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E355" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="356">
@@ -10829,11 +10829,11 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="357">
@@ -10854,11 +10854,11 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E357" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -10869,21 +10869,21 @@
       </c>
       <c r="B358" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
-        <v>433</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -10894,21 +10894,21 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E359" s="7" t="n">
-        <v>215</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -10929,11 +10929,11 @@
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
-        <v>196</v>
+        <v>433</v>
       </c>
     </row>
     <row r="361">
@@ -10954,11 +10954,11 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E361" s="7" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
     </row>
     <row r="362">
@@ -10979,11 +10979,11 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>149</v>
+        <v>196</v>
       </c>
     </row>
     <row r="363">
@@ -11004,11 +11004,11 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>124</v>
+        <v>174</v>
       </c>
     </row>
     <row r="364">
@@ -11029,11 +11029,11 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
     </row>
     <row r="365">
@@ -11054,11 +11054,11 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E365" s="7" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="366">
@@ -11079,11 +11079,11 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
     </row>
     <row r="367">
@@ -11104,11 +11104,11 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E367" s="7" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="368">
@@ -11129,11 +11129,11 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E368" s="7" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="369">
@@ -11154,11 +11154,11 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="370">
@@ -11179,11 +11179,11 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E370" s="7" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="371">
@@ -11204,11 +11204,11 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E371" s="7" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="372">
@@ -11229,11 +11229,11 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="373">
@@ -11254,11 +11254,11 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E373" s="7" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="374">
@@ -11279,11 +11279,11 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E374" s="7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="375">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E375" s="7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="376">
@@ -11329,11 +11329,11 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E376" s="7" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="377">
@@ -11354,11 +11354,11 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E377" s="7" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="378">
@@ -11379,11 +11379,11 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E378" s="7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="379">
@@ -11404,11 +11404,11 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E379" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380">
@@ -11429,11 +11429,11 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E380" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381">
@@ -11454,11 +11454,11 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E381" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="382">
@@ -11479,11 +11479,11 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E382" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="383">
@@ -11504,11 +11504,11 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E383" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="384">
@@ -11529,11 +11529,11 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E384" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="385">
@@ -11554,11 +11554,11 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E385" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="386">
@@ -11569,21 +11569,21 @@
       </c>
       <c r="B386" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E386" s="7" t="n">
-        <v>160</v>
+        <v>6</v>
       </c>
     </row>
     <row r="387">
@@ -11594,21 +11594,21 @@
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
-        <v>149</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -11629,11 +11629,11 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
     </row>
     <row r="389">
@@ -11654,11 +11654,11 @@
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E389" s="7" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="390">
@@ -11679,11 +11679,11 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>77</v>
+        <v>136</v>
       </c>
     </row>
     <row r="391">
@@ -11704,11 +11704,11 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>63</v>
+        <v>107</v>
       </c>
     </row>
     <row r="392">
@@ -11729,11 +11729,11 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="393">
@@ -11754,11 +11754,11 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="394">
@@ -11779,11 +11779,11 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="395">
@@ -11804,11 +11804,11 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="396">
@@ -11829,11 +11829,11 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397">
@@ -11854,11 +11854,11 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="398">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="399">
@@ -11904,11 +11904,11 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="400">
@@ -11929,11 +11929,11 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="401">
@@ -11954,11 +11954,11 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="402">
@@ -11979,11 +11979,11 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="403">
@@ -12004,11 +12004,11 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="404">
@@ -12029,11 +12029,11 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Infografia</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="405">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Infografia</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
@@ -12104,11 +12104,11 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -12129,11 +12129,11 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="409">
@@ -12154,11 +12154,11 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="410">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
@@ -12194,21 +12194,21 @@
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>597</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -12219,21 +12219,21 @@
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -12254,11 +12254,11 @@
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
-        <v>327</v>
+        <v>597</v>
       </c>
     </row>
     <row r="414">
@@ -12279,11 +12279,11 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
     </row>
     <row r="415">
@@ -12304,11 +12304,11 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>166</v>
+        <v>327</v>
       </c>
     </row>
     <row r="416">
@@ -12329,11 +12329,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>151</v>
+        <v>276</v>
       </c>
     </row>
     <row r="417">
@@ -12354,11 +12354,11 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="418">
@@ -12379,11 +12379,11 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="419">
@@ -12404,11 +12404,11 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
     </row>
     <row r="420">
@@ -12429,11 +12429,11 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="421">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="422">
@@ -12479,11 +12479,11 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="423">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
@@ -12529,7 +12529,7 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
@@ -12579,11 +12579,11 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="427">
@@ -12604,11 +12604,11 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="428">
@@ -12629,11 +12629,11 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="429">
@@ -12654,11 +12654,11 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="430">
@@ -12679,11 +12679,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="431">
@@ -12704,11 +12704,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="432">
@@ -12729,11 +12729,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="433">
@@ -12754,11 +12754,11 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434">
@@ -12779,11 +12779,11 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435">
@@ -12804,11 +12804,11 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="436">
@@ -12829,11 +12829,11 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="437">
@@ -12854,7 +12854,7 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
@@ -12879,11 +12879,11 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="439">
@@ -12904,152 +12904,152 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
-        <v>285</v>
+        <v>2</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
-        <v>282</v>
+        <v>2</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>266</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
-        <v>132</v>
+        <v>340</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>132</v>
+        <v>256</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B445" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D445" s="5" t="inlineStr">
@@ -13058,473 +13058,473 @@
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>107</v>
+        <v>251</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>48</v>
+        <v>160</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>45</v>
+        <v>155</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>24</v>
+        <v>131</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>19</v>
+        <v>128</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>19</v>
+        <v>87</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>14</v>
+        <v>85</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D464" s="5" t="inlineStr">
@@ -13533,103 +13533,103 @@
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
@@ -13639,92 +13639,92 @@
     <row r="469">
       <c r="A469" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
-        <v>2</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D472" s="5" t="inlineStr">
@@ -13733,106 +13733,2631 @@
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>2</v>
+        <v>618</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>2</v>
+        <v>440</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B474" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>1</v>
+        <v>375</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>1</v>
+        <v>192</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
         <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B476" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C476" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D476" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E476" s="7" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B477" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C477" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D477" s="5" t="inlineStr">
+        <is>
+          <t>Radio</t>
+        </is>
+      </c>
+      <c r="E477" s="7" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B478" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C478" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D478" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E478" s="7" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B479" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C479" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D479" s="5" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="E479" s="7" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B480" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C480" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D480" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E480" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B481" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C481" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D481" s="5" t="inlineStr">
+        <is>
+          <t>Menu Item</t>
+        </is>
+      </c>
+      <c r="E481" s="7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B482" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C482" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D482" s="5" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
+      <c r="E482" s="7" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B483" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C483" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D483" s="5" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="E483" s="7" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B484" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C484" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D484" s="5" t="inlineStr">
+        <is>
+          <t>Label in</t>
+        </is>
+      </c>
+      <c r="E484" s="7" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B485" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C485" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D485" s="5" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="E485" s="7" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B486" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C486" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D486" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E486" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B487" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C487" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D487" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E487" s="7" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B488" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C488" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D488" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E488" s="7" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B489" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C489" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D489" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E489" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B490" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C490" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D490" s="5" t="inlineStr">
+        <is>
+          <t>Chip Deleteable</t>
+        </is>
+      </c>
+      <c r="E490" s="7" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B491" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C491" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D491" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E491" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B492" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C492" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D492" s="5" t="inlineStr">
+        <is>
+          <t>Menu title</t>
+        </is>
+      </c>
+      <c r="E492" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B493" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C493" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D493" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E493" s="7" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B494" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C494" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D494" s="5" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="E494" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B495" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C495" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D495" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E495" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B496" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C496" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D496" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E496" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B497" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C497" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D497" s="5" t="inlineStr">
+        <is>
+          <t>Dropdown Input</t>
+        </is>
+      </c>
+      <c r="E497" s="7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B498" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C498" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D498" s="5" t="inlineStr">
+        <is>
+          <t>Progress bar</t>
+        </is>
+      </c>
+      <c r="E498" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B499" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C499" s="4" t="inlineStr">
+        <is>
+          <t>VDT — Perfilador Productos Vida</t>
+        </is>
+      </c>
+      <c r="D499" s="5" t="inlineStr">
+        <is>
+          <t>Topbar</t>
+        </is>
+      </c>
+      <c r="E499" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B500" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C500" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D500" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E500" s="7" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B501" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C501" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D501" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E501" s="7" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B502" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C502" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D502" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E502" s="7" t="n">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B503" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C503" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D503" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E503" s="7" t="n">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B504" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C504" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D504" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E504" s="7" t="n">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B505" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C505" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D505" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E505" s="7" t="n">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B506" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C506" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D506" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E506" s="7" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B507" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C507" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D507" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E507" s="7" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B508" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C508" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D508" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E508" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B509" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C509" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D509" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E509" s="7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B510" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C510" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D510" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E510" s="7" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B511" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C511" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D511" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E511" s="7" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B512" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C512" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D512" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E512" s="7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B513" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C513" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D513" s="5" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="E513" s="7" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B514" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C514" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D514" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E514" s="7" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B515" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C515" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D515" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E515" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B516" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C516" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D516" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E516" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B517" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C517" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D517" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E517" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B518" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C518" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D518" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E518" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B519" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C519" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D519" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E519" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B520" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C520" s="4" t="inlineStr">
+        <is>
+          <t>Productos Vida</t>
+        </is>
+      </c>
+      <c r="D520" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E520" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B521" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C521" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D521" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E521" s="7" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B522" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C522" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D522" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E522" s="7" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B523" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C523" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D523" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E523" s="7" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B524" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C524" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D524" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E524" s="7" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B525" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C525" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D525" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E525" s="7" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B526" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C526" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D526" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E526" s="7" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B527" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C527" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D527" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E527" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B528" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C528" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D528" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E528" s="7" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B529" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C529" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D529" s="5" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="E529" s="7" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B530" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C530" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D530" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E530" s="7" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B531" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C531" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D531" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E531" s="7" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B532" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C532" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D532" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E532" s="7" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B533" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C533" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D533" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E533" s="7" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B534" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C534" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D534" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E534" s="7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B535" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C535" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E535" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B536" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C536" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D536" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E536" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B537" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C537" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E537" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D538" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E538" s="7" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B539" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C539" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E539" s="7" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B540" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C540" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E540" s="7" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B541" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E541" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B542" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E542" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C543" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E543" s="7" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B544" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E544" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B545" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C545" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E545" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B546" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C546" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E546" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E547" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E548" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="E549" s="7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E550" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E551" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E552" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E553" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E554" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C555" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E555" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E556" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E557" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E558" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B476" s="4" t="inlineStr">
+      <c r="B559" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C476" s="4" t="inlineStr">
+      <c r="C559" s="4" t="inlineStr">
         <is>
           <t>Landing Alianzas</t>
         </is>
       </c>
-      <c r="D476" s="5" t="inlineStr">
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E559" s="7" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B560" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E560" s="7" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B561" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E561" s="7" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B562" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E562" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B563" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E563" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B564" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C564" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E564" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E565" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B566" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E566" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B567" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D567" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E567" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B568" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D568" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E568" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B569" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C569" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D569" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E569" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B570" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D570" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E570" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B571" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C571" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D571" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E571" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D572" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E572" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E573" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D574" s="5" t="inlineStr">
         <is>
           <t>title_+_social media</t>
         </is>
       </c>
-      <c r="E476" s="7" t="n">
+      <c r="E574" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="E575" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D576" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E576" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D577" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E577" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13847,7 +16372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D236"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15931,11 +18456,11 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Component 16</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D104" s="12" t="n">
-        <v>270</v>
+        <v>311</v>
       </c>
     </row>
     <row r="105">
@@ -15951,11 +18476,11 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>Component 16</t>
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>238</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106">
@@ -16231,11 +18756,11 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D119" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="120">
@@ -16251,11 +18776,11 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>BtnBackNext</t>
+          <t>AGENDA</t>
         </is>
       </c>
       <c r="D120" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121">
@@ -16271,11 +18796,11 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Pregunta formulario</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D121" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122">
@@ -17881,701 +20406,1601 @@
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>celda</t>
         </is>
       </c>
       <c r="D202" s="12" t="n">
-        <v>28</v>
+        <v>312</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Component 120</t>
         </is>
       </c>
       <c r="D203" s="12" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D204" s="12" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D205" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D206" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D207" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>hogar</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D208" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D209" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D210" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D211" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>Viajeros</t>
         </is>
       </c>
       <c r="D212" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D213" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="D214" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>Viajeros Mobile</t>
         </is>
       </c>
       <c r="D215" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Beneficios</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D216" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>SecciónMEP</t>
+          <t>Pasajeros</t>
         </is>
       </c>
       <c r="D217" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Spinner mesagge</t>
         </is>
       </c>
       <c r="D218" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>Spinner</t>
         </is>
       </c>
       <c r="D219" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D220" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>PricingSection</t>
+          <t>Seguridad_72x72</t>
         </is>
       </c>
       <c r="D221" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="D222" s="12" t="n">
-        <v>4</v>
+        <v>174</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>01 Info</t>
         </is>
       </c>
       <c r="D223" s="12" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>problema eléctrico</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D224" s="12" t="n">
-        <v>3</v>
+        <v>58</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D225" s="12" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D226" s="12" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>LogosCollab</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D227" s="12" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>robo de autopartes</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D228" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D229" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>CoberturasIconos</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D230" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D231" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D232" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D233" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="D234" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>send</t>
         </is>
       </c>
       <c r="D235" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
         <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>mail</t>
+        </is>
+      </c>
+      <c r="D236" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>resumen</t>
+        </is>
+      </c>
+      <c r="D237" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Botón primario</t>
+        </is>
+      </c>
+      <c r="D238" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D239" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>download</t>
+        </is>
+      </c>
+      <c r="D240" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="D241" s="12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D242" s="12" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>CardProductPromo</t>
+        </is>
+      </c>
+      <c r="D243" s="12" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>Cotizar</t>
+        </is>
+      </c>
+      <c r="D244" s="12" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>Video</t>
+        </is>
+      </c>
+      <c r="D245" s="12" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Close Icon</t>
+        </is>
+      </c>
+      <c r="D246" s="12" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D247" s="12" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>CardMenúMobile</t>
+        </is>
+      </c>
+      <c r="D248" s="12" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>CardMenú</t>
+        </is>
+      </c>
+      <c r="D249" s="12" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D250" s="12" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>ShieldHeart</t>
+        </is>
+      </c>
+      <c r="D251" s="12" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>BotónCategoría</t>
+        </is>
+      </c>
+      <c r="D252" s="12" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Slider</t>
+        </is>
+      </c>
+      <c r="D253" s="12" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>_Link Icon</t>
+        </is>
+      </c>
+      <c r="D254" s="12" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>_Button Icon</t>
+        </is>
+      </c>
+      <c r="D255" s="12" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Car</t>
+        </is>
+      </c>
+      <c r="D256" s="12" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D257" s="12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>MedicalService</t>
+        </is>
+      </c>
+      <c r="D258" s="12" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>submenu</t>
+        </is>
+      </c>
+      <c r="D259" s="12" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Link Stamp</t>
+        </is>
+      </c>
+      <c r="D260" s="12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>title_+_badges_download</t>
+        </is>
+      </c>
+      <c r="D261" s="12" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="B262" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr">
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D262" s="12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>SecciónDescripción</t>
+        </is>
+      </c>
+      <c r="D263" s="12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D264" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D265" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D266" s="12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>SeccionCanales</t>
+        </is>
+      </c>
+      <c r="D267" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>PersonalInjuy</t>
+        </is>
+      </c>
+      <c r="D268" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D269" s="12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>LogosCollab</t>
+        </is>
+      </c>
+      <c r="D270" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>CoberturasIconos</t>
+        </is>
+      </c>
+      <c r="D271" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D272" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D273" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
         <is>
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D236" s="12" t="n">
-        <v>1</v>
+      <c r="D274" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>problema eléctrico</t>
+        </is>
+      </c>
+      <c r="D275" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>robo de autopartes</t>
+        </is>
+      </c>
+      <c r="D276" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>avión</t>
+        </is>
+      </c>
+      <c r="D277" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>generales</t>
+        </is>
+      </c>
+      <c r="D278" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>download</t>
+        </is>
+      </c>
+      <c r="D279" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>fractura</t>
+        </is>
+      </c>
+      <c r="D280" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="D281" s="12" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -18739,17 +22164,17 @@
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>233</v>
+        <v>1424</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>267</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="5">
@@ -18815,13 +22240,13 @@
         </is>
       </c>
       <c r="F6" s="6" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>13064</v>
+        <v>13859</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>20071</v>
+        <v>21326</v>
       </c>
     </row>
     <row r="7">
@@ -19025,19 +22450,19 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>85%</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0</v>
+        <v>3906</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0</v>
+        <v>4593</v>
       </c>
     </row>
     <row r="13">
@@ -19133,19 +22558,19 @@
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>86%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>0</v>
+        <v>3596</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>0</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="16">
@@ -19171,17 +22596,17 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>1419</v>
+        <v>11118</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>1591</v>
+        <v>13184</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -725,10 +725,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>10368</v>
+        <v>10633</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2842</v>
+        <v>2951</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>34</v>
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>13859</v>
+        <v>13997</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7467</v>
+        <v>7557</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -1457,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10368</v>
+        <v>10633</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2842</v>
+        <v>2951</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>34</v>
@@ -1559,17 +1559,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1801</v>
+        <v>1939</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>358</v>
+        <v>448</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>27</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>81%</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="E217" s="7" t="n">
-        <v>1495</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="218">
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E219" s="7" t="n">
-        <v>1333</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="220">
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="E220" s="7" t="n">
-        <v>1282</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="221">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="E221" s="7" t="n">
-        <v>774</v>
+        <v>804</v>
       </c>
     </row>
     <row r="222">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="E222" s="7" t="n">
-        <v>579</v>
+        <v>608</v>
       </c>
     </row>
     <row r="223">
@@ -7508,7 +7508,7 @@
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="224">
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="E224" s="7" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
     </row>
     <row r="225">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>306</v>
+        <v>316</v>
       </c>
     </row>
     <row r="226">
@@ -7604,11 +7604,11 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228">
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="E228" s="7" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
     </row>
     <row r="229">
@@ -7654,11 +7654,11 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
-        <v>228</v>
+        <v>240</v>
       </c>
     </row>
     <row r="230">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="E230" s="7" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
     </row>
     <row r="231">
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="E231" s="7" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="232">
@@ -7808,7 +7808,7 @@
         </is>
       </c>
       <c r="E235" s="7" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="236">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E237" s="7" t="n">
@@ -7879,11 +7879,11 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="239">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>1216</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="307">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="308">
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="309">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
     </row>
     <row r="310">
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="311">
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="313">
@@ -9754,11 +9754,11 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
@@ -9804,11 +9804,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="316">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318">
@@ -9879,11 +9879,11 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="319">
@@ -9904,11 +9904,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320">
@@ -9929,11 +9929,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E321" s="7" t="n">
@@ -9979,11 +9979,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="323">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
@@ -10029,11 +10029,11 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="325">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E325" s="7" t="n">
@@ -18060,7 +18060,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>328</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86">
@@ -18100,7 +18100,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
     </row>
     <row r="87">
@@ -18116,11 +18116,11 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Component 9</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="88">
@@ -18136,11 +18136,11 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Component 9</t>
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89">
@@ -18160,7 +18160,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="90">
@@ -18176,11 +18176,11 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>Frame 1707479054</t>
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91">
@@ -18196,11 +18196,11 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Frame 1707479054</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92">
@@ -18220,7 +18220,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="93">
@@ -18256,11 +18256,11 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95">
@@ -18276,11 +18276,11 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>informacion de poliza</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96">
@@ -18296,11 +18296,11 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>dólares</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
@@ -18336,11 +18336,11 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
@@ -18356,11 +18356,11 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>dólares</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
@@ -18376,11 +18376,11 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>soles</t>
+          <t>24.timer</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
@@ -18576,11 +18576,11 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D110" s="12" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="111">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D111" s="12" t="n">
@@ -18620,7 +18620,7 @@
         </is>
       </c>
       <c r="D112" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113">
@@ -18636,11 +18636,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D113" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114">
@@ -18656,11 +18656,11 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D114" s="12" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D115" s="12" t="n">
@@ -18696,11 +18696,11 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D116" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117">
@@ -18716,11 +18716,11 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D117" s="12" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118">
@@ -18776,11 +18776,11 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>AGENDA</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D120" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="121">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>AGENDA</t>
         </is>
       </c>
       <c r="D121" s="12" t="n">
@@ -22243,10 +22243,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>13859</v>
+        <v>13997</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>21326</v>
+        <v>21554</v>
       </c>
     </row>
     <row r="7">
@@ -22315,10 +22315,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>10368</v>
+        <v>10633</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>13210</v>
+        <v>13584</v>
       </c>
     </row>
     <row r="9">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -693,10 +693,10 @@
         <v>44</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>172957</v>
+        <v>172968</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>11346</v>
+        <v>11352</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>47</v>
@@ -725,10 +725,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>10633</v>
+        <v>10716</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2951</v>
+        <v>3008</v>
       </c>
       <c r="G9" s="8" t="n">
         <v>34</v>
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>13997</v>
+        <v>14039</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7557</v>
+        <v>7579</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -1423,10 +1423,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>157752</v>
+        <v>157763</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10480</v>
+        <v>10486</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>42</v>
@@ -1457,10 +1457,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10633</v>
+        <v>10716</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>2951</v>
+        <v>3008</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>34</v>
@@ -1559,13 +1559,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1939</v>
+        <v>1981</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>448</v>
+        <v>470</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E577"/>
+  <dimension ref="A1:E580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>7416</v>
+        <v>7421</v>
       </c>
     </row>
     <row r="180">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="E180" s="7" t="n">
-        <v>5248</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="181">
@@ -6683,7 +6683,7 @@
         </is>
       </c>
       <c r="E190" s="7" t="n">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="191">
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="E202" s="7" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="203">
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="E217" s="7" t="n">
-        <v>1532</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="218">
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E219" s="7" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="220">
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="E220" s="7" t="n">
-        <v>1341</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="221">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="E222" s="7" t="n">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="223">
@@ -7504,11 +7504,11 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>441</v>
+        <v>454</v>
       </c>
     </row>
     <row r="224">
@@ -7529,11 +7529,11 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
-        <v>414</v>
+        <v>445</v>
       </c>
     </row>
     <row r="225">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
     <row r="226">
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="E234" s="7" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="235">
@@ -7833,7 +7833,7 @@
         </is>
       </c>
       <c r="E236" s="7" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="237">
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="E237" s="7" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="238">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="308">
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="309">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="310">
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="311">
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="313">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="314">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="317">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="318">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E329" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="330">
@@ -10179,11 +10179,11 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -10204,11 +10204,11 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E331" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
@@ -10239,76 +10239,76 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E333" s="7" t="n">
-        <v>305</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
-        <v>164</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -10329,11 +10329,11 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
-        <v>110</v>
+        <v>305</v>
       </c>
     </row>
     <row r="337">
@@ -10354,11 +10354,11 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E337" s="7" t="n">
-        <v>83</v>
+        <v>243</v>
       </c>
     </row>
     <row r="338">
@@ -10379,11 +10379,11 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
-        <v>76</v>
+        <v>164</v>
       </c>
     </row>
     <row r="339">
@@ -10404,11 +10404,11 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E339" s="7" t="n">
-        <v>61</v>
+        <v>110</v>
       </c>
     </row>
     <row r="340">
@@ -10429,11 +10429,11 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
     </row>
     <row r="341">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E341" s="7" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="342">
@@ -10479,11 +10479,11 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="343">
@@ -10504,11 +10504,11 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E343" s="7" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="344">
@@ -10529,11 +10529,11 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="345">
@@ -10554,11 +10554,11 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E345" s="7" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="346">
@@ -10579,11 +10579,11 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="347">
@@ -10604,11 +10604,11 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E347" s="7" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
     </row>
     <row r="348">
@@ -10629,11 +10629,11 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="349">
@@ -10654,11 +10654,11 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="350">
@@ -10679,11 +10679,11 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="351">
@@ -10704,11 +10704,11 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E351" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352">
@@ -10729,11 +10729,11 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353">
@@ -10754,11 +10754,11 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E353" s="7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="354">
@@ -10779,11 +10779,11 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355">
@@ -10804,11 +10804,11 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E355" s="7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="356">
@@ -10829,11 +10829,11 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="357">
@@ -10854,11 +10854,11 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E357" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="358">
@@ -10879,11 +10879,11 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="359">
@@ -10904,11 +10904,11 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E359" s="7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="360">
@@ -10919,21 +10919,21 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
-        <v>433</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -10944,21 +10944,21 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E361" s="7" t="n">
-        <v>215</v>
+        <v>2</v>
       </c>
     </row>
     <row r="362">
@@ -10969,21 +10969,21 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>196</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
@@ -11004,11 +11004,11 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>174</v>
+        <v>433</v>
       </c>
     </row>
     <row r="364">
@@ -11029,11 +11029,11 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>149</v>
+        <v>215</v>
       </c>
     </row>
     <row r="365">
@@ -11054,11 +11054,11 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E365" s="7" t="n">
-        <v>124</v>
+        <v>196</v>
       </c>
     </row>
     <row r="366">
@@ -11079,11 +11079,11 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>121</v>
+        <v>174</v>
       </c>
     </row>
     <row r="367">
@@ -11104,11 +11104,11 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E367" s="7" t="n">
-        <v>114</v>
+        <v>149</v>
       </c>
     </row>
     <row r="368">
@@ -11129,11 +11129,11 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E368" s="7" t="n">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="369">
@@ -11154,11 +11154,11 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>92</v>
+        <v>121</v>
       </c>
     </row>
     <row r="370">
@@ -11179,11 +11179,11 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E370" s="7" t="n">
-        <v>88</v>
+        <v>114</v>
       </c>
     </row>
     <row r="371">
@@ -11204,11 +11204,11 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E371" s="7" t="n">
-        <v>72</v>
+        <v>102</v>
       </c>
     </row>
     <row r="372">
@@ -11229,11 +11229,11 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="373">
@@ -11254,11 +11254,11 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E373" s="7" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="374">
@@ -11279,11 +11279,11 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E374" s="7" t="n">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="375">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E375" s="7" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="376">
@@ -11329,11 +11329,11 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E376" s="7" t="n">
-        <v>41</v>
+        <v>62</v>
       </c>
     </row>
     <row r="377">
@@ -11354,11 +11354,11 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E377" s="7" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="378">
@@ -11379,11 +11379,11 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E378" s="7" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
     </row>
     <row r="379">
@@ -11404,11 +11404,11 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E379" s="7" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
     </row>
     <row r="380">
@@ -11429,11 +11429,11 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E380" s="7" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="381">
@@ -11454,11 +11454,11 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E381" s="7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="382">
@@ -11479,11 +11479,11 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E382" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383">
@@ -11504,11 +11504,11 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E383" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="384">
@@ -11529,11 +11529,11 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E384" s="7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="385">
@@ -11554,11 +11554,11 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E385" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="386">
@@ -11579,11 +11579,11 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E386" s="7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="387">
@@ -11604,11 +11604,11 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="388">
@@ -11619,21 +11619,21 @@
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>160</v>
+        <v>9</v>
       </c>
     </row>
     <row r="389">
@@ -11644,21 +11644,21 @@
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E389" s="7" t="n">
-        <v>149</v>
+        <v>6</v>
       </c>
     </row>
     <row r="390">
@@ -11669,21 +11669,21 @@
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
     </row>
     <row r="391">
@@ -11704,11 +11704,11 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>107</v>
+        <v>160</v>
       </c>
     </row>
     <row r="392">
@@ -11729,11 +11729,11 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>77</v>
+        <v>149</v>
       </c>
     </row>
     <row r="393">
@@ -11754,11 +11754,11 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>63</v>
+        <v>136</v>
       </c>
     </row>
     <row r="394">
@@ -11779,11 +11779,11 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>60</v>
+        <v>107</v>
       </c>
     </row>
     <row r="395">
@@ -11804,11 +11804,11 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="396">
@@ -11829,11 +11829,11 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>20</v>
+        <v>63</v>
       </c>
     </row>
     <row r="397">
@@ -11854,11 +11854,11 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="398">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="399">
@@ -11904,11 +11904,11 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="400">
@@ -11929,11 +11929,11 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="401">
@@ -11954,11 +11954,11 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="402">
@@ -11979,11 +11979,11 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="403">
@@ -12004,11 +12004,11 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="404">
@@ -12029,11 +12029,11 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="405">
@@ -12054,11 +12054,11 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="406">
@@ -12079,11 +12079,11 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Infografia</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="407">
@@ -12104,11 +12104,11 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="408">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
@@ -12154,11 +12154,11 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Infografia</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410">
@@ -12179,11 +12179,11 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="411">
@@ -12204,11 +12204,11 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412">
@@ -12229,11 +12229,11 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413">
@@ -12244,21 +12244,21 @@
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
-        <v>597</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -12269,21 +12269,21 @@
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
-        <v>331</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
@@ -12294,21 +12294,21 @@
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>327</v>
+        <v>1</v>
       </c>
     </row>
     <row r="416">
@@ -12329,11 +12329,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>276</v>
+        <v>597</v>
       </c>
     </row>
     <row r="417">
@@ -12354,11 +12354,11 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>166</v>
+        <v>331</v>
       </c>
     </row>
     <row r="418">
@@ -12379,11 +12379,11 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>151</v>
+        <v>327</v>
       </c>
     </row>
     <row r="419">
@@ -12404,11 +12404,11 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>116</v>
+        <v>276</v>
       </c>
     </row>
     <row r="420">
@@ -12429,11 +12429,11 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>70</v>
+        <v>166</v>
       </c>
     </row>
     <row r="421">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>60</v>
+        <v>151</v>
       </c>
     </row>
     <row r="422">
@@ -12479,11 +12479,11 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>56</v>
+        <v>116</v>
       </c>
     </row>
     <row r="423">
@@ -12504,11 +12504,11 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="424">
@@ -12529,11 +12529,11 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="425">
@@ -12554,11 +12554,11 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="426">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
@@ -12629,11 +12629,11 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="429">
@@ -12654,11 +12654,11 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="430">
@@ -12679,11 +12679,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="431">
@@ -12704,11 +12704,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="432">
@@ -12729,11 +12729,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="433">
@@ -12754,11 +12754,11 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="434">
@@ -12779,11 +12779,11 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="435">
@@ -12804,11 +12804,11 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="436">
@@ -12829,11 +12829,11 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="437">
@@ -12854,11 +12854,11 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438">
@@ -12879,11 +12879,11 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="439">
@@ -12904,11 +12904,11 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="440">
@@ -12929,11 +12929,11 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="441">
@@ -12954,11 +12954,11 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -12969,21 +12969,21 @@
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>1536</v>
+        <v>8</v>
       </c>
     </row>
     <row r="443">
@@ -12994,21 +12994,21 @@
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
-        <v>340</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444">
@@ -13019,21 +13019,21 @@
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>256</v>
+        <v>2</v>
       </c>
     </row>
     <row r="445">
@@ -13054,11 +13054,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>251</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="446">
@@ -13079,11 +13079,11 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>160</v>
+        <v>340</v>
       </c>
     </row>
     <row r="447">
@@ -13104,11 +13104,11 @@
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>155</v>
+        <v>256</v>
       </c>
     </row>
     <row r="448">
@@ -13129,11 +13129,11 @@
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>131</v>
+        <v>251</v>
       </c>
     </row>
     <row r="449">
@@ -13154,11 +13154,11 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="450">
@@ -13179,11 +13179,11 @@
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>87</v>
+        <v>155</v>
       </c>
     </row>
     <row r="451">
@@ -13204,11 +13204,11 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>85</v>
+        <v>131</v>
       </c>
     </row>
     <row r="452">
@@ -13229,11 +13229,11 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
     </row>
     <row r="453">
@@ -13254,11 +13254,11 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
     </row>
     <row r="454">
@@ -13279,11 +13279,11 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
     </row>
     <row r="455">
@@ -13304,11 +13304,11 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>39</v>
+        <v>64</v>
       </c>
     </row>
     <row r="456">
@@ -13329,11 +13329,11 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="457">
@@ -13354,11 +13354,11 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
     </row>
     <row r="458">
@@ -13379,11 +13379,11 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="459">
@@ -13404,11 +13404,11 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="460">
@@ -13429,11 +13429,11 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="461">
@@ -13454,11 +13454,11 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="462">
@@ -13479,11 +13479,11 @@
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="463">
@@ -13504,11 +13504,11 @@
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="464">
@@ -13529,11 +13529,11 @@
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="465">
@@ -13554,11 +13554,11 @@
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="466">
@@ -13579,11 +13579,11 @@
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="467">
@@ -13604,11 +13604,11 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="468">
@@ -13629,11 +13629,11 @@
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="469">
@@ -13654,11 +13654,11 @@
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="470">
@@ -13679,11 +13679,11 @@
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="471">
@@ -13694,21 +13694,21 @@
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
-        <v>1152</v>
+        <v>10</v>
       </c>
     </row>
     <row r="472">
@@ -13719,21 +13719,21 @@
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>618</v>
+        <v>9</v>
       </c>
     </row>
     <row r="473">
@@ -13744,21 +13744,21 @@
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>440</v>
+        <v>6</v>
       </c>
     </row>
     <row r="474">
@@ -13779,11 +13779,11 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>375</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="475">
@@ -13804,11 +13804,11 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>192</v>
+        <v>618</v>
       </c>
     </row>
     <row r="476">
@@ -13829,11 +13829,11 @@
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E476" s="7" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
     </row>
     <row r="477">
@@ -13854,11 +13854,11 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E477" s="7" t="n">
-        <v>104</v>
+        <v>375</v>
       </c>
     </row>
     <row r="478">
@@ -13879,11 +13879,11 @@
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E478" s="7" t="n">
-        <v>96</v>
+        <v>192</v>
       </c>
     </row>
     <row r="479">
@@ -13904,11 +13904,11 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E479" s="7" t="n">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="480">
@@ -13929,11 +13929,11 @@
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E480" s="7" t="n">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="481">
@@ -13954,11 +13954,11 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E481" s="7" t="n">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="482">
@@ -13979,11 +13979,11 @@
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E482" s="7" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="483">
@@ -14004,11 +14004,11 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E483" s="7" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="484">
@@ -14029,11 +14029,11 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E484" s="7" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
     </row>
     <row r="485">
@@ -14054,11 +14054,11 @@
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E485" s="7" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="486">
@@ -14079,11 +14079,11 @@
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E486" s="7" t="n">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="487">
@@ -14104,11 +14104,11 @@
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E487" s="7" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="488">
@@ -14129,11 +14129,11 @@
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E488" s="7" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
     </row>
     <row r="489">
@@ -14154,11 +14154,11 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E489" s="7" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="490">
@@ -14179,11 +14179,11 @@
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E490" s="7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="491">
@@ -14204,11 +14204,11 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E491" s="7" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="492">
@@ -14229,11 +14229,11 @@
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E492" s="7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="493">
@@ -14254,11 +14254,11 @@
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E493" s="7" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="494">
@@ -14279,11 +14279,11 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E494" s="7" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="495">
@@ -14304,11 +14304,11 @@
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E495" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="496">
@@ -14329,11 +14329,11 @@
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E496" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="497">
@@ -14354,11 +14354,11 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E497" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="498">
@@ -14379,11 +14379,11 @@
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E498" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="499">
@@ -14404,86 +14404,86 @@
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E499" s="7" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E500" s="7" t="n">
-        <v>950</v>
+        <v>7</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E501" s="7" t="n">
-        <v>909</v>
+        <v>6</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>819</v>
+        <v>4</v>
       </c>
     </row>
     <row r="503">
@@ -14504,11 +14504,11 @@
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>678</v>
+        <v>950</v>
       </c>
     </row>
     <row r="504">
@@ -14529,11 +14529,11 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>484</v>
+        <v>909</v>
       </c>
     </row>
     <row r="505">
@@ -14554,11 +14554,11 @@
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>404</v>
+        <v>819</v>
       </c>
     </row>
     <row r="506">
@@ -14579,11 +14579,11 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>214</v>
+        <v>678</v>
       </c>
     </row>
     <row r="507">
@@ -14604,11 +14604,11 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>150</v>
+        <v>484</v>
       </c>
     </row>
     <row r="508">
@@ -14629,11 +14629,11 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>100</v>
+        <v>404</v>
       </c>
     </row>
     <row r="509">
@@ -14654,11 +14654,11 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>86</v>
+        <v>214</v>
       </c>
     </row>
     <row r="510">
@@ -14679,11 +14679,11 @@
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>86</v>
+        <v>150</v>
       </c>
     </row>
     <row r="511">
@@ -14704,11 +14704,11 @@
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="512">
@@ -14729,11 +14729,11 @@
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="513">
@@ -14754,11 +14754,11 @@
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>26</v>
+        <v>86</v>
       </c>
     </row>
     <row r="514">
@@ -14779,11 +14779,11 @@
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="515">
@@ -14804,11 +14804,11 @@
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="516">
@@ -14829,11 +14829,11 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="517">
@@ -14854,11 +14854,11 @@
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="518">
@@ -14879,11 +14879,11 @@
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="519">
@@ -14904,11 +14904,11 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="520">
@@ -14929,11 +14929,11 @@
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521">
@@ -14949,16 +14949,16 @@
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>1995</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522">
@@ -14974,16 +14974,16 @@
       </c>
       <c r="C522" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>350</v>
+        <v>9</v>
       </c>
     </row>
     <row r="523">
@@ -14999,16 +14999,16 @@
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -15029,11 +15029,11 @@
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>315</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="525">
@@ -15054,11 +15054,11 @@
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>302</v>
+        <v>350</v>
       </c>
     </row>
     <row r="526">
@@ -15079,11 +15079,11 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>272</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527">
@@ -15104,11 +15104,11 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>200</v>
+        <v>315</v>
       </c>
     </row>
     <row r="528">
@@ -15129,11 +15129,11 @@
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>168</v>
+        <v>302</v>
       </c>
     </row>
     <row r="529">
@@ -15154,11 +15154,11 @@
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>155</v>
+        <v>272</v>
       </c>
     </row>
     <row r="530">
@@ -15179,11 +15179,11 @@
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
     </row>
     <row r="531">
@@ -15204,11 +15204,11 @@
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>146</v>
+        <v>168</v>
       </c>
     </row>
     <row r="532">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
     </row>
     <row r="533">
@@ -15254,11 +15254,11 @@
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>63</v>
+        <v>152</v>
       </c>
     </row>
     <row r="534">
@@ -15279,11 +15279,11 @@
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>40</v>
+        <v>146</v>
       </c>
     </row>
     <row r="535">
@@ -15304,11 +15304,11 @@
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
     </row>
     <row r="536">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>21</v>
+        <v>63</v>
       </c>
     </row>
     <row r="537">
@@ -15354,11 +15354,11 @@
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="538">
@@ -15374,16 +15374,16 @@
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>285</v>
+        <v>21</v>
       </c>
     </row>
     <row r="539">
@@ -15399,16 +15399,16 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
-        <v>282</v>
+        <v>21</v>
       </c>
     </row>
     <row r="540">
@@ -15424,16 +15424,16 @@
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -15454,11 +15454,11 @@
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>132</v>
+        <v>285</v>
       </c>
     </row>
     <row r="542">
@@ -15479,11 +15479,11 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>132</v>
+        <v>282</v>
       </c>
     </row>
     <row r="543">
@@ -15504,11 +15504,11 @@
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>107</v>
+        <v>266</v>
       </c>
     </row>
     <row r="544">
@@ -15529,11 +15529,11 @@
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
     </row>
     <row r="545">
@@ -15554,11 +15554,11 @@
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
-        <v>45</v>
+        <v>132</v>
       </c>
     </row>
     <row r="546">
@@ -15579,11 +15579,11 @@
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="547">
@@ -15604,11 +15604,11 @@
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E547" s="7" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="548">
@@ -15629,11 +15629,11 @@
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E548" s="7" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="549">
@@ -15654,11 +15654,11 @@
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E549" s="7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="550">
@@ -15679,11 +15679,11 @@
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E550" s="7" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="551">
@@ -15704,11 +15704,11 @@
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E551" s="7" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="552">
@@ -15729,11 +15729,11 @@
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E552" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="553">
@@ -15754,11 +15754,11 @@
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E553" s="7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="554">
@@ -15779,11 +15779,11 @@
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E554" s="7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555">
@@ -15804,11 +15804,11 @@
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E555" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -15829,11 +15829,11 @@
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E556" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -15854,11 +15854,11 @@
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E557" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="558">
@@ -15879,86 +15879,86 @@
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E558" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B559" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E559" s="7" t="n">
-        <v>570</v>
+        <v>3</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B560" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C560" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E560" s="7" t="n">
-        <v>188</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B561" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E561" s="7" t="n">
-        <v>128</v>
+        <v>2</v>
       </c>
     </row>
     <row r="562">
@@ -15979,11 +15979,11 @@
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E562" s="7" t="n">
-        <v>100</v>
+        <v>570</v>
       </c>
     </row>
     <row r="563">
@@ -16004,11 +16004,11 @@
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E563" s="7" t="n">
-        <v>90</v>
+        <v>188</v>
       </c>
     </row>
     <row r="564">
@@ -16029,11 +16029,11 @@
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E564" s="7" t="n">
-        <v>81</v>
+        <v>128</v>
       </c>
     </row>
     <row r="565">
@@ -16054,11 +16054,11 @@
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E565" s="7" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
     </row>
     <row r="566">
@@ -16079,11 +16079,11 @@
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E566" s="7" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="567">
@@ -16104,11 +16104,11 @@
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E567" s="7" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="568">
@@ -16129,11 +16129,11 @@
       </c>
       <c r="D568" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E568" s="7" t="n">
-        <v>18</v>
+        <v>81</v>
       </c>
     </row>
     <row r="569">
@@ -16154,11 +16154,11 @@
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E569" s="7" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="570">
@@ -16179,11 +16179,11 @@
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E570" s="7" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="571">
@@ -16204,11 +16204,11 @@
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E571" s="7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="572">
@@ -16229,11 +16229,11 @@
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E572" s="7" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="573">
@@ -16254,11 +16254,11 @@
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E573" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="574">
@@ -16279,11 +16279,11 @@
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E574" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="575">
@@ -16304,11 +16304,11 @@
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E575" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="576">
@@ -16329,11 +16329,11 @@
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E576" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="577">
@@ -16354,10 +16354,85 @@
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E577" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D578" s="5" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="E578" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D579" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E579" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D580" s="5" t="inlineStr">
+        <is>
           <t>Calendar</t>
         </is>
       </c>
-      <c r="E577" s="7" t="n">
+      <c r="E580" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17680,7 +17755,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="66">
@@ -18000,7 +18075,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82">
@@ -18020,7 +18095,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="83">
@@ -18040,7 +18115,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>439</v>
+        <v>454</v>
       </c>
     </row>
     <row r="84">
@@ -18060,7 +18135,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85">
@@ -18080,7 +18155,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86">
@@ -18256,11 +18331,11 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>informacion de poliza</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="95">
@@ -18276,7 +18351,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
@@ -18316,11 +18391,11 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="98">
@@ -18336,11 +18411,11 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>dólares</t>
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99">
@@ -18356,7 +18431,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>dólares</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
@@ -18376,11 +18451,11 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="101">
@@ -22243,10 +22318,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>13997</v>
+        <v>14039</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>21554</v>
+        <v>21618</v>
       </c>
     </row>
     <row r="7">
@@ -22279,10 +22354,10 @@
         <v>44</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>172957</v>
+        <v>172968</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>184303</v>
+        <v>184320</v>
       </c>
     </row>
     <row r="8">
@@ -22315,10 +22390,10 @@
         <v>5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>10633</v>
+        <v>10716</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>13584</v>
+        <v>13724</v>
       </c>
     </row>
     <row r="9">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>14039</v>
+        <v>14009</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7579</v>
+        <v>7570</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -1559,10 +1559,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1981</v>
+        <v>1951</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>30</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="308">
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="309">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="310">
@@ -9683,7 +9683,7 @@
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="311">
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="313">
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="314">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="317">
@@ -9858,7 +9858,7 @@
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="318">
@@ -22318,10 +22318,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14039</v>
+        <v>14009</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>21618</v>
+        <v>21579</v>
       </c>
     </row>
     <row r="7">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-19</t>
+          <t>Quarter: Q2 2026  |  2026-06-22</t>
         </is>
       </c>
     </row>
@@ -693,10 +693,10 @@
         <v>44</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>172968</v>
+        <v>172970</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>11352</v>
+        <v>11356</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>47</v>
@@ -978,16 +978,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>11118</v>
+        <v>11472</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2066</v>
+        <v>2122</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
@@ -1423,10 +1423,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>157763</v>
+        <v>157765</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>10486</v>
+        <v>10490</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>42</v>
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5094</v>
+        <v>5448</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E580"/>
+  <dimension ref="A1:E581"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>7421</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="180">
@@ -14508,7 +14508,7 @@
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>950</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="504">
@@ -14533,7 +14533,7 @@
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>909</v>
+        <v>959</v>
       </c>
     </row>
     <row r="505">
@@ -14558,7 +14558,7 @@
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>819</v>
+        <v>870</v>
       </c>
     </row>
     <row r="506">
@@ -14583,7 +14583,7 @@
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>678</v>
+        <v>699</v>
       </c>
     </row>
     <row r="507">
@@ -14608,7 +14608,7 @@
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>484</v>
+        <v>506</v>
       </c>
     </row>
     <row r="508">
@@ -14633,7 +14633,7 @@
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>404</v>
+        <v>444</v>
       </c>
     </row>
     <row r="509">
@@ -14658,7 +14658,7 @@
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>214</v>
+        <v>230</v>
       </c>
     </row>
     <row r="510">
@@ -14683,7 +14683,7 @@
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
     </row>
     <row r="511">
@@ -14708,7 +14708,7 @@
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="512">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="513">
@@ -14758,7 +14758,7 @@
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="514">
@@ -14783,7 +14783,7 @@
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="515">
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="516">
@@ -14833,7 +14833,7 @@
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="517">
@@ -14858,7 +14858,7 @@
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="518">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="520">
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="521">
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="522">
@@ -15004,11 +15004,11 @@
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
@@ -15024,16 +15024,16 @@
       </c>
       <c r="C524" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>1995</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15054,11 +15054,11 @@
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>350</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="526">
@@ -15079,11 +15079,11 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>331</v>
+        <v>350</v>
       </c>
     </row>
     <row r="527">
@@ -15104,11 +15104,11 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
     </row>
     <row r="528">
@@ -15129,11 +15129,11 @@
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
     </row>
     <row r="529">
@@ -15154,11 +15154,11 @@
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>272</v>
+        <v>302</v>
       </c>
     </row>
     <row r="530">
@@ -15179,11 +15179,11 @@
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>200</v>
+        <v>272</v>
       </c>
     </row>
     <row r="531">
@@ -15204,11 +15204,11 @@
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="532">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>155</v>
+        <v>168</v>
       </c>
     </row>
     <row r="533">
@@ -15254,11 +15254,11 @@
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="534">
@@ -15279,11 +15279,11 @@
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="535">
@@ -15304,11 +15304,11 @@
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
     </row>
     <row r="536">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="537">
@@ -15354,11 +15354,11 @@
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="538">
@@ -15379,11 +15379,11 @@
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="539">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
@@ -15429,11 +15429,11 @@
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="541">
@@ -15449,16 +15449,16 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>285</v>
+        <v>3</v>
       </c>
     </row>
     <row r="542">
@@ -15479,11 +15479,11 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="543">
@@ -15504,11 +15504,11 @@
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
     </row>
     <row r="544">
@@ -15529,11 +15529,11 @@
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>132</v>
+        <v>266</v>
       </c>
     </row>
     <row r="545">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
@@ -15579,11 +15579,11 @@
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>107</v>
+        <v>132</v>
       </c>
     </row>
     <row r="547">
@@ -15604,11 +15604,11 @@
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E547" s="7" t="n">
-        <v>48</v>
+        <v>107</v>
       </c>
     </row>
     <row r="548">
@@ -15629,11 +15629,11 @@
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E548" s="7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="549">
@@ -15654,11 +15654,11 @@
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E549" s="7" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="550">
@@ -15679,11 +15679,11 @@
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E550" s="7" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="551">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E551" s="7" t="n">
@@ -15729,11 +15729,11 @@
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E552" s="7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="553">
@@ -15754,11 +15754,11 @@
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E553" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="554">
@@ -15779,11 +15779,11 @@
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E554" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="555">
@@ -15804,11 +15804,11 @@
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E555" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="556">
@@ -15829,11 +15829,11 @@
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E556" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="557">
@@ -15854,11 +15854,11 @@
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E557" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558">
@@ -15879,11 +15879,11 @@
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E558" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="559">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E559" s="7" t="n">
@@ -15929,11 +15929,11 @@
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E560" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="561">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E561" s="7" t="n">
@@ -15964,26 +15964,26 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E562" s="7" t="n">
-        <v>570</v>
+        <v>2</v>
       </c>
     </row>
     <row r="563">
@@ -16004,11 +16004,11 @@
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E563" s="7" t="n">
-        <v>188</v>
+        <v>570</v>
       </c>
     </row>
     <row r="564">
@@ -16029,11 +16029,11 @@
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E564" s="7" t="n">
-        <v>128</v>
+        <v>188</v>
       </c>
     </row>
     <row r="565">
@@ -16054,11 +16054,11 @@
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E565" s="7" t="n">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="566">
@@ -16079,11 +16079,11 @@
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E566" s="7" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="567">
@@ -16104,11 +16104,11 @@
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E567" s="7" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="568">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="D568" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E568" s="7" t="n">
@@ -16154,11 +16154,11 @@
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E569" s="7" t="n">
-        <v>60</v>
+        <v>81</v>
       </c>
     </row>
     <row r="570">
@@ -16179,11 +16179,11 @@
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E570" s="7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="571">
@@ -16204,11 +16204,11 @@
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E571" s="7" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
     </row>
     <row r="572">
@@ -16229,11 +16229,11 @@
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E572" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="573">
@@ -16254,11 +16254,11 @@
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E573" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="574">
@@ -16279,11 +16279,11 @@
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E574" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="575">
@@ -16304,11 +16304,11 @@
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E575" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="576">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E576" s="7" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E577" s="7" t="n">
@@ -16379,11 +16379,11 @@
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E578" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="579">
@@ -16404,11 +16404,11 @@
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Logo Horizontal</t>
         </is>
       </c>
       <c r="E579" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="580">
@@ -16429,10 +16429,35 @@
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E580" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
           <t>Calendar</t>
         </is>
       </c>
-      <c r="E580" s="7" t="n">
+      <c r="E581" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21335,7 +21360,7 @@
         </is>
       </c>
       <c r="D244" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245">
@@ -21355,7 +21380,7 @@
         </is>
       </c>
       <c r="D245" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="246">
@@ -21375,7 +21400,7 @@
         </is>
       </c>
       <c r="D246" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247">
@@ -21395,7 +21420,7 @@
         </is>
       </c>
       <c r="D247" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="248">
@@ -21455,7 +21480,7 @@
         </is>
       </c>
       <c r="D250" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="251">
@@ -21475,7 +21500,7 @@
         </is>
       </c>
       <c r="D251" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="252">
@@ -21535,7 +21560,7 @@
         </is>
       </c>
       <c r="D254" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="255">
@@ -21555,7 +21580,7 @@
         </is>
       </c>
       <c r="D255" s="12" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="256">
@@ -21571,7 +21596,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D256" s="12" t="n">
@@ -21591,11 +21616,11 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D257" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="258">
@@ -21611,7 +21636,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D258" s="12" t="n">
@@ -21631,11 +21656,11 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>MedicalService</t>
         </is>
       </c>
       <c r="D259" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="260">
@@ -21655,7 +21680,7 @@
         </is>
       </c>
       <c r="D260" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261">
@@ -21675,7 +21700,7 @@
         </is>
       </c>
       <c r="D261" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="262">
@@ -22162,7 +22187,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -22234,7 +22259,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22270,7 +22295,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22306,7 +22331,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22342,7 +22367,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22354,10 +22379,10 @@
         <v>44</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>172968</v>
+        <v>172970</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>184320</v>
+        <v>184326</v>
       </c>
     </row>
     <row r="8">
@@ -22378,7 +22403,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22414,7 +22439,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22450,7 +22475,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22486,7 +22511,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22522,7 +22547,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22558,7 +22583,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22594,7 +22619,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22630,7 +22655,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -22666,7 +22691,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -22675,13 +22700,13 @@
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>11118</v>
+        <v>11472</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>13184</v>
+        <v>13594</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-22</t>
+          <t>Quarter: Q2 2026  |  2026-06-23</t>
         </is>
       </c>
     </row>
@@ -725,17 +725,17 @@
         <v>5</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>10716</v>
+        <v>8539</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>3008</v>
+        <v>1687</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>14009</v>
+        <v>14010</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7570</v>
+        <v>7576</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -917,10 +917,10 @@
         <v>8</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3596</v>
+        <v>3566</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>29</v>
@@ -1457,17 +1457,17 @@
         <v>5</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>10716</v>
+        <v>8539</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3008</v>
+        <v>1687</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>84%</t>
         </is>
       </c>
     </row>
@@ -1559,13 +1559,13 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -1729,10 +1729,10 @@
         <v>8</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3596</v>
+        <v>3566</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>29</v>
@@ -7354,11 +7354,11 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E217" s="7" t="n">
-        <v>1543</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="218">
@@ -7379,11 +7379,11 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
-        <v>1440</v>
+        <v>998</v>
       </c>
     </row>
     <row r="219">
@@ -7408,7 +7408,7 @@
         </is>
       </c>
       <c r="E219" s="7" t="n">
-        <v>1363</v>
+        <v>993</v>
       </c>
     </row>
     <row r="220">
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="E220" s="7" t="n">
-        <v>1346</v>
+        <v>976</v>
       </c>
     </row>
     <row r="221">
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="E221" s="7" t="n">
-        <v>804</v>
+        <v>756</v>
       </c>
     </row>
     <row r="222">
@@ -7479,11 +7479,11 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
-        <v>610</v>
+        <v>390</v>
       </c>
     </row>
     <row r="223">
@@ -7504,11 +7504,11 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>454</v>
+        <v>390</v>
       </c>
     </row>
     <row r="224">
@@ -7533,7 +7533,7 @@
         </is>
       </c>
       <c r="E224" s="7" t="n">
-        <v>445</v>
+        <v>289</v>
       </c>
     </row>
     <row r="225">
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>326</v>
+        <v>266</v>
       </c>
     </row>
     <row r="226">
@@ -7579,11 +7579,11 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
-        <v>273</v>
+        <v>240</v>
       </c>
     </row>
     <row r="227">
@@ -7604,11 +7604,11 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
-        <v>249</v>
+        <v>229</v>
       </c>
     </row>
     <row r="228">
@@ -7629,11 +7629,11 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="229">
@@ -7654,11 +7654,11 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
-        <v>240</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="E230" s="7" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231">
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="E231" s="7" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="232">
@@ -7779,11 +7779,11 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
-        <v>108</v>
+        <v>60</v>
       </c>
     </row>
     <row r="235">
@@ -7804,11 +7804,11 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Card Dashboard</t>
         </is>
       </c>
       <c r="E235" s="7" t="n">
-        <v>79</v>
+        <v>56</v>
       </c>
     </row>
     <row r="236">
@@ -7829,11 +7829,11 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="237">
@@ -7854,11 +7854,11 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E237" s="7" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="238">
@@ -7879,11 +7879,11 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
     </row>
     <row r="239">
@@ -7904,11 +7904,11 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Card Dashboard</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E239" s="7" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="240">
@@ -7929,11 +7929,11 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="241">
@@ -7954,11 +7954,11 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E241" s="7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="242">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
@@ -8004,11 +8004,11 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E243" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244">
@@ -8029,11 +8029,11 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245">
@@ -8054,11 +8054,11 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E245" s="7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
@@ -8104,11 +8104,11 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E247" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248">
@@ -8129,11 +8129,11 @@
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
@@ -8154,36 +8154,36 @@
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E249" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
-        <v>4</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="251">
@@ -8204,11 +8204,11 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E251" s="7" t="n">
-        <v>2929</v>
+        <v>685</v>
       </c>
     </row>
     <row r="252">
@@ -8229,11 +8229,11 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
-        <v>685</v>
+        <v>653</v>
       </c>
     </row>
     <row r="253">
@@ -8254,11 +8254,11 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
-        <v>653</v>
+        <v>553</v>
       </c>
     </row>
     <row r="254">
@@ -8279,11 +8279,11 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="255">
@@ -8304,11 +8304,11 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E255" s="7" t="n">
-        <v>551</v>
+        <v>512</v>
       </c>
     </row>
     <row r="256">
@@ -8329,11 +8329,11 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
-        <v>512</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257">
@@ -8354,11 +8354,11 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E257" s="7" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258">
@@ -8379,11 +8379,11 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
-        <v>335</v>
+        <v>187</v>
       </c>
     </row>
     <row r="259">
@@ -8404,11 +8404,11 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
-        <v>187</v>
+        <v>145</v>
       </c>
     </row>
     <row r="260">
@@ -8429,11 +8429,11 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="261">
@@ -8454,11 +8454,11 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E261" s="7" t="n">
-        <v>139</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262">
@@ -8479,11 +8479,11 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="263">
@@ -8504,11 +8504,11 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E263" s="7" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264">
@@ -8529,11 +8529,11 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265">
@@ -8554,11 +8554,11 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E265" s="7" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="266">
@@ -8579,11 +8579,11 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="267">
@@ -8604,11 +8604,11 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E267" s="7" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="268">
@@ -8629,11 +8629,11 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269">
@@ -8654,11 +8654,11 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="270">
@@ -8679,11 +8679,11 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="271">
@@ -8704,11 +8704,11 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E271" s="7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="272">
@@ -8729,11 +8729,11 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273">
@@ -8754,11 +8754,11 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E273" s="7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="274">
@@ -8779,11 +8779,11 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275">
@@ -8804,11 +8804,11 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E275" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -8854,11 +8854,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E277" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -8879,11 +8879,11 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E279" s="7" t="n">
@@ -8929,11 +8929,11 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281">
@@ -8954,11 +8954,11 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E281" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -9004,11 +9004,11 @@
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E283" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
@@ -9024,16 +9024,16 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
-        <v>2</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="285">
@@ -9054,11 +9054,11 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E285" s="7" t="n">
-        <v>1316</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="286">
@@ -9079,11 +9079,11 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
-        <v>1258</v>
+        <v>531</v>
       </c>
     </row>
     <row r="287">
@@ -9104,11 +9104,11 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E287" s="7" t="n">
-        <v>531</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288">
@@ -9129,11 +9129,11 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="289">
@@ -9154,11 +9154,11 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="290">
@@ -9179,11 +9179,11 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="291">
@@ -9204,11 +9204,11 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
-        <v>126</v>
+        <v>107</v>
       </c>
     </row>
     <row r="292">
@@ -9229,11 +9229,11 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
     </row>
     <row r="293">
@@ -9254,11 +9254,11 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E293" s="7" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
     </row>
     <row r="294">
@@ -9279,11 +9279,11 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="295">
@@ -9304,11 +9304,11 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="296">
@@ -9329,11 +9329,11 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E297" s="7" t="n">
@@ -9379,11 +9379,11 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -9404,11 +9404,11 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E299" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -9429,11 +9429,11 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E301" s="7" t="n">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -9504,7 +9504,7 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E303" s="7" t="n">
@@ -9529,11 +9529,11 @@
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -9549,16 +9549,16 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>2</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="306">
@@ -9579,11 +9579,11 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>1292</v>
+        <v>144</v>
       </c>
     </row>
     <row r="307">
@@ -9604,11 +9604,11 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>144</v>
+        <v>90</v>
       </c>
     </row>
     <row r="308">
@@ -9629,11 +9629,11 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="309">
@@ -9654,11 +9654,11 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="310">
@@ -9679,11 +9679,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="311">
@@ -9704,11 +9704,11 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="312">
@@ -9729,11 +9729,11 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="313">
@@ -9754,11 +9754,11 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="314">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
@@ -9804,11 +9804,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="316">
@@ -9829,11 +9829,11 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="317">
@@ -9854,11 +9854,11 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318">
@@ -9879,11 +9879,11 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319">
@@ -9904,11 +9904,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
@@ -9929,11 +9929,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E321" s="7" t="n">
@@ -9979,11 +9979,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="323">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
@@ -10029,11 +10029,11 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
@@ -10054,11 +10054,11 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E325" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="326">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E327" s="7" t="n">
@@ -10129,11 +10129,11 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -10154,11 +10154,11 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E329" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
@@ -10204,11 +10204,11 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E331" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E333" s="7" t="n">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
@@ -13183,7 +13183,7 @@
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="451">
@@ -13204,11 +13204,11 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="452">
@@ -13229,11 +13229,11 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="453">
@@ -13254,11 +13254,11 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="454">
@@ -13279,11 +13279,11 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="455">
@@ -13358,7 +13358,7 @@
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="458">
@@ -18116,11 +18116,11 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Pegar Icon</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>499</v>
+        <v>233</v>
       </c>
     </row>
     <row r="83">
@@ -18136,11 +18136,11 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>copy</t>
+          <t>DirectionRight</t>
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>454</v>
+        <v>198</v>
       </c>
     </row>
     <row r="84">
@@ -18156,11 +18156,11 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>348</v>
+        <v>165</v>
       </c>
     </row>
     <row r="85">
@@ -18176,11 +18176,11 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>DirectionRight</t>
+          <t>Pegar Icon</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>281</v>
+        <v>102</v>
       </c>
     </row>
     <row r="86">
@@ -18196,11 +18196,11 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>Component 9</t>
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>165</v>
+        <v>90</v>
       </c>
     </row>
     <row r="87">
@@ -18216,11 +18216,11 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>copy</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>95</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
@@ -18236,11 +18236,11 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Component 9</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>94</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89">
@@ -18256,11 +18256,11 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
@@ -18276,11 +18276,11 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Frame 1707479054</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91">
@@ -18296,11 +18296,11 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>48</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -18316,11 +18316,11 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Frame 1707479133</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="93">
@@ -18336,11 +18336,11 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>informacion de poliza</t>
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
@@ -18356,11 +18356,11 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -18376,11 +18376,11 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>informacion de poliza</t>
+          <t>soles</t>
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="96">
@@ -18396,11 +18396,11 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -18416,11 +18416,11 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>24.timer</t>
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -18436,11 +18436,11 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>dólares</t>
+          <t>File</t>
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -18456,11 +18456,11 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -18476,11 +18476,11 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>circle</t>
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="101">
@@ -18496,11 +18496,11 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>24.timer</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
@@ -20676,11 +20676,11 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D210" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211">
@@ -20696,7 +20696,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>A.white</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D211" s="12" t="n">
@@ -20896,11 +20896,11 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Seguridad_72x72</t>
+          <t>Emergencias</t>
         </is>
       </c>
       <c r="D221" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22343,10 +22343,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14009</v>
+        <v>14010</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>21579</v>
+        <v>21586</v>
       </c>
     </row>
     <row r="7">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22403,22 +22403,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>10716</v>
+        <v>8539</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>13724</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="9">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22475,7 +22475,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -22667,10 +22667,10 @@
         <v>8</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3596</v>
+        <v>3566</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4195</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="16">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -821,10 +821,10 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2296</v>
+        <v>2301</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>28</v>
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2296</v>
+        <v>2301</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>28</v>
@@ -11033,7 +11033,7 @@
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="365">
@@ -11083,7 +11083,7 @@
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="367">
@@ -11158,7 +11158,7 @@
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="370">
@@ -22595,10 +22595,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2296</v>
+        <v>2301</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3143</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="14">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-23</t>
+          <t>Quarter: Q2 2026  |  2026-06-24</t>
         </is>
       </c>
     </row>
@@ -22187,7 +22187,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22295,7 +22295,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22403,7 +22403,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22439,7 +22439,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22475,7 +22475,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22511,7 +22511,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22547,7 +22547,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22583,7 +22583,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22619,7 +22619,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>14010</v>
+        <v>14454</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7576</v>
+        <v>7650</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -920,14 +920,14 @@
         <v>3566</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>29</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -1559,17 +1559,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1952</v>
+        <v>2396</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>467</v>
+        <v>541</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>82%</t>
         </is>
       </c>
     </row>
@@ -1732,14 +1732,14 @@
         <v>3566</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>593</v>
+        <v>638</v>
       </c>
       <c r="G20" s="8" t="n">
         <v>29</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E581"/>
+  <dimension ref="A1:E580"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9558,7 +9558,7 @@
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>1292</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="306">
@@ -9583,7 +9583,7 @@
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>144</v>
+        <v>191</v>
       </c>
     </row>
     <row r="307">
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>90</v>
+        <v>119</v>
       </c>
     </row>
     <row r="308">
@@ -9633,7 +9633,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="309">
@@ -9654,11 +9654,11 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="310">
@@ -9679,11 +9679,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="311">
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="312">
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="313">
@@ -9754,11 +9754,11 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="314">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
@@ -9804,11 +9804,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="316">
@@ -9833,7 +9833,7 @@
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="317">
@@ -9879,7 +9879,7 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
@@ -9904,11 +9904,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320">
@@ -9929,11 +9929,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321">
@@ -9979,11 +9979,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
@@ -10289,26 +10289,26 @@
     <row r="335">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="336">
@@ -10329,11 +10329,11 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
-        <v>305</v>
+        <v>243</v>
       </c>
     </row>
     <row r="337">
@@ -10354,11 +10354,11 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E337" s="7" t="n">
-        <v>243</v>
+        <v>164</v>
       </c>
     </row>
     <row r="338">
@@ -10379,11 +10379,11 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
-        <v>164</v>
+        <v>110</v>
       </c>
     </row>
     <row r="339">
@@ -10404,11 +10404,11 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E339" s="7" t="n">
-        <v>110</v>
+        <v>83</v>
       </c>
     </row>
     <row r="340">
@@ -10429,11 +10429,11 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="341">
@@ -10454,11 +10454,11 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E341" s="7" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
     </row>
     <row r="342">
@@ -10479,11 +10479,11 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="343">
@@ -10504,11 +10504,11 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E343" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="344">
@@ -10529,7 +10529,7 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
@@ -10554,11 +10554,11 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E345" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="346">
@@ -10579,11 +10579,11 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="347">
@@ -10604,11 +10604,11 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E347" s="7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="348">
@@ -10629,11 +10629,11 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="349">
@@ -10654,11 +10654,11 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="350">
@@ -10679,11 +10679,11 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E351" s="7" t="n">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
@@ -10754,11 +10754,11 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E353" s="7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354">
@@ -10779,11 +10779,11 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="355">
@@ -10804,11 +10804,11 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E355" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="356">
@@ -10829,11 +10829,11 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357">
@@ -10854,11 +10854,11 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E357" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="358">
@@ -10879,11 +10879,11 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="359">
@@ -10904,11 +10904,11 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E359" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
@@ -10954,11 +10954,11 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E361" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -10969,21 +10969,21 @@
       </c>
       <c r="B362" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>1</v>
+        <v>433</v>
       </c>
     </row>
     <row r="363">
@@ -11004,11 +11004,11 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>433</v>
+        <v>217</v>
       </c>
     </row>
     <row r="364">
@@ -11029,11 +11029,11 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="365">
@@ -11054,11 +11054,11 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E365" s="7" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="366">
@@ -11079,11 +11079,11 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
     </row>
     <row r="367">
@@ -11104,11 +11104,11 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E367" s="7" t="n">
-        <v>149</v>
+        <v>124</v>
       </c>
     </row>
     <row r="368">
@@ -11129,11 +11129,11 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E368" s="7" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="369">
@@ -11154,11 +11154,11 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="370">
@@ -11179,11 +11179,11 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E370" s="7" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="371">
@@ -11204,11 +11204,11 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E371" s="7" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
     </row>
     <row r="372">
@@ -11229,11 +11229,11 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="373">
@@ -11254,11 +11254,11 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E373" s="7" t="n">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="374">
@@ -11279,11 +11279,11 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E374" s="7" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="375">
@@ -11304,11 +11304,11 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E375" s="7" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="376">
@@ -11329,11 +11329,11 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E376" s="7" t="n">
-        <v>62</v>
+        <v>49</v>
       </c>
     </row>
     <row r="377">
@@ -11354,11 +11354,11 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E377" s="7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="378">
@@ -11379,11 +11379,11 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E378" s="7" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="379">
@@ -11404,11 +11404,11 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E379" s="7" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="380">
@@ -11429,11 +11429,11 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E380" s="7" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="381">
@@ -11454,11 +11454,11 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E381" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E382" s="7" t="n">
@@ -11504,11 +11504,11 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E383" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="384">
@@ -11529,11 +11529,11 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E384" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E385" s="7" t="n">
@@ -11579,11 +11579,11 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E386" s="7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
@@ -11629,11 +11629,11 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="389">
@@ -11654,11 +11654,11 @@
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E389" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -11669,21 +11669,21 @@
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="391">
@@ -11704,11 +11704,11 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="392">
@@ -11729,11 +11729,11 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="393">
@@ -11754,11 +11754,11 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="394">
@@ -11779,11 +11779,11 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>107</v>
+        <v>77</v>
       </c>
     </row>
     <row r="395">
@@ -11804,11 +11804,11 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="396">
@@ -11829,11 +11829,11 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="397">
@@ -11854,11 +11854,11 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="398">
@@ -11879,11 +11879,11 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
     </row>
     <row r="399">
@@ -11904,11 +11904,11 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="400">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
@@ -11954,11 +11954,11 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="402">
@@ -11979,11 +11979,11 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="403">
@@ -12004,11 +12004,11 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="404">
@@ -12029,11 +12029,11 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="405">
@@ -12054,11 +12054,11 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="406">
@@ -12079,11 +12079,11 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="407">
@@ -12104,11 +12104,11 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="408">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Infografia</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Infografia</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
@@ -12204,11 +12204,11 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412">
@@ -12229,11 +12229,11 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
@@ -12294,21 +12294,21 @@
       </c>
       <c r="B415" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>1</v>
+        <v>597</v>
       </c>
     </row>
     <row r="416">
@@ -12329,11 +12329,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>597</v>
+        <v>331</v>
       </c>
     </row>
     <row r="417">
@@ -12354,11 +12354,11 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="418">
@@ -12379,11 +12379,11 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>327</v>
+        <v>276</v>
       </c>
     </row>
     <row r="419">
@@ -12404,11 +12404,11 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>276</v>
+        <v>166</v>
       </c>
     </row>
     <row r="420">
@@ -12429,11 +12429,11 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
     </row>
     <row r="421">
@@ -12454,11 +12454,11 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
     </row>
     <row r="422">
@@ -12479,11 +12479,11 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>116</v>
+        <v>70</v>
       </c>
     </row>
     <row r="423">
@@ -12504,11 +12504,11 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="424">
@@ -12529,11 +12529,11 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="425">
@@ -12554,11 +12554,11 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="426">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
@@ -12679,11 +12679,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="431">
@@ -12704,11 +12704,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="432">
@@ -12729,11 +12729,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="433">
@@ -12754,11 +12754,11 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="434">
@@ -12779,7 +12779,7 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
@@ -12804,11 +12804,11 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="436">
@@ -12829,7 +12829,7 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
@@ -12854,11 +12854,11 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="438">
@@ -12879,11 +12879,11 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="439">
@@ -12904,11 +12904,11 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="440">
@@ -12929,7 +12929,7 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
@@ -12979,11 +12979,11 @@
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="443">
@@ -13004,7 +13004,7 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
@@ -13019,21 +13019,21 @@
       </c>
       <c r="B444" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>2</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="445">
@@ -13054,11 +13054,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>1536</v>
+        <v>340</v>
       </c>
     </row>
     <row r="446">
@@ -13079,11 +13079,11 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>340</v>
+        <v>256</v>
       </c>
     </row>
     <row r="447">
@@ -13104,11 +13104,11 @@
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="448">
@@ -13129,11 +13129,11 @@
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>251</v>
+        <v>160</v>
       </c>
     </row>
     <row r="449">
@@ -13154,11 +13154,11 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="450">
@@ -13179,11 +13179,11 @@
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>149</v>
+        <v>128</v>
       </c>
     </row>
     <row r="451">
@@ -13204,11 +13204,11 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
     </row>
     <row r="452">
@@ -13229,11 +13229,11 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>122</v>
+        <v>85</v>
       </c>
     </row>
     <row r="453">
@@ -13254,11 +13254,11 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="454">
@@ -13279,11 +13279,11 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="455">
@@ -13304,11 +13304,11 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="456">
@@ -13329,11 +13329,11 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="457">
@@ -13354,11 +13354,11 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="458">
@@ -13379,11 +13379,11 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="459">
@@ -13404,11 +13404,11 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="460">
@@ -13429,7 +13429,7 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
@@ -13454,11 +13454,11 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="462">
@@ -13479,7 +13479,7 @@
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
@@ -13504,11 +13504,11 @@
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="464">
@@ -13529,11 +13529,11 @@
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="465">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
@@ -13579,11 +13579,11 @@
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="467">
@@ -13604,7 +13604,7 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
@@ -13654,11 +13654,11 @@
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="470">
@@ -13679,11 +13679,11 @@
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="471">
@@ -13704,11 +13704,11 @@
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="472">
@@ -13729,11 +13729,11 @@
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="473">
@@ -13744,21 +13744,21 @@
       </c>
       <c r="B473" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>6</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="474">
@@ -13779,11 +13779,11 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>1152</v>
+        <v>618</v>
       </c>
     </row>
     <row r="475">
@@ -13804,11 +13804,11 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>618</v>
+        <v>440</v>
       </c>
     </row>
     <row r="476">
@@ -13829,11 +13829,11 @@
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E476" s="7" t="n">
-        <v>440</v>
+        <v>375</v>
       </c>
     </row>
     <row r="477">
@@ -13854,11 +13854,11 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E477" s="7" t="n">
-        <v>375</v>
+        <v>192</v>
       </c>
     </row>
     <row r="478">
@@ -13879,11 +13879,11 @@
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E478" s="7" t="n">
-        <v>192</v>
+        <v>120</v>
       </c>
     </row>
     <row r="479">
@@ -13904,11 +13904,11 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E479" s="7" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="480">
@@ -13929,11 +13929,11 @@
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E480" s="7" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="481">
@@ -13954,11 +13954,11 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E481" s="7" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="482">
@@ -13979,11 +13979,11 @@
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E482" s="7" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="483">
@@ -14004,11 +14004,11 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E483" s="7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="484">
@@ -14029,11 +14029,11 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E484" s="7" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="485">
@@ -14054,11 +14054,11 @@
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E485" s="7" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="486">
@@ -14079,11 +14079,11 @@
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E486" s="7" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="487">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E487" s="7" t="n">
@@ -14129,11 +14129,11 @@
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E488" s="7" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="489">
@@ -14154,11 +14154,11 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E489" s="7" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="490">
@@ -14179,11 +14179,11 @@
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E490" s="7" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="491">
@@ -14204,11 +14204,11 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E491" s="7" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="492">
@@ -14229,11 +14229,11 @@
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E492" s="7" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="493">
@@ -14254,11 +14254,11 @@
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E493" s="7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="494">
@@ -14279,11 +14279,11 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E494" s="7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="495">
@@ -14304,11 +14304,11 @@
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E495" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="496">
@@ -14329,11 +14329,11 @@
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E496" s="7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="497">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E497" s="7" t="n">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E498" s="7" t="n">
@@ -14404,11 +14404,11 @@
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E499" s="7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="500">
@@ -14429,11 +14429,11 @@
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E500" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="501">
@@ -14454,36 +14454,36 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E501" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>4</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="503">
@@ -14504,11 +14504,11 @@
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>1045</v>
+        <v>959</v>
       </c>
     </row>
     <row r="504">
@@ -14529,11 +14529,11 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>959</v>
+        <v>870</v>
       </c>
     </row>
     <row r="505">
@@ -14554,11 +14554,11 @@
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>870</v>
+        <v>699</v>
       </c>
     </row>
     <row r="506">
@@ -14579,11 +14579,11 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>699</v>
+        <v>506</v>
       </c>
     </row>
     <row r="507">
@@ -14604,11 +14604,11 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>506</v>
+        <v>444</v>
       </c>
     </row>
     <row r="508">
@@ -14629,11 +14629,11 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>444</v>
+        <v>230</v>
       </c>
     </row>
     <row r="509">
@@ -14654,11 +14654,11 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>230</v>
+        <v>165</v>
       </c>
     </row>
     <row r="510">
@@ -14679,11 +14679,11 @@
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>165</v>
+        <v>110</v>
       </c>
     </row>
     <row r="511">
@@ -14704,11 +14704,11 @@
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="512">
@@ -14729,11 +14729,11 @@
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="513">
@@ -14754,11 +14754,11 @@
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="514">
@@ -14779,11 +14779,11 @@
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>88</v>
+        <v>33</v>
       </c>
     </row>
     <row r="515">
@@ -14804,11 +14804,11 @@
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="516">
@@ -14829,11 +14829,11 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="517">
@@ -14854,11 +14854,11 @@
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="518">
@@ -14879,11 +14879,11 @@
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="519">
@@ -14904,7 +14904,7 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
@@ -14929,11 +14929,11 @@
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="521">
@@ -14954,11 +14954,11 @@
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="522">
@@ -14979,11 +14979,11 @@
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="523">
@@ -15004,11 +15004,11 @@
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -15024,16 +15024,16 @@
       </c>
       <c r="C524" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>2</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="525">
@@ -15054,11 +15054,11 @@
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>1995</v>
+        <v>350</v>
       </c>
     </row>
     <row r="526">
@@ -15079,11 +15079,11 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>350</v>
+        <v>331</v>
       </c>
     </row>
     <row r="527">
@@ -15104,11 +15104,11 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>331</v>
+        <v>315</v>
       </c>
     </row>
     <row r="528">
@@ -15129,11 +15129,11 @@
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>315</v>
+        <v>302</v>
       </c>
     </row>
     <row r="529">
@@ -15154,11 +15154,11 @@
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>302</v>
+        <v>272</v>
       </c>
     </row>
     <row r="530">
@@ -15179,11 +15179,11 @@
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>272</v>
+        <v>200</v>
       </c>
     </row>
     <row r="531">
@@ -15204,11 +15204,11 @@
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
     </row>
     <row r="532">
@@ -15229,11 +15229,11 @@
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="533">
@@ -15254,11 +15254,11 @@
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="534">
@@ -15279,11 +15279,11 @@
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="535">
@@ -15304,11 +15304,11 @@
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>146</v>
+        <v>71</v>
       </c>
     </row>
     <row r="536">
@@ -15329,11 +15329,11 @@
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="537">
@@ -15354,11 +15354,11 @@
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="538">
@@ -15379,11 +15379,11 @@
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
     </row>
     <row r="539">
@@ -15404,7 +15404,7 @@
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
@@ -15429,11 +15429,11 @@
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
     </row>
     <row r="541">
@@ -15449,16 +15449,16 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>3</v>
+        <v>285</v>
       </c>
     </row>
     <row r="542">
@@ -15479,11 +15479,11 @@
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="543">
@@ -15504,11 +15504,11 @@
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>282</v>
+        <v>266</v>
       </c>
     </row>
     <row r="544">
@@ -15529,11 +15529,11 @@
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>266</v>
+        <v>132</v>
       </c>
     </row>
     <row r="545">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
@@ -15579,11 +15579,11 @@
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="547">
@@ -15604,11 +15604,11 @@
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E547" s="7" t="n">
-        <v>107</v>
+        <v>48</v>
       </c>
     </row>
     <row r="548">
@@ -15629,11 +15629,11 @@
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E548" s="7" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="549">
@@ -15654,11 +15654,11 @@
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E549" s="7" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
     </row>
     <row r="550">
@@ -15679,11 +15679,11 @@
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E550" s="7" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="551">
@@ -15704,7 +15704,7 @@
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E551" s="7" t="n">
@@ -15729,11 +15729,11 @@
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E552" s="7" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="553">
@@ -15754,11 +15754,11 @@
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E553" s="7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="554">
@@ -15779,11 +15779,11 @@
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E554" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555">
@@ -15804,11 +15804,11 @@
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E555" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="556">
@@ -15829,11 +15829,11 @@
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E556" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
@@ -15854,11 +15854,11 @@
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E557" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="558">
@@ -15879,11 +15879,11 @@
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E558" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E559" s="7" t="n">
@@ -15929,11 +15929,11 @@
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E560" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="561">
@@ -15954,7 +15954,7 @@
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E561" s="7" t="n">
@@ -15964,26 +15964,26 @@
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E562" s="7" t="n">
-        <v>2</v>
+        <v>570</v>
       </c>
     </row>
     <row r="563">
@@ -16004,11 +16004,11 @@
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E563" s="7" t="n">
-        <v>570</v>
+        <v>188</v>
       </c>
     </row>
     <row r="564">
@@ -16029,11 +16029,11 @@
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E564" s="7" t="n">
-        <v>188</v>
+        <v>128</v>
       </c>
     </row>
     <row r="565">
@@ -16054,11 +16054,11 @@
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E565" s="7" t="n">
-        <v>128</v>
+        <v>100</v>
       </c>
     </row>
     <row r="566">
@@ -16079,11 +16079,11 @@
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E566" s="7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="567">
@@ -16104,11 +16104,11 @@
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E567" s="7" t="n">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="568">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="D568" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E568" s="7" t="n">
@@ -16154,11 +16154,11 @@
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E569" s="7" t="n">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="570">
@@ -16179,11 +16179,11 @@
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E570" s="7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="571">
@@ -16204,11 +16204,11 @@
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E571" s="7" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="572">
@@ -16229,11 +16229,11 @@
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E572" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="573">
@@ -16254,11 +16254,11 @@
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E573" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="574">
@@ -16279,11 +16279,11 @@
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E574" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="575">
@@ -16304,11 +16304,11 @@
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E575" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="576">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E576" s="7" t="n">
@@ -16354,7 +16354,7 @@
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E577" s="7" t="n">
@@ -16379,11 +16379,11 @@
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Logo Horizontal</t>
         </is>
       </c>
       <c r="E578" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="579">
@@ -16404,11 +16404,11 @@
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E579" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580">
@@ -16429,35 +16429,10 @@
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E580" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B581" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C581" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D581" s="5" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="E581" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18676,11 +18651,11 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>barras</t>
         </is>
       </c>
       <c r="D110" s="12" t="n">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="111">
@@ -18696,11 +18671,11 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="D111" s="12" t="n">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="112">
@@ -18716,11 +18691,11 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>barras</t>
+          <t>billetera</t>
         </is>
       </c>
       <c r="D112" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113">
@@ -18736,11 +18711,11 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>billetera</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D113" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
     </row>
     <row r="114">
@@ -18756,11 +18731,11 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D114" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115">
@@ -18776,11 +18751,11 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D115" s="12" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116">
@@ -18816,11 +18791,11 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D117" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118">
@@ -18836,11 +18811,11 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>ArrowLeft</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D118" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119">
@@ -18856,11 +18831,11 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D119" s="12" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="120">
@@ -18876,11 +18851,11 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D120" s="12" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="121">
@@ -20596,11 +20571,11 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D206" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="207">
@@ -20616,7 +20591,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D207" s="12" t="n">
@@ -20636,7 +20611,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D208" s="12" t="n">
@@ -20656,7 +20631,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D209" s="12" t="n">
@@ -20676,11 +20651,11 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>A.white</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D210" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211">
@@ -20696,7 +20671,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D211" s="12" t="n">
@@ -20716,11 +20691,11 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Viajeros</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D212" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213">
@@ -20736,11 +20711,11 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>iaSpark</t>
         </is>
       </c>
       <c r="D213" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214">
@@ -20756,11 +20731,11 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>DirectionRight</t>
         </is>
       </c>
       <c r="D214" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="215">
@@ -20776,11 +20751,11 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Viajeros Mobile</t>
+          <t>Viajeros</t>
         </is>
       </c>
       <c r="D215" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216">
@@ -20796,11 +20771,11 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Cancel Icon</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D216" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="217">
@@ -20816,11 +20791,11 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Pasajeros</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="D217" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218">
@@ -20836,11 +20811,11 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Spinner mesagge</t>
+          <t>Viajeros Mobile</t>
         </is>
       </c>
       <c r="D218" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219">
@@ -20856,11 +20831,11 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D219" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220">
@@ -20876,11 +20851,11 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>Pasajeros</t>
         </is>
       </c>
       <c r="D220" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221">
@@ -20896,11 +20871,11 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Emergencias</t>
+          <t>Spinner mesagge</t>
         </is>
       </c>
       <c r="D221" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222">
@@ -22343,10 +22318,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14010</v>
+        <v>14454</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>21586</v>
+        <v>22104</v>
       </c>
     </row>
     <row r="7">
@@ -22660,7 +22635,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -22670,7 +22645,7 @@
         <v>3566</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4159</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="16">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-24</t>
+          <t>Quarter: Q2 2026  |  2026-06-25</t>
         </is>
       </c>
     </row>
@@ -821,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>846</v>
@@ -966,62 +966,94 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>11472</v>
+        <v>11371</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>2122</v>
+        <v>706</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>11472</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>2122</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C19" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D19" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E18" s="7" t="n">
+      <c r="E19" s="7" t="n">
         <v>1424</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F19" s="6" t="n">
         <v>201</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G19" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -1042,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1627,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>846</v>
@@ -1780,34 +1812,34 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>5448</v>
+        <v>11371</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>787</v>
+        <v>706</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -1824,24 +1856,24 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>4605</v>
+        <v>5448</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>1163</v>
+        <v>787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -1858,56 +1890,90 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1419</v>
+        <v>4605</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>172</v>
+        <v>1163</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>80%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>1419</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>172</v>
+      </c>
+      <c r="G25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Landing Alianzas</t>
         </is>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D26" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="7" t="n">
+      <c r="E26" s="7" t="n">
         <v>1424</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F26" s="6" t="n">
         <v>201</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G26" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -1924,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E580"/>
+  <dimension ref="A1:E615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10983,7 +11049,7 @@
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="363">
@@ -11008,7 +11074,7 @@
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="364">
@@ -11233,7 +11299,7 @@
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="373">
@@ -11604,11 +11670,11 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="388">
@@ -11629,11 +11695,11 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389">
@@ -14464,17 +14530,17 @@
     <row r="502">
       <c r="A502" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B502" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D502" s="5" t="inlineStr">
@@ -14483,857 +14549,857 @@
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>1045</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B503" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>959</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B504" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>870</v>
+        <v>670</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B505" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>699</v>
+        <v>536</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B506" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>506</v>
+        <v>409</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B507" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>444</v>
+        <v>268</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B508" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C508" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>230</v>
+        <v>171</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B509" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C510" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>110</v>
+        <v>151</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>95</v>
+        <v>150</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C512" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>91</v>
+        <v>149</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>88</v>
+        <v>134</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C514" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C516" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>22</v>
+        <v>81</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C518" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>11</v>
+        <v>75</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C519" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>11</v>
+        <v>67</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C520" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>10</v>
+        <v>67</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C522" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C524" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>1995</v>
+        <v>46</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>350</v>
+        <v>45</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C526" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>331</v>
+        <v>36</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C527" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>315</v>
+        <v>35</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C528" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>302</v>
+        <v>33</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C530" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>200</v>
+        <v>27</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>168</v>
+        <v>25</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C532" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>155</v>
+        <v>20</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>152</v>
+        <v>10</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C534" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>146</v>
+        <v>8</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>71</v>
+        <v>6</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C536" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="537">
@@ -15349,16 +15415,16 @@
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>40</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="538">
@@ -15374,16 +15440,16 @@
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>21</v>
+        <v>959</v>
       </c>
     </row>
     <row r="539">
@@ -15399,16 +15465,16 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
-        <v>21</v>
+        <v>870</v>
       </c>
     </row>
     <row r="540">
@@ -15424,16 +15490,16 @@
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>3</v>
+        <v>699</v>
       </c>
     </row>
     <row r="541">
@@ -15449,16 +15515,16 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>285</v>
+        <v>506</v>
       </c>
     </row>
     <row r="542">
@@ -15474,16 +15540,16 @@
       </c>
       <c r="C542" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>282</v>
+        <v>444</v>
       </c>
     </row>
     <row r="543">
@@ -15499,16 +15565,16 @@
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>266</v>
+        <v>230</v>
       </c>
     </row>
     <row r="544">
@@ -15524,16 +15590,16 @@
       </c>
       <c r="C544" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
     </row>
     <row r="545">
@@ -15549,16 +15615,16 @@
       </c>
       <c r="C545" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="546">
@@ -15574,16 +15640,16 @@
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>107</v>
+        <v>95</v>
       </c>
     </row>
     <row r="547">
@@ -15599,16 +15665,16 @@
       </c>
       <c r="C547" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E547" s="7" t="n">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="548">
@@ -15624,16 +15690,16 @@
       </c>
       <c r="C548" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E548" s="7" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
     </row>
     <row r="549">
@@ -15649,16 +15715,16 @@
       </c>
       <c r="C549" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E549" s="7" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="550">
@@ -15674,16 +15740,16 @@
       </c>
       <c r="C550" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E550" s="7" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="551">
@@ -15699,16 +15765,16 @@
       </c>
       <c r="C551" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E551" s="7" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="552">
@@ -15724,16 +15790,16 @@
       </c>
       <c r="C552" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E552" s="7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="553">
@@ -15749,16 +15815,16 @@
       </c>
       <c r="C553" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E553" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="554">
@@ -15774,16 +15840,16 @@
       </c>
       <c r="C554" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E554" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="555">
@@ -15799,16 +15865,16 @@
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E555" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="556">
@@ -15824,16 +15890,16 @@
       </c>
       <c r="C556" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E556" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="557">
@@ -15849,16 +15915,16 @@
       </c>
       <c r="C557" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E557" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="558">
@@ -15874,16 +15940,16 @@
       </c>
       <c r="C558" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E558" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="559">
@@ -15899,16 +15965,16 @@
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E559" s="7" t="n">
-        <v>3</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="560">
@@ -15924,16 +15990,16 @@
       </c>
       <c r="C560" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E560" s="7" t="n">
-        <v>2</v>
+        <v>350</v>
       </c>
     </row>
     <row r="561">
@@ -15949,257 +16015,257 @@
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E561" s="7" t="n">
-        <v>2</v>
+        <v>331</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B562" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E562" s="7" t="n">
-        <v>570</v>
+        <v>315</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B563" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C563" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E563" s="7" t="n">
-        <v>188</v>
+        <v>302</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B564" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C564" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E564" s="7" t="n">
-        <v>128</v>
+        <v>272</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B565" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E565" s="7" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B566" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C566" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E566" s="7" t="n">
-        <v>90</v>
+        <v>168</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B567" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C567" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E567" s="7" t="n">
-        <v>81</v>
+        <v>155</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B568" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C568" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D568" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E568" s="7" t="n">
-        <v>81</v>
+        <v>152</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B569" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E569" s="7" t="n">
-        <v>60</v>
+        <v>146</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B570" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C570" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E570" s="7" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B571" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D571" s="5" t="inlineStr">
@@ -16208,231 +16274,1106 @@
         </is>
       </c>
       <c r="E571" s="7" t="n">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C572" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E572" s="7" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E573" s="7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C574" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E574" s="7" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E575" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C576" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E576" s="7" t="n">
-        <v>6</v>
+        <v>285</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E577" s="7" t="n">
-        <v>6</v>
+        <v>282</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>Logo Horizontal</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E578" s="7" t="n">
-        <v>2</v>
+        <v>266</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E579" s="7" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D580" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E580" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B581" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E581" s="7" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B582" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C582" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D582" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B583" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D583" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E583" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B584" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D584" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E584" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B585" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D585" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E585" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B586" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D586" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E586" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B587" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C587" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D587" s="5" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="E587" s="7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B588" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D588" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E588" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B589" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D589" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E589" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B590" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C590" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D590" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E590" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B591" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C591" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D591" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E591" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B592" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C592" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D592" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E592" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B593" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C593" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D593" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E593" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B594" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C594" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D594" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E594" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B595" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C595" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D595" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E595" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B596" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C596" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D596" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E596" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B580" s="4" t="inlineStr">
+      <c r="B597" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C580" s="4" t="inlineStr">
+      <c r="C597" s="4" t="inlineStr">
         <is>
           <t>Landing Alianzas</t>
         </is>
       </c>
-      <c r="D580" s="5" t="inlineStr">
+      <c r="D597" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E597" s="7" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B598" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C598" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D598" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E598" s="7" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B599" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C599" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D599" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E599" s="7" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B600" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C600" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D600" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E600" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B601" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C601" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D601" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E601" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B602" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C602" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D602" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E602" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B603" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C603" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D603" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E603" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B604" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C604" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D604" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E604" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B605" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C605" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D605" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E605" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B606" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C606" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D606" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E606" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B607" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C607" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D607" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E607" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B608" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C608" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D608" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E608" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B609" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C609" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D609" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E609" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B610" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C610" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D610" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E610" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B611" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C611" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D611" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E611" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B612" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C612" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D612" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E612" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B613" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C613" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D613" s="5" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="E613" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B614" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C614" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D614" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E614" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B615" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C615" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D615" s="5" t="inlineStr">
         <is>
           <t>Calendar</t>
         </is>
       </c>
-      <c r="E580" s="7" t="n">
+      <c r="E615" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16447,7 +17388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21281,800 +22222,1200 @@
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D242" s="12" t="n">
-        <v>221</v>
+        <v>155</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="D243" s="12" t="n">
-        <v>206</v>
+        <v>31</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="D244" s="12" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="D245" s="12" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="D246" s="12" t="n">
-        <v>101</v>
+        <v>30</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="D247" s="12" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D248" s="12" t="n">
-        <v>79</v>
+        <v>29</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D249" s="12" t="n">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D250" s="12" t="n">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D251" s="12" t="n">
-        <v>71</v>
+        <v>26</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D252" s="12" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D253" s="12" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D254" s="12" t="n">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D255" s="12" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D256" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>cloudupload</t>
         </is>
       </c>
       <c r="D257" s="12" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>card-selector</t>
         </is>
       </c>
       <c r="D258" s="12" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>[SCTR] Planes cotizador</t>
         </is>
       </c>
       <c r="D259" s="12" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D260" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Bullet Icon</t>
         </is>
       </c>
       <c r="D261" s="12" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D262" s="12" t="n">
-        <v>24</v>
+        <v>221</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>CardProductPromo</t>
         </is>
       </c>
       <c r="D263" s="12" t="n">
-        <v>21</v>
+        <v>206</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D264" s="12" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D265" s="12" t="n">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D266" s="12" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D267" s="12" t="n">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>CardMenúMobile</t>
         </is>
       </c>
       <c r="D268" s="12" t="n">
-        <v>12</v>
+        <v>79</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>CardMenú</t>
         </is>
       </c>
       <c r="D269" s="12" t="n">
-        <v>11</v>
+        <v>77</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>LogosCollab</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D270" s="12" t="n">
-        <v>10</v>
+        <v>74</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>CoberturasIconos</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D271" s="12" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>BotónCategoría</t>
         </is>
       </c>
       <c r="D272" s="12" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D273" s="12" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D274" s="12" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>problema eléctrico</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D275" s="12" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>robo de autopartes</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D276" s="12" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>avión</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D277" s="12" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>generales</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D278" s="12" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>MedicalService</t>
         </is>
       </c>
       <c r="D279" s="12" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>fractura</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D280" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>title_+_badges_download</t>
+        </is>
+      </c>
+      <c r="D281" s="12" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
+      <c r="B282" s="4" t="inlineStr">
         <is>
           <t>Embebidos</t>
         </is>
       </c>
-      <c r="C281" s="4" t="inlineStr">
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D282" s="12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>SecciónDescripción</t>
+        </is>
+      </c>
+      <c r="D283" s="12" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D284" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D285" s="12" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D286" s="12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>SeccionCanales</t>
+        </is>
+      </c>
+      <c r="D287" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>PersonalInjuy</t>
+        </is>
+      </c>
+      <c r="D288" s="12" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D289" s="12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>LogosCollab</t>
+        </is>
+      </c>
+      <c r="D290" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>CoberturasIconos</t>
+        </is>
+      </c>
+      <c r="D291" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D292" s="12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D293" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>title_+_badges_download</t>
+        </is>
+      </c>
+      <c r="D294" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>problema eléctrico</t>
+        </is>
+      </c>
+      <c r="D295" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>robo de autopartes</t>
+        </is>
+      </c>
+      <c r="D296" s="12" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>avión</t>
+        </is>
+      </c>
+      <c r="D297" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>generales</t>
+        </is>
+      </c>
+      <c r="D298" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>download</t>
+        </is>
+      </c>
+      <c r="D299" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>fractura</t>
+        </is>
+      </c>
+      <c r="D300" s="12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
         <is>
           <t>doctor</t>
         </is>
       </c>
-      <c r="D281" s="12" t="n">
+      <c r="D301" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22089,7 +23430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22162,7 +23503,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -22234,7 +23575,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22270,7 +23611,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22306,7 +23647,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22342,7 +23683,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22378,7 +23719,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22414,7 +23755,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22450,7 +23791,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22486,7 +23827,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22522,7 +23863,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22558,7 +23899,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22570,10 +23911,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>2301</v>
+        <v>2286</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3147</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="14">
@@ -22594,7 +23935,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22615,7 +23956,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -22630,57 +23971,93 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3566</v>
+        <v>11371</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>4204</v>
+        <v>12077</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>3566</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>Web Corporativa</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Web Corporativa</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F17" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>11472</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H17" s="6" t="n">
         <v>13594</v>
       </c>
     </row>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-25</t>
+          <t>Quarter: Q2 2026  |  2026-06-26</t>
         </is>
       </c>
     </row>
@@ -757,10 +757,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>14454</v>
+        <v>14386</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7650</v>
+        <v>7654</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -850,20 +850,20 @@
         <v>1</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="G13" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>73%</t>
+        <v>0</v>
+      </c>
+      <c r="H13" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1591,17 +1591,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2396</v>
+        <v>2328</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>30</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>81%</t>
         </is>
       </c>
     </row>
@@ -1690,20 +1690,20 @@
         </is>
       </c>
       <c r="D18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>73%</t>
+        <v>0</v>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E615"/>
+  <dimension ref="A1:E590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9624,7 +9624,7 @@
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>1596</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="306">
@@ -9649,7 +9649,7 @@
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="307">
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308">
@@ -9699,7 +9699,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="309">
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="311">
@@ -9774,7 +9774,7 @@
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312">
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313">
@@ -9824,7 +9824,7 @@
         </is>
       </c>
       <c r="E313" s="7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="314">
@@ -9899,7 +9899,7 @@
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317">
@@ -9945,7 +9945,7 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
@@ -9970,11 +9970,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
@@ -9995,11 +9995,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321">
@@ -11735,21 +11735,21 @@
       </c>
       <c r="B390" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>160</v>
+        <v>597</v>
       </c>
     </row>
     <row r="391">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D391" s="5" t="inlineStr">
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>149</v>
+        <v>331</v>
       </c>
     </row>
     <row r="392">
@@ -11785,21 +11785,21 @@
       </c>
       <c r="B392" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>136</v>
+        <v>327</v>
       </c>
     </row>
     <row r="393">
@@ -11810,21 +11810,21 @@
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>107</v>
+        <v>276</v>
       </c>
     </row>
     <row r="394">
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B394" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D394" s="5" t="inlineStr">
@@ -11849,7 +11849,7 @@
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>77</v>
+        <v>166</v>
       </c>
     </row>
     <row r="395">
@@ -11860,21 +11860,21 @@
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>63</v>
+        <v>151</v>
       </c>
     </row>
     <row r="396">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="B396" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D396" s="5" t="inlineStr">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
     </row>
     <row r="397">
@@ -11910,21 +11910,21 @@
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="398">
@@ -11935,21 +11935,21 @@
       </c>
       <c r="B398" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="399">
@@ -11960,21 +11960,21 @@
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>15</v>
+        <v>56</v>
       </c>
     </row>
     <row r="400">
@@ -11985,21 +11985,21 @@
       </c>
       <c r="B400" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="401">
@@ -12010,21 +12010,21 @@
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="402">
@@ -12035,21 +12035,21 @@
       </c>
       <c r="B402" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="403">
@@ -12060,21 +12060,21 @@
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="404">
@@ -12085,21 +12085,21 @@
       </c>
       <c r="B404" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
     </row>
     <row r="405">
@@ -12110,21 +12110,21 @@
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="406">
@@ -12135,21 +12135,21 @@
       </c>
       <c r="B406" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="407">
@@ -12160,21 +12160,21 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
     </row>
     <row r="408">
@@ -12185,21 +12185,21 @@
       </c>
       <c r="B408" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Infografia</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="409">
@@ -12210,21 +12210,21 @@
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="410">
@@ -12235,21 +12235,21 @@
       </c>
       <c r="B410" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411">
@@ -12260,21 +12260,21 @@
       </c>
       <c r="B411" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412">
@@ -12285,21 +12285,21 @@
       </c>
       <c r="B412" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="413">
@@ -12310,21 +12310,21 @@
       </c>
       <c r="B413" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="414">
@@ -12335,21 +12335,21 @@
       </c>
       <c r="B414" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="415">
@@ -12370,11 +12370,11 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>597</v>
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -12395,11 +12395,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>331</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -12420,11 +12420,11 @@
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>327</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -12445,11 +12445,11 @@
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>276</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -12460,21 +12460,21 @@
       </c>
       <c r="B419" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>166</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="420">
@@ -12485,21 +12485,21 @@
       </c>
       <c r="B420" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>151</v>
+        <v>340</v>
       </c>
     </row>
     <row r="421">
@@ -12510,21 +12510,21 @@
       </c>
       <c r="B421" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>116</v>
+        <v>256</v>
       </c>
     </row>
     <row r="422">
@@ -12535,21 +12535,21 @@
       </c>
       <c r="B422" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>70</v>
+        <v>251</v>
       </c>
     </row>
     <row r="423">
@@ -12560,21 +12560,21 @@
       </c>
       <c r="B423" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
     </row>
     <row r="424">
@@ -12585,21 +12585,21 @@
       </c>
       <c r="B424" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>56</v>
+        <v>149</v>
       </c>
     </row>
     <row r="425">
@@ -12610,21 +12610,21 @@
       </c>
       <c r="B425" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
-        <v>48</v>
+        <v>128</v>
       </c>
     </row>
     <row r="426">
@@ -12635,21 +12635,21 @@
       </c>
       <c r="B426" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
-        <v>48</v>
+        <v>122</v>
       </c>
     </row>
     <row r="427">
@@ -12660,21 +12660,21 @@
       </c>
       <c r="B427" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
     </row>
     <row r="428">
@@ -12685,21 +12685,21 @@
       </c>
       <c r="B428" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
     </row>
     <row r="429">
@@ -12710,21 +12710,21 @@
       </c>
       <c r="B429" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="430">
@@ -12735,21 +12735,21 @@
       </c>
       <c r="B430" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="431">
@@ -12760,21 +12760,21 @@
       </c>
       <c r="B431" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="432">
@@ -12785,21 +12785,21 @@
       </c>
       <c r="B432" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="433">
@@ -12810,21 +12810,21 @@
       </c>
       <c r="B433" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="434">
@@ -12835,21 +12835,21 @@
       </c>
       <c r="B434" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="435">
@@ -12860,21 +12860,21 @@
       </c>
       <c r="B435" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="436">
@@ -12885,17 +12885,17 @@
       </c>
       <c r="B436" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
@@ -12910,21 +12910,21 @@
       </c>
       <c r="B437" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438">
@@ -12935,21 +12935,21 @@
       </c>
       <c r="B438" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="439">
@@ -12960,21 +12960,21 @@
       </c>
       <c r="B439" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="440">
@@ -12985,21 +12985,21 @@
       </c>
       <c r="B440" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="441">
@@ -13010,21 +13010,21 @@
       </c>
       <c r="B441" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="442">
@@ -13035,21 +13035,21 @@
       </c>
       <c r="B442" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="443">
@@ -13060,21 +13060,21 @@
       </c>
       <c r="B443" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="444">
@@ -13095,11 +13095,11 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>1536</v>
+        <v>11</v>
       </c>
     </row>
     <row r="445">
@@ -13120,11 +13120,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>340</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446">
@@ -13145,11 +13145,11 @@
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>256</v>
+        <v>9</v>
       </c>
     </row>
     <row r="447">
@@ -13170,11 +13170,11 @@
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>251</v>
+        <v>6</v>
       </c>
     </row>
     <row r="448">
@@ -13185,21 +13185,21 @@
       </c>
       <c r="B448" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>160</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="449">
@@ -13210,21 +13210,21 @@
       </c>
       <c r="B449" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>149</v>
+        <v>618</v>
       </c>
     </row>
     <row r="450">
@@ -13235,21 +13235,21 @@
       </c>
       <c r="B450" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>128</v>
+        <v>440</v>
       </c>
     </row>
     <row r="451">
@@ -13260,21 +13260,21 @@
       </c>
       <c r="B451" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>122</v>
+        <v>375</v>
       </c>
     </row>
     <row r="452">
@@ -13285,21 +13285,21 @@
       </c>
       <c r="B452" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>85</v>
+        <v>192</v>
       </c>
     </row>
     <row r="453">
@@ -13310,21 +13310,21 @@
       </c>
       <c r="B453" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
     </row>
     <row r="454">
@@ -13335,21 +13335,21 @@
       </c>
       <c r="B454" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
     </row>
     <row r="455">
@@ -13360,21 +13360,21 @@
       </c>
       <c r="B455" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
     </row>
     <row r="456">
@@ -13385,21 +13385,21 @@
       </c>
       <c r="B456" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
     </row>
     <row r="457">
@@ -13410,21 +13410,21 @@
       </c>
       <c r="B457" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>39</v>
+        <v>90</v>
       </c>
     </row>
     <row r="458">
@@ -13435,21 +13435,21 @@
       </c>
       <c r="B458" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
     </row>
     <row r="459">
@@ -13460,21 +13460,21 @@
       </c>
       <c r="B459" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>28</v>
+        <v>71</v>
       </c>
     </row>
     <row r="460">
@@ -13485,21 +13485,21 @@
       </c>
       <c r="B460" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="461">
@@ -13510,21 +13510,21 @@
       </c>
       <c r="B461" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="462">
@@ -13535,21 +13535,21 @@
       </c>
       <c r="B462" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="463">
@@ -13560,21 +13560,21 @@
       </c>
       <c r="B463" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
     </row>
     <row r="464">
@@ -13585,21 +13585,21 @@
       </c>
       <c r="B464" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
     </row>
     <row r="465">
@@ -13610,21 +13610,21 @@
       </c>
       <c r="B465" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
     </row>
     <row r="466">
@@ -13635,21 +13635,21 @@
       </c>
       <c r="B466" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="467">
@@ -13660,21 +13660,21 @@
       </c>
       <c r="B467" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="468">
@@ -13685,21 +13685,21 @@
       </c>
       <c r="B468" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="469">
@@ -13710,21 +13710,21 @@
       </c>
       <c r="B469" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="470">
@@ -13735,21 +13735,21 @@
       </c>
       <c r="B470" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="471">
@@ -13760,21 +13760,21 @@
       </c>
       <c r="B471" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="472">
@@ -13785,21 +13785,21 @@
       </c>
       <c r="B472" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="473">
@@ -13820,11 +13820,11 @@
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>1152</v>
+        <v>12</v>
       </c>
     </row>
     <row r="474">
@@ -13845,11 +13845,11 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>618</v>
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -13870,11 +13870,11 @@
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>440</v>
+        <v>6</v>
       </c>
     </row>
     <row r="476">
@@ -13895,11 +13895,11 @@
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E476" s="7" t="n">
-        <v>375</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477">
@@ -13910,21 +13910,21 @@
       </c>
       <c r="B477" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E477" s="7" t="n">
-        <v>192</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="478">
@@ -13935,21 +13935,21 @@
       </c>
       <c r="B478" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E478" s="7" t="n">
-        <v>120</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="479">
@@ -13960,21 +13960,21 @@
       </c>
       <c r="B479" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E479" s="7" t="n">
-        <v>104</v>
+        <v>670</v>
       </c>
     </row>
     <row r="480">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="B480" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D480" s="5" t="inlineStr">
@@ -13999,7 +13999,7 @@
         </is>
       </c>
       <c r="E480" s="7" t="n">
-        <v>96</v>
+        <v>536</v>
       </c>
     </row>
     <row r="481">
@@ -14010,21 +14010,21 @@
       </c>
       <c r="B481" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E481" s="7" t="n">
-        <v>93</v>
+        <v>409</v>
       </c>
     </row>
     <row r="482">
@@ -14035,21 +14035,21 @@
       </c>
       <c r="B482" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E482" s="7" t="n">
-        <v>90</v>
+        <v>268</v>
       </c>
     </row>
     <row r="483">
@@ -14060,21 +14060,21 @@
       </c>
       <c r="B483" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E483" s="7" t="n">
-        <v>80</v>
+        <v>171</v>
       </c>
     </row>
     <row r="484">
@@ -14085,21 +14085,21 @@
       </c>
       <c r="B484" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E484" s="7" t="n">
-        <v>71</v>
+        <v>155</v>
       </c>
     </row>
     <row r="485">
@@ -14110,21 +14110,21 @@
       </c>
       <c r="B485" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E485" s="7" t="n">
-        <v>68</v>
+        <v>151</v>
       </c>
     </row>
     <row r="486">
@@ -14135,21 +14135,21 @@
       </c>
       <c r="B486" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E486" s="7" t="n">
-        <v>57</v>
+        <v>150</v>
       </c>
     </row>
     <row r="487">
@@ -14160,21 +14160,21 @@
       </c>
       <c r="B487" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E487" s="7" t="n">
-        <v>57</v>
+        <v>149</v>
       </c>
     </row>
     <row r="488">
@@ -14185,21 +14185,21 @@
       </c>
       <c r="B488" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E488" s="7" t="n">
-        <v>48</v>
+        <v>134</v>
       </c>
     </row>
     <row r="489">
@@ -14210,21 +14210,21 @@
       </c>
       <c r="B489" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E489" s="7" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
     </row>
     <row r="490">
@@ -14235,12 +14235,12 @@
       </c>
       <c r="B490" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D490" s="5" t="inlineStr">
@@ -14249,7 +14249,7 @@
         </is>
       </c>
       <c r="E490" s="7" t="n">
-        <v>34</v>
+        <v>90</v>
       </c>
     </row>
     <row r="491">
@@ -14260,12 +14260,12 @@
       </c>
       <c r="B491" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D491" s="5" t="inlineStr">
@@ -14274,7 +14274,7 @@
         </is>
       </c>
       <c r="E491" s="7" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="492">
@@ -14285,21 +14285,21 @@
       </c>
       <c r="B492" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E492" s="7" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
     </row>
     <row r="493">
@@ -14310,21 +14310,21 @@
       </c>
       <c r="B493" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E493" s="7" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
     </row>
     <row r="494">
@@ -14335,21 +14335,21 @@
       </c>
       <c r="B494" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E494" s="7" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="495">
@@ -14360,21 +14360,21 @@
       </c>
       <c r="B495" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E495" s="7" t="n">
-        <v>17</v>
+        <v>67</v>
       </c>
     </row>
     <row r="496">
@@ -14385,21 +14385,21 @@
       </c>
       <c r="B496" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E496" s="7" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="497">
@@ -14410,21 +14410,21 @@
       </c>
       <c r="B497" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E497" s="7" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
     </row>
     <row r="498">
@@ -14435,21 +14435,21 @@
       </c>
       <c r="B498" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E498" s="7" t="n">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="499">
@@ -14460,21 +14460,21 @@
       </c>
       <c r="B499" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E499" s="7" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="500">
@@ -14485,21 +14485,21 @@
       </c>
       <c r="B500" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E500" s="7" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="501">
@@ -14510,21 +14510,21 @@
       </c>
       <c r="B501" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E501" s="7" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="502">
@@ -14545,11 +14545,11 @@
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>6432</v>
+        <v>35</v>
       </c>
     </row>
     <row r="503">
@@ -14570,11 +14570,11 @@
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>1072</v>
+        <v>33</v>
       </c>
     </row>
     <row r="504">
@@ -14595,11 +14595,11 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>670</v>
+        <v>30</v>
       </c>
     </row>
     <row r="505">
@@ -14620,11 +14620,11 @@
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>536</v>
+        <v>27</v>
       </c>
     </row>
     <row r="506">
@@ -14645,11 +14645,11 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>409</v>
+        <v>25</v>
       </c>
     </row>
     <row r="507">
@@ -14670,11 +14670,11 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>268</v>
+        <v>20</v>
       </c>
     </row>
     <row r="508">
@@ -14695,11 +14695,11 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>171</v>
+        <v>10</v>
       </c>
     </row>
     <row r="509">
@@ -14720,11 +14720,11 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>155</v>
+        <v>8</v>
       </c>
     </row>
     <row r="510">
@@ -14745,11 +14745,11 @@
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>151</v>
+        <v>6</v>
       </c>
     </row>
     <row r="511">
@@ -14770,636 +14770,636 @@
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>150</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B512" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C512" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>149</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B513" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C513" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>134</v>
+        <v>959</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B514" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C514" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>101</v>
+        <v>870</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B515" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C515" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>90</v>
+        <v>699</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B516" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C516" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>81</v>
+        <v>506</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B517" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C517" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>80</v>
+        <v>444</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B518" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C518" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>75</v>
+        <v>230</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B519" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C519" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>67</v>
+        <v>165</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B520" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C520" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B521" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C521" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B522" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C522" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>65</v>
+        <v>91</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B523" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C523" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B524" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C524" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B525" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C525" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B526" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C526" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B527" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C527" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B528" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C528" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C530" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C532" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C534" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>8</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>6</v>
+        <v>350</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C536" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>2</v>
+        <v>331</v>
       </c>
     </row>
     <row r="537">
@@ -15415,16 +15415,16 @@
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>1045</v>
+        <v>315</v>
       </c>
     </row>
     <row r="538">
@@ -15440,16 +15440,16 @@
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>959</v>
+        <v>302</v>
       </c>
     </row>
     <row r="539">
@@ -15465,16 +15465,16 @@
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
-        <v>870</v>
+        <v>272</v>
       </c>
     </row>
     <row r="540">
@@ -15490,16 +15490,16 @@
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>699</v>
+        <v>200</v>
       </c>
     </row>
     <row r="541">
@@ -15515,16 +15515,16 @@
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>506</v>
+        <v>168</v>
       </c>
     </row>
     <row r="542">
@@ -15540,16 +15540,16 @@
       </c>
       <c r="C542" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>444</v>
+        <v>155</v>
       </c>
     </row>
     <row r="543">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
@@ -15574,7 +15574,7 @@
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>230</v>
+        <v>152</v>
       </c>
     </row>
     <row r="544">
@@ -15590,16 +15590,16 @@
       </c>
       <c r="C544" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>165</v>
+        <v>146</v>
       </c>
     </row>
     <row r="545">
@@ -15615,16 +15615,16 @@
       </c>
       <c r="C545" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
     </row>
     <row r="546">
@@ -15640,16 +15640,16 @@
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
     </row>
     <row r="547">
@@ -15665,16 +15665,16 @@
       </c>
       <c r="C547" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D547" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E547" s="7" t="n">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="548">
@@ -15690,16 +15690,16 @@
       </c>
       <c r="C548" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D548" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E548" s="7" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
     </row>
     <row r="549">
@@ -15715,16 +15715,16 @@
       </c>
       <c r="C549" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D549" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E549" s="7" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="550">
@@ -15740,16 +15740,16 @@
       </c>
       <c r="C550" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D550" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E550" s="7" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="551">
@@ -15765,16 +15765,16 @@
       </c>
       <c r="C551" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D551" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E551" s="7" t="n">
-        <v>22</v>
+        <v>285</v>
       </c>
     </row>
     <row r="552">
@@ -15790,16 +15790,16 @@
       </c>
       <c r="C552" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D552" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E552" s="7" t="n">
-        <v>18</v>
+        <v>282</v>
       </c>
     </row>
     <row r="553">
@@ -15815,16 +15815,16 @@
       </c>
       <c r="C553" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D553" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E553" s="7" t="n">
-        <v>11</v>
+        <v>266</v>
       </c>
     </row>
     <row r="554">
@@ -15840,16 +15840,16 @@
       </c>
       <c r="C554" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D554" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E554" s="7" t="n">
-        <v>11</v>
+        <v>132</v>
       </c>
     </row>
     <row r="555">
@@ -15865,16 +15865,16 @@
       </c>
       <c r="C555" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D555" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E555" s="7" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
     </row>
     <row r="556">
@@ -15890,16 +15890,16 @@
       </c>
       <c r="C556" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D556" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E556" s="7" t="n">
-        <v>9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="557">
@@ -15915,16 +15915,16 @@
       </c>
       <c r="C557" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D557" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E557" s="7" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="558">
@@ -15940,16 +15940,16 @@
       </c>
       <c r="C558" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D558" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E558" s="7" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
     </row>
     <row r="559">
@@ -15965,16 +15965,16 @@
       </c>
       <c r="C559" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D559" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E559" s="7" t="n">
-        <v>1995</v>
+        <v>24</v>
       </c>
     </row>
     <row r="560">
@@ -15990,16 +15990,16 @@
       </c>
       <c r="C560" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D560" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E560" s="7" t="n">
-        <v>350</v>
+        <v>19</v>
       </c>
     </row>
     <row r="561">
@@ -16015,16 +16015,16 @@
       </c>
       <c r="C561" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D561" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E561" s="7" t="n">
-        <v>331</v>
+        <v>19</v>
       </c>
     </row>
     <row r="562">
@@ -16040,16 +16040,16 @@
       </c>
       <c r="C562" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D562" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E562" s="7" t="n">
-        <v>315</v>
+        <v>14</v>
       </c>
     </row>
     <row r="563">
@@ -16065,16 +16065,16 @@
       </c>
       <c r="C563" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D563" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E563" s="7" t="n">
-        <v>302</v>
+        <v>10</v>
       </c>
     </row>
     <row r="564">
@@ -16090,16 +16090,16 @@
       </c>
       <c r="C564" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D564" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E564" s="7" t="n">
-        <v>272</v>
+        <v>9</v>
       </c>
     </row>
     <row r="565">
@@ -16115,16 +16115,16 @@
       </c>
       <c r="C565" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D565" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E565" s="7" t="n">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="566">
@@ -16140,16 +16140,16 @@
       </c>
       <c r="C566" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D566" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E566" s="7" t="n">
-        <v>168</v>
+        <v>5</v>
       </c>
     </row>
     <row r="567">
@@ -16165,16 +16165,16 @@
       </c>
       <c r="C567" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D567" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E567" s="7" t="n">
-        <v>155</v>
+        <v>4</v>
       </c>
     </row>
     <row r="568">
@@ -16190,16 +16190,16 @@
       </c>
       <c r="C568" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D568" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E568" s="7" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
     </row>
     <row r="569">
@@ -16215,16 +16215,16 @@
       </c>
       <c r="C569" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D569" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E569" s="7" t="n">
-        <v>146</v>
+        <v>3</v>
       </c>
     </row>
     <row r="570">
@@ -16240,16 +16240,16 @@
       </c>
       <c r="C570" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D570" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E570" s="7" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="571">
@@ -16265,282 +16265,282 @@
       </c>
       <c r="C571" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Productos Líneas Personales</t>
         </is>
       </c>
       <c r="D571" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E571" s="7" t="n">
-        <v>63</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B572" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C572" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D572" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E572" s="7" t="n">
-        <v>40</v>
+        <v>570</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B573" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C573" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D573" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E573" s="7" t="n">
-        <v>21</v>
+        <v>188</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B574" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C574" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D574" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E574" s="7" t="n">
-        <v>21</v>
+        <v>128</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B575" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C575" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D575" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E575" s="7" t="n">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B576" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C576" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D576" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E576" s="7" t="n">
-        <v>285</v>
+        <v>90</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B577" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C577" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D577" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E577" s="7" t="n">
-        <v>282</v>
+        <v>81</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B578" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C578" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D578" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E578" s="7" t="n">
-        <v>266</v>
+        <v>81</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B579" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C579" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D579" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E579" s="7" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B580" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C580" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D580" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E580" s="7" t="n">
-        <v>132</v>
+        <v>48</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B581" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C581" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D581" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E581" s="7" t="n">
-        <v>107</v>
+        <v>18</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B582" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C582" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D582" s="5" t="inlineStr">
@@ -16549,831 +16549,206 @@
         </is>
       </c>
       <c r="E582" s="7" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B583" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C583" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D583" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E583" s="7" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B584" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C584" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D584" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E584" s="7" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B585" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C585" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D585" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E585" s="7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B586" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C586" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D586" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E586" s="7" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B587" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C587" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D587" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E587" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B588" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C588" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D588" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Logo Horizontal</t>
         </is>
       </c>
       <c r="E588" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B589" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C589" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D589" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E589" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B590" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C590" s="4" t="inlineStr">
         <is>
-          <t>Productos Líneas Personales</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D590" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E590" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B591" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C591" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D591" s="5" t="inlineStr">
-        <is>
-          <t>Breadcrumb</t>
-        </is>
-      </c>
-      <c r="E591" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B592" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D592" s="5" t="inlineStr">
-        <is>
-          <t>Status Control</t>
-        </is>
-      </c>
-      <c r="E592" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B593" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C593" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D593" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E593" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B594" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C594" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D594" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E594" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B595" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C595" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D595" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E595" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B596" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C596" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D596" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E596" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B597" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C597" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D597" s="5" t="inlineStr">
-        <is>
-          <t>type_option</t>
-        </is>
-      </c>
-      <c r="E597" s="7" t="n">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B598" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C598" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D598" s="5" t="inlineStr">
-        <is>
-          <t>Átomo</t>
-        </is>
-      </c>
-      <c r="E598" s="7" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B599" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C599" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D599" s="5" t="inlineStr">
-        <is>
-          <t>Accordion</t>
-        </is>
-      </c>
-      <c r="E599" s="7" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B600" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C600" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D600" s="5" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="E600" s="7" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B601" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C601" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D601" s="5" t="inlineStr">
-        <is>
-          <t>section_footer</t>
-        </is>
-      </c>
-      <c r="E601" s="7" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B602" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C602" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D602" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="E602" s="7" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B603" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C603" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D603" s="5" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E603" s="7" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B604" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C604" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D604" s="5" t="inlineStr">
-        <is>
-          <t>src_option_redes</t>
-        </is>
-      </c>
-      <c r="E604" s="7" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B605" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C605" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D605" s="5" t="inlineStr">
-        <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="E605" s="7" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B606" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C606" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D606" s="5" t="inlineStr">
-        <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="E606" s="7" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B607" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C607" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D607" s="5" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="E607" s="7" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B608" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C608" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D608" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E608" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B609" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C609" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D609" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E609" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B610" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C610" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D610" s="5" t="inlineStr">
-        <is>
-          <t>Breadcrumb</t>
-        </is>
-      </c>
-      <c r="E610" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B611" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C611" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D611" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E611" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B612" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C612" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D612" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E612" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B613" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C613" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D613" s="5" t="inlineStr">
-        <is>
-          <t>Logo Horizontal</t>
-        </is>
-      </c>
-      <c r="E613" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B614" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C614" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D614" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E614" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B615" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C615" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D615" s="5" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="E615" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17388,7 +16763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D301"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -19496,7 +18871,7 @@
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="106">
@@ -19516,7 +18891,7 @@
         </is>
       </c>
       <c r="D106" s="12" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="107">
@@ -19596,7 +18971,7 @@
         </is>
       </c>
       <c r="D110" s="12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="111">
@@ -19616,7 +18991,7 @@
         </is>
       </c>
       <c r="D111" s="12" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112">
@@ -19636,7 +19011,7 @@
         </is>
       </c>
       <c r="D112" s="12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="113">
@@ -19656,7 +19031,7 @@
         </is>
       </c>
       <c r="D113" s="12" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114">
@@ -19672,11 +19047,11 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>create account</t>
+          <t>DirectionUp</t>
         </is>
       </c>
       <c r="D114" s="12" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115">
@@ -19692,7 +19067,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>DirectionUp</t>
+          <t>create account</t>
         </is>
       </c>
       <c r="D115" s="12" t="n">
@@ -19712,11 +19087,11 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D116" s="12" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="117">
@@ -19732,11 +19107,11 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>ArrowLeft</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D117" s="12" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118">
@@ -19752,11 +19127,11 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D118" s="12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119">
@@ -19776,7 +19151,7 @@
         </is>
       </c>
       <c r="D119" s="12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="120">
@@ -20627,16 +20002,16 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Spinner</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D162" s="12" t="n">
-        <v>29</v>
+        <v>109</v>
       </c>
     </row>
     <row r="163">
@@ -20647,16 +20022,16 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>02</t>
         </is>
       </c>
       <c r="D163" s="12" t="n">
-        <v>24</v>
+        <v>107</v>
       </c>
     </row>
     <row r="164">
@@ -20667,16 +20042,16 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Caja formulario complex L M</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D164" s="12" t="n">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="165">
@@ -20687,16 +20062,16 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Contenido desktop</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D165" s="12" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="166">
@@ -20707,16 +20082,16 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Formulario L M complex</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D166" s="12" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
     </row>
     <row r="167">
@@ -20727,16 +20102,16 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Banner mobile</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D167" s="12" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168">
@@ -20747,16 +20122,16 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Smile</t>
         </is>
       </c>
       <c r="D168" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="169">
@@ -20767,16 +20142,16 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Contenido mobile</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D169" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
@@ -20787,16 +20162,16 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D170" s="12" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="171">
@@ -20807,16 +20182,16 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>CajaFormulario</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D171" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="172">
@@ -20827,16 +20202,16 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Carousel</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D172" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
@@ -20847,16 +20222,16 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 1</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D173" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174">
@@ -20867,16 +20242,16 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 3</t>
+          <t>Step 03</t>
         </is>
       </c>
       <c r="D174" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="175">
@@ -20887,16 +20262,16 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 4</t>
+          <t>choque</t>
         </is>
       </c>
       <c r="D175" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="176">
@@ -20907,16 +20282,16 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 5</t>
+          <t>Espejos</t>
         </is>
       </c>
       <c r="D176" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="177">
@@ -20927,16 +20302,16 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Card_Mobile_funciona 6</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D177" s="12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="178">
@@ -20947,16 +20322,16 @@
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Emergencias</t>
+          <t>Background</t>
         </is>
       </c>
       <c r="D178" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="179">
@@ -20967,16 +20342,16 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D179" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="180">
@@ -20987,16 +20362,16 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D180" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181">
@@ -21007,16 +20382,16 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Auto Efectivo</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>BtnAyuda</t>
         </is>
       </c>
       <c r="D181" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="182">
@@ -21027,16 +20402,16 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>celda</t>
         </is>
       </c>
       <c r="D182" s="12" t="n">
-        <v>109</v>
+        <v>312</v>
       </c>
     </row>
     <row r="183">
@@ -21047,16 +20422,16 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>Component 120</t>
         </is>
       </c>
       <c r="D183" s="12" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
     </row>
     <row r="184">
@@ -21067,16 +20442,16 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>directionLeft</t>
         </is>
       </c>
       <c r="D184" s="12" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
     </row>
     <row r="185">
@@ -21087,16 +20462,16 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D185" s="12" t="n">
-        <v>72</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186">
@@ -21107,16 +20482,16 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>DirectionDown</t>
         </is>
       </c>
       <c r="D186" s="12" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="187">
@@ -21127,16 +20502,16 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D187" s="12" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="188">
@@ -21147,16 +20522,16 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Smile</t>
+          <t>Step 01</t>
         </is>
       </c>
       <c r="D188" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="189">
@@ -21167,16 +20542,16 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Step 02</t>
         </is>
       </c>
       <c r="D189" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190">
@@ -21187,16 +20562,16 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D190" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191">
@@ -21207,16 +20582,16 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D191" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192">
@@ -21227,16 +20602,16 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D192" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193">
@@ -21247,16 +20622,16 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>iaSpark</t>
         </is>
       </c>
       <c r="D193" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194">
@@ -21267,16 +20642,16 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Step 03</t>
+          <t>DirectionRight</t>
         </is>
       </c>
       <c r="D194" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="195">
@@ -21287,16 +20662,16 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>choque</t>
+          <t>Viajeros</t>
         </is>
       </c>
       <c r="D195" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196">
@@ -21307,16 +20682,16 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Espejos</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D196" s="12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
@@ -21327,16 +20702,16 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="D197" s="12" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198">
@@ -21347,16 +20722,16 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Background</t>
+          <t>Viajeros Mobile</t>
         </is>
       </c>
       <c r="D198" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199">
@@ -21367,16 +20742,16 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D199" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200">
@@ -21387,16 +20762,16 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Pasajeros</t>
         </is>
       </c>
       <c r="D200" s="12" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201">
@@ -21407,16 +20782,16 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>BtnAyuda</t>
+          <t>Spinner mesagge</t>
         </is>
       </c>
       <c r="D201" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -21427,16 +20802,16 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>celda</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="D202" s="12" t="n">
-        <v>312</v>
+        <v>174</v>
       </c>
     </row>
     <row r="203">
@@ -21447,16 +20822,16 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Component 120</t>
+          <t>01 Info</t>
         </is>
       </c>
       <c r="D203" s="12" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="204">
@@ -21467,16 +20842,16 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
+          <t>ArrowLeft</t>
         </is>
       </c>
       <c r="D204" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="205">
@@ -21487,16 +20862,16 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D205" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="206">
@@ -21507,16 +20882,16 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>DirectionDown</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D206" s="12" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
     </row>
     <row r="207">
@@ -21527,16 +20902,16 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D207" s="12" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="208">
@@ -21547,16 +20922,16 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Step 01</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D208" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="209">
@@ -21567,16 +20942,16 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Step 02</t>
+          <t>A.white</t>
         </is>
       </c>
       <c r="D209" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="210">
@@ -21587,12 +20962,12 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D210" s="12" t="n">
@@ -21607,16 +20982,16 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>A.white</t>
+          <t>Toast</t>
         </is>
       </c>
       <c r="D211" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="212">
@@ -21627,16 +21002,16 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>eye_open</t>
         </is>
       </c>
       <c r="D212" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="213">
@@ -21647,16 +21022,16 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>iaSpark</t>
+          <t>torito</t>
         </is>
       </c>
       <c r="D213" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="214">
@@ -21667,16 +21042,16 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>DirectionRight</t>
+          <t>Tooltip</t>
         </is>
       </c>
       <c r="D214" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215">
@@ -21687,16 +21062,16 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Viajeros</t>
+          <t>send</t>
         </is>
       </c>
       <c r="D215" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="216">
@@ -21707,16 +21082,16 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="D216" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="217">
@@ -21727,16 +21102,16 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>hiking</t>
+          <t>resumen</t>
         </is>
       </c>
       <c r="D217" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="218">
@@ -21747,16 +21122,16 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Viajeros Mobile</t>
+          <t>Botón primario</t>
         </is>
       </c>
       <c r="D218" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219">
@@ -21767,16 +21142,16 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Cancel Icon</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D219" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="220">
@@ -21787,16 +21162,16 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Pasajeros</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D220" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="221">
@@ -21807,16 +21182,16 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Spinner mesagge</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="D221" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222">
@@ -21827,16 +21202,16 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Option</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D222" s="12" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
     </row>
     <row r="223">
@@ -21847,16 +21222,16 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>01 Info</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="D223" s="12" t="n">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224">
@@ -21867,16 +21242,16 @@
       </c>
       <c r="B224" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>ArrowLeft</t>
+          <t>Step 1</t>
         </is>
       </c>
       <c r="D224" s="12" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -21887,16 +21262,16 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>Step 2</t>
         </is>
       </c>
       <c r="D225" s="12" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
@@ -21907,16 +21282,16 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="D226" s="12" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227">
@@ -21927,16 +21302,16 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="D227" s="12" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228">
@@ -21947,16 +21322,16 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D228" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="229">
@@ -21967,16 +21342,16 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>A.white</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D229" s="12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="230">
@@ -21987,16 +21362,16 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Cancel Icon</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D230" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="231">
@@ -22007,16 +21382,16 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Toast</t>
+          <t>Cancel Icon</t>
         </is>
       </c>
       <c r="D231" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="232">
@@ -22027,16 +21402,16 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>eye_open</t>
+          <t>Simple</t>
         </is>
       </c>
       <c r="D232" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233">
@@ -22047,16 +21422,16 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>torito</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D233" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234">
@@ -22067,16 +21442,16 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Tooltip</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D234" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="235">
@@ -22087,16 +21462,16 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>send</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D235" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236">
@@ -22107,16 +21482,16 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D236" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237">
@@ -22127,12 +21502,12 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>resumen</t>
+          <t>cloudupload</t>
         </is>
       </c>
       <c r="D237" s="12" t="n">
@@ -22147,16 +21522,16 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Botón primario</t>
+          <t>card-selector</t>
         </is>
       </c>
       <c r="D238" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239">
@@ -22167,16 +21542,16 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>[SCTR] Planes cotizador</t>
         </is>
       </c>
       <c r="D239" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240">
@@ -22187,16 +21562,16 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D240" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="241">
@@ -22207,1215 +21582,815 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Lock</t>
+          <t>Bullet Icon</t>
         </is>
       </c>
       <c r="D241" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D242" s="12" t="n">
-        <v>155</v>
+        <v>221</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>CardProductPromo</t>
         </is>
       </c>
       <c r="D243" s="12" t="n">
-        <v>31</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Step 1</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D244" s="12" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Step 2</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D245" s="12" t="n">
-        <v>30</v>
+        <v>110</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D246" s="12" t="n">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D247" s="12" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>CardMenúMobile</t>
         </is>
       </c>
       <c r="D248" s="12" t="n">
-        <v>29</v>
+        <v>79</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>CardMenú</t>
         </is>
       </c>
       <c r="D249" s="12" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D250" s="12" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Cancel Icon</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D251" s="12" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>BotónCategoría</t>
         </is>
       </c>
       <c r="D252" s="12" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Cargador circular</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D253" s="12" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D254" s="12" t="n">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D255" s="12" t="n">
-        <v>14</v>
+        <v>54</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D256" s="12" t="n">
-        <v>14</v>
+        <v>48</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>cloudupload</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D257" s="12" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>card-selector</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D258" s="12" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>[SCTR] Planes cotizador</t>
+          <t>MedicalService</t>
         </is>
       </c>
       <c r="D259" s="12" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D260" s="12" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Bullet Icon</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D261" s="12" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D262" s="12" t="n">
-        <v>221</v>
+        <v>24</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>SecciónDescripción</t>
         </is>
       </c>
       <c r="D263" s="12" t="n">
-        <v>206</v>
+        <v>21</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D264" s="12" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D265" s="12" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D266" s="12" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>SeccionCanales</t>
         </is>
       </c>
       <c r="D267" s="12" t="n">
-        <v>83</v>
+        <v>12</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>PersonalInjuy</t>
         </is>
       </c>
       <c r="D268" s="12" t="n">
-        <v>79</v>
+        <v>12</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D269" s="12" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>LogosCollab</t>
         </is>
       </c>
       <c r="D270" s="12" t="n">
-        <v>74</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>CoberturasIconos</t>
         </is>
       </c>
       <c r="D271" s="12" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D272" s="12" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D273" s="12" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D274" s="12" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>problema eléctrico</t>
         </is>
       </c>
       <c r="D275" s="12" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>robo de autopartes</t>
         </is>
       </c>
       <c r="D276" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>avión</t>
         </is>
       </c>
       <c r="D277" s="12" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>generales</t>
         </is>
       </c>
       <c r="D278" s="12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D279" s="12" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>fractura</t>
         </is>
       </c>
       <c r="D280" s="12" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="D281" s="12" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B282" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="D282" s="12" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B283" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C283" s="4" t="inlineStr">
-        <is>
-          <t>SecciónDescripción</t>
-        </is>
-      </c>
-      <c r="D283" s="12" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B284" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C284" s="4" t="inlineStr">
-        <is>
-          <t>Icon</t>
-        </is>
-      </c>
-      <c r="D284" s="12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B285" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C285" s="4" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="D285" s="12" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="286">
-      <c r="A286" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B286" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C286" s="4" t="inlineStr">
-        <is>
-          <t>WithoutShieldHeart</t>
-        </is>
-      </c>
-      <c r="D286" s="12" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B287" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C287" s="4" t="inlineStr">
-        <is>
-          <t>SeccionCanales</t>
-        </is>
-      </c>
-      <c r="D287" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B288" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C288" s="4" t="inlineStr">
-        <is>
-          <t>PersonalInjuy</t>
-        </is>
-      </c>
-      <c r="D288" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B289" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C289" s="4" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D289" s="12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B290" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C290" s="4" t="inlineStr">
-        <is>
-          <t>LogosCollab</t>
-        </is>
-      </c>
-      <c r="D290" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B291" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C291" s="4" t="inlineStr">
-        <is>
-          <t>CoberturasIconos</t>
-        </is>
-      </c>
-      <c r="D291" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B292" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C292" s="4" t="inlineStr">
-        <is>
-          <t>Scroll</t>
-        </is>
-      </c>
-      <c r="D292" s="12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B293" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D293" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B294" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C294" s="4" t="inlineStr">
-        <is>
-          <t>title_+_badges_download</t>
-        </is>
-      </c>
-      <c r="D294" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B295" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C295" s="4" t="inlineStr">
-        <is>
-          <t>problema eléctrico</t>
-        </is>
-      </c>
-      <c r="D295" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B296" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C296" s="4" t="inlineStr">
-        <is>
-          <t>robo de autopartes</t>
-        </is>
-      </c>
-      <c r="D296" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B297" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C297" s="4" t="inlineStr">
-        <is>
-          <t>avión</t>
-        </is>
-      </c>
-      <c r="D297" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B298" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C298" s="4" t="inlineStr">
-        <is>
-          <t>generales</t>
-        </is>
-      </c>
-      <c r="D298" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B299" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C299" s="4" t="inlineStr">
-        <is>
-          <t>download</t>
-        </is>
-      </c>
-      <c r="D299" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B300" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C300" s="4" t="inlineStr">
-        <is>
-          <t>fractura</t>
-        </is>
-      </c>
-      <c r="D300" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B301" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C301" s="4" t="inlineStr">
-        <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="D301" s="12" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23503,22 +22478,22 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>73%</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="F2" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>921</v>
+        <v>0</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -23575,7 +22550,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -23611,7 +22586,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -23647,7 +22622,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -23659,10 +22634,10 @@
         <v>22</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>14454</v>
+        <v>14386</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>22104</v>
+        <v>22040</v>
       </c>
     </row>
     <row r="7">
@@ -23683,7 +22658,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -23719,7 +22694,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -23755,7 +22730,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -23791,7 +22766,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -23827,7 +22802,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -23863,7 +22838,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -23899,7 +22874,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -23935,7 +22910,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -23971,7 +22946,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -24007,7 +22982,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -24043,7 +23018,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -661,17 +661,17 @@
         <v>8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>8343</v>
+        <v>7739</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>845</v>
+        <v>821</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>38</v>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>90%</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
         <v>2</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1308</v>
+        <v>704</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="G8" s="8" t="n">
         <v>20</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>79%</t>
         </is>
       </c>
     </row>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E88" s="7" t="n">
-        <v>576</v>
+        <v>192</v>
       </c>
     </row>
     <row r="89">
@@ -4224,7 +4224,7 @@
         </is>
       </c>
       <c r="E89" s="7" t="n">
-        <v>114</v>
+        <v>102</v>
       </c>
     </row>
     <row r="90">
@@ -4245,11 +4245,11 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91">
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="E91" s="7" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
     </row>
     <row r="92">
@@ -4295,11 +4295,11 @@
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="93">
@@ -4320,11 +4320,11 @@
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E93" s="7" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
@@ -4345,11 +4345,11 @@
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E94" s="7" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95">
@@ -4370,11 +4370,11 @@
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E95" s="7" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
@@ -4395,11 +4395,11 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E96" s="7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="97">
@@ -4420,11 +4420,11 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E97" s="7" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98">
@@ -4445,11 +4445,11 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E98" s="7" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
@@ -4470,11 +4470,11 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E99" s="7" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
@@ -4495,11 +4495,11 @@
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
@@ -4520,11 +4520,11 @@
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E101" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
@@ -4545,11 +4545,11 @@
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -4570,11 +4570,11 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E103" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -4595,11 +4595,11 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E104" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -4620,11 +4620,11 @@
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E105" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
@@ -4645,11 +4645,11 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4670,11 +4670,11 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E107" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
@@ -17707,11 +17707,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>NorthEast</t>
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -17727,11 +17727,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>NorthEast</t>
+          <t>Menú_Desktop</t>
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -17747,11 +17747,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Menú_Desktop</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -17767,11 +17767,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -22735,17 +22735,17 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
         <v>8</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>8343</v>
+        <v>7739</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>9188</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="10">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-26</t>
+          <t>Quarter: Q2 2026  |  2026-06-29</t>
         </is>
       </c>
     </row>
@@ -22478,7 +22478,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -22550,7 +22550,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22586,7 +22586,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22622,7 +22622,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22658,7 +22658,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22694,7 +22694,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22730,7 +22730,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22802,7 +22802,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22838,7 +22838,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -22982,7 +22982,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Por archivo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Familias DS usadas" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Internos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Historial" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Detach rate" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Familias DS usadas" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Internos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Historial" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +86,26 @@
       <color rgb="FFD94F3D"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF212529"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="FF6C757D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF8C8880"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -96,6 +115,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1A7FA8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA7517"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,7 +166,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -510,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -521,6 +553,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -533,7 +566,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-29</t>
+          <t>Quarter: Q2 2026  |  2026-06-30</t>
         </is>
       </c>
     </row>
@@ -578,6 +611,11 @@
           <t>Adopción %</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Detach %</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -610,6 +648,11 @@
           <t>51%</t>
         </is>
       </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -642,6 +685,11 @@
           <t>87%</t>
         </is>
       </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -674,6 +722,11 @@
           <t>90%</t>
         </is>
       </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -706,6 +759,11 @@
           <t>94%</t>
         </is>
       </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -738,6 +796,11 @@
           <t>84%</t>
         </is>
       </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -757,10 +820,10 @@
         <v>22</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>14386</v>
+        <v>14419</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>7654</v>
+        <v>7680</v>
       </c>
       <c r="G10" s="8" t="n">
         <v>36</v>
@@ -770,6 +833,11 @@
           <t>65%</t>
         </is>
       </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -802,6 +870,11 @@
           <t>75%</t>
         </is>
       </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -834,6 +907,11 @@
           <t>73%</t>
         </is>
       </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -866,6 +944,11 @@
           <t>0%</t>
         </is>
       </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -898,6 +981,11 @@
           <t>69%</t>
         </is>
       </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -930,6 +1018,11 @@
           <t>85%</t>
         </is>
       </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -962,6 +1055,11 @@
           <t>85%</t>
         </is>
       </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -981,7 +1079,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>11371</v>
+        <v>11370</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>706</v>
@@ -994,6 +1092,11 @@
           <t>94%</t>
         </is>
       </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1026,6 +1129,11 @@
           <t>84%</t>
         </is>
       </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1058,11 +1166,16 @@
           <t>88%</t>
         </is>
       </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1591,10 +1704,10 @@
         <v>1</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>2328</v>
+        <v>2361</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>545</v>
+        <v>571</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>30</v>
@@ -1829,7 +1942,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>11371</v>
+        <v>11370</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>706</v>
@@ -1985,6 +2098,261 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Detach rate por categoría — Library Analytics API</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Fuente: Figma Library Analytics (Enterprise). Fórmula: detachments / (detachments + insertions) del quarter actual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Detachments</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Insertions</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Total acciones</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Detach %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>MEP</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>17415</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>17437</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>31512</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>31599</v>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>317</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>6526</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>6843</v>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>69191</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>69208</v>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>6637</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>6638</v>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>4334</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4339</v>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>615</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>27625</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>28240</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>19514</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>19541</v>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>10670</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>10704</v>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9649,7 +10017,7 @@
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="307">
@@ -9699,7 +10067,7 @@
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="309">
@@ -9799,7 +10167,7 @@
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="313">
@@ -14549,7 +14917,7 @@
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="503">
@@ -16757,7 +17125,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16810,7 +17178,7 @@
           <t>menú</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="15" t="n">
         <v>1761</v>
       </c>
     </row>
@@ -16830,7 +17198,7 @@
           <t>card_accion</t>
         </is>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="15" t="n">
         <v>217</v>
       </c>
     </row>
@@ -16850,7 +17218,7 @@
           <t>card_atajo_home</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="15" t="n">
         <v>212</v>
       </c>
     </row>
@@ -16870,7 +17238,7 @@
           <t>documento simple</t>
         </is>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="15" t="n">
         <v>100</v>
       </c>
     </row>
@@ -16890,7 +17258,7 @@
           <t>Seguros card</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="15" t="n">
         <v>45</v>
       </c>
     </row>
@@ -16910,7 +17278,7 @@
           <t>Card_ beneficios</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="15" t="n">
         <v>37</v>
       </c>
     </row>
@@ -16930,7 +17298,7 @@
           <t>beneficios vehiculares</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="15" t="n">
         <v>36</v>
       </c>
     </row>
@@ -16950,7 +17318,7 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="15" t="n">
         <v>34</v>
       </c>
     </row>
@@ -16970,7 +17338,7 @@
           <t>carro</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="15" t="n">
         <v>26</v>
       </c>
     </row>
@@ -16990,7 +17358,7 @@
           <t>buscar clínicas</t>
         </is>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="15" t="n">
         <v>26</v>
       </c>
     </row>
@@ -17010,7 +17378,7 @@
           <t>hogar</t>
         </is>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="15" t="n">
         <v>26</v>
       </c>
     </row>
@@ -17030,7 +17398,7 @@
           <t>drag</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D13" s="15" t="n">
         <v>26</v>
       </c>
     </row>
@@ -17050,7 +17418,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D14" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -17070,7 +17438,7 @@
           <t>error duda</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17090,7 +17458,7 @@
           <t>logo beneficios</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D16" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17110,7 +17478,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -17130,7 +17498,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="D18" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -17150,7 +17518,7 @@
           <t>Bottom Navigation</t>
         </is>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17170,7 +17538,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -17190,7 +17558,7 @@
           <t>card_atajo</t>
         </is>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17210,7 +17578,7 @@
           <t>Suggested search (Deprecated)</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="15" t="n">
         <v>65</v>
       </c>
     </row>
@@ -17230,7 +17598,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="D23" s="15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -17250,7 +17618,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D24" s="15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -17270,7 +17638,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="D25" s="15" t="n">
         <v>59</v>
       </c>
     </row>
@@ -17290,7 +17658,7 @@
           <t>celda L</t>
         </is>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="D26" s="15" t="n">
         <v>49</v>
       </c>
     </row>
@@ -17310,7 +17678,7 @@
           <t>Step 04</t>
         </is>
       </c>
-      <c r="D27" s="12" t="n">
+      <c r="D27" s="15" t="n">
         <v>39</v>
       </c>
     </row>
@@ -17330,7 +17698,7 @@
           <t>Step 05</t>
         </is>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="15" t="n">
         <v>39</v>
       </c>
     </row>
@@ -17350,7 +17718,7 @@
           <t>Upload icon</t>
         </is>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="D29" s="15" t="n">
         <v>31</v>
       </c>
     </row>
@@ -17370,7 +17738,7 @@
           <t>Userflow</t>
         </is>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="D30" s="15" t="n">
         <v>27</v>
       </c>
     </row>
@@ -17390,7 +17758,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D31" s="12" t="n">
+      <c r="D31" s="15" t="n">
         <v>21</v>
       </c>
     </row>
@@ -17410,7 +17778,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="D32" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17430,7 +17798,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D33" s="12" t="n">
+      <c r="D33" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17450,7 +17818,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D34" s="12" t="n">
+      <c r="D34" s="15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -17470,7 +17838,7 @@
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="D35" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -17490,7 +17858,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D36" s="12" t="n">
+      <c r="D36" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17510,7 +17878,7 @@
           <t>audifonos</t>
         </is>
       </c>
-      <c r="D37" s="12" t="n">
+      <c r="D37" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -17530,7 +17898,7 @@
           <t>Container Drag and Drop</t>
         </is>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -17550,7 +17918,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="D39" s="15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17570,7 +17938,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D40" s="12" t="n">
+      <c r="D40" s="15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17590,7 +17958,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D41" s="12" t="n">
+      <c r="D41" s="15" t="n">
         <v>5</v>
       </c>
     </row>
@@ -17610,7 +17978,7 @@
           <t>HealthAndSafe</t>
         </is>
       </c>
-      <c r="D42" s="12" t="n">
+      <c r="D42" s="15" t="n">
         <v>96</v>
       </c>
     </row>
@@ -17630,7 +17998,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="D43" s="15" t="n">
         <v>54</v>
       </c>
     </row>
@@ -17650,7 +18018,7 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="D44" s="12" t="n">
+      <c r="D44" s="15" t="n">
         <v>44</v>
       </c>
     </row>
@@ -17670,7 +18038,7 @@
           <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="D45" s="15" t="n">
         <v>35</v>
       </c>
     </row>
@@ -17690,7 +18058,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="15" t="n">
         <v>34</v>
       </c>
     </row>
@@ -17710,7 +18078,7 @@
           <t>NorthEast</t>
         </is>
       </c>
-      <c r="D47" s="12" t="n">
+      <c r="D47" s="15" t="n">
         <v>32</v>
       </c>
     </row>
@@ -17730,7 +18098,7 @@
           <t>Menú_Desktop</t>
         </is>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="D48" s="15" t="n">
         <v>31</v>
       </c>
     </row>
@@ -17750,7 +18118,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D49" s="12" t="n">
+      <c r="D49" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -17770,7 +18138,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="D50" s="15" t="n">
         <v>29</v>
       </c>
     </row>
@@ -17790,7 +18158,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D51" s="12" t="n">
+      <c r="D51" s="15" t="n">
         <v>28</v>
       </c>
     </row>
@@ -17810,7 +18178,7 @@
           <t>beneficios reconocerte</t>
         </is>
       </c>
-      <c r="D52" s="12" t="n">
+      <c r="D52" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -17830,7 +18198,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D53" s="12" t="n">
+      <c r="D53" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -17850,7 +18218,7 @@
           <t>filter</t>
         </is>
       </c>
-      <c r="D54" s="12" t="n">
+      <c r="D54" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -17870,7 +18238,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D55" s="12" t="n">
+      <c r="D55" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -17890,7 +18258,7 @@
           <t>Feed</t>
         </is>
       </c>
-      <c r="D56" s="12" t="n">
+      <c r="D56" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -17910,7 +18278,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D57" s="12" t="n">
+      <c r="D57" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17930,7 +18298,7 @@
           <t>trofeo</t>
         </is>
       </c>
-      <c r="D58" s="12" t="n">
+      <c r="D58" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17950,7 +18318,7 @@
           <t>vida ley</t>
         </is>
       </c>
-      <c r="D59" s="12" t="n">
+      <c r="D59" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17970,7 +18338,7 @@
           <t>tratamiento</t>
         </is>
       </c>
-      <c r="D60" s="12" t="n">
+      <c r="D60" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17990,7 +18358,7 @@
           <t>Right Label</t>
         </is>
       </c>
-      <c r="D61" s="12" t="n">
+      <c r="D61" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -18010,7 +18378,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D62" s="12" t="n">
+      <c r="D62" s="15" t="n">
         <v>2366</v>
       </c>
     </row>
@@ -18030,7 +18398,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D63" s="12" t="n">
+      <c r="D63" s="15" t="n">
         <v>699</v>
       </c>
     </row>
@@ -18050,7 +18418,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D64" s="12" t="n">
+      <c r="D64" s="15" t="n">
         <v>550</v>
       </c>
     </row>
@@ -18070,7 +18438,7 @@
           <t>Home_Header</t>
         </is>
       </c>
-      <c r="D65" s="12" t="n">
+      <c r="D65" s="15" t="n">
         <v>512</v>
       </c>
     </row>
@@ -18090,7 +18458,7 @@
           <t>Action 1</t>
         </is>
       </c>
-      <c r="D66" s="12" t="n">
+      <c r="D66" s="15" t="n">
         <v>496</v>
       </c>
     </row>
@@ -18110,7 +18478,7 @@
           <t>Action 2</t>
         </is>
       </c>
-      <c r="D67" s="12" t="n">
+      <c r="D67" s="15" t="n">
         <v>496</v>
       </c>
     </row>
@@ -18130,7 +18498,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D68" s="12" t="n">
+      <c r="D68" s="15" t="n">
         <v>482</v>
       </c>
     </row>
@@ -18150,7 +18518,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D69" s="12" t="n">
+      <c r="D69" s="15" t="n">
         <v>433</v>
       </c>
     </row>
@@ -18170,7 +18538,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D70" s="12" t="n">
+      <c r="D70" s="15" t="n">
         <v>398</v>
       </c>
     </row>
@@ -18190,7 +18558,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D71" s="12" t="n">
+      <c r="D71" s="15" t="n">
         <v>398</v>
       </c>
     </row>
@@ -18210,7 +18578,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D72" s="12" t="n">
+      <c r="D72" s="15" t="n">
         <v>390</v>
       </c>
     </row>
@@ -18230,7 +18598,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D73" s="12" t="n">
+      <c r="D73" s="15" t="n">
         <v>382</v>
       </c>
     </row>
@@ -18250,7 +18618,7 @@
           <t>save</t>
         </is>
       </c>
-      <c r="D74" s="12" t="n">
+      <c r="D74" s="15" t="n">
         <v>328</v>
       </c>
     </row>
@@ -18270,7 +18638,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D75" s="12" t="n">
+      <c r="D75" s="15" t="n">
         <v>324</v>
       </c>
     </row>
@@ -18290,7 +18658,7 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D76" s="12" t="n">
+      <c r="D76" s="15" t="n">
         <v>312</v>
       </c>
     </row>
@@ -18310,7 +18678,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D77" s="12" t="n">
+      <c r="D77" s="15" t="n">
         <v>295</v>
       </c>
     </row>
@@ -18330,7 +18698,7 @@
           <t>medios de pago</t>
         </is>
       </c>
-      <c r="D78" s="12" t="n">
+      <c r="D78" s="15" t="n">
         <v>280</v>
       </c>
     </row>
@@ -18350,7 +18718,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D79" s="12" t="n">
+      <c r="D79" s="15" t="n">
         <v>116</v>
       </c>
     </row>
@@ -18370,7 +18738,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D80" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -18390,7 +18758,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D81" s="12" t="n">
+      <c r="D81" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -18410,7 +18778,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D82" s="12" t="n">
+      <c r="D82" s="15" t="n">
         <v>233</v>
       </c>
     </row>
@@ -18430,7 +18798,7 @@
           <t>DirectionRight</t>
         </is>
       </c>
-      <c r="D83" s="12" t="n">
+      <c r="D83" s="15" t="n">
         <v>198</v>
       </c>
     </row>
@@ -18450,7 +18818,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D84" s="12" t="n">
+      <c r="D84" s="15" t="n">
         <v>165</v>
       </c>
     </row>
@@ -18470,7 +18838,7 @@
           <t>Pegar Icon</t>
         </is>
       </c>
-      <c r="D85" s="12" t="n">
+      <c r="D85" s="15" t="n">
         <v>102</v>
       </c>
     </row>
@@ -18490,7 +18858,7 @@
           <t>Component 9</t>
         </is>
       </c>
-      <c r="D86" s="12" t="n">
+      <c r="D86" s="15" t="n">
         <v>90</v>
       </c>
     </row>
@@ -18510,7 +18878,7 @@
           <t>copy</t>
         </is>
       </c>
-      <c r="D87" s="12" t="n">
+      <c r="D87" s="15" t="n">
         <v>57</v>
       </c>
     </row>
@@ -18530,7 +18898,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D88" s="12" t="n">
+      <c r="D88" s="15" t="n">
         <v>37</v>
       </c>
     </row>
@@ -18550,7 +18918,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D89" s="12" t="n">
+      <c r="D89" s="15" t="n">
         <v>32</v>
       </c>
     </row>
@@ -18570,7 +18938,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D90" s="12" t="n">
+      <c r="D90" s="15" t="n">
         <v>29</v>
       </c>
     </row>
@@ -18590,7 +18958,7 @@
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="D91" s="12" t="n">
+      <c r="D91" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -18610,7 +18978,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D92" s="12" t="n">
+      <c r="D92" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -18630,7 +18998,7 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D93" s="12" t="n">
+      <c r="D93" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -18650,7 +19018,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D94" s="12" t="n">
+      <c r="D94" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -18670,7 +19038,7 @@
           <t>soles</t>
         </is>
       </c>
-      <c r="D95" s="12" t="n">
+      <c r="D95" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -18690,7 +19058,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D96" s="12" t="n">
+      <c r="D96" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -18710,7 +19078,7 @@
           <t>24.timer</t>
         </is>
       </c>
-      <c r="D97" s="12" t="n">
+      <c r="D97" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -18730,7 +19098,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D98" s="12" t="n">
+      <c r="D98" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -18750,7 +19118,7 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D99" s="15" t="n">
         <v>19</v>
       </c>
     </row>
@@ -18770,7 +19138,7 @@
           <t>circle</t>
         </is>
       </c>
-      <c r="D100" s="12" t="n">
+      <c r="D100" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -18790,7 +19158,7 @@
           <t>Cargador circular</t>
         </is>
       </c>
-      <c r="D101" s="12" t="n">
+      <c r="D101" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18810,7 +19178,7 @@
           <t>desk Table cell</t>
         </is>
       </c>
-      <c r="D102" s="12" t="n">
+      <c r="D102" s="15" t="n">
         <v>2624</v>
       </c>
     </row>
@@ -18830,8 +19198,8 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D103" s="12" t="n">
-        <v>643</v>
+      <c r="D103" s="15" t="n">
+        <v>636</v>
       </c>
     </row>
     <row r="104">
@@ -18850,7 +19218,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D104" s="12" t="n">
+      <c r="D104" s="15" t="n">
         <v>311</v>
       </c>
     </row>
@@ -18870,8 +19238,8 @@
           <t>Component 16</t>
         </is>
       </c>
-      <c r="D105" s="12" t="n">
-        <v>282</v>
+      <c r="D105" s="15" t="n">
+        <v>297</v>
       </c>
     </row>
     <row r="106">
@@ -18890,8 +19258,8 @@
           <t>Botón Primario</t>
         </is>
       </c>
-      <c r="D106" s="12" t="n">
-        <v>188</v>
+      <c r="D106" s="15" t="n">
+        <v>198</v>
       </c>
     </row>
     <row r="107">
@@ -18910,7 +19278,7 @@
           <t>Dropdown filter page</t>
         </is>
       </c>
-      <c r="D107" s="12" t="n">
+      <c r="D107" s="15" t="n">
         <v>159</v>
       </c>
     </row>
@@ -18930,7 +19298,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D108" s="12" t="n">
+      <c r="D108" s="15" t="n">
         <v>159</v>
       </c>
     </row>
@@ -18950,7 +19318,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D109" s="12" t="n">
+      <c r="D109" s="15" t="n">
         <v>135</v>
       </c>
     </row>
@@ -18970,7 +19338,7 @@
           <t>barras</t>
         </is>
       </c>
-      <c r="D110" s="12" t="n">
+      <c r="D110" s="15" t="n">
         <v>127</v>
       </c>
     </row>
@@ -18990,7 +19358,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="D111" s="12" t="n">
+      <c r="D111" s="15" t="n">
         <v>125</v>
       </c>
     </row>
@@ -19010,7 +19378,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D112" s="12" t="n">
+      <c r="D112" s="15" t="n">
         <v>118</v>
       </c>
     </row>
@@ -19030,7 +19398,7 @@
           <t>description</t>
         </is>
       </c>
-      <c r="D113" s="12" t="n">
+      <c r="D113" s="15" t="n">
         <v>117</v>
       </c>
     </row>
@@ -19050,7 +19418,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D114" s="12" t="n">
+      <c r="D114" s="15" t="n">
         <v>116</v>
       </c>
     </row>
@@ -19070,7 +19438,7 @@
           <t>create account</t>
         </is>
       </c>
-      <c r="D115" s="12" t="n">
+      <c r="D115" s="15" t="n">
         <v>116</v>
       </c>
     </row>
@@ -19090,7 +19458,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D116" s="12" t="n">
+      <c r="D116" s="15" t="n">
         <v>104</v>
       </c>
     </row>
@@ -19110,7 +19478,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D117" s="12" t="n">
+      <c r="D117" s="15" t="n">
         <v>103</v>
       </c>
     </row>
@@ -19130,7 +19498,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D118" s="12" t="n">
+      <c r="D118" s="15" t="n">
         <v>102</v>
       </c>
     </row>
@@ -19150,8 +19518,8 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D119" s="12" t="n">
-        <v>98</v>
+      <c r="D119" s="15" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="120">
@@ -19167,11 +19535,11 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>directionLeft</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="n">
-        <v>96</v>
+          <t>BtnBackNext</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>99</v>
       </c>
     </row>
     <row r="121">
@@ -19187,11 +19555,11 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>AGENDA</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="n">
-        <v>92</v>
+          <t>directionLeft</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="122">
@@ -19210,7 +19578,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D122" s="15" t="n">
         <v>41</v>
       </c>
     </row>
@@ -19230,7 +19598,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D123" s="12" t="n">
+      <c r="D123" s="15" t="n">
         <v>31</v>
       </c>
     </row>
@@ -19250,7 +19618,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D124" s="12" t="n">
+      <c r="D124" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -19270,7 +19638,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D125" s="12" t="n">
+      <c r="D125" s="15" t="n">
         <v>29</v>
       </c>
     </row>
@@ -19290,7 +19658,7 @@
           <t>number_deskop</t>
         </is>
       </c>
-      <c r="D126" s="12" t="n">
+      <c r="D126" s="15" t="n">
         <v>24</v>
       </c>
     </row>
@@ -19310,7 +19678,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D127" s="12" t="n">
+      <c r="D127" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19330,7 +19698,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D128" s="12" t="n">
+      <c r="D128" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19350,7 +19718,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D129" s="12" t="n">
+      <c r="D129" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19370,7 +19738,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D130" s="12" t="n">
+      <c r="D130" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19390,7 +19758,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D131" s="12" t="n">
+      <c r="D131" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19410,7 +19778,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D132" s="12" t="n">
+      <c r="D132" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -19430,7 +19798,7 @@
           <t>Póliza Salud</t>
         </is>
       </c>
-      <c r="D133" s="12" t="n">
+      <c r="D133" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -19450,7 +19818,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D134" s="12" t="n">
+      <c r="D134" s="15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -19470,7 +19838,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D135" s="12" t="n">
+      <c r="D135" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -19490,7 +19858,7 @@
           <t>face</t>
         </is>
       </c>
-      <c r="D136" s="12" t="n">
+      <c r="D136" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -19510,7 +19878,7 @@
           <t>soat</t>
         </is>
       </c>
-      <c r="D137" s="12" t="n">
+      <c r="D137" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -19530,7 +19898,7 @@
           <t>01_card selector</t>
         </is>
       </c>
-      <c r="D138" s="12" t="n">
+      <c r="D138" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -19550,7 +19918,7 @@
           <t>vehiculares</t>
         </is>
       </c>
-      <c r="D139" s="12" t="n">
+      <c r="D139" s="15" t="n">
         <v>9</v>
       </c>
     </row>
@@ -19570,7 +19938,7 @@
           <t>Card_Cross_RT_Deskop_Cob</t>
         </is>
       </c>
-      <c r="D140" s="12" t="n">
+      <c r="D140" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -19590,7 +19958,7 @@
           <t>AddCard</t>
         </is>
       </c>
-      <c r="D141" s="12" t="n">
+      <c r="D141" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -19610,7 +19978,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D142" s="12" t="n">
+      <c r="D142" s="15" t="n">
         <v>105</v>
       </c>
     </row>
@@ -19630,7 +19998,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D143" s="12" t="n">
+      <c r="D143" s="15" t="n">
         <v>58</v>
       </c>
     </row>
@@ -19650,7 +20018,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D144" s="12" t="n">
+      <c r="D144" s="15" t="n">
         <v>50</v>
       </c>
     </row>
@@ -19670,7 +20038,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D145" s="12" t="n">
+      <c r="D145" s="15" t="n">
         <v>38</v>
       </c>
     </row>
@@ -19690,7 +20058,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D146" s="12" t="n">
+      <c r="D146" s="15" t="n">
         <v>34</v>
       </c>
     </row>
@@ -19710,7 +20078,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D147" s="12" t="n">
+      <c r="D147" s="15" t="n">
         <v>28</v>
       </c>
     </row>
@@ -19730,7 +20098,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D148" s="12" t="n">
+      <c r="D148" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -19750,7 +20118,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D149" s="12" t="n">
+      <c r="D149" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19770,7 +20138,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D150" s="12" t="n">
+      <c r="D150" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19790,7 +20158,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D151" s="12" t="n">
+      <c r="D151" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19810,7 +20178,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D152" s="12" t="n">
+      <c r="D152" s="15" t="n">
         <v>21</v>
       </c>
     </row>
@@ -19830,7 +20198,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D153" s="12" t="n">
+      <c r="D153" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19850,7 +20218,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D154" s="12" t="n">
+      <c r="D154" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19870,7 +20238,7 @@
           <t>asset_promo</t>
         </is>
       </c>
-      <c r="D155" s="12" t="n">
+      <c r="D155" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19890,7 +20258,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D156" s="12" t="n">
+      <c r="D156" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19910,7 +20278,7 @@
           <t>Image Frame</t>
         </is>
       </c>
-      <c r="D157" s="12" t="n">
+      <c r="D157" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -19930,7 +20298,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D158" s="12" t="n">
+      <c r="D158" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19950,7 +20318,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D159" s="12" t="n">
+      <c r="D159" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19970,7 +20338,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D160" s="12" t="n">
+      <c r="D160" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19990,7 +20358,7 @@
           <t>BtnAyuda</t>
         </is>
       </c>
-      <c r="D161" s="12" t="n">
+      <c r="D161" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20010,7 +20378,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D162" s="12" t="n">
+      <c r="D162" s="15" t="n">
         <v>109</v>
       </c>
     </row>
@@ -20030,7 +20398,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D163" s="12" t="n">
+      <c r="D163" s="15" t="n">
         <v>107</v>
       </c>
     </row>
@@ -20050,7 +20418,7 @@
           <t>Title</t>
         </is>
       </c>
-      <c r="D164" s="12" t="n">
+      <c r="D164" s="15" t="n">
         <v>78</v>
       </c>
     </row>
@@ -20070,7 +20438,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D165" s="12" t="n">
+      <c r="D165" s="15" t="n">
         <v>72</v>
       </c>
     </row>
@@ -20090,7 +20458,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D166" s="12" t="n">
+      <c r="D166" s="15" t="n">
         <v>60</v>
       </c>
     </row>
@@ -20110,7 +20478,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D167" s="12" t="n">
+      <c r="D167" s="15" t="n">
         <v>40</v>
       </c>
     </row>
@@ -20130,7 +20498,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D168" s="12" t="n">
+      <c r="D168" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20150,7 +20518,7 @@
           <t>Car</t>
         </is>
       </c>
-      <c r="D169" s="12" t="n">
+      <c r="D169" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20170,7 +20538,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D170" s="12" t="n">
+      <c r="D170" s="15" t="n">
         <v>24</v>
       </c>
     </row>
@@ -20190,7 +20558,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D171" s="12" t="n">
+      <c r="D171" s="15" t="n">
         <v>22</v>
       </c>
     </row>
@@ -20210,7 +20578,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D172" s="12" t="n">
+      <c r="D172" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20230,7 +20598,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D173" s="12" t="n">
+      <c r="D173" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20250,7 +20618,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D174" s="12" t="n">
+      <c r="D174" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20270,7 +20638,7 @@
           <t>choque</t>
         </is>
       </c>
-      <c r="D175" s="12" t="n">
+      <c r="D175" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20290,7 +20658,7 @@
           <t>Espejos</t>
         </is>
       </c>
-      <c r="D176" s="12" t="n">
+      <c r="D176" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20310,7 +20678,7 @@
           <t>support</t>
         </is>
       </c>
-      <c r="D177" s="12" t="n">
+      <c r="D177" s="15" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20330,7 +20698,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D178" s="12" t="n">
+      <c r="D178" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -20350,7 +20718,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D179" s="12" t="n">
+      <c r="D179" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -20370,7 +20738,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D180" s="12" t="n">
+      <c r="D180" s="15" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20390,7 +20758,7 @@
           <t>BtnAyuda</t>
         </is>
       </c>
-      <c r="D181" s="12" t="n">
+      <c r="D181" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -20410,7 +20778,7 @@
           <t>celda</t>
         </is>
       </c>
-      <c r="D182" s="12" t="n">
+      <c r="D182" s="15" t="n">
         <v>312</v>
       </c>
     </row>
@@ -20430,7 +20798,7 @@
           <t>Component 120</t>
         </is>
       </c>
-      <c r="D183" s="12" t="n">
+      <c r="D183" s="15" t="n">
         <v>56</v>
       </c>
     </row>
@@ -20450,7 +20818,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D184" s="12" t="n">
+      <c r="D184" s="15" t="n">
         <v>53</v>
       </c>
     </row>
@@ -20470,7 +20838,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D185" s="12" t="n">
+      <c r="D185" s="15" t="n">
         <v>28</v>
       </c>
     </row>
@@ -20490,7 +20858,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D186" s="12" t="n">
+      <c r="D186" s="15" t="n">
         <v>27</v>
       </c>
     </row>
@@ -20510,7 +20878,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D187" s="12" t="n">
+      <c r="D187" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20530,7 +20898,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D188" s="12" t="n">
+      <c r="D188" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20550,7 +20918,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D189" s="12" t="n">
+      <c r="D189" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20570,7 +20938,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D190" s="12" t="n">
+      <c r="D190" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20590,7 +20958,7 @@
           <t>A.white</t>
         </is>
       </c>
-      <c r="D191" s="12" t="n">
+      <c r="D191" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20610,7 +20978,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D192" s="12" t="n">
+      <c r="D192" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20630,7 +20998,7 @@
           <t>iaSpark</t>
         </is>
       </c>
-      <c r="D193" s="12" t="n">
+      <c r="D193" s="15" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20650,7 +21018,7 @@
           <t>DirectionRight</t>
         </is>
       </c>
-      <c r="D194" s="12" t="n">
+      <c r="D194" s="15" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20670,7 +21038,7 @@
           <t>Viajeros</t>
         </is>
       </c>
-      <c r="D195" s="12" t="n">
+      <c r="D195" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -20690,7 +21058,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D196" s="12" t="n">
+      <c r="D196" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -20710,7 +21078,7 @@
           <t>hiking</t>
         </is>
       </c>
-      <c r="D197" s="12" t="n">
+      <c r="D197" s="15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -20730,7 +21098,7 @@
           <t>Viajeros Mobile</t>
         </is>
       </c>
-      <c r="D198" s="12" t="n">
+      <c r="D198" s="15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -20750,7 +21118,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D199" s="12" t="n">
+      <c r="D199" s="15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -20770,7 +21138,7 @@
           <t>Pasajeros</t>
         </is>
       </c>
-      <c r="D200" s="12" t="n">
+      <c r="D200" s="15" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20790,7 +21158,7 @@
           <t>Spinner mesagge</t>
         </is>
       </c>
-      <c r="D201" s="12" t="n">
+      <c r="D201" s="15" t="n">
         <v>4</v>
       </c>
     </row>
@@ -20810,7 +21178,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D202" s="12" t="n">
+      <c r="D202" s="15" t="n">
         <v>174</v>
       </c>
     </row>
@@ -20830,7 +21198,7 @@
           <t>01 Info</t>
         </is>
       </c>
-      <c r="D203" s="12" t="n">
+      <c r="D203" s="15" t="n">
         <v>70</v>
       </c>
     </row>
@@ -20850,7 +21218,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D204" s="12" t="n">
+      <c r="D204" s="15" t="n">
         <v>58</v>
       </c>
     </row>
@@ -20870,7 +21238,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D205" s="12" t="n">
+      <c r="D205" s="15" t="n">
         <v>54</v>
       </c>
     </row>
@@ -20890,7 +21258,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D206" s="12" t="n">
+      <c r="D206" s="15" t="n">
         <v>50</v>
       </c>
     </row>
@@ -20910,7 +21278,7 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D207" s="12" t="n">
+      <c r="D207" s="15" t="n">
         <v>47</v>
       </c>
     </row>
@@ -20930,7 +21298,7 @@
           <t>Trend</t>
         </is>
       </c>
-      <c r="D208" s="12" t="n">
+      <c r="D208" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -20950,7 +21318,7 @@
           <t>A.white</t>
         </is>
       </c>
-      <c r="D209" s="12" t="n">
+      <c r="D209" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20970,7 +21338,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D210" s="12" t="n">
+      <c r="D210" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20990,7 +21358,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D211" s="12" t="n">
+      <c r="D211" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21010,7 +21378,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D212" s="12" t="n">
+      <c r="D212" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21030,7 +21398,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D213" s="12" t="n">
+      <c r="D213" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21050,7 +21418,7 @@
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="D214" s="12" t="n">
+      <c r="D214" s="15" t="n">
         <v>13</v>
       </c>
     </row>
@@ -21070,7 +21438,7 @@
           <t>send</t>
         </is>
       </c>
-      <c r="D215" s="12" t="n">
+      <c r="D215" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21090,7 +21458,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D216" s="12" t="n">
+      <c r="D216" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21110,7 +21478,7 @@
           <t>resumen</t>
         </is>
       </c>
-      <c r="D217" s="12" t="n">
+      <c r="D217" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21130,7 +21498,7 @@
           <t>Botón primario</t>
         </is>
       </c>
-      <c r="D218" s="12" t="n">
+      <c r="D218" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21150,7 +21518,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D219" s="12" t="n">
+      <c r="D219" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21170,7 +21538,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D220" s="12" t="n">
+      <c r="D220" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21190,7 +21558,7 @@
           <t>Lock</t>
         </is>
       </c>
-      <c r="D221" s="12" t="n">
+      <c r="D221" s="15" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21210,7 +21578,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D222" s="12" t="n">
+      <c r="D222" s="15" t="n">
         <v>155</v>
       </c>
     </row>
@@ -21230,7 +21598,7 @@
           <t>Step 3</t>
         </is>
       </c>
-      <c r="D223" s="12" t="n">
+      <c r="D223" s="15" t="n">
         <v>31</v>
       </c>
     </row>
@@ -21250,7 +21618,7 @@
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D224" s="12" t="n">
+      <c r="D224" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21270,7 +21638,7 @@
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D225" s="12" t="n">
+      <c r="D225" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21290,7 +21658,7 @@
           <t>Step 4</t>
         </is>
       </c>
-      <c r="D226" s="12" t="n">
+      <c r="D226" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21310,7 +21678,7 @@
           <t>Step 5</t>
         </is>
       </c>
-      <c r="D227" s="12" t="n">
+      <c r="D227" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -21330,7 +21698,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D228" s="12" t="n">
+      <c r="D228" s="15" t="n">
         <v>29</v>
       </c>
     </row>
@@ -21350,7 +21718,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D229" s="12" t="n">
+      <c r="D229" s="15" t="n">
         <v>29</v>
       </c>
     </row>
@@ -21370,7 +21738,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D230" s="12" t="n">
+      <c r="D230" s="15" t="n">
         <v>27</v>
       </c>
     </row>
@@ -21390,7 +21758,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D231" s="12" t="n">
+      <c r="D231" s="15" t="n">
         <v>26</v>
       </c>
     </row>
@@ -21410,7 +21778,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D232" s="12" t="n">
+      <c r="D232" s="15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -21430,7 +21798,7 @@
           <t>Cargador circular</t>
         </is>
       </c>
-      <c r="D233" s="12" t="n">
+      <c r="D233" s="15" t="n">
         <v>16</v>
       </c>
     </row>
@@ -21450,7 +21818,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D234" s="12" t="n">
+      <c r="D234" s="15" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21470,7 +21838,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D235" s="12" t="n">
+      <c r="D235" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21490,7 +21858,7 @@
           <t>Close Icon</t>
         </is>
       </c>
-      <c r="D236" s="12" t="n">
+      <c r="D236" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21510,7 +21878,7 @@
           <t>cloudupload</t>
         </is>
       </c>
-      <c r="D237" s="12" t="n">
+      <c r="D237" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21530,7 +21898,7 @@
           <t>card-selector</t>
         </is>
       </c>
-      <c r="D238" s="12" t="n">
+      <c r="D238" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21550,7 +21918,7 @@
           <t>[SCTR] Planes cotizador</t>
         </is>
       </c>
-      <c r="D239" s="12" t="n">
+      <c r="D239" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21570,7 +21938,7 @@
           <t>description</t>
         </is>
       </c>
-      <c r="D240" s="12" t="n">
+      <c r="D240" s="15" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21590,7 +21958,7 @@
           <t>Bullet Icon</t>
         </is>
       </c>
-      <c r="D241" s="12" t="n">
+      <c r="D241" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21610,7 +21978,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D242" s="12" t="n">
+      <c r="D242" s="15" t="n">
         <v>221</v>
       </c>
     </row>
@@ -21630,7 +21998,7 @@
           <t>CardProductPromo</t>
         </is>
       </c>
-      <c r="D243" s="12" t="n">
+      <c r="D243" s="15" t="n">
         <v>206</v>
       </c>
     </row>
@@ -21650,7 +22018,7 @@
           <t>Cotizar</t>
         </is>
       </c>
-      <c r="D244" s="12" t="n">
+      <c r="D244" s="15" t="n">
         <v>110</v>
       </c>
     </row>
@@ -21670,7 +22038,7 @@
           <t>Video</t>
         </is>
       </c>
-      <c r="D245" s="12" t="n">
+      <c r="D245" s="15" t="n">
         <v>110</v>
       </c>
     </row>
@@ -21690,7 +22058,7 @@
           <t>Close Icon</t>
         </is>
       </c>
-      <c r="D246" s="12" t="n">
+      <c r="D246" s="15" t="n">
         <v>101</v>
       </c>
     </row>
@@ -21710,7 +22078,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D247" s="12" t="n">
+      <c r="D247" s="15" t="n">
         <v>83</v>
       </c>
     </row>
@@ -21730,7 +22098,7 @@
           <t>CardMenúMobile</t>
         </is>
       </c>
-      <c r="D248" s="12" t="n">
+      <c r="D248" s="15" t="n">
         <v>79</v>
       </c>
     </row>
@@ -21750,7 +22118,7 @@
           <t>CardMenú</t>
         </is>
       </c>
-      <c r="D249" s="12" t="n">
+      <c r="D249" s="15" t="n">
         <v>77</v>
       </c>
     </row>
@@ -21770,7 +22138,7 @@
           <t>WithoutShieldHeart</t>
         </is>
       </c>
-      <c r="D250" s="12" t="n">
+      <c r="D250" s="15" t="n">
         <v>74</v>
       </c>
     </row>
@@ -21790,7 +22158,7 @@
           <t>ShieldHeart</t>
         </is>
       </c>
-      <c r="D251" s="12" t="n">
+      <c r="D251" s="15" t="n">
         <v>71</v>
       </c>
     </row>
@@ -21810,7 +22178,7 @@
           <t>BotónCategoría</t>
         </is>
       </c>
-      <c r="D252" s="12" t="n">
+      <c r="D252" s="15" t="n">
         <v>69</v>
       </c>
     </row>
@@ -21830,7 +22198,7 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="D253" s="12" t="n">
+      <c r="D253" s="15" t="n">
         <v>64</v>
       </c>
     </row>
@@ -21850,7 +22218,7 @@
           <t>_Link Icon</t>
         </is>
       </c>
-      <c r="D254" s="12" t="n">
+      <c r="D254" s="15" t="n">
         <v>54</v>
       </c>
     </row>
@@ -21870,7 +22238,7 @@
           <t>_Button Icon</t>
         </is>
       </c>
-      <c r="D255" s="12" t="n">
+      <c r="D255" s="15" t="n">
         <v>54</v>
       </c>
     </row>
@@ -21890,7 +22258,7 @@
           <t>submenu</t>
         </is>
       </c>
-      <c r="D256" s="12" t="n">
+      <c r="D256" s="15" t="n">
         <v>48</v>
       </c>
     </row>
@@ -21910,7 +22278,7 @@
           <t>Car</t>
         </is>
       </c>
-      <c r="D257" s="12" t="n">
+      <c r="D257" s="15" t="n">
         <v>48</v>
       </c>
     </row>
@@ -21930,7 +22298,7 @@
           <t>Trend</t>
         </is>
       </c>
-      <c r="D258" s="12" t="n">
+      <c r="D258" s="15" t="n">
         <v>46</v>
       </c>
     </row>
@@ -21950,7 +22318,7 @@
           <t>MedicalService</t>
         </is>
       </c>
-      <c r="D259" s="12" t="n">
+      <c r="D259" s="15" t="n">
         <v>46</v>
       </c>
     </row>
@@ -21970,7 +22338,7 @@
           <t>Link Stamp</t>
         </is>
       </c>
-      <c r="D260" s="12" t="n">
+      <c r="D260" s="15" t="n">
         <v>36</v>
       </c>
     </row>
@@ -21990,7 +22358,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D261" s="12" t="n">
+      <c r="D261" s="15" t="n">
         <v>35</v>
       </c>
     </row>
@@ -22010,7 +22378,7 @@
           <t>icon</t>
         </is>
       </c>
-      <c r="D262" s="12" t="n">
+      <c r="D262" s="15" t="n">
         <v>24</v>
       </c>
     </row>
@@ -22030,7 +22398,7 @@
           <t>SecciónDescripción</t>
         </is>
       </c>
-      <c r="D263" s="12" t="n">
+      <c r="D263" s="15" t="n">
         <v>21</v>
       </c>
     </row>
@@ -22050,7 +22418,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D264" s="12" t="n">
+      <c r="D264" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -22070,7 +22438,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D265" s="12" t="n">
+      <c r="D265" s="15" t="n">
         <v>18</v>
       </c>
     </row>
@@ -22090,7 +22458,7 @@
           <t>WithoutShieldHeart</t>
         </is>
       </c>
-      <c r="D266" s="12" t="n">
+      <c r="D266" s="15" t="n">
         <v>14</v>
       </c>
     </row>
@@ -22110,7 +22478,7 @@
           <t>SeccionCanales</t>
         </is>
       </c>
-      <c r="D267" s="12" t="n">
+      <c r="D267" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22130,7 +22498,7 @@
           <t>PersonalInjuy</t>
         </is>
       </c>
-      <c r="D268" s="12" t="n">
+      <c r="D268" s="15" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22150,7 +22518,7 @@
           <t>Information</t>
         </is>
       </c>
-      <c r="D269" s="12" t="n">
+      <c r="D269" s="15" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22170,7 +22538,7 @@
           <t>LogosCollab</t>
         </is>
       </c>
-      <c r="D270" s="12" t="n">
+      <c r="D270" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22190,7 +22558,7 @@
           <t>CoberturasIconos</t>
         </is>
       </c>
-      <c r="D271" s="12" t="n">
+      <c r="D271" s="15" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22210,7 +22578,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D272" s="12" t="n">
+      <c r="D272" s="15" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22230,7 +22598,7 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D273" s="12" t="n">
+      <c r="D273" s="15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -22250,7 +22618,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D274" s="12" t="n">
+      <c r="D274" s="15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -22270,7 +22638,7 @@
           <t>problema eléctrico</t>
         </is>
       </c>
-      <c r="D275" s="12" t="n">
+      <c r="D275" s="15" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22290,7 +22658,7 @@
           <t>robo de autopartes</t>
         </is>
       </c>
-      <c r="D276" s="12" t="n">
+      <c r="D276" s="15" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22310,7 +22678,7 @@
           <t>avión</t>
         </is>
       </c>
-      <c r="D277" s="12" t="n">
+      <c r="D277" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22330,7 +22698,7 @@
           <t>generales</t>
         </is>
       </c>
-      <c r="D278" s="12" t="n">
+      <c r="D278" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22350,7 +22718,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D279" s="12" t="n">
+      <c r="D279" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22370,7 +22738,7 @@
           <t>fractura</t>
         </is>
       </c>
-      <c r="D280" s="12" t="n">
+      <c r="D280" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22390,7 +22758,7 @@
           <t>doctor</t>
         </is>
       </c>
-      <c r="D281" s="12" t="n">
+      <c r="D281" s="15" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22399,13 +22767,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -22413,9 +22781,10 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22446,15 +22815,20 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
+          <t>Detach %</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
           <t>Frames RFD</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Inst. DS</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -22478,7 +22852,7 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E2" s="11" t="inlineStr">
@@ -22486,13 +22860,18 @@
           <t>0%</t>
         </is>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="H2" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22522,13 +22901,18 @@
           <t>64%</t>
         </is>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="H3" s="7" t="n">
         <v>9789</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>15276</v>
       </c>
     </row>
@@ -22550,7 +22934,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -22558,13 +22942,18 @@
           <t>88%</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="H4" s="7" t="n">
         <v>1424</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>1625</v>
       </c>
     </row>
@@ -22586,7 +22975,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -22594,13 +22983,18 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="H5" s="7" t="n">
         <v>3018</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>5891</v>
       </c>
     </row>
@@ -22622,7 +23016,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -22630,14 +23024,19 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>14386</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>22040</v>
+      <c r="H6" s="7" t="n">
+        <v>14419</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>22099</v>
       </c>
     </row>
     <row r="7">
@@ -22658,7 +23057,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -22666,13 +23065,18 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="H7" s="7" t="n">
         <v>172970</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>184326</v>
       </c>
     </row>
@@ -22694,7 +23098,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
@@ -22702,13 +23106,18 @@
           <t>84%</t>
         </is>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="H8" s="7" t="n">
         <v>8539</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>10226</v>
       </c>
     </row>
@@ -22730,7 +23139,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -22738,13 +23147,18 @@
           <t>90%</t>
         </is>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="H9" s="7" t="n">
         <v>7739</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>8560</v>
       </c>
     </row>
@@ -22766,7 +23180,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -22774,13 +23188,18 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>1583</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="I10" s="6" t="n">
         <v>2109</v>
       </c>
     </row>
@@ -22802,7 +23221,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -22810,13 +23229,18 @@
           <t>87%</t>
         </is>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="H11" s="7" t="n">
         <v>3852</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>4452</v>
       </c>
     </row>
@@ -22838,7 +23262,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -22846,13 +23270,18 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>3906</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="I12" s="6" t="n">
         <v>4593</v>
       </c>
     </row>
@@ -22874,7 +23303,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -22882,13 +23311,18 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="H13" s="7" t="n">
         <v>2286</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>3132</v>
       </c>
     </row>
@@ -22910,7 +23344,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -22918,13 +23352,18 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>2650</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="I14" s="6" t="n">
         <v>3813</v>
       </c>
     </row>
@@ -22946,7 +23385,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -22954,14 +23393,19 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>11371</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>12077</v>
+      <c r="H15" s="7" t="n">
+        <v>11370</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>12076</v>
       </c>
     </row>
     <row r="16">
@@ -22982,7 +23426,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -22990,13 +23434,18 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>3566</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="I16" s="6" t="n">
         <v>4204</v>
       </c>
     </row>
@@ -23018,7 +23467,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -23026,13 +23475,18 @@
           <t>84%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="H17" s="7" t="n">
         <v>11472</v>
       </c>
-      <c r="H17" s="6" t="n">
+      <c r="I17" s="6" t="n">
         <v>13594</v>
       </c>
     </row>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -1207,20 +1207,20 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="I19" s="10" t="n">
@@ -2135,20 +2135,20 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E571"/>
+  <dimension ref="A1:E590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17035,6 +17035,481 @@
         <v>2</v>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D572" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E572" s="7" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E573" s="7" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D574" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E574" s="7" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E575" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D576" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E576" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D577" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E577" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D578" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E578" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D579" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E579" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D580" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E580" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E581" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B582" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C582" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D582" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B583" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D583" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E583" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B584" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D584" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E584" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B585" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D585" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E585" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B586" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D586" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E586" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B587" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C587" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D587" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E587" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B588" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D588" s="5" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="E588" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B589" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D589" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E589" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B590" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C590" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D590" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E590" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17046,7 +17521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22275,6 +22750,406 @@
       </c>
       <c r="D261" s="16" t="n">
         <v>35</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>icon</t>
+        </is>
+      </c>
+      <c r="D262" s="16" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>SecciónDescripción</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="D264" s="16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="D265" s="16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>WithoutShieldHeart</t>
+        </is>
+      </c>
+      <c r="D266" s="16" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>SeccionCanales</t>
+        </is>
+      </c>
+      <c r="D267" s="16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>PersonalInjuy</t>
+        </is>
+      </c>
+      <c r="D268" s="16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="D269" s="16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>LogosCollab</t>
+        </is>
+      </c>
+      <c r="D270" s="16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>CoberturasIconos</t>
+        </is>
+      </c>
+      <c r="D271" s="16" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Scroll</t>
+        </is>
+      </c>
+      <c r="D272" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Complex</t>
+        </is>
+      </c>
+      <c r="D273" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>title_+_badges_download</t>
+        </is>
+      </c>
+      <c r="D274" s="16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>problema eléctrico</t>
+        </is>
+      </c>
+      <c r="D275" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>robo de autopartes</t>
+        </is>
+      </c>
+      <c r="D276" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>avión</t>
+        </is>
+      </c>
+      <c r="D277" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>generales</t>
+        </is>
+      </c>
+      <c r="D278" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>download</t>
+        </is>
+      </c>
+      <c r="D279" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>fractura</t>
+        </is>
+      </c>
+      <c r="D280" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>doctor</t>
+        </is>
+      </c>
+      <c r="D281" s="16" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -22452,24 +23327,24 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="G4" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="5">

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,12 +78,19 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="FF8C8880"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="FF1D9E75"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF8C8880"/>
+      <b val="1"/>
+      <color rgb="FFBA7517"/>
       <sz val="10"/>
     </font>
     <font>
@@ -106,7 +113,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
       <color rgb="FF8C8880"/>
       <sz val="10"/>
     </font>
@@ -141,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -175,15 +181,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -551,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -563,7 +572,6 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -576,7 +584,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quarter: Q2 2026  |  2026-06-30</t>
+          <t>Quarter: Q3 2026  |  2026-07-01</t>
         </is>
       </c>
     </row>
@@ -623,12 +631,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Desvinculaciones</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>Detach %</t>
+          <t>Desvinculaciones Q</t>
         </is>
       </c>
     </row>
@@ -650,10 +653,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3018</v>
+        <v>3084</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>2873</v>
+        <v>2917</v>
       </c>
       <c r="G5" s="8" t="n">
         <v>24</v>
@@ -663,12 +666,9 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="I5" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,14 @@
       <c r="G6" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
       </c>
-      <c r="I6" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -738,17 +735,14 @@
       <c r="G7" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="I7" s="10" t="n">
-        <v>317</v>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
-          <t>5%</t>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -778,17 +772,14 @@
       <c r="G8" s="8" t="n">
         <v>47</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -818,17 +809,14 @@
       <c r="G9" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="I9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -863,12 +851,9 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -898,18 +883,13 @@
       <c r="G11" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
       </c>
-      <c r="I11" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J11" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I11" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -943,13 +923,8 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="I12" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I12" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -978,18 +953,13 @@
       <c r="G13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I13" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I13" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1023,13 +993,8 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="I14" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I14" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1058,18 +1023,13 @@
       <c r="G15" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="I15" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I15" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1098,18 +1058,13 @@
       <c r="G16" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="I16" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I16" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1138,18 +1093,13 @@
       <c r="G17" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="11" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
       </c>
-      <c r="I17" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="I17" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1178,17 +1128,14 @@
       <c r="G18" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="11" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="I18" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1165,21 @@
       <c r="G19" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="11" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
       </c>
-      <c r="I19" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1356,10 +1300,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="7" t="n">
-        <v>2395</v>
+        <v>2461</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>2420</v>
+        <v>2464</v>
       </c>
       <c r="G3" s="8" t="n">
         <v>12</v>
@@ -1398,7 +1342,7 @@
       <c r="G4" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="11" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
@@ -1432,7 +1376,7 @@
       <c r="G5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="12" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1500,7 +1444,7 @@
       <c r="G7" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -1534,7 +1478,7 @@
       <c r="G8" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>79%</t>
         </is>
@@ -1568,7 +1512,7 @@
       <c r="G9" s="8" t="n">
         <v>38</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="11" t="inlineStr">
         <is>
           <t>92%</t>
         </is>
@@ -1602,7 +1546,7 @@
       <c r="G10" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
@@ -1636,7 +1580,7 @@
       <c r="G11" s="8" t="n">
         <v>42</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="11" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -1670,7 +1614,7 @@
       <c r="G12" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
@@ -1704,7 +1648,7 @@
       <c r="G13" s="8" t="n">
         <v>34</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>77%</t>
         </is>
@@ -1738,7 +1682,7 @@
       <c r="G14" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="H14" s="12" t="inlineStr">
+      <c r="H14" s="13" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -1772,7 +1716,7 @@
       <c r="G15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
@@ -1806,7 +1750,7 @@
       <c r="G16" s="8" t="n">
         <v>27</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="11" t="inlineStr">
         <is>
           <t>75%</t>
         </is>
@@ -1874,7 +1818,7 @@
       <c r="G18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="12" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1942,7 +1886,7 @@
       <c r="G20" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="11" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -1976,7 +1920,7 @@
       <c r="G21" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="11" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
@@ -2010,7 +1954,7 @@
       <c r="G22" s="8" t="n">
         <v>35</v>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="11" t="inlineStr">
         <is>
           <t>94%</t>
         </is>
@@ -2044,7 +1988,7 @@
       <c r="G23" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="11" t="inlineStr">
         <is>
           <t>87%</t>
         </is>
@@ -2078,7 +2022,7 @@
       <c r="G24" s="8" t="n">
         <v>17</v>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="11" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
@@ -2112,7 +2056,7 @@
       <c r="G25" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="11" t="inlineStr">
         <is>
           <t>89%</t>
         </is>
@@ -2146,7 +2090,7 @@
       <c r="G26" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="11" t="inlineStr">
         <is>
           <t>88%</t>
         </is>
@@ -2163,244 +2107,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Desvinculaciones por categoría — Library Analytics API</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Fuente: Figma Library Analytics (Enterprise), agregado por Figma Team del quarter actual. El % es referencial (volumen de inserciones suele ser alto, por lo que el % puede verse cercano a 0 aunque haya desvinculaciones reales).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>Desvinculaciones</t>
-        </is>
-      </c>
-      <c r="C4" s="15" t="inlineStr">
-        <is>
-          <t>Inserciones</t>
-        </is>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Total acciones</t>
-        </is>
-      </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>Detach %</t>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Desvinculaciones Q</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>MEP</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>22</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>17415</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>17437</v>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Somos Corredores</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>31512</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>31599</v>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Protege 365</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>317</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>6526</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>6843</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Nueva Web Empresas</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>69191</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>69208</v>
-      </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Portal Digital de Siniestros</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>6637</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>6638</v>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Modelo Día</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>4334</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>4339</v>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>615</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>27625</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>28240</v>
-      </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>27</v>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>19514</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>19541</v>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>10670</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>10704</v>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -2428,36 +2175,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Componentes con más desvinculaciones — toda la librería Dalton</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>No filtrado por categoría/equipo — la API de Figma no permite ese cruce. Útil para ver qué componentes del sistema tienden a romperse más, independientemente de quién los usa.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Componente</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Desvinculaciones</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Inserciones</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Detach %</t>
         </is>
@@ -2469,15 +2216,15 @@
           <t>type_option</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>485</v>
+      <c r="B5" s="13" t="n">
+        <v>288</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2331</v>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>17.22%</t>
+        <v>0</v>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2487,33 +2234,33 @@
           <t>section_footer</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>86</v>
+      <c r="B6" s="13" t="n">
+        <v>48</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>4193</v>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>2.01%</t>
+        <v>0</v>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Modal Informative</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>58</v>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>30</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>767</v>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>7.03%</t>
+        <v>0</v>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2523,31 +2270,31 @@
           <t>Button</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>53</v>
+      <c r="B8" s="13" t="n">
+        <v>24</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>69524</v>
-      </c>
-      <c r="D8" s="11" t="inlineStr">
-        <is>
-          <t>0.08%</t>
+        <v>220</v>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>9.84%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>50</v>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>24</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -2556,18 +2303,18 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>40</v>
+          <t>Radio Atom</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>20</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>3726</v>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>1.06%</t>
+        <v>0</v>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -2577,159 +2324,159 @@
           <t>Radio Outline</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
-        <v>34</v>
+      <c r="B11" s="13" t="n">
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>851</v>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>3.84%</t>
+        <v>6</v>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Radio Atom</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>24</v>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>8156</v>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>0.29%</t>
+        <v>0</v>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Chips Status</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>23</v>
+          <t>Checkbox With Text</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>10545</v>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>0.22%</t>
+        <v>16</v>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>38.46%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>23</v>
+          <t>Checkbox Atom</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1396</v>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>1.62%</t>
+        <v>0</v>
+      </c>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>21</v>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>932</v>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>2.2%</t>
+        <v>129</v>
+      </c>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>6.52%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>19</v>
+          <t>Chips Status</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>16685</v>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>0.11%</t>
+        <v>2</v>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Checkbox With Text</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>16</v>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>4019</v>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>0.4%</t>
+        <v>0</v>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>13</v>
+          <t>Simple</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>1097</v>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>1.17%</t>
+        <v>28</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>15.15%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Checkbox Atom</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>11</v>
+          <t>Stepper Desktop</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>3789</v>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>0.29%</t>
+        <v>14</v>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>17.65%</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3004,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>691</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21">
@@ -3282,7 +3029,7 @@
         </is>
       </c>
       <c r="E21" s="7" t="n">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="22">
@@ -3307,7 +3054,7 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23">
@@ -3357,7 +3104,7 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
@@ -3382,7 +3129,7 @@
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26">
@@ -3407,7 +3154,7 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27">
@@ -3432,7 +3179,7 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28">
@@ -3457,7 +3204,7 @@
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
@@ -17568,8 +17315,8 @@
           <t>menú</t>
         </is>
       </c>
-      <c r="D2" s="16" t="n">
-        <v>1761</v>
+      <c r="D2" s="18" t="n">
+        <v>1786</v>
       </c>
     </row>
     <row r="3">
@@ -17588,8 +17335,8 @@
           <t>card_accion</t>
         </is>
       </c>
-      <c r="D3" s="16" t="n">
-        <v>217</v>
+      <c r="D3" s="18" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -17608,8 +17355,8 @@
           <t>card_atajo_home</t>
         </is>
       </c>
-      <c r="D4" s="16" t="n">
-        <v>212</v>
+      <c r="D4" s="18" t="n">
+        <v>218</v>
       </c>
     </row>
     <row r="5">
@@ -17628,7 +17375,7 @@
           <t>documento simple</t>
         </is>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="18" t="n">
         <v>100</v>
       </c>
     </row>
@@ -17648,8 +17395,8 @@
           <t>Seguros card</t>
         </is>
       </c>
-      <c r="D6" s="16" t="n">
-        <v>45</v>
+      <c r="D6" s="18" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -17668,8 +17415,8 @@
           <t>Card_ beneficios</t>
         </is>
       </c>
-      <c r="D7" s="16" t="n">
-        <v>37</v>
+      <c r="D7" s="18" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -17688,8 +17435,8 @@
           <t>beneficios vehiculares</t>
         </is>
       </c>
-      <c r="D8" s="16" t="n">
-        <v>36</v>
+      <c r="D8" s="18" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -17708,8 +17455,8 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
-        <v>34</v>
+      <c r="D9" s="18" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -17728,8 +17475,8 @@
           <t>carro</t>
         </is>
       </c>
-      <c r="D10" s="16" t="n">
-        <v>26</v>
+      <c r="D10" s="18" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -17748,8 +17495,8 @@
           <t>buscar clínicas</t>
         </is>
       </c>
-      <c r="D11" s="16" t="n">
-        <v>26</v>
+      <c r="D11" s="18" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -17768,8 +17515,8 @@
           <t>hogar</t>
         </is>
       </c>
-      <c r="D12" s="16" t="n">
-        <v>26</v>
+      <c r="D12" s="18" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -17788,7 +17535,7 @@
           <t>drag</t>
         </is>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -17808,7 +17555,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="18" t="n">
         <v>25</v>
       </c>
     </row>
@@ -17825,11 +17572,11 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>error duda</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>23</v>
+          <t>logo beneficios</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -17845,10 +17592,10 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>logo beneficios</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="n">
+          <t>error duda</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17868,7 +17615,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -17888,7 +17635,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -17908,7 +17655,7 @@
           <t>Bottom Navigation</t>
         </is>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17928,7 +17675,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="18" t="n">
         <v>13</v>
       </c>
     </row>
@@ -17948,7 +17695,7 @@
           <t>card_atajo</t>
         </is>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -17968,7 +17715,7 @@
           <t>Suggested search (Deprecated)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="18" t="n">
         <v>65</v>
       </c>
     </row>
@@ -17988,7 +17735,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="D23" s="18" t="n">
         <v>59</v>
       </c>
     </row>
@@ -18008,7 +17755,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="D24" s="18" t="n">
         <v>59</v>
       </c>
     </row>
@@ -18028,7 +17775,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="D25" s="18" t="n">
         <v>59</v>
       </c>
     </row>
@@ -18048,7 +17795,7 @@
           <t>celda L</t>
         </is>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="D26" s="18" t="n">
         <v>49</v>
       </c>
     </row>
@@ -18068,7 +17815,7 @@
           <t>Step 04</t>
         </is>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="18" t="n">
         <v>39</v>
       </c>
     </row>
@@ -18088,7 +17835,7 @@
           <t>Step 05</t>
         </is>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="18" t="n">
         <v>39</v>
       </c>
     </row>
@@ -18108,7 +17855,7 @@
           <t>Upload icon</t>
         </is>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="18" t="n">
         <v>31</v>
       </c>
     </row>
@@ -18128,7 +17875,7 @@
           <t>Userflow</t>
         </is>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="18" t="n">
         <v>27</v>
       </c>
     </row>
@@ -18148,7 +17895,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="18" t="n">
         <v>21</v>
       </c>
     </row>
@@ -18168,7 +17915,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D32" s="16" t="n">
+      <c r="D32" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -18188,7 +17935,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -18208,7 +17955,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="18" t="n">
         <v>11</v>
       </c>
     </row>
@@ -18228,7 +17975,7 @@
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="D35" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18248,7 +17995,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18268,7 +18015,7 @@
           <t>audifonos</t>
         </is>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18288,7 +18035,7 @@
           <t>Container Drag and Drop</t>
         </is>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="D38" s="18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -18308,7 +18055,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -18328,7 +18075,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D40" s="16" t="n">
+      <c r="D40" s="18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -18348,7 +18095,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18368,7 +18115,7 @@
           <t>HealthAndSafe</t>
         </is>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="18" t="n">
         <v>96</v>
       </c>
     </row>
@@ -18388,7 +18135,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="18" t="n">
         <v>54</v>
       </c>
     </row>
@@ -18408,7 +18155,7 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="18" t="n">
         <v>44</v>
       </c>
     </row>
@@ -18428,7 +18175,7 @@
           <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="18" t="n">
         <v>35</v>
       </c>
     </row>
@@ -18448,7 +18195,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="D46" s="18" t="n">
         <v>34</v>
       </c>
     </row>
@@ -18468,7 +18215,7 @@
           <t>NorthEast</t>
         </is>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="D47" s="18" t="n">
         <v>32</v>
       </c>
     </row>
@@ -18488,7 +18235,7 @@
           <t>Menú_Desktop</t>
         </is>
       </c>
-      <c r="D48" s="16" t="n">
+      <c r="D48" s="18" t="n">
         <v>31</v>
       </c>
     </row>
@@ -18508,7 +18255,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="D49" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -18528,7 +18275,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D50" s="16" t="n">
+      <c r="D50" s="18" t="n">
         <v>29</v>
       </c>
     </row>
@@ -18548,7 +18295,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D51" s="16" t="n">
+      <c r="D51" s="18" t="n">
         <v>28</v>
       </c>
     </row>
@@ -18568,7 +18315,7 @@
           <t>beneficios reconocerte</t>
         </is>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="D52" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18588,7 +18335,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="D53" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18608,7 +18355,7 @@
           <t>filter</t>
         </is>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="D54" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18628,7 +18375,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="D55" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -18648,7 +18395,7 @@
           <t>Feed</t>
         </is>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="D56" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -18668,7 +18415,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D57" s="16" t="n">
+      <c r="D57" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -18688,7 +18435,7 @@
           <t>trofeo</t>
         </is>
       </c>
-      <c r="D58" s="16" t="n">
+      <c r="D58" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -18708,7 +18455,7 @@
           <t>vida ley</t>
         </is>
       </c>
-      <c r="D59" s="16" t="n">
+      <c r="D59" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -18728,7 +18475,7 @@
           <t>tratamiento</t>
         </is>
       </c>
-      <c r="D60" s="16" t="n">
+      <c r="D60" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -18748,7 +18495,7 @@
           <t>Right Label</t>
         </is>
       </c>
-      <c r="D61" s="16" t="n">
+      <c r="D61" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -18768,7 +18515,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D62" s="16" t="n">
+      <c r="D62" s="18" t="n">
         <v>2366</v>
       </c>
     </row>
@@ -18788,7 +18535,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D63" s="16" t="n">
+      <c r="D63" s="18" t="n">
         <v>699</v>
       </c>
     </row>
@@ -18808,7 +18555,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D64" s="16" t="n">
+      <c r="D64" s="18" t="n">
         <v>550</v>
       </c>
     </row>
@@ -18828,7 +18575,7 @@
           <t>Home_Header</t>
         </is>
       </c>
-      <c r="D65" s="16" t="n">
+      <c r="D65" s="18" t="n">
         <v>512</v>
       </c>
     </row>
@@ -18848,7 +18595,7 @@
           <t>Action 1</t>
         </is>
       </c>
-      <c r="D66" s="16" t="n">
+      <c r="D66" s="18" t="n">
         <v>496</v>
       </c>
     </row>
@@ -18868,7 +18615,7 @@
           <t>Action 2</t>
         </is>
       </c>
-      <c r="D67" s="16" t="n">
+      <c r="D67" s="18" t="n">
         <v>496</v>
       </c>
     </row>
@@ -18888,7 +18635,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D68" s="16" t="n">
+      <c r="D68" s="18" t="n">
         <v>482</v>
       </c>
     </row>
@@ -18908,7 +18655,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D69" s="16" t="n">
+      <c r="D69" s="18" t="n">
         <v>433</v>
       </c>
     </row>
@@ -18928,7 +18675,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D70" s="16" t="n">
+      <c r="D70" s="18" t="n">
         <v>398</v>
       </c>
     </row>
@@ -18948,7 +18695,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D71" s="16" t="n">
+      <c r="D71" s="18" t="n">
         <v>398</v>
       </c>
     </row>
@@ -18968,7 +18715,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D72" s="16" t="n">
+      <c r="D72" s="18" t="n">
         <v>390</v>
       </c>
     </row>
@@ -18988,7 +18735,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D73" s="16" t="n">
+      <c r="D73" s="18" t="n">
         <v>382</v>
       </c>
     </row>
@@ -19008,7 +18755,7 @@
           <t>save</t>
         </is>
       </c>
-      <c r="D74" s="16" t="n">
+      <c r="D74" s="18" t="n">
         <v>328</v>
       </c>
     </row>
@@ -19028,7 +18775,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D75" s="16" t="n">
+      <c r="D75" s="18" t="n">
         <v>324</v>
       </c>
     </row>
@@ -19048,7 +18795,7 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D76" s="16" t="n">
+      <c r="D76" s="18" t="n">
         <v>312</v>
       </c>
     </row>
@@ -19068,7 +18815,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D77" s="16" t="n">
+      <c r="D77" s="18" t="n">
         <v>295</v>
       </c>
     </row>
@@ -19088,7 +18835,7 @@
           <t>medios de pago</t>
         </is>
       </c>
-      <c r="D78" s="16" t="n">
+      <c r="D78" s="18" t="n">
         <v>280</v>
       </c>
     </row>
@@ -19108,7 +18855,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D79" s="16" t="n">
+      <c r="D79" s="18" t="n">
         <v>116</v>
       </c>
     </row>
@@ -19128,7 +18875,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D80" s="16" t="n">
+      <c r="D80" s="18" t="n">
         <v>104</v>
       </c>
     </row>
@@ -19148,7 +18895,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D81" s="16" t="n">
+      <c r="D81" s="18" t="n">
         <v>104</v>
       </c>
     </row>
@@ -19168,7 +18915,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D82" s="16" t="n">
+      <c r="D82" s="18" t="n">
         <v>233</v>
       </c>
     </row>
@@ -19188,7 +18935,7 @@
           <t>DirectionRight</t>
         </is>
       </c>
-      <c r="D83" s="16" t="n">
+      <c r="D83" s="18" t="n">
         <v>198</v>
       </c>
     </row>
@@ -19208,7 +18955,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D84" s="16" t="n">
+      <c r="D84" s="18" t="n">
         <v>165</v>
       </c>
     </row>
@@ -19228,7 +18975,7 @@
           <t>Pegar Icon</t>
         </is>
       </c>
-      <c r="D85" s="16" t="n">
+      <c r="D85" s="18" t="n">
         <v>102</v>
       </c>
     </row>
@@ -19248,7 +18995,7 @@
           <t>Component 9</t>
         </is>
       </c>
-      <c r="D86" s="16" t="n">
+      <c r="D86" s="18" t="n">
         <v>90</v>
       </c>
     </row>
@@ -19268,7 +19015,7 @@
           <t>copy</t>
         </is>
       </c>
-      <c r="D87" s="16" t="n">
+      <c r="D87" s="18" t="n">
         <v>57</v>
       </c>
     </row>
@@ -19288,7 +19035,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D88" s="16" t="n">
+      <c r="D88" s="18" t="n">
         <v>37</v>
       </c>
     </row>
@@ -19308,7 +19055,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D89" s="16" t="n">
+      <c r="D89" s="18" t="n">
         <v>32</v>
       </c>
     </row>
@@ -19328,7 +19075,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D90" s="16" t="n">
+      <c r="D90" s="18" t="n">
         <v>29</v>
       </c>
     </row>
@@ -19348,7 +19095,7 @@
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="D91" s="16" t="n">
+      <c r="D91" s="18" t="n">
         <v>25</v>
       </c>
     </row>
@@ -19368,7 +19115,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D92" s="16" t="n">
+      <c r="D92" s="18" t="n">
         <v>25</v>
       </c>
     </row>
@@ -19388,7 +19135,7 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D93" s="16" t="n">
+      <c r="D93" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19408,7 +19155,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D94" s="16" t="n">
+      <c r="D94" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19428,7 +19175,7 @@
           <t>soles</t>
         </is>
       </c>
-      <c r="D95" s="16" t="n">
+      <c r="D95" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -19448,7 +19195,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D96" s="16" t="n">
+      <c r="D96" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19468,7 +19215,7 @@
           <t>24.timer</t>
         </is>
       </c>
-      <c r="D97" s="16" t="n">
+      <c r="D97" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19488,7 +19235,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D98" s="16" t="n">
+      <c r="D98" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19508,7 +19255,7 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="D99" s="16" t="n">
+      <c r="D99" s="18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -19528,7 +19275,7 @@
           <t>circle</t>
         </is>
       </c>
-      <c r="D100" s="16" t="n">
+      <c r="D100" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19548,7 +19295,7 @@
           <t>Cargador circular</t>
         </is>
       </c>
-      <c r="D101" s="16" t="n">
+      <c r="D101" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19568,7 +19315,7 @@
           <t>desk Table cell</t>
         </is>
       </c>
-      <c r="D102" s="16" t="n">
+      <c r="D102" s="18" t="n">
         <v>2624</v>
       </c>
     </row>
@@ -19588,7 +19335,7 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D103" s="16" t="n">
+      <c r="D103" s="18" t="n">
         <v>636</v>
       </c>
     </row>
@@ -19608,7 +19355,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D104" s="16" t="n">
+      <c r="D104" s="18" t="n">
         <v>311</v>
       </c>
     </row>
@@ -19628,7 +19375,7 @@
           <t>Component 16</t>
         </is>
       </c>
-      <c r="D105" s="16" t="n">
+      <c r="D105" s="18" t="n">
         <v>297</v>
       </c>
     </row>
@@ -19648,7 +19395,7 @@
           <t>Botón Primario</t>
         </is>
       </c>
-      <c r="D106" s="16" t="n">
+      <c r="D106" s="18" t="n">
         <v>198</v>
       </c>
     </row>
@@ -19668,7 +19415,7 @@
           <t>Dropdown filter page</t>
         </is>
       </c>
-      <c r="D107" s="16" t="n">
+      <c r="D107" s="18" t="n">
         <v>159</v>
       </c>
     </row>
@@ -19688,7 +19435,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D108" s="16" t="n">
+      <c r="D108" s="18" t="n">
         <v>159</v>
       </c>
     </row>
@@ -19708,7 +19455,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D109" s="16" t="n">
+      <c r="D109" s="18" t="n">
         <v>135</v>
       </c>
     </row>
@@ -19728,7 +19475,7 @@
           <t>barras</t>
         </is>
       </c>
-      <c r="D110" s="16" t="n">
+      <c r="D110" s="18" t="n">
         <v>127</v>
       </c>
     </row>
@@ -19748,7 +19495,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="D111" s="16" t="n">
+      <c r="D111" s="18" t="n">
         <v>125</v>
       </c>
     </row>
@@ -19768,7 +19515,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D112" s="16" t="n">
+      <c r="D112" s="18" t="n">
         <v>118</v>
       </c>
     </row>
@@ -19788,7 +19535,7 @@
           <t>description</t>
         </is>
       </c>
-      <c r="D113" s="16" t="n">
+      <c r="D113" s="18" t="n">
         <v>117</v>
       </c>
     </row>
@@ -19808,7 +19555,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D114" s="16" t="n">
+      <c r="D114" s="18" t="n">
         <v>116</v>
       </c>
     </row>
@@ -19828,7 +19575,7 @@
           <t>create account</t>
         </is>
       </c>
-      <c r="D115" s="16" t="n">
+      <c r="D115" s="18" t="n">
         <v>116</v>
       </c>
     </row>
@@ -19848,7 +19595,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D116" s="16" t="n">
+      <c r="D116" s="18" t="n">
         <v>104</v>
       </c>
     </row>
@@ -19868,7 +19615,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D117" s="16" t="n">
+      <c r="D117" s="18" t="n">
         <v>103</v>
       </c>
     </row>
@@ -19888,7 +19635,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D118" s="16" t="n">
+      <c r="D118" s="18" t="n">
         <v>102</v>
       </c>
     </row>
@@ -19908,7 +19655,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D119" s="16" t="n">
+      <c r="D119" s="18" t="n">
         <v>100</v>
       </c>
     </row>
@@ -19928,7 +19675,7 @@
           <t>BtnBackNext</t>
         </is>
       </c>
-      <c r="D120" s="16" t="n">
+      <c r="D120" s="18" t="n">
         <v>99</v>
       </c>
     </row>
@@ -19948,7 +19695,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D121" s="16" t="n">
+      <c r="D121" s="18" t="n">
         <v>96</v>
       </c>
     </row>
@@ -19968,7 +19715,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D122" s="16" t="n">
+      <c r="D122" s="18" t="n">
         <v>41</v>
       </c>
     </row>
@@ -19988,7 +19735,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D123" s="16" t="n">
+      <c r="D123" s="18" t="n">
         <v>31</v>
       </c>
     </row>
@@ -20008,7 +19755,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D124" s="16" t="n">
+      <c r="D124" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20028,7 +19775,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D125" s="16" t="n">
+      <c r="D125" s="18" t="n">
         <v>29</v>
       </c>
     </row>
@@ -20048,7 +19795,7 @@
           <t>number_deskop</t>
         </is>
       </c>
-      <c r="D126" s="16" t="n">
+      <c r="D126" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -20068,7 +19815,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D127" s="16" t="n">
+      <c r="D127" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -20088,7 +19835,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D128" s="16" t="n">
+      <c r="D128" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -20108,7 +19855,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D129" s="16" t="n">
+      <c r="D129" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20128,7 +19875,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D130" s="16" t="n">
+      <c r="D130" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20148,7 +19895,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D131" s="16" t="n">
+      <c r="D131" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20168,7 +19915,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D132" s="16" t="n">
+      <c r="D132" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -20188,7 +19935,7 @@
           <t>Póliza Salud</t>
         </is>
       </c>
-      <c r="D133" s="16" t="n">
+      <c r="D133" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -20208,7 +19955,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D134" s="16" t="n">
+      <c r="D134" s="18" t="n">
         <v>13</v>
       </c>
     </row>
@@ -20228,7 +19975,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D135" s="16" t="n">
+      <c r="D135" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -20248,7 +19995,7 @@
           <t>face</t>
         </is>
       </c>
-      <c r="D136" s="16" t="n">
+      <c r="D136" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20268,7 +20015,7 @@
           <t>soat</t>
         </is>
       </c>
-      <c r="D137" s="16" t="n">
+      <c r="D137" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20288,7 +20035,7 @@
           <t>01_card selector</t>
         </is>
       </c>
-      <c r="D138" s="16" t="n">
+      <c r="D138" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -20308,7 +20055,7 @@
           <t>vehiculares</t>
         </is>
       </c>
-      <c r="D139" s="16" t="n">
+      <c r="D139" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -20328,7 +20075,7 @@
           <t>Card_Cross_RT_Deskop_Cob</t>
         </is>
       </c>
-      <c r="D140" s="16" t="n">
+      <c r="D140" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -20348,7 +20095,7 @@
           <t>AddCard</t>
         </is>
       </c>
-      <c r="D141" s="16" t="n">
+      <c r="D141" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -20368,7 +20115,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D142" s="16" t="n">
+      <c r="D142" s="18" t="n">
         <v>105</v>
       </c>
     </row>
@@ -20388,7 +20135,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D143" s="16" t="n">
+      <c r="D143" s="18" t="n">
         <v>58</v>
       </c>
     </row>
@@ -20408,7 +20155,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D144" s="16" t="n">
+      <c r="D144" s="18" t="n">
         <v>50</v>
       </c>
     </row>
@@ -20428,7 +20175,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D145" s="16" t="n">
+      <c r="D145" s="18" t="n">
         <v>38</v>
       </c>
     </row>
@@ -20448,7 +20195,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D146" s="16" t="n">
+      <c r="D146" s="18" t="n">
         <v>34</v>
       </c>
     </row>
@@ -20468,7 +20215,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D147" s="16" t="n">
+      <c r="D147" s="18" t="n">
         <v>28</v>
       </c>
     </row>
@@ -20488,7 +20235,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D148" s="16" t="n">
+      <c r="D148" s="18" t="n">
         <v>25</v>
       </c>
     </row>
@@ -20508,7 +20255,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D149" s="16" t="n">
+      <c r="D149" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -20528,7 +20275,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D150" s="16" t="n">
+      <c r="D150" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -20548,7 +20295,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D151" s="16" t="n">
+      <c r="D151" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -20568,7 +20315,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D152" s="16" t="n">
+      <c r="D152" s="18" t="n">
         <v>21</v>
       </c>
     </row>
@@ -20588,7 +20335,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D153" s="16" t="n">
+      <c r="D153" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20608,7 +20355,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D154" s="16" t="n">
+      <c r="D154" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -20628,7 +20375,7 @@
           <t>asset_promo</t>
         </is>
       </c>
-      <c r="D155" s="16" t="n">
+      <c r="D155" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20648,7 +20395,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D156" s="16" t="n">
+      <c r="D156" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -20668,7 +20415,7 @@
           <t>Image Frame</t>
         </is>
       </c>
-      <c r="D157" s="16" t="n">
+      <c r="D157" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -20688,7 +20435,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D158" s="16" t="n">
+      <c r="D158" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20708,7 +20455,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D159" s="16" t="n">
+      <c r="D159" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20728,7 +20475,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D160" s="16" t="n">
+      <c r="D160" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -20748,7 +20495,7 @@
           <t>BtnAyuda</t>
         </is>
       </c>
-      <c r="D161" s="16" t="n">
+      <c r="D161" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -20768,7 +20515,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D162" s="16" t="n">
+      <c r="D162" s="18" t="n">
         <v>109</v>
       </c>
     </row>
@@ -20788,7 +20535,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D163" s="16" t="n">
+      <c r="D163" s="18" t="n">
         <v>107</v>
       </c>
     </row>
@@ -20808,7 +20555,7 @@
           <t>Title</t>
         </is>
       </c>
-      <c r="D164" s="16" t="n">
+      <c r="D164" s="18" t="n">
         <v>78</v>
       </c>
     </row>
@@ -20828,7 +20575,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D165" s="16" t="n">
+      <c r="D165" s="18" t="n">
         <v>72</v>
       </c>
     </row>
@@ -20848,7 +20595,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D166" s="16" t="n">
+      <c r="D166" s="18" t="n">
         <v>60</v>
       </c>
     </row>
@@ -20868,7 +20615,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D167" s="16" t="n">
+      <c r="D167" s="18" t="n">
         <v>40</v>
       </c>
     </row>
@@ -20888,7 +20635,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D168" s="16" t="n">
+      <c r="D168" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20908,7 +20655,7 @@
           <t>Car</t>
         </is>
       </c>
-      <c r="D169" s="16" t="n">
+      <c r="D169" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -20928,7 +20675,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D170" s="16" t="n">
+      <c r="D170" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -20948,7 +20695,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D171" s="16" t="n">
+      <c r="D171" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -20968,7 +20715,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D172" s="16" t="n">
+      <c r="D172" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -20988,7 +20735,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D173" s="16" t="n">
+      <c r="D173" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -21008,7 +20755,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D174" s="16" t="n">
+      <c r="D174" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -21028,7 +20775,7 @@
           <t>choque</t>
         </is>
       </c>
-      <c r="D175" s="16" t="n">
+      <c r="D175" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -21048,7 +20795,7 @@
           <t>Espejos</t>
         </is>
       </c>
-      <c r="D176" s="16" t="n">
+      <c r="D176" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -21068,7 +20815,7 @@
           <t>support</t>
         </is>
       </c>
-      <c r="D177" s="16" t="n">
+      <c r="D177" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -21088,7 +20835,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D178" s="16" t="n">
+      <c r="D178" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -21108,7 +20855,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D179" s="16" t="n">
+      <c r="D179" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -21128,7 +20875,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D180" s="16" t="n">
+      <c r="D180" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -21148,7 +20895,7 @@
           <t>BtnAyuda</t>
         </is>
       </c>
-      <c r="D181" s="16" t="n">
+      <c r="D181" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -21168,7 +20915,7 @@
           <t>celda</t>
         </is>
       </c>
-      <c r="D182" s="16" t="n">
+      <c r="D182" s="18" t="n">
         <v>312</v>
       </c>
     </row>
@@ -21188,7 +20935,7 @@
           <t>Component 120</t>
         </is>
       </c>
-      <c r="D183" s="16" t="n">
+      <c r="D183" s="18" t="n">
         <v>56</v>
       </c>
     </row>
@@ -21208,7 +20955,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D184" s="16" t="n">
+      <c r="D184" s="18" t="n">
         <v>53</v>
       </c>
     </row>
@@ -21228,7 +20975,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D185" s="16" t="n">
+      <c r="D185" s="18" t="n">
         <v>28</v>
       </c>
     </row>
@@ -21248,7 +20995,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D186" s="16" t="n">
+      <c r="D186" s="18" t="n">
         <v>27</v>
       </c>
     </row>
@@ -21268,7 +21015,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D187" s="16" t="n">
+      <c r="D187" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21288,7 +21035,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D188" s="16" t="n">
+      <c r="D188" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21308,7 +21055,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D189" s="16" t="n">
+      <c r="D189" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21328,7 +21075,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D190" s="16" t="n">
+      <c r="D190" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21348,7 +21095,7 @@
           <t>A.white</t>
         </is>
       </c>
-      <c r="D191" s="16" t="n">
+      <c r="D191" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21368,7 +21115,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D192" s="16" t="n">
+      <c r="D192" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21388,7 +21135,7 @@
           <t>iaSpark</t>
         </is>
       </c>
-      <c r="D193" s="16" t="n">
+      <c r="D193" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21408,7 +21155,7 @@
           <t>DirectionRight</t>
         </is>
       </c>
-      <c r="D194" s="16" t="n">
+      <c r="D194" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -21428,7 +21175,7 @@
           <t>Viajeros</t>
         </is>
       </c>
-      <c r="D195" s="16" t="n">
+      <c r="D195" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21448,7 +21195,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D196" s="16" t="n">
+      <c r="D196" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21468,7 +21215,7 @@
           <t>hiking</t>
         </is>
       </c>
-      <c r="D197" s="16" t="n">
+      <c r="D197" s="18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21488,7 +21235,7 @@
           <t>Viajeros Mobile</t>
         </is>
       </c>
-      <c r="D198" s="16" t="n">
+      <c r="D198" s="18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21508,7 +21255,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D199" s="16" t="n">
+      <c r="D199" s="18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21528,7 +21275,7 @@
           <t>Pasajeros</t>
         </is>
       </c>
-      <c r="D200" s="16" t="n">
+      <c r="D200" s="18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21548,7 +21295,7 @@
           <t>Spinner mesagge</t>
         </is>
       </c>
-      <c r="D201" s="16" t="n">
+      <c r="D201" s="18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -21568,7 +21315,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D202" s="16" t="n">
+      <c r="D202" s="18" t="n">
         <v>174</v>
       </c>
     </row>
@@ -21588,7 +21335,7 @@
           <t>01 Info</t>
         </is>
       </c>
-      <c r="D203" s="16" t="n">
+      <c r="D203" s="18" t="n">
         <v>70</v>
       </c>
     </row>
@@ -21608,7 +21355,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D204" s="16" t="n">
+      <c r="D204" s="18" t="n">
         <v>58</v>
       </c>
     </row>
@@ -21628,7 +21375,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D205" s="16" t="n">
+      <c r="D205" s="18" t="n">
         <v>54</v>
       </c>
     </row>
@@ -21648,7 +21395,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D206" s="16" t="n">
+      <c r="D206" s="18" t="n">
         <v>50</v>
       </c>
     </row>
@@ -21668,7 +21415,7 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D207" s="16" t="n">
+      <c r="D207" s="18" t="n">
         <v>47</v>
       </c>
     </row>
@@ -21688,7 +21435,7 @@
           <t>Trend</t>
         </is>
       </c>
-      <c r="D208" s="16" t="n">
+      <c r="D208" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -21708,7 +21455,7 @@
           <t>A.white</t>
         </is>
       </c>
-      <c r="D209" s="16" t="n">
+      <c r="D209" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -21728,7 +21475,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D210" s="16" t="n">
+      <c r="D210" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21748,7 +21495,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D211" s="16" t="n">
+      <c r="D211" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21768,7 +21515,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D212" s="16" t="n">
+      <c r="D212" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21788,7 +21535,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D213" s="16" t="n">
+      <c r="D213" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21808,7 +21555,7 @@
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="D214" s="16" t="n">
+      <c r="D214" s="18" t="n">
         <v>13</v>
       </c>
     </row>
@@ -21828,7 +21575,7 @@
           <t>send</t>
         </is>
       </c>
-      <c r="D215" s="16" t="n">
+      <c r="D215" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21848,7 +21595,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D216" s="16" t="n">
+      <c r="D216" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21868,7 +21615,7 @@
           <t>resumen</t>
         </is>
       </c>
-      <c r="D217" s="16" t="n">
+      <c r="D217" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -21888,7 +21635,7 @@
           <t>Botón primario</t>
         </is>
       </c>
-      <c r="D218" s="16" t="n">
+      <c r="D218" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21908,7 +21655,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D219" s="16" t="n">
+      <c r="D219" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21928,7 +21675,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D220" s="16" t="n">
+      <c r="D220" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21948,7 +21695,7 @@
           <t>Lock</t>
         </is>
       </c>
-      <c r="D221" s="16" t="n">
+      <c r="D221" s="18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21968,7 +21715,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D222" s="16" t="n">
+      <c r="D222" s="18" t="n">
         <v>155</v>
       </c>
     </row>
@@ -21988,7 +21735,7 @@
           <t>Step 3</t>
         </is>
       </c>
-      <c r="D223" s="16" t="n">
+      <c r="D223" s="18" t="n">
         <v>31</v>
       </c>
     </row>
@@ -22008,7 +21755,7 @@
           <t>Step 1</t>
         </is>
       </c>
-      <c r="D224" s="16" t="n">
+      <c r="D224" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -22028,7 +21775,7 @@
           <t>Step 2</t>
         </is>
       </c>
-      <c r="D225" s="16" t="n">
+      <c r="D225" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -22048,7 +21795,7 @@
           <t>Step 4</t>
         </is>
       </c>
-      <c r="D226" s="16" t="n">
+      <c r="D226" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -22068,7 +21815,7 @@
           <t>Step 5</t>
         </is>
       </c>
-      <c r="D227" s="16" t="n">
+      <c r="D227" s="18" t="n">
         <v>30</v>
       </c>
     </row>
@@ -22088,7 +21835,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D228" s="16" t="n">
+      <c r="D228" s="18" t="n">
         <v>29</v>
       </c>
     </row>
@@ -22108,7 +21855,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D229" s="16" t="n">
+      <c r="D229" s="18" t="n">
         <v>29</v>
       </c>
     </row>
@@ -22128,7 +21875,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D230" s="16" t="n">
+      <c r="D230" s="18" t="n">
         <v>27</v>
       </c>
     </row>
@@ -22148,7 +21895,7 @@
           <t>Cancel Icon</t>
         </is>
       </c>
-      <c r="D231" s="16" t="n">
+      <c r="D231" s="18" t="n">
         <v>26</v>
       </c>
     </row>
@@ -22168,7 +21915,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D232" s="16" t="n">
+      <c r="D232" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -22188,7 +21935,7 @@
           <t>Cargador circular</t>
         </is>
       </c>
-      <c r="D233" s="16" t="n">
+      <c r="D233" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -22208,7 +21955,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D234" s="16" t="n">
+      <c r="D234" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -22228,7 +21975,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D235" s="16" t="n">
+      <c r="D235" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -22248,7 +21995,7 @@
           <t>Close Icon</t>
         </is>
       </c>
-      <c r="D236" s="16" t="n">
+      <c r="D236" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -22268,7 +22015,7 @@
           <t>cloudupload</t>
         </is>
       </c>
-      <c r="D237" s="16" t="n">
+      <c r="D237" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22288,7 +22035,7 @@
           <t>card-selector</t>
         </is>
       </c>
-      <c r="D238" s="16" t="n">
+      <c r="D238" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22308,7 +22055,7 @@
           <t>[SCTR] Planes cotizador</t>
         </is>
       </c>
-      <c r="D239" s="16" t="n">
+      <c r="D239" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22328,7 +22075,7 @@
           <t>description</t>
         </is>
       </c>
-      <c r="D240" s="16" t="n">
+      <c r="D240" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22348,7 +22095,7 @@
           <t>Bullet Icon</t>
         </is>
       </c>
-      <c r="D241" s="16" t="n">
+      <c r="D241" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22368,7 +22115,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D242" s="16" t="n">
+      <c r="D242" s="18" t="n">
         <v>221</v>
       </c>
     </row>
@@ -22388,7 +22135,7 @@
           <t>CardProductPromo</t>
         </is>
       </c>
-      <c r="D243" s="16" t="n">
+      <c r="D243" s="18" t="n">
         <v>206</v>
       </c>
     </row>
@@ -22408,7 +22155,7 @@
           <t>Cotizar</t>
         </is>
       </c>
-      <c r="D244" s="16" t="n">
+      <c r="D244" s="18" t="n">
         <v>110</v>
       </c>
     </row>
@@ -22428,7 +22175,7 @@
           <t>Video</t>
         </is>
       </c>
-      <c r="D245" s="16" t="n">
+      <c r="D245" s="18" t="n">
         <v>110</v>
       </c>
     </row>
@@ -22448,7 +22195,7 @@
           <t>Close Icon</t>
         </is>
       </c>
-      <c r="D246" s="16" t="n">
+      <c r="D246" s="18" t="n">
         <v>101</v>
       </c>
     </row>
@@ -22468,7 +22215,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D247" s="16" t="n">
+      <c r="D247" s="18" t="n">
         <v>83</v>
       </c>
     </row>
@@ -22488,7 +22235,7 @@
           <t>CardMenúMobile</t>
         </is>
       </c>
-      <c r="D248" s="16" t="n">
+      <c r="D248" s="18" t="n">
         <v>79</v>
       </c>
     </row>
@@ -22508,7 +22255,7 @@
           <t>CardMenú</t>
         </is>
       </c>
-      <c r="D249" s="16" t="n">
+      <c r="D249" s="18" t="n">
         <v>77</v>
       </c>
     </row>
@@ -22528,7 +22275,7 @@
           <t>WithoutShieldHeart</t>
         </is>
       </c>
-      <c r="D250" s="16" t="n">
+      <c r="D250" s="18" t="n">
         <v>74</v>
       </c>
     </row>
@@ -22548,7 +22295,7 @@
           <t>ShieldHeart</t>
         </is>
       </c>
-      <c r="D251" s="16" t="n">
+      <c r="D251" s="18" t="n">
         <v>71</v>
       </c>
     </row>
@@ -22568,7 +22315,7 @@
           <t>BotónCategoría</t>
         </is>
       </c>
-      <c r="D252" s="16" t="n">
+      <c r="D252" s="18" t="n">
         <v>69</v>
       </c>
     </row>
@@ -22588,7 +22335,7 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="D253" s="16" t="n">
+      <c r="D253" s="18" t="n">
         <v>64</v>
       </c>
     </row>
@@ -22608,7 +22355,7 @@
           <t>_Link Icon</t>
         </is>
       </c>
-      <c r="D254" s="16" t="n">
+      <c r="D254" s="18" t="n">
         <v>54</v>
       </c>
     </row>
@@ -22628,7 +22375,7 @@
           <t>_Button Icon</t>
         </is>
       </c>
-      <c r="D255" s="16" t="n">
+      <c r="D255" s="18" t="n">
         <v>54</v>
       </c>
     </row>
@@ -22648,7 +22395,7 @@
           <t>submenu</t>
         </is>
       </c>
-      <c r="D256" s="16" t="n">
+      <c r="D256" s="18" t="n">
         <v>48</v>
       </c>
     </row>
@@ -22668,7 +22415,7 @@
           <t>Car</t>
         </is>
       </c>
-      <c r="D257" s="16" t="n">
+      <c r="D257" s="18" t="n">
         <v>48</v>
       </c>
     </row>
@@ -22688,7 +22435,7 @@
           <t>Trend</t>
         </is>
       </c>
-      <c r="D258" s="16" t="n">
+      <c r="D258" s="18" t="n">
         <v>46</v>
       </c>
     </row>
@@ -22708,7 +22455,7 @@
           <t>MedicalService</t>
         </is>
       </c>
-      <c r="D259" s="16" t="n">
+      <c r="D259" s="18" t="n">
         <v>46</v>
       </c>
     </row>
@@ -22728,7 +22475,7 @@
           <t>Link Stamp</t>
         </is>
       </c>
-      <c r="D260" s="16" t="n">
+      <c r="D260" s="18" t="n">
         <v>36</v>
       </c>
     </row>
@@ -22748,7 +22495,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D261" s="16" t="n">
+      <c r="D261" s="18" t="n">
         <v>35</v>
       </c>
     </row>
@@ -22768,7 +22515,7 @@
           <t>icon</t>
         </is>
       </c>
-      <c r="D262" s="16" t="n">
+      <c r="D262" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -22788,7 +22535,7 @@
           <t>SecciónDescripción</t>
         </is>
       </c>
-      <c r="D263" s="16" t="n">
+      <c r="D263" s="18" t="n">
         <v>21</v>
       </c>
     </row>
@@ -22808,7 +22555,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D264" s="16" t="n">
+      <c r="D264" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -22828,7 +22575,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D265" s="16" t="n">
+      <c r="D265" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -22848,7 +22595,7 @@
           <t>WithoutShieldHeart</t>
         </is>
       </c>
-      <c r="D266" s="16" t="n">
+      <c r="D266" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -22868,7 +22615,7 @@
           <t>SeccionCanales</t>
         </is>
       </c>
-      <c r="D267" s="16" t="n">
+      <c r="D267" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22888,7 +22635,7 @@
           <t>PersonalInjuy</t>
         </is>
       </c>
-      <c r="D268" s="16" t="n">
+      <c r="D268" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -22908,7 +22655,7 @@
           <t>Information</t>
         </is>
       </c>
-      <c r="D269" s="16" t="n">
+      <c r="D269" s="18" t="n">
         <v>11</v>
       </c>
     </row>
@@ -22928,7 +22675,7 @@
           <t>LogosCollab</t>
         </is>
       </c>
-      <c r="D270" s="16" t="n">
+      <c r="D270" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22948,7 +22695,7 @@
           <t>CoberturasIconos</t>
         </is>
       </c>
-      <c r="D271" s="16" t="n">
+      <c r="D271" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -22968,7 +22715,7 @@
           <t>Scroll</t>
         </is>
       </c>
-      <c r="D272" s="16" t="n">
+      <c r="D272" s="18" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22988,7 +22735,7 @@
           <t>Complex</t>
         </is>
       </c>
-      <c r="D273" s="16" t="n">
+      <c r="D273" s="18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -23008,7 +22755,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D274" s="16" t="n">
+      <c r="D274" s="18" t="n">
         <v>6</v>
       </c>
     </row>
@@ -23028,7 +22775,7 @@
           <t>problema eléctrico</t>
         </is>
       </c>
-      <c r="D275" s="16" t="n">
+      <c r="D275" s="18" t="n">
         <v>5</v>
       </c>
     </row>
@@ -23048,7 +22795,7 @@
           <t>robo de autopartes</t>
         </is>
       </c>
-      <c r="D276" s="16" t="n">
+      <c r="D276" s="18" t="n">
         <v>4</v>
       </c>
     </row>
@@ -23068,7 +22815,7 @@
           <t>avión</t>
         </is>
       </c>
-      <c r="D277" s="16" t="n">
+      <c r="D277" s="18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23088,7 +22835,7 @@
           <t>generales</t>
         </is>
       </c>
-      <c r="D278" s="16" t="n">
+      <c r="D278" s="18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23108,7 +22855,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D279" s="16" t="n">
+      <c r="D279" s="18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23128,7 +22875,7 @@
           <t>fractura</t>
         </is>
       </c>
-      <c r="D280" s="16" t="n">
+      <c r="D280" s="18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23148,7 +22895,7 @@
           <t>doctor</t>
         </is>
       </c>
-      <c r="D281" s="16" t="n">
+      <c r="D281" s="18" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23163,7 +22910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -23171,7 +22918,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -23205,7 +22952,7 @@
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Detach %</t>
+          <t>Desvinculaciones Q</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
@@ -23245,15 +22992,13 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="F2" s="12" t="n">
+        <v>615</v>
       </c>
       <c r="G2" s="6" t="n">
         <v>0</v>
@@ -23268,7 +23013,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Auto Efectivo</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -23278,43 +23023,41 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>530</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>9789</v>
+        <v>0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>15276</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -23324,38 +23067,38 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E4" s="10" t="inlineStr">
-        <is>
-          <t>88%</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>64%</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="6" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>1424</v>
+        <v>9789</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>1625</v>
+        <v>15276</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>MEP</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -23368,76 +23111,74 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
-      </c>
-      <c r="F5" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>34</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>3018</v>
+        <v>1424</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5891</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>65%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>14419</v>
+        <v>1424</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>22099</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -23450,76 +23191,74 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>22</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>172970</v>
+        <v>3018</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>184326</v>
+        <v>5891</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>84%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>51%</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>8539</v>
+        <v>3084</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>10226</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -23532,76 +23271,74 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>7739</v>
+        <v>14419</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>8560</v>
+        <v>22099</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>75%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>65%</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1583</v>
+        <v>14419</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2109</v>
+        <v>22099</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Somos Corredores</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Somos Corredores</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -23614,76 +23351,74 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>17</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>3852</v>
+        <v>172970</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>4452</v>
+        <v>184326</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>94%</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G12" s="6" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>3906</v>
+        <v>172970</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>4593</v>
+        <v>184326</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -23696,76 +23431,74 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>2286</v>
+        <v>8539</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>3132</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>69%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>84%</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>2650</v>
+        <v>8539</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>3813</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -23778,105 +23511,690 @@
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>317</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>11370</v>
+        <v>7739</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>12076</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Q2 2026</t>
+          <t>Q3 2026</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>85%</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>90%</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="6" t="n">
         <v>8</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>3566</v>
+        <v>7739</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>4204</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
+          <t>SOAT</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>1583</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SOAT</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1583</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>3852</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>3852</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>3906</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>VDT</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>3906</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>2286</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>2286</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>2650</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Vehicular Todo Riesgo</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>2650</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>3813</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Venta Directa</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>11370</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Venta Directa</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>11370</v>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>12076</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Q2 2026</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>615</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>3566</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Viajes</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>3566</v>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>4204</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>Web Corporativa</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Web Corporativa</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Q2 2026</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E31" s="11" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n">
+      <c r="F31" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="G31" s="6" t="n">
         <v>73</v>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H31" s="7" t="n">
         <v>11472</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I31" s="6" t="n">
+        <v>13594</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Q3 2026</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>11472</v>
+      </c>
+      <c r="I32" s="6" t="n">
         <v>13594</v>
       </c>
     </row>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -666,10 +666,8 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I5" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -703,10 +701,8 @@
           <t>87%</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I6" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -724,26 +720,24 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>7739</v>
+        <v>4898</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>821</v>
+        <v>673</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -777,10 +771,8 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I8" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -814,10 +806,8 @@
           <t>84%</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I9" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -851,10 +841,8 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I10" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -1082,20 +1070,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>11370</v>
+        <v>6030</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>706</v>
+        <v>332</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>35</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="I17" s="12" t="n">
@@ -1117,20 +1105,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>11472</v>
+        <v>359</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2122</v>
+        <v>53</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1154,26 +1142,24 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1424</v>
+        <v>296</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1501,20 +1487,20 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>7035</v>
+        <v>4194</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>634</v>
+        <v>486</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>90%</t>
         </is>
       </c>
     </row>
@@ -1943,20 +1929,20 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>11370</v>
+        <v>6030</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>706</v>
+        <v>332</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>35</v>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
     </row>
@@ -1977,16 +1963,16 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>5448</v>
+        <v>359</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>787</v>
+        <v>53</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
@@ -2011,20 +1997,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4605</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1163</v>
+        <v>0</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>80%</t>
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2045,20 +2031,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>1419</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>21</v>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2079,20 +2065,20 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1424</v>
+        <v>296</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2143,11 +2129,81 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>MEP</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Somos Corredores</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Protege 365</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Nueva Web Empresas</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Portal Digital de Siniestros</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Modelo Día</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Ecommerce</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
         <v>530</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2217,14 +2273,14 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>288</v>
+        <v>485</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>2351</v>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -2235,32 +2291,32 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>4229</v>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Modal Informative</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>775</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>6.96%</t>
         </is>
       </c>
     </row>
@@ -2271,25 +2327,25 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>220</v>
+        <v>71255</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>9.84%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
@@ -2303,18 +2359,18 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Radio Atom</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>3758</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -2325,158 +2381,158 @@
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>6</v>
+        <v>891</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>3.68%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Radio Atom</t>
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>8726</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Checkbox With Text</t>
+          <t>Chips Status</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>16</v>
+        <v>11044</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>38.46%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Checkbox Atom</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1408</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>129</v>
+        <v>1000</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>6.52%</t>
+          <t>2.06%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Chips Status</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>2</v>
+        <v>17659</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Checkbox With Text</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0</v>
+        <v>4138</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Simple</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>28</v>
+        <v>1261</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t>15.15%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Stepper Desktop</t>
+          <t>Checkbox Atom</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>14</v>
+        <v>3791</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>17.65%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E590"/>
+  <dimension ref="A1:E546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5204,7 +5260,7 @@
         </is>
       </c>
       <c r="E108" s="7" t="n">
-        <v>2688</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="109">
@@ -5225,11 +5281,11 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>640</v>
+        <v>489</v>
       </c>
     </row>
     <row r="110">
@@ -5250,11 +5306,11 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
-        <v>634</v>
+        <v>480</v>
       </c>
     </row>
     <row r="111">
@@ -5275,11 +5331,11 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>448</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112">
@@ -5300,11 +5356,11 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
-        <v>280</v>
+        <v>208</v>
       </c>
     </row>
     <row r="113">
@@ -5325,11 +5381,11 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>262</v>
+        <v>173</v>
       </c>
     </row>
     <row r="114">
@@ -5350,11 +5406,11 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
-        <v>224</v>
+        <v>138</v>
       </c>
     </row>
     <row r="115">
@@ -5375,11 +5431,11 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>219</v>
+        <v>130</v>
       </c>
     </row>
     <row r="116">
@@ -5400,11 +5456,11 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
-        <v>186</v>
+        <v>120</v>
       </c>
     </row>
     <row r="117">
@@ -5425,11 +5481,11 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
-        <v>160</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118">
@@ -5450,11 +5506,11 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="119">
@@ -5479,7 +5535,7 @@
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="120">
@@ -5500,11 +5556,11 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Beneficio | card</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121">
@@ -5525,11 +5581,11 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>105</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122">
@@ -5550,11 +5606,11 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="123">
@@ -5575,11 +5631,11 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Beneficio | card</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
     </row>
     <row r="124">
@@ -5600,11 +5656,11 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125">
@@ -5625,11 +5681,11 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126">
@@ -5650,11 +5706,11 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="127">
@@ -5675,11 +5731,11 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="128">
@@ -5700,11 +5756,11 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="129">
@@ -5725,11 +5781,11 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Banner | errores</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="130">
@@ -5750,11 +5806,11 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131">
@@ -5775,11 +5831,11 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="132">
@@ -5800,11 +5856,11 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Banner | errores</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133">
@@ -5825,11 +5881,11 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134">
@@ -5850,11 +5906,11 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
@@ -5875,11 +5931,11 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136">
@@ -5900,11 +5956,11 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
@@ -5925,11 +5981,11 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
@@ -5950,11 +6006,11 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139">
@@ -5979,7 +6035,7 @@
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
@@ -6000,11 +6056,11 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -6025,11 +6081,11 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
@@ -6054,7 +6110,7 @@
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -6075,61 +6131,61 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Web Privada</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
-        <v>2</v>
+        <v>9216</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Protege 365</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Web Privada</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="146">
@@ -6150,11 +6206,11 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
-        <v>9216</v>
+        <v>960</v>
       </c>
     </row>
     <row r="147">
@@ -6175,11 +6231,11 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>1536</v>
+        <v>768</v>
       </c>
     </row>
     <row r="148">
@@ -6200,11 +6256,11 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
-        <v>960</v>
+        <v>493</v>
       </c>
     </row>
     <row r="149">
@@ -6225,11 +6281,11 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
-        <v>768</v>
+        <v>384</v>
       </c>
     </row>
     <row r="150">
@@ -6250,11 +6306,11 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
-        <v>493</v>
+        <v>295</v>
       </c>
     </row>
     <row r="151">
@@ -6275,11 +6331,11 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>384</v>
+        <v>295</v>
       </c>
     </row>
     <row r="152">
@@ -6300,7 +6356,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -6325,11 +6381,11 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>295</v>
+        <v>200</v>
       </c>
     </row>
     <row r="154">
@@ -6350,11 +6406,11 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
-        <v>295</v>
+        <v>192</v>
       </c>
     </row>
     <row r="155">
@@ -6375,11 +6431,11 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>200</v>
+        <v>96</v>
       </c>
     </row>
     <row r="156">
@@ -6400,11 +6456,11 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
-        <v>192</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157">
@@ -6425,7 +6481,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -6450,11 +6506,11 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="159">
@@ -6475,11 +6531,11 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
     </row>
     <row r="160">
@@ -6500,11 +6556,11 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="161">
@@ -6525,11 +6581,11 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="162">
@@ -6550,11 +6606,11 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163">
@@ -6575,11 +6631,11 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164">
@@ -6600,11 +6656,11 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165">
@@ -6625,11 +6681,11 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166">
@@ -6650,11 +6706,11 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167">
@@ -6675,11 +6731,11 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -6700,7 +6756,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -6725,7 +6781,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -6750,7 +6806,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -6775,11 +6831,11 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172">
@@ -6800,11 +6856,11 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -6820,16 +6876,16 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>Home Empresas</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>1</v>
+        <v>87113</v>
       </c>
     </row>
     <row r="174">
@@ -6845,16 +6901,16 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>Home Empresas</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
-        <v>1</v>
+        <v>15407</v>
       </c>
     </row>
     <row r="175">
@@ -6875,11 +6931,11 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>87113</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="176">
@@ -6900,11 +6956,11 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
-        <v>15407</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="177">
@@ -6925,11 +6981,11 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>8152</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="178">
@@ -6950,11 +7006,11 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
-        <v>7872</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="179">
@@ -6975,11 +7031,11 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>7423</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="180">
@@ -7000,11 +7056,11 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
-        <v>5251</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="181">
@@ -7025,11 +7081,11 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>3935</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="182">
@@ -7050,11 +7106,11 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
-        <v>3067</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="183">
@@ -7075,11 +7131,11 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>2281</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="184">
@@ -7100,11 +7156,11 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
-        <v>1676</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="185">
@@ -7125,11 +7181,11 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>1554</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="186">
@@ -7150,11 +7206,11 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
-        <v>1536</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="187">
@@ -7175,11 +7231,11 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>1278</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="188">
@@ -7200,11 +7256,11 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
-        <v>1241</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="189">
@@ -7225,11 +7281,11 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>1166</v>
+        <v>984</v>
       </c>
     </row>
     <row r="190">
@@ -7250,11 +7306,11 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
-        <v>1095</v>
+        <v>984</v>
       </c>
     </row>
     <row r="191">
@@ -7275,11 +7331,11 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
-        <v>984</v>
+        <v>948</v>
       </c>
     </row>
     <row r="192">
@@ -7300,11 +7356,11 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
-        <v>984</v>
+        <v>780</v>
       </c>
     </row>
     <row r="193">
@@ -7325,11 +7381,11 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>948</v>
+        <v>762</v>
       </c>
     </row>
     <row r="194">
@@ -7350,11 +7406,11 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
-        <v>780</v>
+        <v>759</v>
       </c>
     </row>
     <row r="195">
@@ -7375,11 +7431,11 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E195" s="7" t="n">
-        <v>762</v>
+        <v>397</v>
       </c>
     </row>
     <row r="196">
@@ -7400,11 +7456,11 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
-        <v>759</v>
+        <v>364</v>
       </c>
     </row>
     <row r="197">
@@ -7425,11 +7481,11 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
-        <v>397</v>
+        <v>329</v>
       </c>
     </row>
     <row r="198">
@@ -7450,11 +7506,11 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
-        <v>364</v>
+        <v>280</v>
       </c>
     </row>
     <row r="199">
@@ -7475,11 +7531,11 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E199" s="7" t="n">
-        <v>329</v>
+        <v>222</v>
       </c>
     </row>
     <row r="200">
@@ -7500,11 +7556,11 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
-        <v>280</v>
+        <v>217</v>
       </c>
     </row>
     <row r="201">
@@ -7525,11 +7581,11 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E201" s="7" t="n">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="202">
@@ -7550,11 +7606,11 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
-        <v>217</v>
+        <v>97</v>
       </c>
     </row>
     <row r="203">
@@ -7575,11 +7631,11 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E203" s="7" t="n">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="204">
@@ -7600,11 +7656,11 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="205">
@@ -7625,11 +7681,11 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E205" s="7" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="206">
@@ -7650,11 +7706,11 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="207">
@@ -7675,11 +7731,11 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E207" s="7" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="208">
@@ -7700,11 +7756,11 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="209">
@@ -7725,11 +7781,11 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E209" s="7" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="210">
@@ -7750,11 +7806,11 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="211">
@@ -7775,11 +7831,11 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E211" s="7" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212">
@@ -7800,11 +7856,11 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="213">
@@ -7825,11 +7881,11 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E213" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214">
@@ -7850,61 +7906,61 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Home Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E215" s="7" t="n">
-        <v>10</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Home Empresas</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
-        <v>6</v>
+        <v>998</v>
       </c>
     </row>
     <row r="217">
@@ -7925,11 +7981,11 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E217" s="7" t="n">
-        <v>1440</v>
+        <v>993</v>
       </c>
     </row>
     <row r="218">
@@ -7950,11 +8006,11 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
-        <v>998</v>
+        <v>976</v>
       </c>
     </row>
     <row r="219">
@@ -7975,11 +8031,11 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E219" s="7" t="n">
-        <v>993</v>
+        <v>756</v>
       </c>
     </row>
     <row r="220">
@@ -8000,11 +8056,11 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
-        <v>976</v>
+        <v>390</v>
       </c>
     </row>
     <row r="221">
@@ -8025,11 +8081,11 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E221" s="7" t="n">
-        <v>756</v>
+        <v>390</v>
       </c>
     </row>
     <row r="222">
@@ -8050,11 +8106,11 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
-        <v>390</v>
+        <v>289</v>
       </c>
     </row>
     <row r="223">
@@ -8075,11 +8131,11 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>390</v>
+        <v>266</v>
       </c>
     </row>
     <row r="224">
@@ -8100,11 +8156,11 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
-        <v>289</v>
+        <v>240</v>
       </c>
     </row>
     <row r="225">
@@ -8125,11 +8181,11 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>266</v>
+        <v>229</v>
       </c>
     </row>
     <row r="226">
@@ -8150,11 +8206,11 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="227">
@@ -8175,11 +8231,11 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
-        <v>229</v>
+        <v>204</v>
       </c>
     </row>
     <row r="228">
@@ -8200,11 +8256,11 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
-        <v>229</v>
+        <v>199</v>
       </c>
     </row>
     <row r="229">
@@ -8225,11 +8281,11 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
-        <v>204</v>
+        <v>152</v>
       </c>
     </row>
     <row r="230">
@@ -8250,11 +8306,11 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
-        <v>199</v>
+        <v>150</v>
       </c>
     </row>
     <row r="231">
@@ -8275,11 +8331,11 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E231" s="7" t="n">
-        <v>152</v>
+        <v>120</v>
       </c>
     </row>
     <row r="232">
@@ -8300,11 +8356,11 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
     </row>
     <row r="233">
@@ -8325,11 +8381,11 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Card Dashboard</t>
         </is>
       </c>
       <c r="E233" s="7" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
     </row>
     <row r="234">
@@ -8350,11 +8406,11 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="235">
@@ -8375,11 +8431,11 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Card Dashboard</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E235" s="7" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="236">
@@ -8400,11 +8456,11 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="237">
@@ -8425,11 +8481,11 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E237" s="7" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="238">
@@ -8450,11 +8506,11 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="239">
@@ -8475,11 +8531,11 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E239" s="7" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="240">
@@ -8500,11 +8556,11 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="241">
@@ -8525,11 +8581,11 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E241" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="242">
@@ -8550,11 +8606,11 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="243">
@@ -8575,11 +8631,11 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E243" s="7" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="244">
@@ -8600,11 +8656,11 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="245">
@@ -8625,11 +8681,11 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E245" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246">
@@ -8650,11 +8706,11 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247">
@@ -8675,61 +8731,61 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E247" s="7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
-        <v>7</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E249" s="7" t="n">
-        <v>4</v>
+        <v>685</v>
       </c>
     </row>
     <row r="250">
@@ -8750,11 +8806,11 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
-        <v>2929</v>
+        <v>653</v>
       </c>
     </row>
     <row r="251">
@@ -8775,11 +8831,11 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E251" s="7" t="n">
-        <v>685</v>
+        <v>553</v>
       </c>
     </row>
     <row r="252">
@@ -8800,11 +8856,11 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
-        <v>653</v>
+        <v>551</v>
       </c>
     </row>
     <row r="253">
@@ -8825,11 +8881,11 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
-        <v>553</v>
+        <v>512</v>
       </c>
     </row>
     <row r="254">
@@ -8850,11 +8906,11 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
-        <v>551</v>
+        <v>347</v>
       </c>
     </row>
     <row r="255">
@@ -8875,11 +8931,11 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E255" s="7" t="n">
-        <v>512</v>
+        <v>335</v>
       </c>
     </row>
     <row r="256">
@@ -8900,11 +8956,11 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
-        <v>347</v>
+        <v>187</v>
       </c>
     </row>
     <row r="257">
@@ -8925,11 +8981,11 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E257" s="7" t="n">
-        <v>335</v>
+        <v>145</v>
       </c>
     </row>
     <row r="258">
@@ -8950,11 +9006,11 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
     </row>
     <row r="259">
@@ -8975,11 +9031,11 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
-        <v>145</v>
+        <v>120</v>
       </c>
     </row>
     <row r="260">
@@ -9000,11 +9056,11 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
-        <v>139</v>
+        <v>110</v>
       </c>
     </row>
     <row r="261">
@@ -9025,11 +9081,11 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E261" s="7" t="n">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="262">
@@ -9050,11 +9106,11 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="263">
@@ -9075,11 +9131,11 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E263" s="7" t="n">
-        <v>106</v>
+        <v>80</v>
       </c>
     </row>
     <row r="264">
@@ -9100,11 +9156,11 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="265">
@@ -9125,11 +9181,11 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E265" s="7" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
     </row>
     <row r="266">
@@ -9150,11 +9206,11 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="267">
@@ -9175,11 +9231,11 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E267" s="7" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="268">
@@ -9200,11 +9256,11 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="269">
@@ -9225,11 +9281,11 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="270">
@@ -9250,11 +9306,11 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="271">
@@ -9275,11 +9331,11 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E271" s="7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="272">
@@ -9300,11 +9356,11 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="273">
@@ -9325,11 +9381,11 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E273" s="7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="274">
@@ -9350,11 +9406,11 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="275">
@@ -9375,11 +9431,11 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E275" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276">
@@ -9400,11 +9456,11 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277">
@@ -9425,11 +9481,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E277" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278">
@@ -9450,11 +9506,11 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279">
@@ -9475,11 +9531,11 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E279" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="280">
@@ -9500,11 +9556,11 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="281">
@@ -9525,11 +9581,11 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E281" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
@@ -9545,16 +9601,16 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
-        <v>4</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="283">
@@ -9570,16 +9626,16 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E283" s="7" t="n">
-        <v>2</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="284">
@@ -9600,11 +9656,11 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
-        <v>1316</v>
+        <v>531</v>
       </c>
     </row>
     <row r="285">
@@ -9625,11 +9681,11 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E285" s="7" t="n">
-        <v>1258</v>
+        <v>184</v>
       </c>
     </row>
     <row r="286">
@@ -9650,11 +9706,11 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
-        <v>531</v>
+        <v>178</v>
       </c>
     </row>
     <row r="287">
@@ -9675,11 +9731,11 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E287" s="7" t="n">
-        <v>184</v>
+        <v>161</v>
       </c>
     </row>
     <row r="288">
@@ -9700,11 +9756,11 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
     </row>
     <row r="289">
@@ -9725,11 +9781,11 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
-        <v>161</v>
+        <v>107</v>
       </c>
     </row>
     <row r="290">
@@ -9750,11 +9806,11 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
     </row>
     <row r="291">
@@ -9775,11 +9831,11 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
-        <v>107</v>
+        <v>68</v>
       </c>
     </row>
     <row r="292">
@@ -9800,11 +9856,11 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="293">
@@ -9825,11 +9881,11 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E293" s="7" t="n">
-        <v>68</v>
+        <v>36</v>
       </c>
     </row>
     <row r="294">
@@ -9850,11 +9906,11 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
-        <v>64</v>
+        <v>12</v>
       </c>
     </row>
     <row r="295">
@@ -9875,11 +9931,11 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="296">
@@ -9900,11 +9956,11 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="297">
@@ -9925,11 +9981,11 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E297" s="7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="298">
@@ -9950,11 +10006,11 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="299">
@@ -9975,11 +10031,11 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E299" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -10000,7 +10056,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
@@ -10025,7 +10081,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E301" s="7" t="n">
@@ -10050,11 +10106,11 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
@@ -10070,16 +10126,16 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E303" s="7" t="n">
-        <v>3</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="304">
@@ -10095,16 +10151,16 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
-        <v>2</v>
+        <v>209</v>
       </c>
     </row>
     <row r="305">
@@ -10125,11 +10181,11 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>1558</v>
+        <v>113</v>
       </c>
     </row>
     <row r="306">
@@ -10150,11 +10206,11 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>209</v>
+        <v>80</v>
       </c>
     </row>
     <row r="307">
@@ -10175,11 +10231,11 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="308">
@@ -10200,11 +10256,11 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="309">
@@ -10225,11 +10281,11 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
     </row>
     <row r="310">
@@ -10250,11 +10306,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="311">
@@ -10275,11 +10331,11 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="312">
@@ -10300,11 +10356,11 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="313">
@@ -10325,7 +10381,7 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
@@ -10350,11 +10406,11 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315">
@@ -10375,11 +10431,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="316">
@@ -10400,11 +10456,11 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="317">
@@ -10425,11 +10481,11 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318">
@@ -10450,11 +10506,11 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="319">
@@ -10475,11 +10531,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320">
@@ -10500,11 +10556,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="321">
@@ -10525,11 +10581,11 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E321" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="322">
@@ -10550,11 +10606,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323">
@@ -10575,11 +10631,11 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="324">
@@ -10600,11 +10656,11 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="325">
@@ -10625,7 +10681,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E325" s="7" t="n">
@@ -10650,11 +10706,11 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -10675,11 +10731,11 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E327" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="328">
@@ -10700,11 +10756,11 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
@@ -10725,11 +10781,11 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E329" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -10750,11 +10806,11 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -10775,7 +10831,7 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E331" s="7" t="n">
@@ -10800,7 +10856,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
@@ -10810,51 +10866,51 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E333" s="7" t="n">
-        <v>1</v>
+        <v>305</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
-        <v>1</v>
+        <v>243</v>
       </c>
     </row>
     <row r="335">
@@ -10875,11 +10931,11 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
-        <v>305</v>
+        <v>164</v>
       </c>
     </row>
     <row r="336">
@@ -10900,11 +10956,11 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
-        <v>243</v>
+        <v>110</v>
       </c>
     </row>
     <row r="337">
@@ -10925,11 +10981,11 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E337" s="7" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
     </row>
     <row r="338">
@@ -10950,11 +11006,11 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
-        <v>110</v>
+        <v>76</v>
       </c>
     </row>
     <row r="339">
@@ -10975,11 +11031,11 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E339" s="7" t="n">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="340">
@@ -11000,11 +11056,11 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="341">
@@ -11025,11 +11081,11 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E341" s="7" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="342">
@@ -11050,11 +11106,11 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="343">
@@ -11075,11 +11131,11 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E343" s="7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="344">
@@ -11100,11 +11156,11 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="345">
@@ -11125,11 +11181,11 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E345" s="7" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="346">
@@ -11150,11 +11206,11 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="347">
@@ -11175,11 +11231,11 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E347" s="7" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="348">
@@ -11200,11 +11256,11 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349">
@@ -11225,11 +11281,11 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
@@ -11250,7 +11306,7 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
@@ -11275,11 +11331,11 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E351" s="7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="352">
@@ -11300,11 +11356,11 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="353">
@@ -11325,11 +11381,11 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E353" s="7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="354">
@@ -11350,11 +11406,11 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="355">
@@ -11375,11 +11431,11 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E355" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="356">
@@ -11400,11 +11456,11 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="357">
@@ -11425,11 +11481,11 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E357" s="7" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -11450,11 +11506,11 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -11475,11 +11531,11 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E359" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
@@ -11490,21 +11546,21 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
-        <v>2</v>
+        <v>432</v>
       </c>
     </row>
     <row r="361">
@@ -11515,21 +11571,21 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E361" s="7" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
     </row>
     <row r="362">
@@ -11550,11 +11606,11 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>432</v>
+        <v>196</v>
       </c>
     </row>
     <row r="363">
@@ -11575,11 +11631,11 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>213</v>
+        <v>176</v>
       </c>
     </row>
     <row r="364">
@@ -11600,11 +11656,11 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>196</v>
+        <v>149</v>
       </c>
     </row>
     <row r="365">
@@ -11625,11 +11681,11 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E365" s="7" t="n">
-        <v>176</v>
+        <v>124</v>
       </c>
     </row>
     <row r="366">
@@ -11650,11 +11706,11 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="367">
@@ -11675,11 +11731,11 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E367" s="7" t="n">
-        <v>124</v>
+        <v>114</v>
       </c>
     </row>
     <row r="368">
@@ -11700,11 +11756,11 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E368" s="7" t="n">
-        <v>122</v>
+        <v>102</v>
       </c>
     </row>
     <row r="369">
@@ -11725,11 +11781,11 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>114</v>
+        <v>92</v>
       </c>
     </row>
     <row r="370">
@@ -11750,11 +11806,11 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E370" s="7" t="n">
-        <v>102</v>
+        <v>82</v>
       </c>
     </row>
     <row r="371">
@@ -11775,11 +11831,11 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E371" s="7" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="372">
@@ -11800,11 +11856,11 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
     </row>
     <row r="373">
@@ -11825,11 +11881,11 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E373" s="7" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="374">
@@ -11850,11 +11906,11 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E374" s="7" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="375">
@@ -11875,11 +11931,11 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E375" s="7" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
     </row>
     <row r="376">
@@ -11900,11 +11956,11 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E376" s="7" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="377">
@@ -11925,11 +11981,11 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E377" s="7" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
     </row>
     <row r="378">
@@ -11950,11 +12006,11 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E378" s="7" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
     </row>
     <row r="379">
@@ -11975,11 +12031,11 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E379" s="7" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="380">
@@ -12000,11 +12056,11 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E380" s="7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="381">
@@ -12025,11 +12081,11 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E381" s="7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="382">
@@ -12050,11 +12106,11 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E382" s="7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="383">
@@ -12075,11 +12131,11 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E383" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="384">
@@ -12100,11 +12156,11 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E384" s="7" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="385">
@@ -12125,11 +12181,11 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E385" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="386">
@@ -12150,11 +12206,11 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E386" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="387">
@@ -12175,11 +12231,11 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="388">
@@ -12190,21 +12246,21 @@
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>5</v>
+        <v>597</v>
       </c>
     </row>
     <row r="389">
@@ -12215,21 +12271,21 @@
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E389" s="7" t="n">
-        <v>2</v>
+        <v>331</v>
       </c>
     </row>
     <row r="390">
@@ -12250,11 +12306,11 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>597</v>
+        <v>327</v>
       </c>
     </row>
     <row r="391">
@@ -12275,11 +12331,11 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>331</v>
+        <v>276</v>
       </c>
     </row>
     <row r="392">
@@ -12300,11 +12356,11 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>327</v>
+        <v>166</v>
       </c>
     </row>
     <row r="393">
@@ -12325,11 +12381,11 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>276</v>
+        <v>151</v>
       </c>
     </row>
     <row r="394">
@@ -12350,11 +12406,11 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>166</v>
+        <v>116</v>
       </c>
     </row>
     <row r="395">
@@ -12375,11 +12431,11 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>151</v>
+        <v>70</v>
       </c>
     </row>
     <row r="396">
@@ -12400,11 +12456,11 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>116</v>
+        <v>60</v>
       </c>
     </row>
     <row r="397">
@@ -12425,11 +12481,11 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="398">
@@ -12450,11 +12506,11 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="399">
@@ -12475,11 +12531,11 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="400">
@@ -12500,7 +12556,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
@@ -12525,7 +12581,7 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
@@ -12550,7 +12606,7 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
@@ -12575,11 +12631,11 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="404">
@@ -12600,11 +12656,11 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="405">
@@ -12625,11 +12681,11 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="406">
@@ -12650,11 +12706,11 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="407">
@@ -12675,11 +12731,11 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="408">
@@ -12700,11 +12756,11 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="409">
@@ -12725,11 +12781,11 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="410">
@@ -12750,11 +12806,11 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="411">
@@ -12775,11 +12831,11 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
     </row>
     <row r="412">
@@ -12800,11 +12856,11 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="413">
@@ -12825,11 +12881,11 @@
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="414">
@@ -12850,7 +12906,7 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
@@ -12875,11 +12931,11 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="416">
@@ -12900,11 +12956,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="417">
@@ -12915,21 +12971,21 @@
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>2</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="418">
@@ -12940,21 +12996,21 @@
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>2</v>
+        <v>340</v>
       </c>
     </row>
     <row r="419">
@@ -12975,11 +13031,11 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>1536</v>
+        <v>256</v>
       </c>
     </row>
     <row r="420">
@@ -13000,11 +13056,11 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>340</v>
+        <v>251</v>
       </c>
     </row>
     <row r="421">
@@ -13025,11 +13081,11 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>256</v>
+        <v>160</v>
       </c>
     </row>
     <row r="422">
@@ -13050,11 +13106,11 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>251</v>
+        <v>149</v>
       </c>
     </row>
     <row r="423">
@@ -13075,11 +13131,11 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>160</v>
+        <v>128</v>
       </c>
     </row>
     <row r="424">
@@ -13100,11 +13156,11 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="425">
@@ -13125,11 +13181,11 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="426">
@@ -13150,11 +13206,11 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
-        <v>122</v>
+        <v>78</v>
       </c>
     </row>
     <row r="427">
@@ -13175,11 +13231,11 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="428">
@@ -13200,11 +13256,11 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="429">
@@ -13225,11 +13281,11 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="430">
@@ -13250,11 +13306,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="431">
@@ -13275,11 +13331,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="432">
@@ -13300,11 +13356,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="433">
@@ -13325,11 +13381,11 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="434">
@@ -13350,11 +13406,11 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="435">
@@ -13375,11 +13431,11 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="436">
@@ -13400,11 +13456,11 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="437">
@@ -13425,11 +13481,11 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="438">
@@ -13450,11 +13506,11 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="439">
@@ -13475,11 +13531,11 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="440">
@@ -13500,11 +13556,11 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="441">
@@ -13525,7 +13581,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
@@ -13550,11 +13606,11 @@
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="443">
@@ -13575,11 +13631,11 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="444">
@@ -13600,11 +13656,11 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="445">
@@ -13625,11 +13681,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="446">
@@ -13640,21 +13696,21 @@
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>9</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="447">
@@ -13665,21 +13721,21 @@
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>6</v>
+        <v>618</v>
       </c>
     </row>
     <row r="448">
@@ -13700,11 +13756,11 @@
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>1152</v>
+        <v>440</v>
       </c>
     </row>
     <row r="449">
@@ -13725,11 +13781,11 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>618</v>
+        <v>375</v>
       </c>
     </row>
     <row r="450">
@@ -13750,11 +13806,11 @@
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>440</v>
+        <v>192</v>
       </c>
     </row>
     <row r="451">
@@ -13775,11 +13831,11 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>375</v>
+        <v>120</v>
       </c>
     </row>
     <row r="452">
@@ -13800,11 +13856,11 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>192</v>
+        <v>104</v>
       </c>
     </row>
     <row r="453">
@@ -13825,11 +13881,11 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="454">
@@ -13850,11 +13906,11 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
     </row>
     <row r="455">
@@ -13875,11 +13931,11 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="456">
@@ -13900,11 +13956,11 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="457">
@@ -13925,11 +13981,11 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="458">
@@ -13950,11 +14006,11 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="459">
@@ -13975,11 +14031,11 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>71</v>
+        <v>57</v>
       </c>
     </row>
     <row r="460">
@@ -14000,11 +14056,11 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
     </row>
     <row r="461">
@@ -14025,11 +14081,11 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="462">
@@ -14050,11 +14106,11 @@
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="463">
@@ -14075,11 +14131,11 @@
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="464">
@@ -14100,11 +14156,11 @@
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="465">
@@ -14125,11 +14181,11 @@
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="466">
@@ -14150,11 +14206,11 @@
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="467">
@@ -14175,11 +14231,11 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="468">
@@ -14200,11 +14256,11 @@
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="469">
@@ -14225,11 +14281,11 @@
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="470">
@@ -14250,11 +14306,11 @@
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="471">
@@ -14275,7 +14331,7 @@
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
@@ -14300,11 +14356,11 @@
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="473">
@@ -14325,11 +14381,11 @@
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="474">
@@ -14350,11 +14406,11 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="475">
@@ -14365,21 +14421,21 @@
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>6</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="476">
@@ -14390,21 +14446,21 @@
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E476" s="7" t="n">
-        <v>4</v>
+        <v>576</v>
       </c>
     </row>
     <row r="477">
@@ -14425,11 +14481,11 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E477" s="7" t="n">
-        <v>6432</v>
+        <v>360</v>
       </c>
     </row>
     <row r="478">
@@ -14450,11 +14506,11 @@
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E478" s="7" t="n">
-        <v>1072</v>
+        <v>288</v>
       </c>
     </row>
     <row r="479">
@@ -14475,11 +14531,11 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E479" s="7" t="n">
-        <v>670</v>
+        <v>205</v>
       </c>
     </row>
     <row r="480">
@@ -14500,11 +14556,11 @@
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E480" s="7" t="n">
-        <v>536</v>
+        <v>144</v>
       </c>
     </row>
     <row r="481">
@@ -14525,11 +14581,11 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E481" s="7" t="n">
-        <v>409</v>
+        <v>83</v>
       </c>
     </row>
     <row r="482">
@@ -14550,11 +14606,11 @@
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E482" s="7" t="n">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="483">
@@ -14575,11 +14631,11 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E483" s="7" t="n">
-        <v>171</v>
+        <v>75</v>
       </c>
     </row>
     <row r="484">
@@ -14600,11 +14656,11 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E484" s="7" t="n">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="485">
@@ -14625,11 +14681,11 @@
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E485" s="7" t="n">
-        <v>151</v>
+        <v>73</v>
       </c>
     </row>
     <row r="486">
@@ -14650,11 +14706,11 @@
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E486" s="7" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
     </row>
     <row r="487">
@@ -14675,11 +14731,11 @@
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E487" s="7" t="n">
-        <v>149</v>
+        <v>48</v>
       </c>
     </row>
     <row r="488">
@@ -14700,11 +14756,11 @@
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E488" s="7" t="n">
-        <v>134</v>
+        <v>45</v>
       </c>
     </row>
     <row r="489">
@@ -14725,11 +14781,11 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E489" s="7" t="n">
-        <v>101</v>
+        <v>44</v>
       </c>
     </row>
     <row r="490">
@@ -14750,11 +14806,11 @@
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E490" s="7" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="491">
@@ -14775,11 +14831,11 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E491" s="7" t="n">
-        <v>81</v>
+        <v>37</v>
       </c>
     </row>
     <row r="492">
@@ -14800,11 +14856,11 @@
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E492" s="7" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="493">
@@ -14825,11 +14881,11 @@
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E493" s="7" t="n">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="494">
@@ -14850,11 +14906,11 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E494" s="7" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="495">
@@ -14875,11 +14931,11 @@
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E495" s="7" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="496">
@@ -14900,11 +14956,11 @@
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E496" s="7" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="497">
@@ -14925,11 +14981,11 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E497" s="7" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
     </row>
     <row r="498">
@@ -14950,11 +15006,11 @@
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E498" s="7" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="499">
@@ -14975,11 +15031,11 @@
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E499" s="7" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="500">
@@ -15000,11 +15056,11 @@
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E500" s="7" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="501">
@@ -15025,11 +15081,11 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E501" s="7" t="n">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="502">
@@ -15050,11 +15106,11 @@
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="503">
@@ -15075,11 +15131,11 @@
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="504">
@@ -15100,11 +15156,11 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="505">
@@ -15125,11 +15181,11 @@
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="506">
@@ -15150,11 +15206,11 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="507">
@@ -15175,11 +15231,11 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="508">
@@ -15200,11 +15256,11 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="509">
@@ -15225,61 +15281,61 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C510" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="512">
@@ -15300,11 +15356,11 @@
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>1045</v>
+        <v>47</v>
       </c>
     </row>
     <row r="513">
@@ -15325,11 +15381,11 @@
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>959</v>
+        <v>34</v>
       </c>
     </row>
     <row r="514">
@@ -15350,11 +15406,11 @@
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>870</v>
+        <v>31</v>
       </c>
     </row>
     <row r="515">
@@ -15375,11 +15431,11 @@
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>699</v>
+        <v>27</v>
       </c>
     </row>
     <row r="516">
@@ -15400,11 +15456,11 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>506</v>
+        <v>15</v>
       </c>
     </row>
     <row r="517">
@@ -15425,11 +15481,11 @@
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>444</v>
+        <v>12</v>
       </c>
     </row>
     <row r="518">
@@ -15450,11 +15506,11 @@
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>230</v>
+        <v>10</v>
       </c>
     </row>
     <row r="519">
@@ -15475,11 +15531,11 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>165</v>
+        <v>8</v>
       </c>
     </row>
     <row r="520">
@@ -15500,11 +15556,11 @@
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="521">
@@ -15525,11 +15581,11 @@
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="522">
@@ -15550,11 +15606,11 @@
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>91</v>
+        <v>3</v>
       </c>
     </row>
     <row r="523">
@@ -15575,11 +15631,11 @@
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
     </row>
     <row r="524">
@@ -15600,11 +15656,11 @@
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="525">
@@ -15625,11 +15681,11 @@
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="526">
@@ -15650,11 +15706,11 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -15675,11 +15731,11 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528">
@@ -15700,1560 +15756,460 @@
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>11</v>
+        <v>95</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C530" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C532" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C534" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>1995</v>
+        <v>19</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>350</v>
+        <v>15</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C536" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>331</v>
+        <v>10</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>315</v>
+        <v>8</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>302</v>
+        <v>6</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
-        <v>272</v>
+        <v>3</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>200</v>
+        <v>2</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>168</v>
+        <v>2</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C542" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>152</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C544" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C545" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
-        <v>71</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Embebidos</t>
         </is>
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>Menú / Home</t>
+          <t>Landing Alianzas</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E546" s="7" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B547" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C547" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D547" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E547" s="7" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B548" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C548" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D548" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E548" s="7" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B549" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C549" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D549" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E549" s="7" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B550" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C550" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D550" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E550" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B551" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C551" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D551" s="5" t="inlineStr">
-        <is>
-          <t>type_option</t>
-        </is>
-      </c>
-      <c r="E551" s="7" t="n">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B552" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C552" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D552" s="5" t="inlineStr">
-        <is>
-          <t>Átomo</t>
-        </is>
-      </c>
-      <c r="E552" s="7" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B553" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C553" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D553" s="5" t="inlineStr">
-        <is>
-          <t>Accordion</t>
-        </is>
-      </c>
-      <c r="E553" s="7" t="n">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B554" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C554" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D554" s="5" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="E554" s="7" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B555" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C555" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D555" s="5" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E555" s="7" t="n">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B556" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C556" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D556" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="E556" s="7" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B557" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D557" s="5" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="E557" s="7" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B558" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C558" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D558" s="5" t="inlineStr">
-        <is>
-          <t>section_footer</t>
-        </is>
-      </c>
-      <c r="E558" s="7" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B559" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C559" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D559" s="5" t="inlineStr">
-        <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="E559" s="7" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B560" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C560" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D560" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E560" s="7" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B561" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C561" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D561" s="5" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="E561" s="7" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B562" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C562" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D562" s="5" t="inlineStr">
-        <is>
-          <t>Discount Badge</t>
-        </is>
-      </c>
-      <c r="E562" s="7" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B563" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C563" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D563" s="5" t="inlineStr">
-        <is>
-          <t>src_option_redes</t>
-        </is>
-      </c>
-      <c r="E563" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B564" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C564" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D564" s="5" t="inlineStr">
-        <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="E564" s="7" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B565" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C565" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D565" s="5" t="inlineStr">
-        <is>
-          <t>Slider Controls</t>
-        </is>
-      </c>
-      <c r="E565" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B566" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C566" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D566" s="5" t="inlineStr">
-        <is>
-          <t>Breadcrumb</t>
-        </is>
-      </c>
-      <c r="E566" s="7" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B567" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D567" s="5" t="inlineStr">
-        <is>
-          <t>Status Control</t>
-        </is>
-      </c>
-      <c r="E567" s="7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B568" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D568" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E568" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B569" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C569" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D569" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E569" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B570" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C570" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D570" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E570" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B571" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C571" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D571" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E571" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B572" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C572" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D572" s="5" t="inlineStr">
-        <is>
-          <t>type_option</t>
-        </is>
-      </c>
-      <c r="E572" s="7" t="n">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B573" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C573" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D573" s="5" t="inlineStr">
-        <is>
-          <t>Átomo</t>
-        </is>
-      </c>
-      <c r="E573" s="7" t="n">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B574" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C574" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D574" s="5" t="inlineStr">
-        <is>
-          <t>Accordion</t>
-        </is>
-      </c>
-      <c r="E574" s="7" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B575" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C575" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D575" s="5" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="E575" s="7" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B576" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C576" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D576" s="5" t="inlineStr">
-        <is>
-          <t>section_footer</t>
-        </is>
-      </c>
-      <c r="E576" s="7" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B577" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C577" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D577" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="E577" s="7" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B578" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C578" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D578" s="5" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E578" s="7" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B579" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C579" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D579" s="5" t="inlineStr">
-        <is>
-          <t>src_option_redes</t>
-        </is>
-      </c>
-      <c r="E579" s="7" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B580" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C580" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D580" s="5" t="inlineStr">
-        <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="E580" s="7" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B581" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C581" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D581" s="5" t="inlineStr">
-        <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="E581" s="7" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B582" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C582" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D582" s="5" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="E582" s="7" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B583" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C583" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D583" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E583" s="7" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B584" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C584" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D584" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E584" s="7" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B585" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C585" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D585" s="5" t="inlineStr">
-        <is>
-          <t>Breadcrumb</t>
-        </is>
-      </c>
-      <c r="E585" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B586" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C586" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D586" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E586" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B587" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C587" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D587" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E587" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B588" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C588" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D588" s="5" t="inlineStr">
-        <is>
-          <t>Logo Horizontal</t>
-        </is>
-      </c>
-      <c r="E588" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B589" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C589" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D589" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E589" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B590" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C590" s="4" t="inlineStr">
-        <is>
-          <t>Landing Alianzas</t>
-        </is>
-      </c>
-      <c r="D590" s="5" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="E590" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17268,7 +16224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -18136,7 +17092,7 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -18152,11 +17108,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
@@ -18172,11 +17128,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Atajos | Beneficios (new)</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
@@ -18192,11 +17148,11 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Menu_Mobile</t>
+          <t>NorthEast</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -18212,11 +17168,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>NorthEast</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -18232,11 +17188,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Menú_Desktop</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49">
@@ -18252,11 +17208,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
@@ -18272,11 +17228,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Menú_Desktop</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -18292,11 +17248,11 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>Menu_Mobile</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -18312,11 +17268,11 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>beneficios reconocerte</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -18332,7 +17288,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>beneficios reconocerte</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -18372,7 +17328,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Feed</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
@@ -18392,11 +17348,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>vida ley</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -18412,11 +17368,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Infotip</t>
+          <t>tratamiento</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58">
@@ -18432,11 +17388,11 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>trofeo</t>
+          <t>Right Label</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
@@ -18452,11 +17408,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>vida ley</t>
+          <t>PersonalInjuy</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
@@ -18472,11 +17428,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>tratamiento</t>
+          <t>Suggested search (Deprecated)</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61">
@@ -18492,11 +17448,11 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Right Label</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62">
@@ -21716,7 +20672,7 @@
         </is>
       </c>
       <c r="D222" s="18" t="n">
-        <v>155</v>
+        <v>75</v>
       </c>
     </row>
     <row r="223">
@@ -21732,11 +20688,11 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D223" s="18" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224">
@@ -21756,7 +20712,7 @@
         </is>
       </c>
       <c r="D224" s="18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="225">
@@ -21776,7 +20732,7 @@
         </is>
       </c>
       <c r="D225" s="18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="226">
@@ -21792,11 +20748,11 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="D226" s="18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="227">
@@ -21812,11 +20768,11 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="D227" s="18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="228">
@@ -21832,11 +20788,11 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="D228" s="18" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="229">
@@ -21852,11 +20808,11 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D229" s="18" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="230">
@@ -21872,11 +20828,11 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D230" s="18" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="231">
@@ -21896,7 +20852,7 @@
         </is>
       </c>
       <c r="D231" s="18" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="232">
@@ -21916,7 +20872,7 @@
         </is>
       </c>
       <c r="D232" s="18" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="233">
@@ -21932,11 +20888,11 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Cargador circular</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D233" s="18" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234">
@@ -21952,11 +20908,11 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D234" s="18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="235">
@@ -21972,11 +20928,11 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D235" s="18" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="236">
@@ -21992,11 +20948,11 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D236" s="18" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237">
@@ -22016,7 +20972,7 @@
         </is>
       </c>
       <c r="D237" s="18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238">
@@ -22036,7 +20992,7 @@
         </is>
       </c>
       <c r="D238" s="18" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239">
@@ -22052,11 +21008,11 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>[SCTR] Planes cotizador</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D239" s="18" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="240">
@@ -22072,11 +21028,11 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D240" s="18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -22092,11 +21048,11 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Bullet Icon</t>
+          <t>datos pacifico</t>
         </is>
       </c>
       <c r="D241" s="18" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242">
@@ -22112,11 +21068,11 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D242" s="18" t="n">
-        <v>221</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243">
@@ -22132,11 +21088,11 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D243" s="18" t="n">
-        <v>206</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244">
@@ -22152,11 +21108,11 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D244" s="18" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245">
@@ -22172,11 +21128,11 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D245" s="18" t="n">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="246">
@@ -22192,11 +21148,11 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D246" s="18" t="n">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="247">
@@ -22216,7 +21172,7 @@
         </is>
       </c>
       <c r="D247" s="18" t="n">
-        <v>83</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248">
@@ -22232,11 +21188,11 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D248" s="18" t="n">
-        <v>79</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249">
@@ -22252,11 +21208,11 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D249" s="18" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
@@ -22276,7 +21232,7 @@
         </is>
       </c>
       <c r="D250" s="18" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251">
@@ -22292,11 +21248,11 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D251" s="18" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252">
@@ -22312,11 +21268,11 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D252" s="18" t="n">
-        <v>69</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
@@ -22332,11 +21288,11 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D253" s="18" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
@@ -22352,11 +21308,11 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D254" s="18" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255">
@@ -22372,11 +21328,11 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D255" s="18" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256">
@@ -22392,11 +21348,11 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>Link Details</t>
         </is>
       </c>
       <c r="D256" s="18" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -22412,11 +21368,11 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D257" s="18" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -22432,11 +21388,11 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>user</t>
         </is>
       </c>
       <c r="D258" s="18" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
@@ -22452,11 +21408,11 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D259" s="18" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -22472,11 +21428,11 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D260" s="18" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -22492,11 +21448,11 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D261" s="18" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -22512,11 +21468,11 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>icon</t>
+          <t>SecciónDescripción</t>
         </is>
       </c>
       <c r="D262" s="18" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="263">
@@ -22532,11 +21488,11 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>SecciónDescripción</t>
+          <t>icon</t>
         </is>
       </c>
       <c r="D263" s="18" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
     </row>
     <row r="264">
@@ -22552,11 +21508,11 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D264" s="18" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="265">
@@ -22572,11 +21528,11 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Image</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D265" s="18" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="266">
@@ -22592,11 +21548,11 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>Image</t>
         </is>
       </c>
       <c r="D266" s="18" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="267">
@@ -22612,11 +21568,11 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>SeccionCanales</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D267" s="18" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -22632,11 +21588,11 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>LogosCollab</t>
         </is>
       </c>
       <c r="D268" s="18" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="269">
@@ -22652,11 +21608,11 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>boleta y factura</t>
         </is>
       </c>
       <c r="D269" s="18" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="270">
@@ -22672,11 +21628,11 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>LogosCollab</t>
+          <t>SeccionCanales</t>
         </is>
       </c>
       <c r="D270" s="18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="271">
@@ -22696,7 +21652,7 @@
         </is>
       </c>
       <c r="D271" s="18" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="272">
@@ -22712,11 +21668,11 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>PersonalInjuy</t>
         </is>
       </c>
       <c r="D272" s="18" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="273">
@@ -22732,11 +21688,11 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Complex</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="D273" s="18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274">
@@ -22752,11 +21708,11 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Complex</t>
         </is>
       </c>
       <c r="D274" s="18" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -22772,11 +21728,11 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>problema eléctrico</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D275" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -22792,11 +21748,11 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>robo de autopartes</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D276" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -22812,11 +21768,11 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>avión</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D277" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -22832,71 +21788,11 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>generales</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D278" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B279" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C279" s="4" t="inlineStr">
-        <is>
-          <t>download</t>
-        </is>
-      </c>
-      <c r="D279" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B280" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>fractura</t>
-        </is>
-      </c>
-      <c r="D280" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B281" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>doctor</t>
-        </is>
-      </c>
-      <c r="D281" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -23152,22 +22048,20 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1424</v>
+        <v>296</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>1625</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7">
@@ -23235,10 +22129,8 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>17</v>
@@ -23315,10 +22207,8 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>22</v>
@@ -23395,10 +22285,8 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>44</v>
@@ -23475,10 +22363,8 @@
           <t>84%</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>5</v>
@@ -23552,22 +22438,20 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>7739</v>
+        <v>4898</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>8560</v>
+        <v>5571</v>
       </c>
     </row>
     <row r="17">
@@ -23713,10 +22597,8 @@
           <t>87%</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="F20" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>12</v>
@@ -24024,20 +22906,20 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
         <v>530</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>11370</v>
+        <v>6030</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>12076</v>
+        <v>6362</v>
       </c>
     </row>
     <row r="29">
@@ -24180,7 +23062,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -24189,13 +23071,13 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>11472</v>
+        <v>359</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>13594</v>
+        <v>412</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -720,20 +720,20 @@
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4898</v>
+        <v>7739</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>673</v>
+        <v>821</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
@@ -1070,20 +1070,20 @@
         <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>6030</v>
+        <v>11370</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>332</v>
+        <v>706</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>35</v>
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="I17" s="12" t="n">
@@ -1105,20 +1105,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>359</v>
+        <v>10590</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>53</v>
+        <v>2027</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1142,20 +1142,20 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>0</v>
+      </c>
+      <c r="H19" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="I19" s="12" t="n">
@@ -1487,20 +1487,20 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>4194</v>
+        <v>7035</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>486</v>
+        <v>634</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>92%</t>
         </is>
       </c>
     </row>
@@ -1929,20 +1929,20 @@
         </is>
       </c>
       <c r="D22" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>6030</v>
+        <v>11370</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>332</v>
+        <v>706</v>
       </c>
       <c r="G22" s="8" t="n">
         <v>35</v>
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>94%</t>
         </is>
       </c>
     </row>
@@ -1963,16 +1963,16 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>359</v>
+        <v>5448</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>53</v>
+        <v>787</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
@@ -1997,20 +1997,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>4605</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -2031,20 +2031,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0</v>
+        <v>537</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>18</v>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>87%</t>
         </is>
       </c>
     </row>
@@ -2065,20 +2065,20 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>89%</t>
+        <v>0</v>
+      </c>
+      <c r="H26" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E546"/>
+  <dimension ref="A1:E568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="E108" s="7" t="n">
-        <v>1248</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="109">
@@ -5281,11 +5281,11 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E109" s="7" t="n">
-        <v>489</v>
+        <v>640</v>
       </c>
     </row>
     <row r="110">
@@ -5306,11 +5306,11 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
-        <v>480</v>
+        <v>634</v>
       </c>
     </row>
     <row r="111">
@@ -5331,11 +5331,11 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E111" s="7" t="n">
-        <v>212</v>
+        <v>448</v>
       </c>
     </row>
     <row r="112">
@@ -5356,11 +5356,11 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
-        <v>208</v>
+        <v>280</v>
       </c>
     </row>
     <row r="113">
@@ -5381,11 +5381,11 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E113" s="7" t="n">
-        <v>173</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114">
@@ -5406,11 +5406,11 @@
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
-        <v>138</v>
+        <v>224</v>
       </c>
     </row>
     <row r="115">
@@ -5431,11 +5431,11 @@
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E115" s="7" t="n">
-        <v>130</v>
+        <v>219</v>
       </c>
     </row>
     <row r="116">
@@ -5456,11 +5456,11 @@
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
     </row>
     <row r="117">
@@ -5481,11 +5481,11 @@
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E117" s="7" t="n">
-        <v>104</v>
+        <v>160</v>
       </c>
     </row>
     <row r="118">
@@ -5506,11 +5506,11 @@
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="119">
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="E119" s="7" t="n">
-        <v>94</v>
+        <v>112</v>
       </c>
     </row>
     <row r="120">
@@ -5556,11 +5556,11 @@
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>Beneficio | card</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
     </row>
     <row r="121">
@@ -5581,11 +5581,11 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E121" s="7" t="n">
-        <v>69</v>
+        <v>105</v>
       </c>
     </row>
     <row r="122">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
-        <v>69</v>
+        <v>93</v>
       </c>
     </row>
     <row r="123">
@@ -5631,11 +5631,11 @@
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Beneficio | card</t>
         </is>
       </c>
       <c r="E123" s="7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="124">
@@ -5656,11 +5656,11 @@
       </c>
       <c r="D124" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="125">
@@ -5681,11 +5681,11 @@
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E125" s="7" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
     </row>
     <row r="126">
@@ -5706,11 +5706,11 @@
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
     </row>
     <row r="127">
@@ -5731,11 +5731,11 @@
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E127" s="7" t="n">
-        <v>33</v>
+        <v>56</v>
       </c>
     </row>
     <row r="128">
@@ -5756,11 +5756,11 @@
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
     </row>
     <row r="129">
@@ -5781,11 +5781,11 @@
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Banner | errores</t>
         </is>
       </c>
       <c r="E129" s="7" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
     </row>
     <row r="130">
@@ -5806,11 +5806,11 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131">
@@ -5831,11 +5831,11 @@
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E131" s="7" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132">
@@ -5856,11 +5856,11 @@
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>Banner | errores</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E132" s="7" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="133">
@@ -5881,11 +5881,11 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E133" s="7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="135">
@@ -5931,11 +5931,11 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E135" s="7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
@@ -5956,11 +5956,11 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137">
@@ -5981,11 +5981,11 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E137" s="7" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138">
@@ -6006,11 +6006,11 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139">
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="E139" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140">
@@ -6056,11 +6056,11 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141">
@@ -6081,11 +6081,11 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E141" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142">
@@ -6110,7 +6110,7 @@
         </is>
       </c>
       <c r="E142" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -6131,61 +6131,61 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E143" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>Web Privada</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
-        <v>9216</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Nueva Web Empresas</t>
+          <t>Protege 365</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>TRIN</t>
+          <t>Web Privada</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E145" s="7" t="n">
-        <v>1536</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6206,11 +6206,11 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E146" s="7" t="n">
-        <v>960</v>
+        <v>9216</v>
       </c>
     </row>
     <row r="147">
@@ -6231,11 +6231,11 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E147" s="7" t="n">
-        <v>768</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="148">
@@ -6256,11 +6256,11 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
-        <v>493</v>
+        <v>960</v>
       </c>
     </row>
     <row r="149">
@@ -6281,11 +6281,11 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E149" s="7" t="n">
-        <v>384</v>
+        <v>768</v>
       </c>
     </row>
     <row r="150">
@@ -6306,11 +6306,11 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E150" s="7" t="n">
-        <v>295</v>
+        <v>493</v>
       </c>
     </row>
     <row r="151">
@@ -6331,11 +6331,11 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E151" s="7" t="n">
-        <v>295</v>
+        <v>384</v>
       </c>
     </row>
     <row r="152">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -6381,11 +6381,11 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E153" s="7" t="n">
-        <v>200</v>
+        <v>295</v>
       </c>
     </row>
     <row r="154">
@@ -6406,11 +6406,11 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
-        <v>192</v>
+        <v>295</v>
       </c>
     </row>
     <row r="155">
@@ -6431,11 +6431,11 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E155" s="7" t="n">
-        <v>96</v>
+        <v>200</v>
       </c>
     </row>
     <row r="156">
@@ -6456,11 +6456,11 @@
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
-        <v>96</v>
+        <v>192</v>
       </c>
     </row>
     <row r="157">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E157" s="7" t="n">
@@ -6506,11 +6506,11 @@
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
     </row>
     <row r="159">
@@ -6531,11 +6531,11 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E159" s="7" t="n">
-        <v>59</v>
+        <v>96</v>
       </c>
     </row>
     <row r="160">
@@ -6556,11 +6556,11 @@
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="161">
@@ -6581,11 +6581,11 @@
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E161" s="7" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="162">
@@ -6606,11 +6606,11 @@
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="163">
@@ -6631,11 +6631,11 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E163" s="7" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="164">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E165" s="7" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166">
@@ -6706,11 +6706,11 @@
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
@@ -6731,11 +6731,11 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E167" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E169" s="7" t="n">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="D170" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -6831,11 +6831,11 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E171" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
@@ -6856,11 +6856,11 @@
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>Carrusel</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
@@ -6876,16 +6876,16 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Home Empresas</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E173" s="7" t="n">
-        <v>87113</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174">
@@ -6901,16 +6901,16 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Home Empresas</t>
+          <t>TRIN</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Carrusel</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
-        <v>15407</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -6931,11 +6931,11 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E175" s="7" t="n">
-        <v>8152</v>
+        <v>87113</v>
       </c>
     </row>
     <row r="176">
@@ -6956,11 +6956,11 @@
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
-        <v>7872</v>
+        <v>15407</v>
       </c>
     </row>
     <row r="177">
@@ -6981,11 +6981,11 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E177" s="7" t="n">
-        <v>7423</v>
+        <v>8152</v>
       </c>
     </row>
     <row r="178">
@@ -7006,11 +7006,11 @@
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
-        <v>5251</v>
+        <v>7872</v>
       </c>
     </row>
     <row r="179">
@@ -7031,11 +7031,11 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E179" s="7" t="n">
-        <v>3935</v>
+        <v>7423</v>
       </c>
     </row>
     <row r="180">
@@ -7056,11 +7056,11 @@
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
-        <v>3067</v>
+        <v>5251</v>
       </c>
     </row>
     <row r="181">
@@ -7081,11 +7081,11 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E181" s="7" t="n">
-        <v>2281</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="182">
@@ -7106,11 +7106,11 @@
       </c>
       <c r="D182" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
-        <v>1676</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="183">
@@ -7131,11 +7131,11 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E183" s="7" t="n">
-        <v>1554</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="184">
@@ -7156,11 +7156,11 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Notification Item</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
-        <v>1536</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="185">
@@ -7181,11 +7181,11 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E185" s="7" t="n">
-        <v>1278</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="186">
@@ -7206,11 +7206,11 @@
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Notification Item</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
-        <v>1241</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="187">
@@ -7231,11 +7231,11 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E187" s="7" t="n">
-        <v>1166</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="188">
@@ -7256,11 +7256,11 @@
       </c>
       <c r="D188" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
-        <v>1095</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="189">
@@ -7281,11 +7281,11 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E189" s="7" t="n">
-        <v>984</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="190">
@@ -7306,11 +7306,11 @@
       </c>
       <c r="D190" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
-        <v>984</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="191">
@@ -7331,11 +7331,11 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E191" s="7" t="n">
-        <v>948</v>
+        <v>984</v>
       </c>
     </row>
     <row r="192">
@@ -7356,11 +7356,11 @@
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
-        <v>780</v>
+        <v>984</v>
       </c>
     </row>
     <row r="193">
@@ -7381,11 +7381,11 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E193" s="7" t="n">
-        <v>762</v>
+        <v>948</v>
       </c>
     </row>
     <row r="194">
@@ -7406,11 +7406,11 @@
       </c>
       <c r="D194" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
-        <v>759</v>
+        <v>780</v>
       </c>
     </row>
     <row r="195">
@@ -7431,11 +7431,11 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E195" s="7" t="n">
-        <v>397</v>
+        <v>762</v>
       </c>
     </row>
     <row r="196">
@@ -7456,11 +7456,11 @@
       </c>
       <c r="D196" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
-        <v>364</v>
+        <v>759</v>
       </c>
     </row>
     <row r="197">
@@ -7481,11 +7481,11 @@
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E197" s="7" t="n">
-        <v>329</v>
+        <v>397</v>
       </c>
     </row>
     <row r="198">
@@ -7506,11 +7506,11 @@
       </c>
       <c r="D198" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
-        <v>280</v>
+        <v>364</v>
       </c>
     </row>
     <row r="199">
@@ -7531,11 +7531,11 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E199" s="7" t="n">
-        <v>222</v>
+        <v>329</v>
       </c>
     </row>
     <row r="200">
@@ -7556,11 +7556,11 @@
       </c>
       <c r="D200" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
-        <v>217</v>
+        <v>280</v>
       </c>
     </row>
     <row r="201">
@@ -7581,11 +7581,11 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E201" s="7" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
     </row>
     <row r="202">
@@ -7606,11 +7606,11 @@
       </c>
       <c r="D202" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
-        <v>97</v>
+        <v>217</v>
       </c>
     </row>
     <row r="203">
@@ -7631,11 +7631,11 @@
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E203" s="7" t="n">
-        <v>77</v>
+        <v>212</v>
       </c>
     </row>
     <row r="204">
@@ -7656,11 +7656,11 @@
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="205">
@@ -7681,11 +7681,11 @@
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E205" s="7" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
     </row>
     <row r="206">
@@ -7706,11 +7706,11 @@
       </c>
       <c r="D206" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="207">
@@ -7731,11 +7731,11 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E207" s="7" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="208">
@@ -7756,11 +7756,11 @@
       </c>
       <c r="D208" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="209">
@@ -7781,11 +7781,11 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E209" s="7" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="210">
@@ -7806,11 +7806,11 @@
       </c>
       <c r="D210" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
     </row>
     <row r="211">
@@ -7831,11 +7831,11 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E211" s="7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212">
@@ -7856,11 +7856,11 @@
       </c>
       <c r="D212" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="213">
@@ -7881,11 +7881,11 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E213" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214">
@@ -7906,61 +7906,61 @@
       </c>
       <c r="D214" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Home Empresas</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E215" s="7" t="n">
-        <v>1440</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Nueva Web Empresas</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Portal Digital de Siniestros</t>
+          <t>Home Empresas</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
-        <v>998</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217">
@@ -7981,11 +7981,11 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E217" s="7" t="n">
-        <v>993</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="218">
@@ -8006,11 +8006,11 @@
       </c>
       <c r="D218" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
-        <v>976</v>
+        <v>998</v>
       </c>
     </row>
     <row r="219">
@@ -8031,11 +8031,11 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E219" s="7" t="n">
-        <v>756</v>
+        <v>993</v>
       </c>
     </row>
     <row r="220">
@@ -8056,11 +8056,11 @@
       </c>
       <c r="D220" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
-        <v>390</v>
+        <v>976</v>
       </c>
     </row>
     <row r="221">
@@ -8081,11 +8081,11 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E221" s="7" t="n">
-        <v>390</v>
+        <v>756</v>
       </c>
     </row>
     <row r="222">
@@ -8106,11 +8106,11 @@
       </c>
       <c r="D222" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
     </row>
     <row r="223">
@@ -8131,11 +8131,11 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E223" s="7" t="n">
-        <v>266</v>
+        <v>390</v>
       </c>
     </row>
     <row r="224">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="D224" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
-        <v>240</v>
+        <v>289</v>
       </c>
     </row>
     <row r="225">
@@ -8181,11 +8181,11 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E225" s="7" t="n">
-        <v>229</v>
+        <v>266</v>
       </c>
     </row>
     <row r="226">
@@ -8206,11 +8206,11 @@
       </c>
       <c r="D226" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="227">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E227" s="7" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
     </row>
     <row r="228">
@@ -8256,11 +8256,11 @@
       </c>
       <c r="D228" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
     </row>
     <row r="229">
@@ -8281,11 +8281,11 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E229" s="7" t="n">
-        <v>152</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230">
@@ -8306,11 +8306,11 @@
       </c>
       <c r="D230" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
-        <v>150</v>
+        <v>199</v>
       </c>
     </row>
     <row r="231">
@@ -8331,11 +8331,11 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E231" s="7" t="n">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="232">
@@ -8356,11 +8356,11 @@
       </c>
       <c r="D232" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
     </row>
     <row r="233">
@@ -8381,11 +8381,11 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>Card Dashboard</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E233" s="7" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
     </row>
     <row r="234">
@@ -8406,11 +8406,11 @@
       </c>
       <c r="D234" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="235">
@@ -8431,11 +8431,11 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Card Dashboard</t>
         </is>
       </c>
       <c r="E235" s="7" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="236">
@@ -8456,11 +8456,11 @@
       </c>
       <c r="D236" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="237">
@@ -8481,11 +8481,11 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E237" s="7" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="238">
@@ -8506,11 +8506,11 @@
       </c>
       <c r="D238" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="239">
@@ -8531,11 +8531,11 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E239" s="7" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="240">
@@ -8556,11 +8556,11 @@
       </c>
       <c r="D240" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="241">
@@ -8581,11 +8581,11 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E241" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="242">
@@ -8606,11 +8606,11 @@
       </c>
       <c r="D242" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E242" s="7" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="243">
@@ -8631,11 +8631,11 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E243" s="7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="244">
@@ -8656,11 +8656,11 @@
       </c>
       <c r="D244" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="245">
@@ -8681,11 +8681,11 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E245" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
@@ -8706,11 +8706,11 @@
       </c>
       <c r="D246" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="247">
@@ -8731,61 +8731,61 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E247" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="D248" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
-        <v>2929</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Modelo Día 2026</t>
+          <t>Portal Digital de Siniestros</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E249" s="7" t="n">
-        <v>685</v>
+        <v>4</v>
       </c>
     </row>
     <row r="250">
@@ -8806,11 +8806,11 @@
       </c>
       <c r="D250" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
-        <v>653</v>
+        <v>2929</v>
       </c>
     </row>
     <row r="251">
@@ -8831,11 +8831,11 @@
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E251" s="7" t="n">
-        <v>553</v>
+        <v>685</v>
       </c>
     </row>
     <row r="252">
@@ -8856,11 +8856,11 @@
       </c>
       <c r="D252" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
-        <v>551</v>
+        <v>653</v>
       </c>
     </row>
     <row r="253">
@@ -8881,11 +8881,11 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E253" s="7" t="n">
-        <v>512</v>
+        <v>553</v>
       </c>
     </row>
     <row r="254">
@@ -8906,11 +8906,11 @@
       </c>
       <c r="D254" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
-        <v>347</v>
+        <v>551</v>
       </c>
     </row>
     <row r="255">
@@ -8931,11 +8931,11 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E255" s="7" t="n">
-        <v>335</v>
+        <v>512</v>
       </c>
     </row>
     <row r="256">
@@ -8956,11 +8956,11 @@
       </c>
       <c r="D256" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
-        <v>187</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257">
@@ -8981,11 +8981,11 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E257" s="7" t="n">
-        <v>145</v>
+        <v>335</v>
       </c>
     </row>
     <row r="258">
@@ -9006,11 +9006,11 @@
       </c>
       <c r="D258" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
-        <v>139</v>
+        <v>187</v>
       </c>
     </row>
     <row r="259">
@@ -9031,11 +9031,11 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E259" s="7" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
     </row>
     <row r="260">
@@ -9056,11 +9056,11 @@
       </c>
       <c r="D260" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
-        <v>110</v>
+        <v>139</v>
       </c>
     </row>
     <row r="261">
@@ -9081,11 +9081,11 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E261" s="7" t="n">
-        <v>106</v>
+        <v>120</v>
       </c>
     </row>
     <row r="262">
@@ -9106,11 +9106,11 @@
       </c>
       <c r="D262" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
-        <v>94</v>
+        <v>110</v>
       </c>
     </row>
     <row r="263">
@@ -9131,11 +9131,11 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E263" s="7" t="n">
-        <v>80</v>
+        <v>106</v>
       </c>
     </row>
     <row r="264">
@@ -9156,11 +9156,11 @@
       </c>
       <c r="D264" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="265">
@@ -9181,11 +9181,11 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E265" s="7" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="266">
@@ -9206,11 +9206,11 @@
       </c>
       <c r="D266" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="267">
@@ -9231,11 +9231,11 @@
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E267" s="7" t="n">
-        <v>26</v>
+        <v>59</v>
       </c>
     </row>
     <row r="268">
@@ -9256,11 +9256,11 @@
       </c>
       <c r="D268" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="269">
@@ -9281,11 +9281,11 @@
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E269" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="270">
@@ -9306,11 +9306,11 @@
       </c>
       <c r="D270" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="271">
@@ -9331,11 +9331,11 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E271" s="7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="272">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="D272" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="273">
@@ -9381,11 +9381,11 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E273" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="274">
@@ -9406,11 +9406,11 @@
       </c>
       <c r="D274" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="275">
@@ -9431,11 +9431,11 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E275" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="276">
@@ -9456,11 +9456,11 @@
       </c>
       <c r="D276" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="277">
@@ -9481,11 +9481,11 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E277" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278">
@@ -9506,11 +9506,11 @@
       </c>
       <c r="D278" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279">
@@ -9531,11 +9531,11 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E279" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280">
@@ -9556,11 +9556,11 @@
       </c>
       <c r="D280" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E280" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281">
@@ -9581,11 +9581,11 @@
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E281" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282">
@@ -9601,16 +9601,16 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D282" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
-        <v>1316</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283">
@@ -9626,16 +9626,16 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Portal de Suscripción &amp; Emisión</t>
+          <t>Modelo Día 2026</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E283" s="7" t="n">
-        <v>1258</v>
+        <v>2</v>
       </c>
     </row>
     <row r="284">
@@ -9656,11 +9656,11 @@
       </c>
       <c r="D284" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
-        <v>531</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="285">
@@ -9681,11 +9681,11 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Table</t>
         </is>
       </c>
       <c r="E285" s="7" t="n">
-        <v>184</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="286">
@@ -9706,11 +9706,11 @@
       </c>
       <c r="D286" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
-        <v>178</v>
+        <v>531</v>
       </c>
     </row>
     <row r="287">
@@ -9731,11 +9731,11 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E287" s="7" t="n">
-        <v>161</v>
+        <v>184</v>
       </c>
     </row>
     <row r="288">
@@ -9756,11 +9756,11 @@
       </c>
       <c r="D288" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
-        <v>126</v>
+        <v>178</v>
       </c>
     </row>
     <row r="289">
@@ -9781,11 +9781,11 @@
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E289" s="7" t="n">
-        <v>107</v>
+        <v>161</v>
       </c>
     </row>
     <row r="290">
@@ -9806,11 +9806,11 @@
       </c>
       <c r="D290" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
-        <v>83</v>
+        <v>126</v>
       </c>
     </row>
     <row r="291">
@@ -9831,11 +9831,11 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E291" s="7" t="n">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="292">
@@ -9856,11 +9856,11 @@
       </c>
       <c r="D292" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="293">
@@ -9881,11 +9881,11 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E293" s="7" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="294">
@@ -9906,11 +9906,11 @@
       </c>
       <c r="D294" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
-        <v>12</v>
+        <v>64</v>
       </c>
     </row>
     <row r="295">
@@ -9931,11 +9931,11 @@
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E295" s="7" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="296">
@@ -9956,11 +9956,11 @@
       </c>
       <c r="D296" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="297">
@@ -9981,11 +9981,11 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E297" s="7" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="298">
@@ -10006,11 +10006,11 @@
       </c>
       <c r="D298" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="299">
@@ -10031,11 +10031,11 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E299" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="D300" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E301" s="7" t="n">
@@ -10106,11 +10106,11 @@
       </c>
       <c r="D302" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="303">
@@ -10126,16 +10126,16 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>Sidebar</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E303" s="7" t="n">
-        <v>1558</v>
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -10151,16 +10151,16 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>Portal de Suscripción &amp; Emisión</t>
         </is>
       </c>
       <c r="D304" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
-        <v>209</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
@@ -10181,11 +10181,11 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Sidebar</t>
         </is>
       </c>
       <c r="E305" s="7" t="n">
-        <v>113</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="306">
@@ -10206,11 +10206,11 @@
       </c>
       <c r="D306" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
-        <v>80</v>
+        <v>209</v>
       </c>
     </row>
     <row r="307">
@@ -10231,11 +10231,11 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E307" s="7" t="n">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="308">
@@ -10256,11 +10256,11 @@
       </c>
       <c r="D308" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="309">
@@ -10281,11 +10281,11 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E309" s="7" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
     </row>
     <row r="310">
@@ -10306,11 +10306,11 @@
       </c>
       <c r="D310" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="311">
@@ -10331,11 +10331,11 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E311" s="7" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="312">
@@ -10356,11 +10356,11 @@
       </c>
       <c r="D312" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="313">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E313" s="7" t="n">
@@ -10406,11 +10406,11 @@
       </c>
       <c r="D314" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="315">
@@ -10431,11 +10431,11 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E315" s="7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="316">
@@ -10456,11 +10456,11 @@
       </c>
       <c r="D316" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="317">
@@ -10481,11 +10481,11 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>Main Search</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E317" s="7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="318">
@@ -10506,11 +10506,11 @@
       </c>
       <c r="D318" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="319">
@@ -10531,11 +10531,11 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>Pagination</t>
+          <t>Main Search</t>
         </is>
       </c>
       <c r="E319" s="7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
@@ -10556,11 +10556,11 @@
       </c>
       <c r="D320" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="321">
@@ -10581,11 +10581,11 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Pagination</t>
         </is>
       </c>
       <c r="E321" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322">
@@ -10606,11 +10606,11 @@
       </c>
       <c r="D322" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="323">
@@ -10631,11 +10631,11 @@
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E323" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="324">
@@ -10656,11 +10656,11 @@
       </c>
       <c r="D324" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>Controls</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E325" s="7" t="n">
@@ -10706,11 +10706,11 @@
       </c>
       <c r="D326" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="327">
@@ -10731,11 +10731,11 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>Text Area</t>
+          <t>Controls</t>
         </is>
       </c>
       <c r="E327" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="328">
@@ -10756,11 +10756,11 @@
       </c>
       <c r="D328" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -10781,11 +10781,11 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Text Area</t>
         </is>
       </c>
       <c r="E329" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="330">
@@ -10806,11 +10806,11 @@
       </c>
       <c r="D330" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
@@ -10831,7 +10831,7 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E331" s="7" t="n">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="D332" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
@@ -10866,51 +10866,51 @@
     <row r="333">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E333" s="7" t="n">
-        <v>305</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>Ecommerce</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Modelo Día</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>SOAT</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D334" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
-        <v>243</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -10931,11 +10931,11 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E335" s="7" t="n">
-        <v>164</v>
+        <v>305</v>
       </c>
     </row>
     <row r="336">
@@ -10956,11 +10956,11 @@
       </c>
       <c r="D336" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
-        <v>110</v>
+        <v>243</v>
       </c>
     </row>
     <row r="337">
@@ -10981,11 +10981,11 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E337" s="7" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
     </row>
     <row r="338">
@@ -11006,11 +11006,11 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="339">
@@ -11031,11 +11031,11 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E339" s="7" t="n">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="340">
@@ -11056,11 +11056,11 @@
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="341">
@@ -11081,11 +11081,11 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E341" s="7" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="342">
@@ -11106,11 +11106,11 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="343">
@@ -11131,11 +11131,11 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E343" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="344">
@@ -11156,11 +11156,11 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="345">
@@ -11181,11 +11181,11 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E345" s="7" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="346">
@@ -11206,11 +11206,11 @@
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="347">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E347" s="7" t="n">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="348">
@@ -11256,11 +11256,11 @@
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="349">
@@ -11281,11 +11281,11 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E349" s="7" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="350">
@@ -11306,7 +11306,7 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
@@ -11331,11 +11331,11 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E351" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352">
@@ -11356,11 +11356,11 @@
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353">
@@ -11381,11 +11381,11 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E353" s="7" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="354">
@@ -11406,11 +11406,11 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="355">
@@ -11431,11 +11431,11 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E355" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="356">
@@ -11456,11 +11456,11 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="357">
@@ -11481,11 +11481,11 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E357" s="7" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="358">
@@ -11506,11 +11506,11 @@
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="359">
@@ -11531,11 +11531,11 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E359" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="360">
@@ -11546,21 +11546,21 @@
       </c>
       <c r="B360" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
-        <v>432</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
@@ -11571,21 +11571,21 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Vehicular</t>
+          <t>SOAT</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E361" s="7" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E362" s="7" t="n">
-        <v>196</v>
+        <v>432</v>
       </c>
     </row>
     <row r="363">
@@ -11631,11 +11631,11 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E363" s="7" t="n">
-        <v>176</v>
+        <v>213</v>
       </c>
     </row>
     <row r="364">
@@ -11656,11 +11656,11 @@
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E364" s="7" t="n">
-        <v>149</v>
+        <v>196</v>
       </c>
     </row>
     <row r="365">
@@ -11681,11 +11681,11 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E365" s="7" t="n">
-        <v>124</v>
+        <v>176</v>
       </c>
     </row>
     <row r="366">
@@ -11706,11 +11706,11 @@
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E366" s="7" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="367">
@@ -11731,11 +11731,11 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E367" s="7" t="n">
-        <v>114</v>
+        <v>124</v>
       </c>
     </row>
     <row r="368">
@@ -11756,11 +11756,11 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E368" s="7" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
     </row>
     <row r="369">
@@ -11781,11 +11781,11 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E369" s="7" t="n">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="370">
@@ -11806,11 +11806,11 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E370" s="7" t="n">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="371">
@@ -11831,11 +11831,11 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E371" s="7" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
     </row>
     <row r="372">
@@ -11856,11 +11856,11 @@
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E372" s="7" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="373">
@@ -11881,11 +11881,11 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E373" s="7" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="374">
@@ -11906,11 +11906,11 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E374" s="7" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="375">
@@ -11931,11 +11931,11 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E375" s="7" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
     </row>
     <row r="376">
@@ -11956,11 +11956,11 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E376" s="7" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="377">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E377" s="7" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="378">
@@ -12006,11 +12006,11 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E378" s="7" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="379">
@@ -12031,11 +12031,11 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E379" s="7" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="380">
@@ -12056,11 +12056,11 @@
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E380" s="7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="381">
@@ -12081,11 +12081,11 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E381" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382">
@@ -12106,11 +12106,11 @@
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E382" s="7" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="383">
@@ -12131,11 +12131,11 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E383" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="384">
@@ -12156,11 +12156,11 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E384" s="7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="385">
@@ -12181,11 +12181,11 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E385" s="7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="386">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E386" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="387">
@@ -12231,11 +12231,11 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E387" s="7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="388">
@@ -12246,21 +12246,21 @@
       </c>
       <c r="B388" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E388" s="7" t="n">
-        <v>597</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389">
@@ -12271,21 +12271,21 @@
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Vehicular Todo Riesgo</t>
+          <t>Vehicular</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E389" s="7" t="n">
-        <v>331</v>
+        <v>2</v>
       </c>
     </row>
     <row r="390">
@@ -12306,11 +12306,11 @@
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E390" s="7" t="n">
-        <v>327</v>
+        <v>597</v>
       </c>
     </row>
     <row r="391">
@@ -12331,11 +12331,11 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E391" s="7" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
     </row>
     <row r="392">
@@ -12356,11 +12356,11 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E392" s="7" t="n">
-        <v>166</v>
+        <v>327</v>
       </c>
     </row>
     <row r="393">
@@ -12381,11 +12381,11 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E393" s="7" t="n">
-        <v>151</v>
+        <v>276</v>
       </c>
     </row>
     <row r="394">
@@ -12406,11 +12406,11 @@
       </c>
       <c r="D394" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E394" s="7" t="n">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="395">
@@ -12431,11 +12431,11 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E395" s="7" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
     </row>
     <row r="396">
@@ -12456,11 +12456,11 @@
       </c>
       <c r="D396" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E396" s="7" t="n">
-        <v>60</v>
+        <v>116</v>
       </c>
     </row>
     <row r="397">
@@ -12481,11 +12481,11 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E397" s="7" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
     </row>
     <row r="398">
@@ -12506,11 +12506,11 @@
       </c>
       <c r="D398" s="5" t="inlineStr">
         <is>
-          <t>Cards</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E398" s="7" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="399">
@@ -12531,11 +12531,11 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E399" s="7" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="400">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="D400" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>Cards</t>
         </is>
       </c>
       <c r="E400" s="7" t="n">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E401" s="7" t="n">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="D402" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E402" s="7" t="n">
@@ -12631,11 +12631,11 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E403" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="404">
@@ -12656,11 +12656,11 @@
       </c>
       <c r="D404" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E404" s="7" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="405">
@@ -12681,11 +12681,11 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E405" s="7" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="406">
@@ -12706,11 +12706,11 @@
       </c>
       <c r="D406" s="5" t="inlineStr">
         <is>
-          <t>Links</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E406" s="7" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="407">
@@ -12731,11 +12731,11 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E407" s="7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="408">
@@ -12756,11 +12756,11 @@
       </c>
       <c r="D408" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="E408" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="409">
@@ -12781,11 +12781,11 @@
       </c>
       <c r="D409" s="5" t="inlineStr">
         <is>
-          <t>Commercial Chips</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E409" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="410">
@@ -12806,11 +12806,11 @@
       </c>
       <c r="D410" s="5" t="inlineStr">
         <is>
-          <t>Bottom Bar</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E410" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="411">
@@ -12831,11 +12831,11 @@
       </c>
       <c r="D411" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Commercial Chips</t>
         </is>
       </c>
       <c r="E411" s="7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412">
@@ -12856,11 +12856,11 @@
       </c>
       <c r="D412" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Bottom Bar</t>
         </is>
       </c>
       <c r="E412" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="413">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="D413" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E413" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="414">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="D414" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E414" s="7" t="n">
@@ -12931,11 +12931,11 @@
       </c>
       <c r="D415" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E415" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="416">
@@ -12956,11 +12956,11 @@
       </c>
       <c r="D416" s="5" t="inlineStr">
         <is>
-          <t>Comparador</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E416" s="7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="417">
@@ -12971,21 +12971,21 @@
       </c>
       <c r="B417" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D417" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E417" s="7" t="n">
-        <v>1536</v>
+        <v>2</v>
       </c>
     </row>
     <row r="418">
@@ -12996,21 +12996,21 @@
       </c>
       <c r="B418" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Viajes</t>
+          <t>Vehicular Todo Riesgo</t>
         </is>
       </c>
       <c r="D418" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Comparador</t>
         </is>
       </c>
       <c r="E418" s="7" t="n">
-        <v>340</v>
+        <v>2</v>
       </c>
     </row>
     <row r="419">
@@ -13031,11 +13031,11 @@
       </c>
       <c r="D419" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E419" s="7" t="n">
-        <v>256</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="420">
@@ -13056,11 +13056,11 @@
       </c>
       <c r="D420" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E420" s="7" t="n">
-        <v>251</v>
+        <v>340</v>
       </c>
     </row>
     <row r="421">
@@ -13081,11 +13081,11 @@
       </c>
       <c r="D421" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E421" s="7" t="n">
-        <v>160</v>
+        <v>256</v>
       </c>
     </row>
     <row r="422">
@@ -13106,11 +13106,11 @@
       </c>
       <c r="D422" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E422" s="7" t="n">
-        <v>149</v>
+        <v>251</v>
       </c>
     </row>
     <row r="423">
@@ -13131,11 +13131,11 @@
       </c>
       <c r="D423" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E423" s="7" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="424">
@@ -13156,11 +13156,11 @@
       </c>
       <c r="D424" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E424" s="7" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
     </row>
     <row r="425">
@@ -13181,11 +13181,11 @@
       </c>
       <c r="D425" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E425" s="7" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="426">
@@ -13206,11 +13206,11 @@
       </c>
       <c r="D426" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E426" s="7" t="n">
-        <v>78</v>
+        <v>122</v>
       </c>
     </row>
     <row r="427">
@@ -13231,11 +13231,11 @@
       </c>
       <c r="D427" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E427" s="7" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="428">
@@ -13256,11 +13256,11 @@
       </c>
       <c r="D428" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E428" s="7" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="429">
@@ -13281,11 +13281,11 @@
       </c>
       <c r="D429" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E429" s="7" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
     </row>
     <row r="430">
@@ -13306,11 +13306,11 @@
       </c>
       <c r="D430" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E430" s="7" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="431">
@@ -13331,11 +13331,11 @@
       </c>
       <c r="D431" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E431" s="7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="432">
@@ -13356,11 +13356,11 @@
       </c>
       <c r="D432" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E432" s="7" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="433">
@@ -13381,11 +13381,11 @@
       </c>
       <c r="D433" s="5" t="inlineStr">
         <is>
-          <t>Indicator step</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E433" s="7" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="434">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="D434" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E434" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="435">
@@ -13431,11 +13431,11 @@
       </c>
       <c r="D435" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Indicator step</t>
         </is>
       </c>
       <c r="E435" s="7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="436">
@@ -13456,11 +13456,11 @@
       </c>
       <c r="D436" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E436" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="437">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="D437" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E437" s="7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="438">
@@ -13506,11 +13506,11 @@
       </c>
       <c r="D438" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E438" s="7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="439">
@@ -13531,11 +13531,11 @@
       </c>
       <c r="D439" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E439" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="440">
@@ -13556,11 +13556,11 @@
       </c>
       <c r="D440" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E440" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="441">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="D441" s="5" t="inlineStr">
         <is>
-          <t>Bar Progress</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E441" s="7" t="n">
@@ -13606,11 +13606,11 @@
       </c>
       <c r="D442" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E442" s="7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="443">
@@ -13631,11 +13631,11 @@
       </c>
       <c r="D443" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Bar Progress</t>
         </is>
       </c>
       <c r="E443" s="7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="444">
@@ -13656,11 +13656,11 @@
       </c>
       <c r="D444" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E444" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="445">
@@ -13681,11 +13681,11 @@
       </c>
       <c r="D445" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E445" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="446">
@@ -13696,21 +13696,21 @@
       </c>
       <c r="B446" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D446" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E446" s="7" t="n">
-        <v>1152</v>
+        <v>9</v>
       </c>
     </row>
     <row r="447">
@@ -13721,21 +13721,21 @@
       </c>
       <c r="B447" s="4" t="inlineStr">
         <is>
-          <t>VDT</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>VDT — Perfilador Productos Vida</t>
+          <t>Viajes</t>
         </is>
       </c>
       <c r="D447" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E447" s="7" t="n">
-        <v>618</v>
+        <v>6</v>
       </c>
     </row>
     <row r="448">
@@ -13756,11 +13756,11 @@
       </c>
       <c r="D448" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E448" s="7" t="n">
-        <v>440</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="449">
@@ -13781,11 +13781,11 @@
       </c>
       <c r="D449" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E449" s="7" t="n">
-        <v>375</v>
+        <v>618</v>
       </c>
     </row>
     <row r="450">
@@ -13806,11 +13806,11 @@
       </c>
       <c r="D450" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E450" s="7" t="n">
-        <v>192</v>
+        <v>440</v>
       </c>
     </row>
     <row r="451">
@@ -13831,11 +13831,11 @@
       </c>
       <c r="D451" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E451" s="7" t="n">
-        <v>120</v>
+        <v>375</v>
       </c>
     </row>
     <row r="452">
@@ -13856,11 +13856,11 @@
       </c>
       <c r="D452" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E452" s="7" t="n">
-        <v>104</v>
+        <v>192</v>
       </c>
     </row>
     <row r="453">
@@ -13881,11 +13881,11 @@
       </c>
       <c r="D453" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E453" s="7" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
     </row>
     <row r="454">
@@ -13906,11 +13906,11 @@
       </c>
       <c r="D454" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E454" s="7" t="n">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="455">
@@ -13931,11 +13931,11 @@
       </c>
       <c r="D455" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E455" s="7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="456">
@@ -13956,11 +13956,11 @@
       </c>
       <c r="D456" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E456" s="7" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="457">
@@ -13981,11 +13981,11 @@
       </c>
       <c r="D457" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E457" s="7" t="n">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="458">
@@ -14006,11 +14006,11 @@
       </c>
       <c r="D458" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E458" s="7" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
     </row>
     <row r="459">
@@ -14031,11 +14031,11 @@
       </c>
       <c r="D459" s="5" t="inlineStr">
         <is>
-          <t>Label in</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E459" s="7" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="460">
@@ -14056,11 +14056,11 @@
       </c>
       <c r="D460" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E460" s="7" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
     </row>
     <row r="461">
@@ -14081,11 +14081,11 @@
       </c>
       <c r="D461" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Label in</t>
         </is>
       </c>
       <c r="E461" s="7" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="462">
@@ -14106,11 +14106,11 @@
       </c>
       <c r="D462" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E462" s="7" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
     </row>
     <row r="463">
@@ -14131,11 +14131,11 @@
       </c>
       <c r="D463" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E463" s="7" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="464">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="D464" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E464" s="7" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="465">
@@ -14181,11 +14181,11 @@
       </c>
       <c r="D465" s="5" t="inlineStr">
         <is>
-          <t>Chip Deleteable</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E465" s="7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="466">
@@ -14206,11 +14206,11 @@
       </c>
       <c r="D466" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E466" s="7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
     </row>
     <row r="467">
@@ -14231,11 +14231,11 @@
       </c>
       <c r="D467" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Chip Deleteable</t>
         </is>
       </c>
       <c r="E467" s="7" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="468">
@@ -14256,11 +14256,11 @@
       </c>
       <c r="D468" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E468" s="7" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="469">
@@ -14281,11 +14281,11 @@
       </c>
       <c r="D469" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E469" s="7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="470">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="D470" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E470" s="7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="471">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="D471" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E471" s="7" t="n">
@@ -14356,11 +14356,11 @@
       </c>
       <c r="D472" s="5" t="inlineStr">
         <is>
-          <t>Dropdown Input</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E472" s="7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="473">
@@ -14381,11 +14381,11 @@
       </c>
       <c r="D473" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E473" s="7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="474">
@@ -14406,11 +14406,11 @@
       </c>
       <c r="D474" s="5" t="inlineStr">
         <is>
-          <t>Topbar</t>
+          <t>Dropdown Input</t>
         </is>
       </c>
       <c r="E474" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="475">
@@ -14421,21 +14421,21 @@
       </c>
       <c r="B475" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D475" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E475" s="7" t="n">
-        <v>3456</v>
+        <v>6</v>
       </c>
     </row>
     <row r="476">
@@ -14446,21 +14446,21 @@
       </c>
       <c r="B476" s="4" t="inlineStr">
         <is>
-          <t>Venta Directa</t>
+          <t>VDT</t>
         </is>
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Vida Ley &amp; SCTR</t>
+          <t>VDT — Perfilador Productos Vida</t>
         </is>
       </c>
       <c r="D476" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Topbar</t>
         </is>
       </c>
       <c r="E476" s="7" t="n">
-        <v>576</v>
+        <v>4</v>
       </c>
     </row>
     <row r="477">
@@ -14481,11 +14481,11 @@
       </c>
       <c r="D477" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E477" s="7" t="n">
-        <v>360</v>
+        <v>6432</v>
       </c>
     </row>
     <row r="478">
@@ -14506,11 +14506,11 @@
       </c>
       <c r="D478" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E478" s="7" t="n">
-        <v>288</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="479">
@@ -14531,11 +14531,11 @@
       </c>
       <c r="D479" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E479" s="7" t="n">
-        <v>205</v>
+        <v>670</v>
       </c>
     </row>
     <row r="480">
@@ -14556,11 +14556,11 @@
       </c>
       <c r="D480" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E480" s="7" t="n">
-        <v>144</v>
+        <v>536</v>
       </c>
     </row>
     <row r="481">
@@ -14581,11 +14581,11 @@
       </c>
       <c r="D481" s="5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E481" s="7" t="n">
-        <v>83</v>
+        <v>409</v>
       </c>
     </row>
     <row r="482">
@@ -14606,11 +14606,11 @@
       </c>
       <c r="D482" s="5" t="inlineStr">
         <is>
-          <t>Progress bar</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E482" s="7" t="n">
-        <v>75</v>
+        <v>268</v>
       </c>
     </row>
     <row r="483">
@@ -14631,11 +14631,11 @@
       </c>
       <c r="D483" s="5" t="inlineStr">
         <is>
-          <t>Indicator Circle</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="E483" s="7" t="n">
-        <v>75</v>
+        <v>171</v>
       </c>
     </row>
     <row r="484">
@@ -14656,11 +14656,11 @@
       </c>
       <c r="D484" s="5" t="inlineStr">
         <is>
-          <t>Indicator number</t>
+          <t>Indicator Circle</t>
         </is>
       </c>
       <c r="E484" s="7" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="485">
@@ -14681,11 +14681,11 @@
       </c>
       <c r="D485" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Progress bar</t>
         </is>
       </c>
       <c r="E485" s="7" t="n">
-        <v>73</v>
+        <v>151</v>
       </c>
     </row>
     <row r="486">
@@ -14706,11 +14706,11 @@
       </c>
       <c r="D486" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>Indicator number</t>
         </is>
       </c>
       <c r="E486" s="7" t="n">
-        <v>72</v>
+        <v>150</v>
       </c>
     </row>
     <row r="487">
@@ -14731,11 +14731,11 @@
       </c>
       <c r="D487" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E487" s="7" t="n">
-        <v>48</v>
+        <v>149</v>
       </c>
     </row>
     <row r="488">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="D488" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E488" s="7" t="n">
-        <v>45</v>
+        <v>134</v>
       </c>
     </row>
     <row r="489">
@@ -14781,11 +14781,11 @@
       </c>
       <c r="D489" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E489" s="7" t="n">
-        <v>44</v>
+        <v>101</v>
       </c>
     </row>
     <row r="490">
@@ -14806,11 +14806,11 @@
       </c>
       <c r="D490" s="5" t="inlineStr">
         <is>
-          <t>Menu Item</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E490" s="7" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="491">
@@ -14831,11 +14831,11 @@
       </c>
       <c r="D491" s="5" t="inlineStr">
         <is>
-          <t>Radio</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E491" s="7" t="n">
-        <v>37</v>
+        <v>81</v>
       </c>
     </row>
     <row r="492">
@@ -14856,11 +14856,11 @@
       </c>
       <c r="D492" s="5" t="inlineStr">
         <is>
-          <t>Footer</t>
+          <t>Menu Item</t>
         </is>
       </c>
       <c r="E492" s="7" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
     </row>
     <row r="493">
@@ -14881,11 +14881,11 @@
       </c>
       <c r="D493" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Select</t>
         </is>
       </c>
       <c r="E493" s="7" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="494">
@@ -14906,11 +14906,11 @@
       </c>
       <c r="D494" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Footer</t>
         </is>
       </c>
       <c r="E494" s="7" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="495">
@@ -14931,11 +14931,11 @@
       </c>
       <c r="D495" s="5" t="inlineStr">
         <is>
-          <t>Select</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E495" s="7" t="n">
-        <v>34</v>
+        <v>67</v>
       </c>
     </row>
     <row r="496">
@@ -14956,11 +14956,11 @@
       </c>
       <c r="D496" s="5" t="inlineStr">
         <is>
-          <t>Left Label</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E496" s="7" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="497">
@@ -14981,11 +14981,11 @@
       </c>
       <c r="D497" s="5" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Radio</t>
         </is>
       </c>
       <c r="E497" s="7" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="498">
@@ -15006,11 +15006,11 @@
       </c>
       <c r="D498" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Left Label</t>
         </is>
       </c>
       <c r="E498" s="7" t="n">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="499">
@@ -15031,11 +15031,11 @@
       </c>
       <c r="D499" s="5" t="inlineStr">
         <is>
-          <t>Loader</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E499" s="7" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
     </row>
     <row r="500">
@@ -15056,11 +15056,11 @@
       </c>
       <c r="D500" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E500" s="7" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="501">
@@ -15081,11 +15081,11 @@
       </c>
       <c r="D501" s="5" t="inlineStr">
         <is>
-          <t>Tracking</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E501" s="7" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="502">
@@ -15106,11 +15106,11 @@
       </c>
       <c r="D502" s="5" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Loader</t>
         </is>
       </c>
       <c r="E502" s="7" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="503">
@@ -15131,11 +15131,11 @@
       </c>
       <c r="D503" s="5" t="inlineStr">
         <is>
-          <t>Stepper</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E503" s="7" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
     </row>
     <row r="504">
@@ -15156,11 +15156,11 @@
       </c>
       <c r="D504" s="5" t="inlineStr">
         <is>
-          <t>Discount Badge</t>
+          <t>Tracking</t>
         </is>
       </c>
       <c r="E504" s="7" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="505">
@@ -15181,11 +15181,11 @@
       </c>
       <c r="D505" s="5" t="inlineStr">
         <is>
-          <t>Menu title</t>
+          <t>Stepper</t>
         </is>
       </c>
       <c r="E505" s="7" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="506">
@@ -15206,11 +15206,11 @@
       </c>
       <c r="D506" s="5" t="inlineStr">
         <is>
-          <t>File uploader</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E506" s="7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="507">
@@ -15231,11 +15231,11 @@
       </c>
       <c r="D507" s="5" t="inlineStr">
         <is>
-          <t>Toggle</t>
+          <t>Menu title</t>
         </is>
       </c>
       <c r="E507" s="7" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="508">
@@ -15256,11 +15256,11 @@
       </c>
       <c r="D508" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>File uploader</t>
         </is>
       </c>
       <c r="E508" s="7" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="509">
@@ -15281,61 +15281,61 @@
       </c>
       <c r="D509" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>Toggle</t>
         </is>
       </c>
       <c r="E509" s="7" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B510" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C510" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D510" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E510" s="7" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Ecommerce</t>
         </is>
       </c>
       <c r="B511" s="4" t="inlineStr">
         <is>
-          <t>Web Corporativa</t>
+          <t>Venta Directa</t>
         </is>
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>Productos Vida</t>
+          <t>Vida Ley &amp; SCTR</t>
         </is>
       </c>
       <c r="D511" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E511" s="7" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="512">
@@ -15356,11 +15356,11 @@
       </c>
       <c r="D512" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E512" s="7" t="n">
-        <v>47</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="513">
@@ -15381,11 +15381,11 @@
       </c>
       <c r="D513" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E513" s="7" t="n">
-        <v>34</v>
+        <v>959</v>
       </c>
     </row>
     <row r="514">
@@ -15406,11 +15406,11 @@
       </c>
       <c r="D514" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Accordion</t>
         </is>
       </c>
       <c r="E514" s="7" t="n">
-        <v>31</v>
+        <v>870</v>
       </c>
     </row>
     <row r="515">
@@ -15431,11 +15431,11 @@
       </c>
       <c r="D515" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E515" s="7" t="n">
-        <v>27</v>
+        <v>699</v>
       </c>
     </row>
     <row r="516">
@@ -15456,11 +15456,11 @@
       </c>
       <c r="D516" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E516" s="7" t="n">
-        <v>15</v>
+        <v>506</v>
       </c>
     </row>
     <row r="517">
@@ -15481,11 +15481,11 @@
       </c>
       <c r="D517" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E517" s="7" t="n">
-        <v>12</v>
+        <v>444</v>
       </c>
     </row>
     <row r="518">
@@ -15506,11 +15506,11 @@
       </c>
       <c r="D518" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E518" s="7" t="n">
-        <v>10</v>
+        <v>230</v>
       </c>
     </row>
     <row r="519">
@@ -15531,11 +15531,11 @@
       </c>
       <c r="D519" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E519" s="7" t="n">
-        <v>8</v>
+        <v>165</v>
       </c>
     </row>
     <row r="520">
@@ -15556,11 +15556,11 @@
       </c>
       <c r="D520" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E520" s="7" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
     </row>
     <row r="521">
@@ -15581,11 +15581,11 @@
       </c>
       <c r="D521" s="5" t="inlineStr">
         <is>
-          <t>Calendar</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E521" s="7" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
     </row>
     <row r="522">
@@ -15606,11 +15606,11 @@
       </c>
       <c r="D522" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Calendar</t>
         </is>
       </c>
       <c r="E522" s="7" t="n">
-        <v>3</v>
+        <v>91</v>
       </c>
     </row>
     <row r="523">
@@ -15631,11 +15631,11 @@
       </c>
       <c r="D523" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E523" s="7" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
     </row>
     <row r="524">
@@ -15656,11 +15656,11 @@
       </c>
       <c r="D524" s="5" t="inlineStr">
         <is>
-          <t>Slider Controls</t>
+          <t>title_+_options</t>
         </is>
       </c>
       <c r="E524" s="7" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
     </row>
     <row r="525">
@@ -15681,11 +15681,11 @@
       </c>
       <c r="D525" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Discount Badge</t>
         </is>
       </c>
       <c r="E525" s="7" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="526">
@@ -15706,11 +15706,11 @@
       </c>
       <c r="D526" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>src_option_stores_download</t>
         </is>
       </c>
       <c r="E526" s="7" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="527">
@@ -15731,11 +15731,11 @@
       </c>
       <c r="D527" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E527" s="7" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="528">
@@ -15756,460 +15756,1010 @@
       </c>
       <c r="D528" s="5" t="inlineStr">
         <is>
-          <t>Status Control</t>
+          <t>title_+_phones</t>
         </is>
       </c>
       <c r="E528" s="7" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B529" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C529" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D529" s="5" t="inlineStr">
         <is>
-          <t>type_option</t>
+          <t>title_+_social media</t>
         </is>
       </c>
       <c r="E529" s="7" t="n">
-        <v>95</v>
+        <v>11</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B530" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C530" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D530" s="5" t="inlineStr">
         <is>
-          <t>Átomo</t>
+          <t>Breadcrumb</t>
         </is>
       </c>
       <c r="E530" s="7" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B531" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C531" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D531" s="5" t="inlineStr">
         <is>
-          <t>Accordion</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E531" s="7" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B532" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C532" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D532" s="5" t="inlineStr">
         <is>
-          <t>Tab</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="E532" s="7" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B533" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C533" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Productos Vida</t>
         </is>
       </c>
       <c r="D533" s="5" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Hero</t>
         </is>
       </c>
       <c r="E533" s="7" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B534" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C534" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D534" s="5" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>type_option</t>
         </is>
       </c>
       <c r="E534" s="7" t="n">
-        <v>19</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B535" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C535" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D535" s="5" t="inlineStr">
         <is>
-          <t>section_footer</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="E535" s="7" t="n">
-        <v>15</v>
+        <v>350</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B536" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C536" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D536" s="5" t="inlineStr">
         <is>
-          <t>src_option_redes</t>
+          <t>Button</t>
         </is>
       </c>
       <c r="E536" s="7" t="n">
-        <v>10</v>
+        <v>331</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B537" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C537" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D537" s="5" t="inlineStr">
         <is>
-          <t>reemplazar slot</t>
+          <t>section_footer</t>
         </is>
       </c>
       <c r="E537" s="7" t="n">
-        <v>8</v>
+        <v>315</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B538" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C538" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D538" s="5" t="inlineStr">
         <is>
-          <t>Alert</t>
+          <t>Tab</t>
         </is>
       </c>
       <c r="E538" s="7" t="n">
-        <v>6</v>
+        <v>302</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B539" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C539" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D539" s="5" t="inlineStr">
         <is>
-          <t>title_+_options</t>
+          <t>Átomo</t>
         </is>
       </c>
       <c r="E539" s="7" t="n">
-        <v>3</v>
+        <v>272</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B540" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C540" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D540" s="5" t="inlineStr">
         <is>
-          <t>Hero</t>
+          <t>src_option_redes</t>
         </is>
       </c>
       <c r="E540" s="7" t="n">
-        <v>2</v>
+        <v>200</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B541" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C541" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D541" s="5" t="inlineStr">
         <is>
-          <t>src_option_stores_download</t>
+          <t>reemplazar slot</t>
         </is>
       </c>
       <c r="E541" s="7" t="n">
-        <v>2</v>
+        <v>168</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B542" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C542" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D542" s="5" t="inlineStr">
         <is>
-          <t>Breadcrumb</t>
+          <t>Header</t>
         </is>
       </c>
       <c r="E542" s="7" t="n">
-        <v>1</v>
+        <v>155</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B543" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C543" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D543" s="5" t="inlineStr">
         <is>
-          <t>title_+_phones</t>
+          <t>Alert</t>
         </is>
       </c>
       <c r="E543" s="7" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B544" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C544" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D544" s="5" t="inlineStr">
         <is>
-          <t>title_+_social media</t>
+          <t>Slider Controls</t>
         </is>
       </c>
       <c r="E544" s="7" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B545" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C545" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D545" s="5" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Status Control</t>
         </is>
       </c>
       <c r="E545" s="7" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="B546" s="4" t="inlineStr">
         <is>
-          <t>Embebidos</t>
+          <t>Web Corporativa</t>
         </is>
       </c>
       <c r="C546" s="4" t="inlineStr">
         <is>
-          <t>Landing Alianzas</t>
+          <t>Menú / Home</t>
         </is>
       </c>
       <c r="D546" s="5" t="inlineStr">
         <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E546" s="7" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E547" s="7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E548" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E549" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E550" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E551" s="7" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E552" s="7" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E553" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E554" s="7" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C555" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E555" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E556" s="7" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E557" s="7" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E558" s="7" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B559" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E559" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B560" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
           <t>Calendar</t>
         </is>
       </c>
-      <c r="E546" s="7" t="n">
+      <c r="E560" s="7" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B561" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E561" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B562" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="E562" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B563" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E563" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B564" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C564" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E564" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E565" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B566" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E566" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B567" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D567" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E567" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B568" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D568" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E568" s="7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16224,7 +16774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D278"/>
+  <dimension ref="A1:D261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -17092,7 +17642,7 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44">
@@ -17108,11 +17658,11 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Atajos | Beneficios (new)</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -17128,11 +17678,11 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
@@ -17148,11 +17698,11 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>NorthEast</t>
+          <t>Menu_Mobile</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47">
@@ -17168,11 +17718,11 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Line Tracking Vertical</t>
+          <t>NorthEast</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48">
@@ -17188,11 +17738,11 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>whatsapp</t>
+          <t>Menú_Desktop</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="49">
@@ -17208,11 +17758,11 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>Line Tracking Vertical</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -17228,11 +17778,11 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Menú_Desktop</t>
+          <t>whatsapp</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="51">
@@ -17248,11 +17798,11 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Menu_Mobile</t>
+          <t>datos personales</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
@@ -17268,11 +17818,11 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>beneficios reconocerte</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53">
@@ -17288,7 +17838,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>beneficios reconocerte</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -17328,7 +17878,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Feed</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
@@ -17348,11 +17898,11 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>vida ley</t>
+          <t>Feed</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -17368,11 +17918,11 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>tratamiento</t>
+          <t>Infotip</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58">
@@ -17388,11 +17938,11 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Right Label</t>
+          <t>trofeo</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59">
@@ -17408,11 +17958,11 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>PersonalInjuy</t>
+          <t>vida ley</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
@@ -17428,11 +17978,11 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Suggested search (Deprecated)</t>
+          <t>tratamiento</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -17448,11 +17998,11 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>laptop</t>
+          <t>Right Label</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
@@ -20672,7 +21222,7 @@
         </is>
       </c>
       <c r="D222" s="18" t="n">
-        <v>75</v>
+        <v>155</v>
       </c>
     </row>
     <row r="223">
@@ -20688,11 +21238,11 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Step 3</t>
         </is>
       </c>
       <c r="D223" s="18" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="224">
@@ -20712,7 +21262,7 @@
         </is>
       </c>
       <c r="D224" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="225">
@@ -20732,7 +21282,7 @@
         </is>
       </c>
       <c r="D225" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="226">
@@ -20748,11 +21298,11 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Step 3</t>
+          <t>Step 4</t>
         </is>
       </c>
       <c r="D226" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="227">
@@ -20768,11 +21318,11 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Step 4</t>
+          <t>Step 5</t>
         </is>
       </c>
       <c r="D227" s="18" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="228">
@@ -20788,11 +21338,11 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Step 5</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D228" s="18" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="229">
@@ -20808,11 +21358,11 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Indicator Mobile</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D229" s="18" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
     </row>
     <row r="230">
@@ -20828,11 +21378,11 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>Indicator Mobile</t>
         </is>
       </c>
       <c r="D230" s="18" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="231">
@@ -20852,7 +21402,7 @@
         </is>
       </c>
       <c r="D231" s="18" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="232">
@@ -20872,7 +21422,7 @@
         </is>
       </c>
       <c r="D232" s="18" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233">
@@ -20888,11 +21438,11 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>Cargador circular</t>
         </is>
       </c>
       <c r="D233" s="18" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="234">
@@ -20908,11 +21458,11 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Cargador circular</t>
+          <t>advertencia</t>
         </is>
       </c>
       <c r="D234" s="18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="235">
@@ -20928,11 +21478,11 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>advertencia</t>
+          <t>add</t>
         </is>
       </c>
       <c r="D235" s="18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="236">
@@ -20948,11 +21498,11 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>add</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D236" s="18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237">
@@ -20972,7 +21522,7 @@
         </is>
       </c>
       <c r="D237" s="18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="238">
@@ -20992,7 +21542,7 @@
         </is>
       </c>
       <c r="D238" s="18" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="239">
@@ -21008,11 +21558,11 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>[SCTR] Planes cotizador</t>
         </is>
       </c>
       <c r="D239" s="18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="240">
@@ -21028,11 +21578,11 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>datos personales</t>
+          <t>description</t>
         </is>
       </c>
       <c r="D240" s="18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="241">
@@ -21048,11 +21598,11 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>datos pacifico</t>
+          <t>Bullet Icon</t>
         </is>
       </c>
       <c r="D241" s="18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="242">
@@ -21068,11 +21618,11 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D242" s="18" t="n">
-        <v>6</v>
+        <v>217</v>
       </c>
     </row>
     <row r="243">
@@ -21088,11 +21638,11 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>CardProductPromo</t>
         </is>
       </c>
       <c r="D243" s="18" t="n">
-        <v>6</v>
+        <v>206</v>
       </c>
     </row>
     <row r="244">
@@ -21108,11 +21658,11 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D244" s="18" t="n">
-        <v>6</v>
+        <v>102</v>
       </c>
     </row>
     <row r="245">
@@ -21128,11 +21678,11 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D245" s="18" t="n">
-        <v>5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="246">
@@ -21148,11 +21698,11 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D246" s="18" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="247">
@@ -21168,11 +21718,11 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>CardMenúMobile</t>
         </is>
       </c>
       <c r="D247" s="18" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
     </row>
     <row r="248">
@@ -21188,11 +21738,11 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>CardMenú</t>
         </is>
       </c>
       <c r="D248" s="18" t="n">
-        <v>3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="249">
@@ -21208,11 +21758,11 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D249" s="18" t="n">
-        <v>2</v>
+        <v>71</v>
       </c>
     </row>
     <row r="250">
@@ -21228,11 +21778,11 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>BotónCategoría</t>
         </is>
       </c>
       <c r="D250" s="18" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
     </row>
     <row r="251">
@@ -21248,11 +21798,11 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>Slider</t>
         </is>
       </c>
       <c r="D251" s="18" t="n">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="252">
@@ -21268,11 +21818,11 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D252" s="18" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="253">
@@ -21288,11 +21838,11 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>support</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D253" s="18" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
     </row>
     <row r="254">
@@ -21308,11 +21858,11 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>download</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D254" s="18" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="255">
@@ -21328,11 +21878,11 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D255" s="18" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="256">
@@ -21348,11 +21898,11 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Link Details</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D256" s="18" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="257">
@@ -21368,11 +21918,11 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Trend</t>
         </is>
       </c>
       <c r="D257" s="18" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="258">
@@ -21388,11 +21938,11 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>user</t>
+          <t>MedicalService</t>
         </is>
       </c>
       <c r="D258" s="18" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="259">
@@ -21408,11 +21958,11 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>notifications</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D259" s="18" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="260">
@@ -21428,11 +21978,11 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>title_+_badges_download</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D260" s="18" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="261">
@@ -21448,351 +21998,11 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>ProductTabs</t>
         </is>
       </c>
       <c r="D261" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B262" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C262" s="4" t="inlineStr">
-        <is>
-          <t>SecciónDescripción</t>
-        </is>
-      </c>
-      <c r="D262" s="18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B263" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C263" s="4" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="D263" s="18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B264" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C264" s="4" t="inlineStr">
-        <is>
-          <t>WithoutShieldHeart</t>
-        </is>
-      </c>
-      <c r="D264" s="18" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B265" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C265" s="4" t="inlineStr">
-        <is>
-          <t>Icon</t>
-        </is>
-      </c>
-      <c r="D265" s="18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B266" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C266" s="4" t="inlineStr">
-        <is>
-          <t>Image</t>
-        </is>
-      </c>
-      <c r="D266" s="18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B267" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C267" s="4" t="inlineStr">
-        <is>
-          <t>Scroll</t>
-        </is>
-      </c>
-      <c r="D267" s="18" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B268" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C268" s="4" t="inlineStr">
-        <is>
-          <t>LogosCollab</t>
-        </is>
-      </c>
-      <c r="D268" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B269" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C269" s="4" t="inlineStr">
-        <is>
-          <t>boleta y factura</t>
-        </is>
-      </c>
-      <c r="D269" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B270" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C270" s="4" t="inlineStr">
-        <is>
-          <t>SeccionCanales</t>
-        </is>
-      </c>
-      <c r="D270" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>CoberturasIconos</t>
-        </is>
-      </c>
-      <c r="D271" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>PersonalInjuy</t>
-        </is>
-      </c>
-      <c r="D272" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="D273" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>Complex</t>
-        </is>
-      </c>
-      <c r="D274" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B275" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C275" s="4" t="inlineStr">
-        <is>
-          <t>title_+_badges_download</t>
-        </is>
-      </c>
-      <c r="D275" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B276" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C276" s="4" t="inlineStr">
-        <is>
-          <t>Close Icon</t>
-        </is>
-      </c>
-      <c r="D276" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B277" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C277" s="4" t="inlineStr">
-        <is>
-          <t>Cotizar</t>
-        </is>
-      </c>
-      <c r="D277" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B278" s="4" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="C278" s="4" t="inlineStr">
-        <is>
-          <t>Video</t>
-        </is>
-      </c>
-      <c r="D278" s="18" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -22046,22 +22256,22 @@
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>89%</t>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="F6" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>296</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22438,20 +22648,20 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="F16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>4898</v>
+        <v>7739</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>5571</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="17">
@@ -22906,20 +23116,20 @@
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
         <v>530</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>6030</v>
+        <v>11370</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>6362</v>
+        <v>12076</v>
       </c>
     </row>
     <row r="29">
@@ -23062,7 +23272,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -23071,13 +23281,13 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>359</v>
+        <v>10590</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>412</v>
+        <v>12617</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -1105,20 +1105,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>10590</v>
+        <v>5448</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>2027</v>
+        <v>787</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1997,20 +1997,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4605</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1163</v>
+        <v>0</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="H24" s="11" t="inlineStr">
-        <is>
-          <t>80%</t>
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2031,20 +2031,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>87%</t>
+        <v>0</v>
+      </c>
+      <c r="H25" s="13" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E568"/>
+  <dimension ref="A1:E533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15886,881 +15886,6 @@
       </c>
       <c r="E533" s="7" t="n">
         <v>2</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B534" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C534" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D534" s="5" t="inlineStr">
-        <is>
-          <t>type_option</t>
-        </is>
-      </c>
-      <c r="E534" s="7" t="n">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B535" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C535" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D535" s="5" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E535" s="7" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B536" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C536" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D536" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="E536" s="7" t="n">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B537" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C537" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D537" s="5" t="inlineStr">
-        <is>
-          <t>section_footer</t>
-        </is>
-      </c>
-      <c r="E537" s="7" t="n">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B538" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C538" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D538" s="5" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="E538" s="7" t="n">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B539" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C539" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D539" s="5" t="inlineStr">
-        <is>
-          <t>Átomo</t>
-        </is>
-      </c>
-      <c r="E539" s="7" t="n">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B540" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C540" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D540" s="5" t="inlineStr">
-        <is>
-          <t>src_option_redes</t>
-        </is>
-      </c>
-      <c r="E540" s="7" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B541" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C541" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D541" s="5" t="inlineStr">
-        <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="E541" s="7" t="n">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B542" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C542" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D542" s="5" t="inlineStr">
-        <is>
-          <t>Header</t>
-        </is>
-      </c>
-      <c r="E542" s="7" t="n">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B543" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C543" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D543" s="5" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="E543" s="7" t="n">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B544" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C544" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D544" s="5" t="inlineStr">
-        <is>
-          <t>Slider Controls</t>
-        </is>
-      </c>
-      <c r="E544" s="7" t="n">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B545" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C545" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D545" s="5" t="inlineStr">
-        <is>
-          <t>Status Control</t>
-        </is>
-      </c>
-      <c r="E545" s="7" t="n">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B546" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C546" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D546" s="5" t="inlineStr">
-        <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="E546" s="7" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B547" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C547" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D547" s="5" t="inlineStr">
-        <is>
-          <t>src_option_stores_download</t>
-        </is>
-      </c>
-      <c r="E547" s="7" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B548" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C548" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D548" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E548" s="7" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B549" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C549" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D549" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E549" s="7" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B550" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C550" s="4" t="inlineStr">
-        <is>
-          <t>Menú / Home</t>
-        </is>
-      </c>
-      <c r="D550" s="5" t="inlineStr">
-        <is>
-          <t>Hero</t>
-        </is>
-      </c>
-      <c r="E550" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B551" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C551" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D551" s="5" t="inlineStr">
-        <is>
-          <t>type_option</t>
-        </is>
-      </c>
-      <c r="E551" s="7" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B552" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C552" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D552" s="5" t="inlineStr">
-        <is>
-          <t>Átomo</t>
-        </is>
-      </c>
-      <c r="E552" s="7" t="n">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B553" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C553" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D553" s="5" t="inlineStr">
-        <is>
-          <t>Accordion</t>
-        </is>
-      </c>
-      <c r="E553" s="7" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B554" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C554" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D554" s="5" t="inlineStr">
-        <is>
-          <t>Tab</t>
-        </is>
-      </c>
-      <c r="E554" s="7" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B555" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C555" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D555" s="5" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="E555" s="7" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B556" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C556" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D556" s="5" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="E556" s="7" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B557" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D557" s="5" t="inlineStr">
-        <is>
-          <t>Alert</t>
-        </is>
-      </c>
-      <c r="E557" s="7" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B558" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C558" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D558" s="5" t="inlineStr">
-        <is>
-          <t>section_footer</t>
-        </is>
-      </c>
-      <c r="E558" s="7" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B559" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C559" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D559" s="5" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E559" s="7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B560" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C560" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D560" s="5" t="inlineStr">
-        <is>
-          <t>Calendar</t>
-        </is>
-      </c>
-      <c r="E560" s="7" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B561" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C561" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D561" s="5" t="inlineStr">
-        <is>
-          <t>reemplazar slot</t>
-        </is>
-      </c>
-      <c r="E561" s="7" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B562" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C562" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D562" s="5" t="inlineStr">
-        <is>
-          <t>Discount Badge</t>
-        </is>
-      </c>
-      <c r="E562" s="7" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B563" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C563" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D563" s="5" t="inlineStr">
-        <is>
-          <t>title_+_options</t>
-        </is>
-      </c>
-      <c r="E563" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B564" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C564" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D564" s="5" t="inlineStr">
-        <is>
-          <t>Breadcrumb</t>
-        </is>
-      </c>
-      <c r="E564" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B565" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C565" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D565" s="5" t="inlineStr">
-        <is>
-          <t>Slider Controls</t>
-        </is>
-      </c>
-      <c r="E565" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B566" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C566" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D566" s="5" t="inlineStr">
-        <is>
-          <t>title_+_phones</t>
-        </is>
-      </c>
-      <c r="E566" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B567" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D567" s="5" t="inlineStr">
-        <is>
-          <t>title_+_social media</t>
-        </is>
-      </c>
-      <c r="E567" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="B568" s="4" t="inlineStr">
-        <is>
-          <t>Web Corporativa</t>
-        </is>
-      </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>Productos Líneas Personales</t>
-        </is>
-      </c>
-      <c r="D568" s="5" t="inlineStr">
-        <is>
-          <t>Status Control</t>
-        </is>
-      </c>
-      <c r="E568" s="7" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21618,11 +20743,11 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Icon</t>
+          <t>Cotizar</t>
         </is>
       </c>
       <c r="D242" s="18" t="n">
-        <v>217</v>
+        <v>91</v>
       </c>
     </row>
     <row r="243">
@@ -21638,11 +20763,11 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>CardProductPromo</t>
+          <t>Video</t>
         </is>
       </c>
       <c r="D243" s="18" t="n">
-        <v>206</v>
+        <v>91</v>
       </c>
     </row>
     <row r="244">
@@ -21658,11 +20783,11 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Cotizar</t>
+          <t>Close Icon</t>
         </is>
       </c>
       <c r="D244" s="18" t="n">
-        <v>102</v>
+        <v>73</v>
       </c>
     </row>
     <row r="245">
@@ -21678,11 +20803,11 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Video</t>
+          <t>Scroll</t>
         </is>
       </c>
       <c r="D245" s="18" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
     </row>
     <row r="246">
@@ -21698,11 +20823,11 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Close Icon</t>
+          <t>_Link Icon</t>
         </is>
       </c>
       <c r="D246" s="18" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
     </row>
     <row r="247">
@@ -21718,11 +20843,11 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>CardMenúMobile</t>
+          <t>ShieldHeart</t>
         </is>
       </c>
       <c r="D247" s="18" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="248">
@@ -21738,11 +20863,11 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>CardMenú</t>
+          <t>WithoutShieldHeart</t>
         </is>
       </c>
       <c r="D248" s="18" t="n">
-        <v>77</v>
+        <v>50</v>
       </c>
     </row>
     <row r="249">
@@ -21758,11 +20883,11 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>_Button Icon</t>
         </is>
       </c>
       <c r="D249" s="18" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="250">
@@ -21778,11 +20903,11 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>BotónCategoría</t>
+          <t>submenu</t>
         </is>
       </c>
       <c r="D250" s="18" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="251">
@@ -21798,11 +20923,11 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Slider</t>
+          <t>Link Stamp</t>
         </is>
       </c>
       <c r="D251" s="18" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="252">
@@ -21818,11 +20943,11 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>WithoutShieldHeart</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D252" s="18" t="n">
-        <v>62</v>
+        <v>22</v>
       </c>
     </row>
     <row r="253">
@@ -21838,11 +20963,11 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>ShieldHeart</t>
+          <t>support</t>
         </is>
       </c>
       <c r="D253" s="18" t="n">
-        <v>61</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254">
@@ -21858,11 +20983,11 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>_Link Icon</t>
+          <t>download</t>
         </is>
       </c>
       <c r="D254" s="18" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="255">
@@ -21878,11 +21003,11 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>_Button Icon</t>
+          <t>Link Details</t>
         </is>
       </c>
       <c r="D255" s="18" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
     </row>
     <row r="256">
@@ -21898,11 +21023,11 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Icon</t>
         </is>
       </c>
       <c r="D256" s="18" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
     </row>
     <row r="257">
@@ -21918,11 +21043,11 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Trend</t>
+          <t>vida inversión</t>
         </is>
       </c>
       <c r="D257" s="18" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="258">
@@ -21938,11 +21063,11 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>MedicalService</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="D258" s="18" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="259">
@@ -21958,11 +21083,11 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>submenu</t>
+          <t>user</t>
         </is>
       </c>
       <c r="D259" s="18" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="260">
@@ -21978,11 +21103,11 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Link Stamp</t>
+          <t>notifications</t>
         </is>
       </c>
       <c r="D260" s="18" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="261">
@@ -21998,11 +21123,11 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>ProductTabs</t>
+          <t>title_+_badges_download</t>
         </is>
       </c>
       <c r="D261" s="18" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -23272,7 +22397,7 @@
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="F32" s="10" t="inlineStr">
@@ -23281,13 +22406,13 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>10590</v>
+        <v>5448</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>12617</v>
+        <v>6235</v>
       </c>
     </row>
   </sheetData>

--- a/docs/reporte-adopcion.xlsx
+++ b/docs/reporte-adopcion.xlsx
@@ -90,12 +90,6 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFBA7517"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="FFD94F3D"/>
       <sz val="10"/>
     </font>
@@ -114,6 +108,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="FF8C8880"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FFBA7517"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -181,18 +181,18 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -666,8 +666,10 @@
           <t>51%</t>
         </is>
       </c>
-      <c r="I5" s="10" t="n">
-        <v>0</v>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -701,8 +703,10 @@
           <t>87%</t>
         </is>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>1</v>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -736,8 +740,10 @@
           <t>90%</t>
         </is>
       </c>
-      <c r="I7" s="10" t="n">
-        <v>0</v>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -771,8 +777,10 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
@@ -806,8 +814,10 @@
           <t>84%</t>
         </is>
       </c>
-      <c r="I9" s="10" t="n">
-        <v>0</v>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
@@ -841,8 +851,10 @@
           <t>65%</t>
         </is>
       </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
@@ -876,8 +888,10 @@
           <t>75%</t>
         </is>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>530</v>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
@@ -911,8 +925,10 @@
           <t>73%</t>
         </is>
       </c>
-      <c r="I12" s="12" t="n">
-        <v>530</v>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
@@ -941,13 +957,15 @@
       <c r="G13" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="13" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="I13" s="12" t="n">
-        <v>530</v>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -981,8 +999,10 @@
           <t>69%</t>
         </is>
       </c>
-      <c r="I14" s="12" t="n">
-        <v>530</v>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
@@ -1016,8 +1036,10 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>530</v>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -1051,8 +1073,10 @@
           <t>85%</t>
         </is>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>530</v>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -1086,8 +1110,10 @@
           <t>94%</t>
         </is>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>530</v>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -1105,20 +1131,20 @@
         <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>5448</v>
+        <v>11472</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>787</v>
+        <v>2122</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="I18" s="10" t="inlineStr">
@@ -1142,24 +1168,26 @@
         <v>1</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1362,7 +1390,7 @@
       <c r="G5" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="H5" s="13" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
@@ -1668,7 +1696,7 @@
       <c r="G14" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="H14" s="13" t="inlineStr">
+      <c r="H14" s="12" t="inlineStr">
         <is>
           <t>47%</t>
         </is>
@@ -1804,7 +1832,7 @@
       <c r="G18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="12" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
@@ -1997,20 +2025,20 @@
         </is>
       </c>
       <c r="D24" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>4605</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0</v>
+        <v>1163</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>17</v>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>80%</t>
         </is>
       </c>
     </row>
@@ -2031,20 +2059,20 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>0</v>
+        <v>1419</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>21</v>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>89%</t>
         </is>
       </c>
     </row>
@@ -2065,20 +2093,20 @@
         </is>
       </c>
       <c r="D26" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1424</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0</v>
+        <v>201</v>
       </c>
       <c r="G26" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="13" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>19</v>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>88%</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2101,109 +2129,29 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Desvinculaciones por categoría — Library Analytics API</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Fuente: Figma Library Analytics (Enterprise), agregado por Figma Team del quarter actual. El % es referencial (volumen de inserciones suele ser alto, por lo que el % puede verse cercano a 0 aunque haya desvinculaciones reales).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Desvinculaciones Q</t>
         </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>MEP</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Somos Corredores</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Protege 365</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Nueva Web Empresas</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Portal Digital de Siniestros</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Modelo Día</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Ecommerce</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Embebidos</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2231,36 +2179,36 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Componentes con más desvinculaciones — toda la librería Dalton</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>No filtrado por categoría/equipo — la API de Figma no permite ese cruce. Útil para ver qué componentes del sistema tienden a romperse más, independientemente de quién los usa.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Componente</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Desvinculaciones</t>
         </is>
       </c>
-      <c r="C4" s="16" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>Inserciones</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>Detach %</t>
         </is>
@@ -2272,13 +2220,13 @@
           <t>type_option</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="12" t="n">
         <v>485</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>2351</v>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
         <is>
           <t>17.1%</t>
         </is>
@@ -2290,13 +2238,13 @@
           <t>section_footer</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>86</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>4229</v>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
         <is>
           <t>1.99%</t>
         </is>
@@ -2308,13 +2256,13 @@
           <t>Modal Informative</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="12" t="n">
         <v>58</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>775</v>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>6.96%</t>
         </is>
@@ -2326,13 +2274,13 @@
           <t>Button</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="12" t="n">
         <v>53</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>71255</v>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>0.07%</t>
         </is>
@@ -2344,13 +2292,13 @@
           <t>src_option_redes</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="12" t="n">
         <v>50</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="16" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
@@ -2362,13 +2310,13 @@
           <t>reemplazar slot</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>40</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>3758</v>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>1.05%</t>
         </is>
@@ -2380,13 +2328,13 @@
           <t>Radio Outline</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <v>34</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>891</v>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
         <is>
           <t>3.68%</t>
         </is>
@@ -2398,13 +2346,13 @@
           <t>Radio Atom</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="12" t="n">
         <v>24</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>8726</v>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
         <is>
           <t>0.27%</t>
         </is>
@@ -2416,13 +2364,13 @@
           <t>Chips Status</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="12" t="n">
         <v>23</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>11044</v>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>0.21%</t>
         </is>
@@ -2434,13 +2382,13 @@
           <t>title_+_options</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <v>23</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>1408</v>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>1.61%</t>
         </is>
@@ -2452,13 +2400,13 @@
           <t>Accordion</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="12" t="n">
         <v>21</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="16" t="inlineStr">
         <is>
           <t>2.06%</t>
         </is>
@@ -2470,13 +2418,13 @@
           <t>Input</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>20</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>17659</v>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="16" t="inlineStr">
         <is>
           <t>0.11%</t>
         </is>
@@ -2488,13 +2436,13 @@
           <t>Checkbox With Text</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="12" t="n">
         <v>16</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>4138</v>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>0.39%</t>
         </is>
@@ -2506,13 +2454,13 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="12" t="n">
         <v>13</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>1261</v>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="16" t="inlineStr">
         <is>
           <t>1.02%</t>
         </is>
@@ -2524,13 +2472,13 @@
           <t>Checkbox Atom</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="12" t="n">
         <v>11</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>3791</v>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="16" t="inlineStr">
         <is>
           <t>0.29%</t>
         </is>
@@ -2551,7 +2499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E533"/>
+  <dimension ref="A1:E590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15888,6 +15836,1431 @@
         <v>2</v>
       </c>
     </row>
+    <row r="534">
+      <c r="A534" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B534" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C534" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D534" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E534" s="7" t="n">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B535" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C535" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D535" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E535" s="7" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B536" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C536" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D536" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E536" s="7" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B537" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C537" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D537" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E537" s="7" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C538" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D538" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E538" s="7" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B539" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C539" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D539" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E539" s="7" t="n">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B540" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C540" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D540" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E540" s="7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B541" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C541" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D541" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E541" s="7" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B542" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C542" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D542" s="5" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="E542" s="7" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C543" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D543" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E543" s="7" t="n">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B544" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C544" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D544" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E544" s="7" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B545" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C545" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D545" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E545" s="7" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B546" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C546" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D546" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E546" s="7" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C547" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D547" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E547" s="7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B548" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C548" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D548" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E548" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C549" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D549" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E549" s="7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B550" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C550" s="4" t="inlineStr">
+        <is>
+          <t>Menú / Home</t>
+        </is>
+      </c>
+      <c r="D550" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E550" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B551" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C551" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D551" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E551" s="7" t="n">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B552" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C552" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D552" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E552" s="7" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B553" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C553" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D553" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E553" s="7" t="n">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B554" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C554" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D554" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E554" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B555" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C555" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D555" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E555" s="7" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C556" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D556" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E556" s="7" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B557" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C557" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D557" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E557" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C558" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D558" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E558" s="7" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B559" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C559" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D559" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E559" s="7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B560" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C560" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D560" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E560" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B561" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C561" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D561" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E561" s="7" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B562" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C562" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D562" s="5" t="inlineStr">
+        <is>
+          <t>Discount Badge</t>
+        </is>
+      </c>
+      <c r="E562" s="7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B563" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C563" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D563" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E563" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B564" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C564" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D564" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E564" s="7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C565" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D565" s="5" t="inlineStr">
+        <is>
+          <t>Slider Controls</t>
+        </is>
+      </c>
+      <c r="E565" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B566" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C566" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D566" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E566" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B567" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C567" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D567" s="5" t="inlineStr">
+        <is>
+          <t>Status Control</t>
+        </is>
+      </c>
+      <c r="E567" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B568" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C568" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D568" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E568" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B569" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C569" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D569" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E569" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B570" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C570" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D570" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E570" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="B571" s="4" t="inlineStr">
+        <is>
+          <t>Web Corporativa</t>
+        </is>
+      </c>
+      <c r="C571" s="4" t="inlineStr">
+        <is>
+          <t>Productos Líneas Personales</t>
+        </is>
+      </c>
+      <c r="D571" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E571" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B572" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C572" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D572" s="5" t="inlineStr">
+        <is>
+          <t>type_option</t>
+        </is>
+      </c>
+      <c r="E572" s="7" t="n">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B573" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C573" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D573" s="5" t="inlineStr">
+        <is>
+          <t>Átomo</t>
+        </is>
+      </c>
+      <c r="E573" s="7" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B574" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C574" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D574" s="5" t="inlineStr">
+        <is>
+          <t>Accordion</t>
+        </is>
+      </c>
+      <c r="E574" s="7" t="n">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B575" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C575" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D575" s="5" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="E575" s="7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B576" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C576" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D576" s="5" t="inlineStr">
+        <is>
+          <t>section_footer</t>
+        </is>
+      </c>
+      <c r="E576" s="7" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B577" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C577" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D577" s="5" t="inlineStr">
+        <is>
+          <t>Button</t>
+        </is>
+      </c>
+      <c r="E577" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B578" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C578" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D578" s="5" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E578" s="7" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B579" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C579" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D579" s="5" t="inlineStr">
+        <is>
+          <t>src_option_redes</t>
+        </is>
+      </c>
+      <c r="E579" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C580" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D580" s="5" t="inlineStr">
+        <is>
+          <t>reemplazar slot</t>
+        </is>
+      </c>
+      <c r="E580" s="7" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B581" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C581" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D581" s="5" t="inlineStr">
+        <is>
+          <t>title_+_options</t>
+        </is>
+      </c>
+      <c r="E581" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B582" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C582" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D582" s="5" t="inlineStr">
+        <is>
+          <t>Alert</t>
+        </is>
+      </c>
+      <c r="E582" s="7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B583" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C583" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D583" s="5" t="inlineStr">
+        <is>
+          <t>src_option_stores_download</t>
+        </is>
+      </c>
+      <c r="E583" s="7" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B584" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C584" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D584" s="5" t="inlineStr">
+        <is>
+          <t>Hero</t>
+        </is>
+      </c>
+      <c r="E584" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B585" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C585" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D585" s="5" t="inlineStr">
+        <is>
+          <t>Breadcrumb</t>
+        </is>
+      </c>
+      <c r="E585" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B586" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C586" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D586" s="5" t="inlineStr">
+        <is>
+          <t>title_+_phones</t>
+        </is>
+      </c>
+      <c r="E586" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B587" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C587" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D587" s="5" t="inlineStr">
+        <is>
+          <t>title_+_social media</t>
+        </is>
+      </c>
+      <c r="E587" s="7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B588" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C588" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D588" s="5" t="inlineStr">
+        <is>
+          <t>Logo Horizontal</t>
+        </is>
+      </c>
+      <c r="E588" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B589" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C589" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D589" s="5" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="E589" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="B590" s="4" t="inlineStr">
+        <is>
+          <t>Embebidos</t>
+        </is>
+      </c>
+      <c r="C590" s="4" t="inlineStr">
+        <is>
+          <t>Landing Alianzas</t>
+        </is>
+      </c>
+      <c r="D590" s="5" t="inlineStr">
+        <is>
+          <t>Calendar</t>
+        </is>
+      </c>
+      <c r="E590" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15899,7 +17272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D261"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -15946,7 +17319,7 @@
           <t>menú</t>
         </is>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>1786</v>
       </c>
     </row>
@@ -15966,7 +17339,7 @@
           <t>card_accion</t>
         </is>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="17" t="n">
         <v>220</v>
       </c>
     </row>
@@ -15986,7 +17359,7 @@
           <t>card_atajo_home</t>
         </is>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="17" t="n">
         <v>218</v>
       </c>
     </row>
@@ -16006,7 +17379,7 @@
           <t>documento simple</t>
         </is>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>100</v>
       </c>
     </row>
@@ -16026,7 +17399,7 @@
           <t>Seguros card</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>48</v>
       </c>
     </row>
@@ -16046,7 +17419,7 @@
           <t>Card_ beneficios</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>38</v>
       </c>
     </row>
@@ -16066,7 +17439,7 @@
           <t>beneficios vehiculares</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>37</v>
       </c>
     </row>
@@ -16086,7 +17459,7 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>35</v>
       </c>
     </row>
@@ -16106,7 +17479,7 @@
           <t>carro</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -16126,7 +17499,7 @@
           <t>buscar clínicas</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -16146,7 +17519,7 @@
           <t>hogar</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -16166,7 +17539,7 @@
           <t>drag</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="17" t="n">
         <v>26</v>
       </c>
     </row>
@@ -16186,7 +17559,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -16206,7 +17579,7 @@
           <t>logo beneficios</t>
         </is>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -16226,7 +17599,7 @@
           <t>error duda</t>
         </is>
       </c>
-      <c r="D16" s="18" t="n">
+      <c r="D16" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -16246,7 +17619,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D17" s="18" t="n">
+      <c r="D17" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -16266,7 +17639,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D18" s="18" t="n">
+      <c r="D18" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -16286,7 +17659,7 @@
           <t>Bottom Navigation</t>
         </is>
       </c>
-      <c r="D19" s="18" t="n">
+      <c r="D19" s="17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -16306,7 +17679,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="17" t="n">
         <v>13</v>
       </c>
     </row>
@@ -16326,7 +17699,7 @@
           <t>card_atajo</t>
         </is>
       </c>
-      <c r="D21" s="18" t="n">
+      <c r="D21" s="17" t="n">
         <v>12</v>
       </c>
     </row>
@@ -16346,7 +17719,7 @@
           <t>Suggested search (Deprecated)</t>
         </is>
       </c>
-      <c r="D22" s="18" t="n">
+      <c r="D22" s="17" t="n">
         <v>65</v>
       </c>
     </row>
@@ -16366,7 +17739,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D23" s="18" t="n">
+      <c r="D23" s="17" t="n">
         <v>59</v>
       </c>
     </row>
@@ -16386,7 +17759,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D24" s="18" t="n">
+      <c r="D24" s="17" t="n">
         <v>59</v>
       </c>
     </row>
@@ -16406,7 +17779,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D25" s="17" t="n">
         <v>59</v>
       </c>
     </row>
@@ -16426,7 +17799,7 @@
           <t>celda L</t>
         </is>
       </c>
-      <c r="D26" s="18" t="n">
+      <c r="D26" s="17" t="n">
         <v>49</v>
       </c>
     </row>
@@ -16446,7 +17819,7 @@
           <t>Step 04</t>
         </is>
       </c>
-      <c r="D27" s="18" t="n">
+      <c r="D27" s="17" t="n">
         <v>39</v>
       </c>
     </row>
@@ -16466,7 +17839,7 @@
           <t>Step 05</t>
         </is>
       </c>
-      <c r="D28" s="18" t="n">
+      <c r="D28" s="17" t="n">
         <v>39</v>
       </c>
     </row>
@@ -16486,7 +17859,7 @@
           <t>Upload icon</t>
         </is>
       </c>
-      <c r="D29" s="18" t="n">
+      <c r="D29" s="17" t="n">
         <v>31</v>
       </c>
     </row>
@@ -16506,7 +17879,7 @@
           <t>Userflow</t>
         </is>
       </c>
-      <c r="D30" s="18" t="n">
+      <c r="D30" s="17" t="n">
         <v>27</v>
       </c>
     </row>
@@ -16526,7 +17899,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D31" s="18" t="n">
+      <c r="D31" s="17" t="n">
         <v>21</v>
       </c>
     </row>
@@ -16546,7 +17919,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D32" s="18" t="n">
+      <c r="D32" s="17" t="n">
         <v>12</v>
       </c>
     </row>
@@ -16566,7 +17939,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D33" s="18" t="n">
+      <c r="D33" s="17" t="n">
         <v>12</v>
       </c>
     </row>
@@ -16586,7 +17959,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D34" s="18" t="n">
+      <c r="D34" s="17" t="n">
         <v>11</v>
       </c>
     </row>
@@ -16606,7 +17979,7 @@
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -16626,7 +17999,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16646,7 +18019,7 @@
           <t>audifonos</t>
         </is>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -16666,7 +18039,7 @@
           <t>Container Drag and Drop</t>
         </is>
       </c>
-      <c r="D38" s="18" t="n">
+      <c r="D38" s="17" t="n">
         <v>7</v>
       </c>
     </row>
@@ -16686,7 +18059,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D39" s="18" t="n">
+      <c r="D39" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -16706,7 +18079,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D40" s="18" t="n">
+      <c r="D40" s="17" t="n">
         <v>6</v>
       </c>
     </row>
@@ -16726,7 +18099,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D41" s="18" t="n">
+      <c r="D41" s="17" t="n">
         <v>5</v>
       </c>
     </row>
@@ -16746,7 +18119,7 @@
           <t>HealthAndSafe</t>
         </is>
       </c>
-      <c r="D42" s="18" t="n">
+      <c r="D42" s="17" t="n">
         <v>96</v>
       </c>
     </row>
@@ -16766,7 +18139,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D43" s="18" t="n">
+      <c r="D43" s="17" t="n">
         <v>54</v>
       </c>
     </row>
@@ -16786,7 +18159,7 @@
           <t>Slider</t>
         </is>
       </c>
-      <c r="D44" s="18" t="n">
+      <c r="D44" s="17" t="n">
         <v>44</v>
       </c>
     </row>
@@ -16806,7 +18179,7 @@
           <t>Atajos | Beneficios (new)</t>
         </is>
       </c>
-      <c r="D45" s="18" t="n">
+      <c r="D45" s="17" t="n">
         <v>35</v>
       </c>
     </row>
@@ -16826,7 +18199,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D46" s="18" t="n">
+      <c r="D46" s="17" t="n">
         <v>34</v>
       </c>
     </row>
@@ -16846,7 +18219,7 @@
           <t>NorthEast</t>
         </is>
       </c>
-      <c r="D47" s="18" t="n">
+      <c r="D47" s="17" t="n">
         <v>32</v>
       </c>
     </row>
@@ -16866,7 +18239,7 @@
           <t>Menú_Desktop</t>
         </is>
       </c>
-      <c r="D48" s="18" t="n">
+      <c r="D48" s="17" t="n">
         <v>31</v>
       </c>
     </row>
@@ -16886,7 +18259,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D49" s="18" t="n">
+      <c r="D49" s="17" t="n">
         <v>30</v>
       </c>
     </row>
@@ -16906,7 +18279,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D50" s="18" t="n">
+      <c r="D50" s="17" t="n">
         <v>29</v>
       </c>
     </row>
@@ -16926,7 +18299,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D51" s="18" t="n">
+      <c r="D51" s="17" t="n">
         <v>28</v>
       </c>
     </row>
@@ -16946,7 +18319,7 @@
           <t>beneficios reconocerte</t>
         </is>
       </c>
-      <c r="D52" s="18" t="n">
+      <c r="D52" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -16966,7 +18339,7 @@
           <t>advertencia</t>
         </is>
       </c>
-      <c r="D53" s="18" t="n">
+      <c r="D53" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -16986,7 +18359,7 @@
           <t>filter</t>
         </is>
       </c>
-      <c r="D54" s="18" t="n">
+      <c r="D54" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -17006,7 +18379,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D55" s="18" t="n">
+      <c r="D55" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -17026,7 +18399,7 @@
           <t>Feed</t>
         </is>
       </c>
-      <c r="D56" s="18" t="n">
+      <c r="D56" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -17046,7 +18419,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D57" s="18" t="n">
+      <c r="D57" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17066,7 +18439,7 @@
           <t>trofeo</t>
         </is>
       </c>
-      <c r="D58" s="18" t="n">
+      <c r="D58" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -17086,7 +18459,7 @@
           <t>vida ley</t>
         </is>
       </c>
-      <c r="D59" s="18" t="n">
+      <c r="D59" s="17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17106,7 +18479,7 @@
           <t>tratamiento</t>
         </is>
       </c>
-      <c r="D60" s="18" t="n">
+      <c r="D60" s="17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17126,7 +18499,7 @@
           <t>Right Label</t>
         </is>
       </c>
-      <c r="D61" s="18" t="n">
+      <c r="D61" s="17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -17146,7 +18519,7 @@
           <t>celda S</t>
         </is>
       </c>
-      <c r="D62" s="18" t="n">
+      <c r="D62" s="17" t="n">
         <v>2366</v>
       </c>
     </row>
@@ -17166,7 +18539,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D63" s="18" t="n">
+      <c r="D63" s="17" t="n">
         <v>699</v>
       </c>
     </row>
@@ -17186,7 +18559,7 @@
           <t>title_+_badges_download</t>
         </is>
       </c>
-      <c r="D64" s="18" t="n">
+      <c r="D64" s="17" t="n">
         <v>550</v>
       </c>
     </row>
@@ -17206,7 +18579,7 @@
           <t>Home_Header</t>
         </is>
       </c>
-      <c r="D65" s="18" t="n">
+      <c r="D65" s="17" t="n">
         <v>512</v>
       </c>
     </row>
@@ -17226,7 +18599,7 @@
           <t>Action 1</t>
         </is>
       </c>
-      <c r="D66" s="18" t="n">
+      <c r="D66" s="17" t="n">
         <v>496</v>
       </c>
     </row>
@@ -17246,7 +18619,7 @@
           <t>Action 2</t>
         </is>
       </c>
-      <c r="D67" s="18" t="n">
+      <c r="D67" s="17" t="n">
         <v>496</v>
       </c>
     </row>
@@ -17266,7 +18639,7 @@
           <t>Menu_Mobile</t>
         </is>
       </c>
-      <c r="D68" s="18" t="n">
+      <c r="D68" s="17" t="n">
         <v>482</v>
       </c>
     </row>
@@ -17286,7 +18659,7 @@
           <t>titulo-fila</t>
         </is>
       </c>
-      <c r="D69" s="18" t="n">
+      <c r="D69" s="17" t="n">
         <v>433</v>
       </c>
     </row>
@@ -17306,7 +18679,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D70" s="18" t="n">
+      <c r="D70" s="17" t="n">
         <v>398</v>
       </c>
     </row>
@@ -17326,7 +18699,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D71" s="18" t="n">
+      <c r="D71" s="17" t="n">
         <v>398</v>
       </c>
     </row>
@@ -17346,7 +18719,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D72" s="18" t="n">
+      <c r="D72" s="17" t="n">
         <v>390</v>
       </c>
     </row>
@@ -17366,7 +18739,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D73" s="18" t="n">
+      <c r="D73" s="17" t="n">
         <v>382</v>
       </c>
     </row>
@@ -17386,7 +18759,7 @@
           <t>save</t>
         </is>
       </c>
-      <c r="D74" s="18" t="n">
+      <c r="D74" s="17" t="n">
         <v>328</v>
       </c>
     </row>
@@ -17406,7 +18779,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D75" s="18" t="n">
+      <c r="D75" s="17" t="n">
         <v>324</v>
       </c>
     </row>
@@ -17426,7 +18799,7 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D76" s="18" t="n">
+      <c r="D76" s="17" t="n">
         <v>312</v>
       </c>
     </row>
@@ -17446,7 +18819,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D77" s="18" t="n">
+      <c r="D77" s="17" t="n">
         <v>295</v>
       </c>
     </row>
@@ -17466,7 +18839,7 @@
           <t>medios de pago</t>
         </is>
       </c>
-      <c r="D78" s="18" t="n">
+      <c r="D78" s="17" t="n">
         <v>280</v>
       </c>
     </row>
@@ -17486,7 +18859,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D79" s="18" t="n">
+      <c r="D79" s="17" t="n">
         <v>116</v>
       </c>
     </row>
@@ -17506,7 +18879,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D80" s="18" t="n">
+      <c r="D80" s="17" t="n">
         <v>104</v>
       </c>
     </row>
@@ -17526,7 +18899,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D81" s="18" t="n">
+      <c r="D81" s="17" t="n">
         <v>104</v>
       </c>
     </row>
@@ -17546,7 +18919,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D82" s="18" t="n">
+      <c r="D82" s="17" t="n">
         <v>233</v>
       </c>
     </row>
@@ -17566,7 +18939,7 @@
           <t>DirectionRight</t>
         </is>
       </c>
-      <c r="D83" s="18" t="n">
+      <c r="D83" s="17" t="n">
         <v>198</v>
       </c>
     </row>
@@ -17586,7 +18959,7 @@
           <t>Option</t>
         </is>
       </c>
-      <c r="D84" s="18" t="n">
+      <c r="D84" s="17" t="n">
         <v>165</v>
       </c>
     </row>
@@ -17606,7 +18979,7 @@
           <t>Pegar Icon</t>
         </is>
       </c>
-      <c r="D85" s="18" t="n">
+      <c r="D85" s="17" t="n">
         <v>102</v>
       </c>
     </row>
@@ -17626,7 +18999,7 @@
           <t>Component 9</t>
         </is>
       </c>
-      <c r="D86" s="18" t="n">
+      <c r="D86" s="17" t="n">
         <v>90</v>
       </c>
     </row>
@@ -17646,7 +19019,7 @@
           <t>copy</t>
         </is>
       </c>
-      <c r="D87" s="18" t="n">
+      <c r="D87" s="17" t="n">
         <v>57</v>
       </c>
     </row>
@@ -17666,7 +19039,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D88" s="18" t="n">
+      <c r="D88" s="17" t="n">
         <v>37</v>
       </c>
     </row>
@@ -17686,7 +19059,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D89" s="18" t="n">
+      <c r="D89" s="17" t="n">
         <v>32</v>
       </c>
     </row>
@@ -17706,7 +19079,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D90" s="18" t="n">
+      <c r="D90" s="17" t="n">
         <v>29</v>
       </c>
     </row>
@@ -17726,7 +19099,7 @@
           <t>Tooltip</t>
         </is>
       </c>
-      <c r="D91" s="18" t="n">
+      <c r="D91" s="17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -17746,7 +19119,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D92" s="18" t="n">
+      <c r="D92" s="17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -17766,7 +19139,7 @@
           <t>informacion de poliza</t>
         </is>
       </c>
-      <c r="D93" s="18" t="n">
+      <c r="D93" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17786,7 +19159,7 @@
           <t>datos personales</t>
         </is>
       </c>
-      <c r="D94" s="18" t="n">
+      <c r="D94" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17806,7 +19179,7 @@
           <t>soles</t>
         </is>
       </c>
-      <c r="D95" s="18" t="n">
+      <c r="D95" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -17826,7 +19199,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D96" s="18" t="n">
+      <c r="D96" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -17846,7 +19219,7 @@
           <t>24.timer</t>
         </is>
       </c>
-      <c r="D97" s="18" t="n">
+      <c r="D97" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -17866,7 +19239,7 @@
           <t>File</t>
         </is>
       </c>
-      <c r="D98" s="18" t="n">
+      <c r="D98" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -17886,7 +19259,7 @@
           <t>Action</t>
         </is>
       </c>
-      <c r="D99" s="18" t="n">
+      <c r="D99" s="17" t="n">
         <v>19</v>
       </c>
     </row>
@@ -17906,7 +19279,7 @@
           <t>circle</t>
         </is>
       </c>
-      <c r="D100" s="18" t="n">
+      <c r="D100" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -17926,7 +19299,7 @@
           <t>Cargador circular</t>
         </is>
       </c>
-      <c r="D101" s="18" t="n">
+      <c r="D101" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -17946,7 +19319,7 @@
           <t>desk Table cell</t>
         </is>
       </c>
-      <c r="D102" s="18" t="n">
+      <c r="D102" s="17" t="n">
         <v>2624</v>
       </c>
     </row>
@@ -17966,7 +19339,7 @@
           <t>Control</t>
         </is>
       </c>
-      <c r="D103" s="18" t="n">
+      <c r="D103" s="17" t="n">
         <v>636</v>
       </c>
     </row>
@@ -17986,7 +19359,7 @@
           <t>DirectionDown</t>
         </is>
       </c>
-      <c r="D104" s="18" t="n">
+      <c r="D104" s="17" t="n">
         <v>311</v>
       </c>
     </row>
@@ -18006,7 +19379,7 @@
           <t>Component 16</t>
         </is>
       </c>
-      <c r="D105" s="18" t="n">
+      <c r="D105" s="17" t="n">
         <v>297</v>
       </c>
     </row>
@@ -18026,7 +19399,7 @@
           <t>Botón Primario</t>
         </is>
       </c>
-      <c r="D106" s="18" t="n">
+      <c r="D106" s="17" t="n">
         <v>198</v>
       </c>
     </row>
@@ -18046,7 +19419,7 @@
           <t>Dropdown filter page</t>
         </is>
       </c>
-      <c r="D107" s="18" t="n">
+      <c r="D107" s="17" t="n">
         <v>159</v>
       </c>
     </row>
@@ -18066,7 +19439,7 @@
           <t>width fixed pagination</t>
         </is>
       </c>
-      <c r="D108" s="18" t="n">
+      <c r="D108" s="17" t="n">
         <v>159</v>
       </c>
     </row>
@@ -18086,7 +19459,7 @@
           <t>Line Tracking Vertical</t>
         </is>
       </c>
-      <c r="D109" s="18" t="n">
+      <c r="D109" s="17" t="n">
         <v>135</v>
       </c>
     </row>
@@ -18106,7 +19479,7 @@
           <t>barras</t>
         </is>
       </c>
-      <c r="D110" s="18" t="n">
+      <c r="D110" s="17" t="n">
         <v>127</v>
       </c>
     </row>
@@ -18126,7 +19499,7 @@
           <t>Article</t>
         </is>
       </c>
-      <c r="D111" s="18" t="n">
+      <c r="D111" s="17" t="n">
         <v>125</v>
       </c>
     </row>
@@ -18146,7 +19519,7 @@
           <t>billetera</t>
         </is>
       </c>
-      <c r="D112" s="18" t="n">
+      <c r="D112" s="17" t="n">
         <v>118</v>
       </c>
     </row>
@@ -18166,7 +19539,7 @@
           <t>description</t>
         </is>
       </c>
-      <c r="D113" s="18" t="n">
+      <c r="D113" s="17" t="n">
         <v>117</v>
       </c>
     </row>
@@ -18186,7 +19559,7 @@
           <t>DirectionUp</t>
         </is>
       </c>
-      <c r="D114" s="18" t="n">
+      <c r="D114" s="17" t="n">
         <v>116</v>
       </c>
     </row>
@@ -18206,7 +19579,7 @@
           <t>create account</t>
         </is>
       </c>
-      <c r="D115" s="18" t="n">
+      <c r="D115" s="17" t="n">
         <v>116</v>
       </c>
     </row>
@@ -18226,7 +19599,7 @@
           <t>ArrowLeft</t>
         </is>
       </c>
-      <c r="D116" s="18" t="n">
+      <c r="D116" s="17" t="n">
         <v>104</v>
       </c>
     </row>
@@ -18246,7 +19619,7 @@
           <t>Icon</t>
         </is>
       </c>
-      <c r="D117" s="18" t="n">
+      <c r="D117" s="17" t="n">
         <v>103</v>
       </c>
     </row>
@@ -18266,7 +19639,7 @@
           <t>Page</t>
         </is>
       </c>
-      <c r="D118" s="18" t="n">
+      <c r="D118" s="17" t="n">
         <v>102</v>
       </c>
     </row>
@@ -18286,7 +19659,7 @@
           <t>download</t>
         </is>
       </c>
-      <c r="D119" s="18" t="n">
+      <c r="D119" s="17" t="n">
         <v>100</v>
       </c>
     </row>
@@ -18306,7 +19679,7 @@
           <t>BtnBackNext</t>
         </is>
       </c>
-      <c r="D120" s="18" t="n">
+      <c r="D120" s="17" t="n">
         <v>99</v>
       </c>
     </row>
@@ -18326,7 +19699,7 @@
           <t>directionLeft</t>
         </is>
       </c>
-      <c r="D121" s="18" t="n">
+      <c r="D121" s="17" t="n">
         <v>96</v>
       </c>
     </row>
@@ -18346,7 +19719,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D122" s="18" t="n">
+      <c r="D122" s="17" t="n">
         <v>41</v>
       </c>
     </row>
@@ -18366,7 +19739,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D123" s="18" t="n">
+      <c r="D123" s="17" t="n">
         <v>31</v>
       </c>
     </row>
@@ -18386,7 +19759,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D124" s="18" t="n">
+      <c r="D124" s="17" t="n">
         <v>30</v>
       </c>
     </row>
@@ -18406,7 +19779,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D125" s="18" t="n">
+      <c r="D125" s="17" t="n">
         <v>29</v>
       </c>
     </row>
@@ -18426,7 +19799,7 @@
           <t>number_deskop</t>
         </is>
       </c>
-      <c r="D126" s="18" t="n">
+      <c r="D126" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -18446,7 +19819,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D127" s="18" t="n">
+      <c r="D127" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -18466,7 +19839,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D128" s="18" t="n">
+      <c r="D128" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -18486,7 +19859,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D129" s="18" t="n">
+      <c r="D129" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18506,7 +19879,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D130" s="18" t="n">
+      <c r="D130" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18526,7 +19899,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D131" s="18" t="n">
+      <c r="D131" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -18546,7 +19919,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D132" s="18" t="n">
+      <c r="D132" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -18566,7 +19939,7 @@
           <t>Póliza Salud</t>
         </is>
       </c>
-      <c r="D133" s="18" t="n">
+      <c r="D133" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -18586,7 +19959,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D134" s="18" t="n">
+      <c r="D134" s="17" t="n">
         <v>13</v>
       </c>
     </row>
@@ -18606,7 +19979,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D135" s="18" t="n">
+      <c r="D135" s="17" t="n">
         <v>12</v>
       </c>
     </row>
@@ -18626,7 +19999,7 @@
           <t>face</t>
         </is>
       </c>
-      <c r="D136" s="18" t="n">
+      <c r="D136" s="17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18646,7 +20019,7 @@
           <t>soat</t>
         </is>
       </c>
-      <c r="D137" s="18" t="n">
+      <c r="D137" s="17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18666,7 +20039,7 @@
           <t>01_card selector</t>
         </is>
       </c>
-      <c r="D138" s="18" t="n">
+      <c r="D138" s="17" t="n">
         <v>10</v>
       </c>
     </row>
@@ -18686,7 +20059,7 @@
           <t>vehiculares</t>
         </is>
       </c>
-      <c r="D139" s="18" t="n">
+      <c r="D139" s="17" t="n">
         <v>9</v>
       </c>
     </row>
@@ -18706,7 +20079,7 @@
           <t>Card_Cross_RT_Deskop_Cob</t>
         </is>
       </c>
-      <c r="D140" s="18" t="n">
+      <c r="D140" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18726,7 +20099,7 @@
           <t>AddCard</t>
         </is>
       </c>
-      <c r="D141" s="18" t="n">
+      <c r="D141" s="17" t="n">
         <v>8</v>
       </c>
     </row>
@@ -18746,7 +20119,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D142" s="18" t="n">
+      <c r="D142" s="17" t="n">
         <v>105</v>
       </c>
     </row>
@@ -18766,7 +20139,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D143" s="18" t="n">
+      <c r="D143" s="17" t="n">
         <v>58</v>
       </c>
     </row>
@@ -18786,7 +20159,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D144" s="18" t="n">
+      <c r="D144" s="17" t="n">
         <v>50</v>
       </c>
     </row>
@@ -18806,7 +20179,7 @@
           <t>whatsapp</t>
         </is>
       </c>
-      <c r="D145" s="18" t="n">
+      <c r="D145" s="17" t="n">
         <v>38</v>
       </c>
     </row>
@@ -18826,7 +20199,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D146" s="18" t="n">
+      <c r="D146" s="17" t="n">
         <v>34</v>
       </c>
     </row>
@@ -18846,7 +20219,7 @@
           <t>Infotip</t>
         </is>
       </c>
-      <c r="D147" s="18" t="n">
+      <c r="D147" s="17" t="n">
         <v>28</v>
       </c>
     </row>
@@ -18866,7 +20239,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D148" s="18" t="n">
+      <c r="D148" s="17" t="n">
         <v>25</v>
       </c>
     </row>
@@ -18886,7 +20259,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D149" s="18" t="n">
+      <c r="D149" s="17" t="n">
         <v>23</v>
       </c>
     </row>
@@ -18906,7 +20279,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D150" s="18" t="n">
+      <c r="D150" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -18926,7 +20299,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D151" s="18" t="n">
+      <c r="D151" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -18946,7 +20319,7 @@
           <t>eye_open</t>
         </is>
       </c>
-      <c r="D152" s="18" t="n">
+      <c r="D152" s="17" t="n">
         <v>21</v>
       </c>
     </row>
@@ -18966,7 +20339,7 @@
           <t>torito</t>
         </is>
       </c>
-      <c r="D153" s="18" t="n">
+      <c r="D153" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -18986,7 +20359,7 @@
           <t>tarjeta de crédito</t>
         </is>
       </c>
-      <c r="D154" s="18" t="n">
+      <c r="D154" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19006,7 +20379,7 @@
           <t>asset_promo</t>
         </is>
       </c>
-      <c r="D155" s="18" t="n">
+      <c r="D155" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19026,7 +20399,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D156" s="18" t="n">
+      <c r="D156" s="17" t="n">
         <v>17</v>
       </c>
     </row>
@@ -19046,7 +20419,7 @@
           <t>Image Frame</t>
         </is>
       </c>
-      <c r="D157" s="18" t="n">
+      <c r="D157" s="17" t="n">
         <v>16</v>
       </c>
     </row>
@@ -19066,7 +20439,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D158" s="18" t="n">
+      <c r="D158" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19086,7 +20459,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D159" s="18" t="n">
+      <c r="D159" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19106,7 +20479,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D160" s="18" t="n">
+      <c r="D160" s="17" t="n">
         <v>15</v>
       </c>
     </row>
@@ -19126,7 +20499,7 @@
           <t>BtnAyuda</t>
         </is>
       </c>
-      <c r="D161" s="18" t="n">
+      <c r="D161" s="17" t="n">
         <v>14</v>
       </c>
     </row>
@@ -19146,7 +20519,7 @@
           <t>add</t>
         </is>
       </c>
-      <c r="D162" s="18" t="n">
+      <c r="D162" s="17" t="n">
         <v>109</v>
       </c>
     </row>
@@ -19166,7 +20539,7 @@
           <t>02</t>
         </is>
       </c>
-      <c r="D163" s="18" t="n">
+      <c r="D163" s="17" t="n">
         <v>107</v>
       </c>
     </row>
@@ -19186,7 +20559,7 @@
           <t>Title</t>
         </is>
       </c>
-      <c r="D164" s="18" t="n">
+      <c r="D164" s="17" t="n">
         <v>78</v>
       </c>
     </row>
@@ -19206,7 +20579,7 @@
           <t>Toast</t>
         </is>
       </c>
-      <c r="D165" s="18" t="n">
+      <c r="D165" s="17" t="n">
         <v>72</v>
       </c>
     </row>
@@ -19226,7 +20599,7 @@
           <t>Simple</t>
         </is>
       </c>
-      <c r="D166" s="18" t="n">
+      <c r="D166" s="17" t="n">
         <v>60</v>
       </c>
     </row>
@@ -19246,7 +20619,7 @@
           <t>01</t>
         </is>
       </c>
-      <c r="D167" s="18" t="n">
+      <c r="D167" s="17" t="n">
         <v>40</v>
       </c>
     </row>
@@ -19266,7 +20639,7 @@
           <t>Smile</t>
         </is>
       </c>
-      <c r="D168" s="18" t="n">
+      <c r="D168" s="17" t="n">
         <v>30</v>
       </c>
     </row>
@@ -19286,7 +20659,7 @@
           <t>Car</t>
         </is>
       </c>
-      <c r="D169" s="18" t="n">
+      <c r="D169" s="17" t="n">
         <v>30</v>
       </c>
     </row>
@@ -19306,7 +20679,7 @@
           <t>Indicator Mobile</t>
         </is>
       </c>
-      <c r="D170" s="18" t="n">
+      <c r="D170" s="17" t="n">
         <v>24</v>
       </c>
     </row>
@@ -19326,7 +20699,7 @@
           <t>mail</t>
         </is>
       </c>
-      <c r="D171" s="18" t="n">
+      <c r="D171" s="17" t="n">
         <v>22</v>
       </c>
     </row>
@@ -19346,7 +20719,7 @@
           <t>Step 01</t>
         </is>
       </c>
-      <c r="D172" s="18" t="n">
+      <c r="D172" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19366,7 +20739,7 @@
           <t>Step 02</t>
         </is>
       </c>
-      <c r="D173" s="18" t="n">
+      <c r="D173" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19386,7 +20759,7 @@
           <t>Step 03</t>
         </is>
       </c>
-      <c r="D174" s="18" t="n">
+      <c r="D174" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19406,7 +20779,7 @@
           <t>choque</t>
         </is>
       </c>
-      <c r="D175" s="18" t="n">
+      <c r="D175" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19426,7 +20799,7 @@
           <t>Espejos</t>
         </is>
       </c>
-      <c r="D176" s="18" t="n">
+      <c r="D176" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19446,7 +20819,7 @@
           <t>support</t>
         </is>
       </c>
-      <c r="D177" s="18" t="n">
+      <c r="D177" s="17" t="n">
         <v>20</v>
       </c>
     </row>
@@ -19466,7 +20839,7 @@
           <t>Background</t>
         </is>
       </c>
-      <c r="D178" s="18" t="n">
+      <c r="D178" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19486,7 +20859,7 @@
           <t>Image</t>
         </is>
       </c>
-      <c r="D179" s="18" t="n">
+      <c r="D179" s="17" t="n">
         <v>18</v>
       </c>
     </row>
@@ -19506,7 